--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>170654</v>
+        <v>171260.59375</v>
       </c>
       <c r="C62" t="n">
-        <v>167.559998</v>
+        <v>168.350006</v>
       </c>
       <c r="D62" t="n">
-        <v>105.550003</v>
+        <v>105.809998</v>
       </c>
       <c r="E62" t="n">
-        <v>433.700012</v>
+        <v>435.450012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1431</v>
+        <v>5.1453</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8966</v>
+        <v>5.8964</v>
       </c>
       <c r="H62" t="n">
-        <v>7482.709961</v>
+        <v>7492.100098</v>
       </c>
       <c r="I62" t="n">
-        <v>25870.650391</v>
+        <v>25918.525391</v>
       </c>
       <c r="J62" t="n">
-        <v>52348.390625</v>
+        <v>52299.730469</v>
       </c>
       <c r="K62" t="n">
-        <v>4125.299805</v>
+        <v>4133.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>73.989998</v>
+        <v>73.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>78.650002</v>
+        <v>77.910004</v>
       </c>
       <c r="N62" t="n">
-        <v>1187.5</v>
+        <v>1185.5</v>
       </c>
       <c r="O62" t="n">
-        <v>451</v>
+        <v>451.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.796401</v>
+        <v>-0.443779</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.881399</v>
+        <v>-0.414077</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.250417</v>
+        <v>-2.009637</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.447603</v>
+        <v>-0.045904</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.7466</v>
+        <v>-0.704141</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.347468</v>
+        <v>-0.350845</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.222018</v>
+        <v>-0.096805</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.308743</v>
+        <v>-1.12611</v>
       </c>
       <c r="X62" t="n">
-        <v>0.055795</v>
+        <v>-0.037211</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.545425</v>
+        <v>2.754239</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.460429</v>
+        <v>5.223018</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.857931</v>
+        <v>6.843123</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.335348</v>
+        <v>6.156257</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.267111</v>
+        <v>9.388249999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>171260.59375</v>
+        <v>172742</v>
       </c>
       <c r="C62" t="n">
-        <v>168.350006</v>
+        <v>169.800003</v>
       </c>
       <c r="D62" t="n">
-        <v>105.809998</v>
+        <v>107.760002</v>
       </c>
       <c r="E62" t="n">
-        <v>435.450012</v>
+        <v>435.079987</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1453</v>
+        <v>5.1146</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8964</v>
+        <v>5.8474</v>
       </c>
       <c r="H62" t="n">
-        <v>7492.100098</v>
+        <v>7543.640137</v>
       </c>
       <c r="I62" t="n">
-        <v>25918.525391</v>
+        <v>26206.890625</v>
       </c>
       <c r="J62" t="n">
-        <v>52299.730469</v>
+        <v>52487.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4133.700195</v>
+        <v>4117.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>73.129997</v>
+        <v>71.949997</v>
       </c>
       <c r="M62" t="n">
-        <v>77.910004</v>
+        <v>76.360001</v>
       </c>
       <c r="N62" t="n">
-        <v>1185.5</v>
+        <v>1180.25</v>
       </c>
       <c r="O62" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.443779</v>
+        <v>0.417384</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.414077</v>
+        <v>0.443656</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.009637</v>
+        <v>-0.203743</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.045904</v>
+        <v>-0.130841</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.704141</v>
+        <v>-1.296596</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.350845</v>
+        <v>-1.178941</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.096805</v>
+        <v>0.590454</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.12611</v>
+        <v>-0.026055</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.037211</v>
+        <v>0.321509</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.754239</v>
+        <v>2.356516</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.223018</v>
+        <v>3.525175</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.843123</v>
+        <v>4.717502</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.156257</v>
+        <v>5.686143</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.388249999999999</v>
+        <v>9.448819</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>172742</v>
+        <v>177866</v>
       </c>
       <c r="C62" t="n">
-        <v>169.800003</v>
+        <v>175.009995</v>
       </c>
       <c r="D62" t="n">
-        <v>107.760002</v>
+        <v>111.080002</v>
       </c>
       <c r="E62" t="n">
-        <v>435.079987</v>
+        <v>436.290009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1146</v>
+        <v>5.1075</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8474</v>
+        <v>5.8296</v>
       </c>
       <c r="H62" t="n">
-        <v>7543.640137</v>
+        <v>7575.390137</v>
       </c>
       <c r="I62" t="n">
-        <v>26206.890625</v>
+        <v>26281.609375</v>
       </c>
       <c r="J62" t="n">
-        <v>52487.410156</v>
+        <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4117.700195</v>
+        <v>4104.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>71.949997</v>
+        <v>71.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>76.360001</v>
+        <v>76.010002</v>
       </c>
       <c r="N62" t="n">
-        <v>1180.25</v>
+        <v>1196.5</v>
       </c>
       <c r="O62" t="n">
-        <v>451.75</v>
+        <v>438</v>
       </c>
       <c r="P62" t="n">
-        <v>0.417384</v>
+        <v>3.396038</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.443656</v>
+        <v>3.525579</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.203743</v>
+        <v>2.870901</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.130841</v>
+        <v>0.14691</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.296596</v>
+        <v>-1.433616</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.178941</v>
+        <v>-1.479767</v>
       </c>
       <c r="V62" t="n">
-        <v>0.590454</v>
+        <v>1.013824</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.026055</v>
+        <v>0.258981</v>
       </c>
       <c r="X62" t="n">
-        <v>0.321509</v>
+        <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.356516</v>
+        <v>2.018449</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.525175</v>
+        <v>2.748207</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.717502</v>
+        <v>4.237526</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.686143</v>
+        <v>7.141258</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.448819</v>
+        <v>6.117505</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5911,7 +5911,7 @@
         <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4104.100098</v>
+        <v>4113.700195</v>
       </c>
       <c r="L62" t="n">
         <v>71.410004</v>
@@ -5920,10 +5920,10 @@
         <v>76.010002</v>
       </c>
       <c r="N62" t="n">
-        <v>1196.5</v>
+        <v>1190.75</v>
       </c>
       <c r="O62" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="P62" t="n">
         <v>3.396038</v>
@@ -5953,7 +5953,7 @@
         <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.018449</v>
+        <v>2.257086</v>
       </c>
       <c r="Z62" t="n">
         <v>2.748207</v>
@@ -5962,10 +5962,10 @@
         <v>4.237526</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.141258</v>
+        <v>6.626371</v>
       </c>
       <c r="AC62" t="n">
-        <v>6.117505</v>
+        <v>11.689885</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>436.290009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1075</v>
+        <v>5.1165</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8296</v>
+        <v>5.8455</v>
       </c>
       <c r="H62" t="n">
         <v>7575.390137</v>
@@ -5911,19 +5911,19 @@
         <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4113.700195</v>
+        <v>4067.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>71.410004</v>
+        <v>74.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>76.010002</v>
+        <v>78.879997</v>
       </c>
       <c r="N62" t="n">
-        <v>1190.75</v>
+        <v>1196.25</v>
       </c>
       <c r="O62" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
       <c r="P62" t="n">
         <v>3.396038</v>
@@ -5938,10 +5938,10 @@
         <v>0.14691</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.433616</v>
+        <v>-1.259934</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.479767</v>
+        <v>-1.211055</v>
       </c>
       <c r="V62" t="n">
         <v>1.013824</v>
@@ -5953,19 +5953,19 @@
         <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.257086</v>
+        <v>1.118596</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.748207</v>
+        <v>6.661867</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.237526</v>
+        <v>8.17334</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.626371</v>
+        <v>7.118872</v>
       </c>
       <c r="AC62" t="n">
-        <v>11.689885</v>
+        <v>13.204119</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>177866</v>
+        <v>175739</v>
       </c>
       <c r="C62" t="n">
-        <v>175.009995</v>
+        <v>172.25</v>
       </c>
       <c r="D62" t="n">
-        <v>111.080002</v>
+        <v>109.199997</v>
       </c>
       <c r="E62" t="n">
-        <v>436.290009</v>
+        <v>434.600006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1165</v>
+        <v>5.1318</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8455</v>
+        <v>5.8466</v>
       </c>
       <c r="H62" t="n">
-        <v>7575.390137</v>
+        <v>7515.339844</v>
       </c>
       <c r="I62" t="n">
-        <v>26281.609375</v>
+        <v>25873.179688</v>
       </c>
       <c r="J62" t="n">
-        <v>52637.011719</v>
+        <v>52498.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4067.899902</v>
+        <v>4029</v>
       </c>
       <c r="L62" t="n">
-        <v>74.129997</v>
+        <v>80.510002</v>
       </c>
       <c r="M62" t="n">
-        <v>78.879997</v>
+        <v>86.900002</v>
       </c>
       <c r="N62" t="n">
-        <v>1196.25</v>
+        <v>1187.5</v>
       </c>
       <c r="O62" t="n">
-        <v>467.25</v>
+        <v>457.5</v>
       </c>
       <c r="P62" t="n">
-        <v>3.396038</v>
+        <v>2.159582</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.525579</v>
+        <v>1.892929</v>
       </c>
       <c r="R62" t="n">
-        <v>2.870901</v>
+        <v>1.129833</v>
       </c>
       <c r="S62" t="n">
-        <v>0.14691</v>
+        <v>-0.241016</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.259934</v>
+        <v>-0.964664</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.211055</v>
+        <v>-1.192464</v>
       </c>
       <c r="V62" t="n">
-        <v>1.013824</v>
+        <v>0.213085</v>
       </c>
       <c r="W62" t="n">
-        <v>0.258981</v>
+        <v>-1.299095</v>
       </c>
       <c r="X62" t="n">
-        <v>0.607449</v>
+        <v>0.342974</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.118596</v>
+        <v>0.151634</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.661867</v>
+        <v>15.84173</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.17334</v>
+        <v>19.1717</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.118872</v>
+        <v>6.335348</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.204119</v>
+        <v>10.841914</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,19 +5887,19 @@
         <v>175739</v>
       </c>
       <c r="C62" t="n">
-        <v>172.25</v>
+        <v>173.600006</v>
       </c>
       <c r="D62" t="n">
-        <v>109.199997</v>
+        <v>110.400002</v>
       </c>
       <c r="E62" t="n">
-        <v>434.600006</v>
+        <v>432</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1318</v>
+        <v>5.0745</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8466</v>
+        <v>5.7922</v>
       </c>
       <c r="H62" t="n">
         <v>7515.339844</v>
@@ -5911,37 +5911,37 @@
         <v>52498.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4029</v>
+        <v>4035.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>80.510002</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>86.900002</v>
+        <v>85.260002</v>
       </c>
       <c r="N62" t="n">
-        <v>1187.5</v>
+        <v>1195.5</v>
       </c>
       <c r="O62" t="n">
-        <v>457.5</v>
+        <v>465</v>
       </c>
       <c r="P62" t="n">
         <v>2.159582</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.892929</v>
+        <v>2.691513</v>
       </c>
       <c r="R62" t="n">
-        <v>1.129833</v>
+        <v>2.241154</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.241016</v>
+        <v>-0.837827</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.964664</v>
+        <v>-2.070462</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.192464</v>
+        <v>-2.111823</v>
       </c>
       <c r="V62" t="n">
         <v>0.213085</v>
@@ -5953,19 +5953,19 @@
         <v>0.342974</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.151634</v>
+        <v>0.32315</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.84173</v>
+        <v>14.84892</v>
       </c>
       <c r="AA62" t="n">
-        <v>19.1717</v>
+        <v>16.922661</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.335348</v>
+        <v>7.051713</v>
       </c>
       <c r="AC62" t="n">
-        <v>10.841914</v>
+        <v>12.658995</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175739</v>
+        <v>175690.03125</v>
       </c>
       <c r="C62" t="n">
-        <v>173.600006</v>
+        <v>172.649994</v>
       </c>
       <c r="D62" t="n">
-        <v>110.400002</v>
+        <v>109.639999</v>
       </c>
       <c r="E62" t="n">
-        <v>432</v>
+        <v>432.140015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0745</v>
+        <v>5.0804</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7922</v>
+        <v>5.8103</v>
       </c>
       <c r="H62" t="n">
-        <v>7515.339844</v>
+        <v>7533.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>25873.179688</v>
+        <v>26095.494141</v>
       </c>
       <c r="J62" t="n">
-        <v>52498.640625</v>
+        <v>52471</v>
       </c>
       <c r="K62" t="n">
-        <v>4035.899902</v>
+        <v>4041.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>79.81999999999999</v>
+        <v>79.040001</v>
       </c>
       <c r="M62" t="n">
-        <v>85.260002</v>
+        <v>84.449997</v>
       </c>
       <c r="N62" t="n">
-        <v>1195.5</v>
+        <v>1195</v>
       </c>
       <c r="O62" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P62" t="n">
-        <v>2.159582</v>
+        <v>2.131116</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.691513</v>
+        <v>2.129542</v>
       </c>
       <c r="R62" t="n">
-        <v>2.241154</v>
+        <v>1.537318</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.837827</v>
+        <v>-0.805688</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.070462</v>
+        <v>-1.956603</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.111823</v>
+        <v>-1.805937</v>
       </c>
       <c r="V62" t="n">
-        <v>0.213085</v>
+        <v>0.458841</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.299095</v>
+        <v>-0.45101</v>
       </c>
       <c r="X62" t="n">
-        <v>0.342974</v>
+        <v>0.290144</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.32315</v>
+        <v>0.469814</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.84892</v>
+        <v>13.72662</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.922661</v>
+        <v>15.811847</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.051713</v>
+        <v>7.00694</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.658995</v>
+        <v>13.385827</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175690.03125</v>
+        <v>176011</v>
       </c>
       <c r="C62" t="n">
-        <v>172.649994</v>
+        <v>172.759995</v>
       </c>
       <c r="D62" t="n">
-        <v>109.639999</v>
+        <v>109.690002</v>
       </c>
       <c r="E62" t="n">
-        <v>432.140015</v>
+        <v>433.399994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0804</v>
+        <v>5.0761</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8103</v>
+        <v>5.8178</v>
       </c>
       <c r="H62" t="n">
-        <v>7533.77002</v>
+        <v>7572.399902</v>
       </c>
       <c r="I62" t="n">
-        <v>26095.494141</v>
+        <v>26269.230469</v>
       </c>
       <c r="J62" t="n">
-        <v>52471</v>
+        <v>52658.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4041.800049</v>
+        <v>4029.300049</v>
       </c>
       <c r="L62" t="n">
-        <v>79.040001</v>
+        <v>79.489998</v>
       </c>
       <c r="M62" t="n">
-        <v>84.449997</v>
+        <v>84.660004</v>
       </c>
       <c r="N62" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="O62" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="P62" t="n">
-        <v>2.131116</v>
+        <v>2.3177</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.129542</v>
+        <v>2.194612</v>
       </c>
       <c r="R62" t="n">
-        <v>1.537318</v>
+        <v>1.583626</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.805688</v>
+        <v>-0.51647</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.956603</v>
+        <v>-2.039589</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.805937</v>
+        <v>-1.679184</v>
       </c>
       <c r="V62" t="n">
-        <v>0.458841</v>
+        <v>0.97395</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.45101</v>
+        <v>0.211758</v>
       </c>
       <c r="X62" t="n">
-        <v>0.290144</v>
+        <v>0.6487889999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.469814</v>
+        <v>0.159093</v>
       </c>
       <c r="Z62" t="n">
-        <v>13.72662</v>
+        <v>14.374098</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.811847</v>
+        <v>16.099843</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.385827</v>
+        <v>14.112659</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176011</v>
+        <v>173825</v>
       </c>
       <c r="C62" t="n">
-        <v>172.759995</v>
+        <v>170.770004</v>
       </c>
       <c r="D62" t="n">
-        <v>109.690002</v>
+        <v>108.419998</v>
       </c>
       <c r="E62" t="n">
-        <v>433.399994</v>
+        <v>433.040009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0761</v>
+        <v>5.1028</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8178</v>
+        <v>5.8311</v>
       </c>
       <c r="H62" t="n">
-        <v>7572.399902</v>
+        <v>7533.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26269.230469</v>
+        <v>25881.949219</v>
       </c>
       <c r="J62" t="n">
-        <v>52658.640625</v>
+        <v>52552.96875</v>
       </c>
       <c r="K62" t="n">
-        <v>4029.300049</v>
+        <v>3995.699951</v>
       </c>
       <c r="L62" t="n">
-        <v>79.489998</v>
+        <v>80.139999</v>
       </c>
       <c r="M62" t="n">
-        <v>84.660004</v>
+        <v>85.949997</v>
       </c>
       <c r="N62" t="n">
-        <v>1204.5</v>
+        <v>1195</v>
       </c>
       <c r="O62" t="n">
-        <v>471</v>
+        <v>463.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3177</v>
+        <v>1.046947</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.194612</v>
+        <v>1.017451</v>
       </c>
       <c r="R62" t="n">
-        <v>1.583626</v>
+        <v>0.407478</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.51647</v>
+        <v>-0.599101</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.039589</v>
+        <v>-1.524322</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.679184</v>
+        <v>-1.454415</v>
       </c>
       <c r="V62" t="n">
-        <v>0.97395</v>
+        <v>0.458841</v>
       </c>
       <c r="W62" t="n">
-        <v>0.211758</v>
+        <v>-1.265641</v>
       </c>
       <c r="X62" t="n">
-        <v>0.6487889999999999</v>
+        <v>0.446814</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.159093</v>
+        <v>-0.676128</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.374098</v>
+        <v>15.309352</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.099843</v>
+        <v>17.868896</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.857623</v>
+        <v>7.00694</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.112659</v>
+        <v>12.295578</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173825</v>
+        <v>173714</v>
       </c>
       <c r="C62" t="n">
-        <v>170.770004</v>
+        <v>170.630005</v>
       </c>
       <c r="D62" t="n">
-        <v>108.419998</v>
+        <v>107.43</v>
       </c>
       <c r="E62" t="n">
-        <v>433.040009</v>
+        <v>429.119995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1028</v>
+        <v>5.1108</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8311</v>
+        <v>5.8439</v>
       </c>
       <c r="H62" t="n">
-        <v>7533.77002</v>
+        <v>7457.689941</v>
       </c>
       <c r="I62" t="n">
-        <v>25881.949219</v>
+        <v>25520.240234</v>
       </c>
       <c r="J62" t="n">
-        <v>52552.96875</v>
+        <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>3995.699951</v>
+        <v>4012.699951</v>
       </c>
       <c r="L62" t="n">
-        <v>80.139999</v>
+        <v>82.489998</v>
       </c>
       <c r="M62" t="n">
-        <v>85.949997</v>
+        <v>88.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="O62" t="n">
-        <v>463.5</v>
+        <v>444.75</v>
       </c>
       <c r="P62" t="n">
-        <v>1.046947</v>
+        <v>0.982421</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.017451</v>
+        <v>0.934636</v>
       </c>
       <c r="R62" t="n">
-        <v>0.407478</v>
+        <v>-0.509356</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.599101</v>
+        <v>-1.498909</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.524322</v>
+        <v>-1.369937</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.454415</v>
+        <v>-1.238091</v>
       </c>
       <c r="V62" t="n">
-        <v>0.458841</v>
+        <v>-0.555646</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.265641</v>
+        <v>-2.645487</v>
       </c>
       <c r="X62" t="n">
-        <v>0.446814</v>
+        <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.676128</v>
+        <v>-0.253547</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.309352</v>
+        <v>18.690644</v>
       </c>
       <c r="AA62" t="n">
-        <v>17.868896</v>
+        <v>20.817335</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.295578</v>
+        <v>7.752877</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5911,19 +5911,19 @@
         <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>4012.699951</v>
+        <v>4018.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>82.489998</v>
+        <v>81.779999</v>
       </c>
       <c r="M62" t="n">
         <v>88.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1204.5</v>
+        <v>1203</v>
       </c>
       <c r="O62" t="n">
-        <v>444.75</v>
+        <v>467.5</v>
       </c>
       <c r="P62" t="n">
         <v>0.982421</v>
@@ -5953,19 +5953,19 @@
         <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.253547</v>
+        <v>-0.101913</v>
       </c>
       <c r="Z62" t="n">
-        <v>18.690644</v>
+        <v>17.669063</v>
       </c>
       <c r="AA62" t="n">
         <v>20.817335</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.857623</v>
+        <v>7.723304</v>
       </c>
       <c r="AC62" t="n">
-        <v>7.752877</v>
+        <v>13.264688</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>429.119995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1108</v>
+        <v>5.1072</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8439</v>
+        <v>5.8329</v>
       </c>
       <c r="H62" t="n">
         <v>7457.689941</v>
@@ -5911,19 +5911,19 @@
         <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>4018.800049</v>
+        <v>4020</v>
       </c>
       <c r="L62" t="n">
-        <v>81.779999</v>
+        <v>81.400002</v>
       </c>
       <c r="M62" t="n">
-        <v>88.099998</v>
+        <v>88.220001</v>
       </c>
       <c r="N62" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="O62" t="n">
-        <v>467.5</v>
+        <v>475.25</v>
       </c>
       <c r="P62" t="n">
         <v>0.982421</v>
@@ -5938,10 +5938,10 @@
         <v>-1.498909</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.369937</v>
+        <v>-1.439404</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.238091</v>
+        <v>-1.423994</v>
       </c>
       <c r="V62" t="n">
         <v>-0.555646</v>
@@ -5953,19 +5953,19 @@
         <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.101913</v>
+        <v>-0.072085</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.669063</v>
+        <v>17.122304</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.817335</v>
+        <v>20.981903</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.723304</v>
+        <v>9.245578999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.264688</v>
+        <v>15.142338</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173714</v>
+        <v>173371</v>
       </c>
       <c r="C62" t="n">
-        <v>170.630005</v>
+        <v>170.300003</v>
       </c>
       <c r="D62" t="n">
-        <v>107.43</v>
+        <v>106.230003</v>
       </c>
       <c r="E62" t="n">
-        <v>429.119995</v>
+        <v>426.970001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1072</v>
+        <v>5.0921</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8329</v>
+        <v>5.8157</v>
       </c>
       <c r="H62" t="n">
-        <v>7457.689941</v>
+        <v>7443.279785</v>
       </c>
       <c r="I62" t="n">
-        <v>25520.240234</v>
+        <v>25508.070312</v>
       </c>
       <c r="J62" t="n">
-        <v>52146.421875</v>
+        <v>51839.261719</v>
       </c>
       <c r="K62" t="n">
-        <v>4020</v>
+        <v>4064.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>81.400002</v>
+        <v>83.620003</v>
       </c>
       <c r="M62" t="n">
-        <v>88.220001</v>
+        <v>90.400002</v>
       </c>
       <c r="N62" t="n">
-        <v>1220</v>
+        <v>1226.5</v>
       </c>
       <c r="O62" t="n">
-        <v>475.25</v>
+        <v>471.5</v>
       </c>
       <c r="P62" t="n">
-        <v>0.982421</v>
+        <v>0.78303</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.934636</v>
+        <v>0.739426</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.509356</v>
+        <v>-1.62067</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.498909</v>
+        <v>-1.992423</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.439404</v>
+        <v>-1.73081</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.423994</v>
+        <v>-1.714674</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.555646</v>
+        <v>-0.747798</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.645487</v>
+        <v>-2.691912</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.330237</v>
+        <v>-0.917326</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.072085</v>
+        <v>1.041541</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.122304</v>
+        <v>20.316551</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.981903</v>
+        <v>23.971481</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.245578999999999</v>
+        <v>9.827624999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.142338</v>
+        <v>14.233798</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173371</v>
+        <v>173326</v>
       </c>
       <c r="C62" t="n">
-        <v>170.300003</v>
+        <v>170.339996</v>
       </c>
       <c r="D62" t="n">
-        <v>106.230003</v>
+        <v>105.949997</v>
       </c>
       <c r="E62" t="n">
-        <v>426.970001</v>
+        <v>430.109985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0921</v>
+        <v>5.072</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8157</v>
+        <v>5.7838</v>
       </c>
       <c r="H62" t="n">
-        <v>7443.279785</v>
+        <v>7509.200195</v>
       </c>
       <c r="I62" t="n">
-        <v>25508.070312</v>
+        <v>25837.210938</v>
       </c>
       <c r="J62" t="n">
-        <v>51839.261719</v>
+        <v>52224.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4064.800049</v>
+        <v>4122.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>83.620003</v>
+        <v>87.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>90.400002</v>
+        <v>84.800003</v>
       </c>
       <c r="N62" t="n">
-        <v>1226.5</v>
+        <v>1227</v>
       </c>
       <c r="O62" t="n">
-        <v>471.5</v>
+        <v>481</v>
       </c>
       <c r="P62" t="n">
-        <v>0.78303</v>
+        <v>0.756871</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.739426</v>
+        <v>0.763084</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.62067</v>
+        <v>-1.879984</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.992423</v>
+        <v>-1.271665</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.73081</v>
+        <v>-2.118709</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.714674</v>
+        <v>-2.253782</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.747798</v>
+        <v>0.131216</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.691912</v>
+        <v>-1.436308</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.917326</v>
+        <v>-0.180734</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.041541</v>
+        <v>2.483281</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.316551</v>
+        <v>25.366903</v>
       </c>
       <c r="AA62" t="n">
-        <v>23.971481</v>
+        <v>16.291834</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.827624999999999</v>
+        <v>9.872398</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.233798</v>
+        <v>16.535433</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173326</v>
+        <v>177548</v>
       </c>
       <c r="C62" t="n">
-        <v>170.339996</v>
+        <v>174.699997</v>
       </c>
       <c r="D62" t="n">
-        <v>105.949997</v>
+        <v>107.5</v>
       </c>
       <c r="E62" t="n">
-        <v>430.109985</v>
+        <v>428.859985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.072</v>
+        <v>5.0572</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7838</v>
+        <v>5.7601</v>
       </c>
       <c r="H62" t="n">
-        <v>7509.200195</v>
+        <v>7498.959961</v>
       </c>
       <c r="I62" t="n">
-        <v>25837.210938</v>
+        <v>25690.900391</v>
       </c>
       <c r="J62" t="n">
-        <v>52224.640625</v>
+        <v>52218.578125</v>
       </c>
       <c r="K62" t="n">
-        <v>4122.799805</v>
+        <v>4077.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>87.129997</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>84.800003</v>
+        <v>93.30999799999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="O62" t="n">
-        <v>481</v>
+        <v>488.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0.756871</v>
+        <v>3.21118</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.763084</v>
+        <v>3.342203</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.879984</v>
+        <v>-0.44453</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.271665</v>
+        <v>-1.558593</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.118709</v>
+        <v>-2.404326</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.253782</v>
+        <v>-2.654316</v>
       </c>
       <c r="V62" t="n">
-        <v>0.131216</v>
+        <v>-0.005332</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.436308</v>
+        <v>-1.994453</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.180734</v>
+        <v>-0.192322</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.483281</v>
+        <v>1.367173</v>
       </c>
       <c r="Z62" t="n">
-        <v>25.366903</v>
+        <v>31.035971</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.291834</v>
+        <v>27.96215</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.872398</v>
+        <v>11.394672</v>
       </c>
       <c r="AC62" t="n">
-        <v>16.535433</v>
+        <v>18.413083</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>177548</v>
+        <v>176724</v>
       </c>
       <c r="C62" t="n">
-        <v>174.699997</v>
+        <v>173.449997</v>
       </c>
       <c r="D62" t="n">
-        <v>107.5</v>
+        <v>106.18</v>
       </c>
       <c r="E62" t="n">
-        <v>428.859985</v>
+        <v>425.519989</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0572</v>
+        <v>5.0821</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7601</v>
+        <v>5.7826</v>
       </c>
       <c r="H62" t="n">
-        <v>7498.959961</v>
+        <v>7408.299805</v>
       </c>
       <c r="I62" t="n">
-        <v>25690.900391</v>
+        <v>25137.689453</v>
       </c>
       <c r="J62" t="n">
-        <v>52218.578125</v>
+        <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4077.899902</v>
+        <v>4062.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>91.06999999999999</v>
+        <v>89.879997</v>
       </c>
       <c r="M62" t="n">
-        <v>93.30999799999999</v>
+        <v>92</v>
       </c>
       <c r="N62" t="n">
-        <v>1244</v>
+        <v>1247.5</v>
       </c>
       <c r="O62" t="n">
-        <v>488.75</v>
+        <v>487</v>
       </c>
       <c r="P62" t="n">
-        <v>3.21118</v>
+        <v>2.732177</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.342203</v>
+        <v>2.602777</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.44453</v>
+        <v>-1.666978</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.558593</v>
+        <v>-2.325262</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.404326</v>
+        <v>-1.923798</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.654316</v>
+        <v>-2.274066</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.005332</v>
+        <v>-1.214238</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.994453</v>
+        <v>-4.10484</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.192322</v>
+        <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.367173</v>
+        <v>0.974426</v>
       </c>
       <c r="Z62" t="n">
-        <v>31.035971</v>
+        <v>29.323737</v>
       </c>
       <c r="AA62" t="n">
-        <v>27.96215</v>
+        <v>26.165664</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.394672</v>
+        <v>11.708081</v>
       </c>
       <c r="AC62" t="n">
-        <v>18.413083</v>
+        <v>17.989098</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176724</v>
+        <v>174042</v>
       </c>
       <c r="C62" t="n">
-        <v>173.449997</v>
+        <v>170.949997</v>
       </c>
       <c r="D62" t="n">
-        <v>106.18</v>
+        <v>105.050003</v>
       </c>
       <c r="E62" t="n">
-        <v>425.519989</v>
+        <v>425.049988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0821</v>
+        <v>5.0751</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7826</v>
+        <v>5.7816</v>
       </c>
       <c r="H62" t="n">
-        <v>7408.299805</v>
+        <v>7411.97998</v>
       </c>
       <c r="I62" t="n">
-        <v>25137.689453</v>
+        <v>24975.820312</v>
       </c>
       <c r="J62" t="n">
-        <v>51711.648438</v>
+        <v>51947.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4062.100098</v>
+        <v>4067.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>89.879997</v>
+        <v>89.30999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>92</v>
+        <v>96.779999</v>
       </c>
       <c r="N62" t="n">
-        <v>1247.5</v>
+        <v>1248</v>
       </c>
       <c r="O62" t="n">
-        <v>487</v>
+        <v>464.25</v>
       </c>
       <c r="P62" t="n">
-        <v>2.732177</v>
+        <v>1.173092</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.602777</v>
+        <v>1.123924</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.666978</v>
+        <v>-2.713466</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.325262</v>
+        <v>-2.433147</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.923798</v>
+        <v>-2.058886</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.274066</v>
+        <v>-2.290964</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.214238</v>
+        <v>-1.165165</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.10484</v>
+        <v>-4.722338</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.161239</v>
+        <v>-0.710923</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.974426</v>
+        <v>1.111144</v>
       </c>
       <c r="Z62" t="n">
-        <v>29.323737</v>
+        <v>28.503594</v>
       </c>
       <c r="AA62" t="n">
-        <v>26.165664</v>
+        <v>32.720792</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.708081</v>
+        <v>11.752854</v>
       </c>
       <c r="AC62" t="n">
-        <v>17.989098</v>
+        <v>12.477286</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,7 +5884,7 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>174042</v>
+        <v>176724</v>
       </c>
       <c r="C62" t="n">
         <v>170.949997</v>
@@ -5902,16 +5902,16 @@
         <v>5.7816</v>
       </c>
       <c r="H62" t="n">
-        <v>7411.97998</v>
+        <v>7408.299805</v>
       </c>
       <c r="I62" t="n">
-        <v>24975.820312</v>
+        <v>25137.689453</v>
       </c>
       <c r="J62" t="n">
-        <v>51947.25</v>
+        <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4067.600098</v>
+        <v>4070.800049</v>
       </c>
       <c r="L62" t="n">
         <v>89.30999799999999</v>
@@ -5920,13 +5920,13 @@
         <v>96.779999</v>
       </c>
       <c r="N62" t="n">
-        <v>1248</v>
+        <v>1253.5</v>
       </c>
       <c r="O62" t="n">
-        <v>464.25</v>
+        <v>487.25</v>
       </c>
       <c r="P62" t="n">
-        <v>1.173092</v>
+        <v>2.732177</v>
       </c>
       <c r="Q62" t="n">
         <v>1.123924</v>
@@ -5944,16 +5944,16 @@
         <v>-2.290964</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.165165</v>
+        <v>-1.214238</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.722338</v>
+        <v>-4.10484</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.710923</v>
+        <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.111144</v>
+        <v>1.190687</v>
       </c>
       <c r="Z62" t="n">
         <v>28.503594</v>
@@ -5962,10 +5962,10 @@
         <v>32.720792</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.752854</v>
+        <v>12.245355</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.477286</v>
+        <v>18.049667</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>425.049988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0751</v>
+        <v>5.0846</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7816</v>
+        <v>5.7877</v>
       </c>
       <c r="H62" t="n">
         <v>7408.299805</v>
@@ -5911,19 +5911,19 @@
         <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4070.800049</v>
+        <v>4089.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>89.30999799999999</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>96.779999</v>
+        <v>90.550003</v>
       </c>
       <c r="N62" t="n">
-        <v>1253.5</v>
+        <v>1220.25</v>
       </c>
       <c r="O62" t="n">
-        <v>487.25</v>
+        <v>473.75</v>
       </c>
       <c r="P62" t="n">
         <v>2.732177</v>
@@ -5938,10 +5938,10 @@
         <v>-2.433147</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.058886</v>
+        <v>-1.875551</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.290964</v>
+        <v>-2.187871</v>
       </c>
       <c r="V62" t="n">
         <v>-1.214238</v>
@@ -5953,19 +5953,19 @@
         <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.190687</v>
+        <v>1.665465</v>
       </c>
       <c r="Z62" t="n">
-        <v>28.503594</v>
+        <v>20.76259</v>
       </c>
       <c r="AA62" t="n">
-        <v>32.720792</v>
+        <v>24.177188</v>
       </c>
       <c r="AB62" t="n">
-        <v>12.245355</v>
+        <v>9.267965</v>
       </c>
       <c r="AC62" t="n">
-        <v>18.049667</v>
+        <v>14.778922</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176724</v>
+        <v>175335</v>
       </c>
       <c r="C62" t="n">
-        <v>170.949997</v>
+        <v>172.75</v>
       </c>
       <c r="D62" t="n">
-        <v>105.050003</v>
+        <v>106.699997</v>
       </c>
       <c r="E62" t="n">
-        <v>425.049988</v>
+        <v>426.859985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0846</v>
+        <v>5.1097</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7877</v>
+        <v>5.8091</v>
       </c>
       <c r="H62" t="n">
-        <v>7408.299805</v>
+        <v>7413.180176</v>
       </c>
       <c r="I62" t="n">
-        <v>25137.689453</v>
+        <v>24932.080078</v>
       </c>
       <c r="J62" t="n">
-        <v>51711.648438</v>
+        <v>52210.078125</v>
       </c>
       <c r="K62" t="n">
-        <v>4089.899902</v>
+        <v>4026.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>83.93000000000001</v>
+        <v>81.860001</v>
       </c>
       <c r="M62" t="n">
-        <v>90.550003</v>
+        <v>87.160004</v>
       </c>
       <c r="N62" t="n">
-        <v>1220.25</v>
+        <v>1208.5</v>
       </c>
       <c r="O62" t="n">
-        <v>473.75</v>
+        <v>475.75</v>
       </c>
       <c r="P62" t="n">
-        <v>2.732177</v>
+        <v>1.924731</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.123924</v>
+        <v>2.1887</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.713466</v>
+        <v>-1.185411</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.433147</v>
+        <v>-2.017677</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.875551</v>
+        <v>-1.391157</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.187871</v>
+        <v>-1.826212</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.214238</v>
+        <v>-1.149161</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.10484</v>
+        <v>-4.889198</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.161239</v>
+        <v>-0.208568</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.665465</v>
+        <v>0.091978</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.76259</v>
+        <v>17.784174</v>
       </c>
       <c r="AA62" t="n">
-        <v>24.177188</v>
+        <v>19.528258</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.267965</v>
+        <v>8.215805</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.778922</v>
+        <v>15.263477</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,22 +5887,22 @@
         <v>175335</v>
       </c>
       <c r="C62" t="n">
-        <v>172.75</v>
+        <v>173.740005</v>
       </c>
       <c r="D62" t="n">
-        <v>106.699997</v>
+        <v>107.169998</v>
       </c>
       <c r="E62" t="n">
-        <v>426.859985</v>
+        <v>428.609985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1097</v>
+        <v>5.1259</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8091</v>
+        <v>5.8325</v>
       </c>
       <c r="H62" t="n">
-        <v>7413.180176</v>
+        <v>7428.779785</v>
       </c>
       <c r="I62" t="n">
         <v>24932.080078</v>
@@ -5911,40 +5911,40 @@
         <v>52210.078125</v>
       </c>
       <c r="K62" t="n">
-        <v>4026.600098</v>
+        <v>4092.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>81.860001</v>
+        <v>82.660004</v>
       </c>
       <c r="M62" t="n">
-        <v>87.160004</v>
+        <v>87.91999800000001</v>
       </c>
       <c r="N62" t="n">
-        <v>1208.5</v>
+        <v>1207.75</v>
       </c>
       <c r="O62" t="n">
-        <v>475.75</v>
+        <v>478.5</v>
       </c>
       <c r="P62" t="n">
         <v>1.924731</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1887</v>
+        <v>2.774329</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.185411</v>
+        <v>-0.750144</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.017677</v>
+        <v>-1.615978</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.391157</v>
+        <v>-1.078532</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.826212</v>
+        <v>-1.430755</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.149161</v>
+        <v>-0.941148</v>
       </c>
       <c r="W62" t="n">
         <v>-4.889198</v>
@@ -5953,19 +5953,19 @@
         <v>-0.208568</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.091978</v>
+        <v>1.727609</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.784174</v>
+        <v>18.935257</v>
       </c>
       <c r="AA62" t="n">
-        <v>19.528258</v>
+        <v>20.570489</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.215805</v>
+        <v>8.148645999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.263477</v>
+        <v>15.92974</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175335</v>
+        <v>173885</v>
       </c>
       <c r="C62" t="n">
-        <v>173.740005</v>
+        <v>170.550003</v>
       </c>
       <c r="D62" t="n">
-        <v>107.169998</v>
+        <v>105.099998</v>
       </c>
       <c r="E62" t="n">
-        <v>428.609985</v>
+        <v>421.559998</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1259</v>
+        <v>5.099</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8325</v>
+        <v>5.8475</v>
       </c>
       <c r="H62" t="n">
-        <v>7428.779785</v>
+        <v>7316.149902</v>
       </c>
       <c r="I62" t="n">
-        <v>24932.080078</v>
+        <v>24442.939453</v>
       </c>
       <c r="J62" t="n">
-        <v>52210.078125</v>
+        <v>51594.140625</v>
       </c>
       <c r="K62" t="n">
-        <v>4092.399902</v>
+        <v>4136.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>82.660004</v>
+        <v>83.41999800000001</v>
       </c>
       <c r="M62" t="n">
-        <v>87.91999800000001</v>
+        <v>89.889999</v>
       </c>
       <c r="N62" t="n">
-        <v>1207.75</v>
+        <v>1193.25</v>
       </c>
       <c r="O62" t="n">
-        <v>478.5</v>
+        <v>473.5</v>
       </c>
       <c r="P62" t="n">
-        <v>1.924731</v>
+        <v>1.081826</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.774329</v>
+        <v>0.887311</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.750144</v>
+        <v>-2.667165</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.615978</v>
+        <v>-3.234247</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.078532</v>
+        <v>-1.597654</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.430755</v>
+        <v>-1.177257</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.941148</v>
+        <v>-2.443008</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.889198</v>
+        <v>-6.755169</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.208568</v>
+        <v>-1.385837</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.727609</v>
+        <v>2.831289</v>
       </c>
       <c r="Z62" t="n">
-        <v>18.935257</v>
+        <v>20.028774</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.570489</v>
+        <v>23.272081</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.148645999999999</v>
+        <v>6.850235</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.92974</v>
+        <v>14.718353</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -583,36 +583,16 @@
       <c r="E2" t="n">
         <v>250.350006</v>
       </c>
-      <c r="F2" t="n">
-        <v>5.0804</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.0387</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4395.259766</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14672.679688</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34935.46875</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1812.599976</v>
-      </c>
-      <c r="L2" t="n">
-        <v>73.949997</v>
-      </c>
-      <c r="M2" t="n">
-        <v>76.33000199999999</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1414.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>547</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -686,36 +666,16 @@
       <c r="S3" t="n">
         <v>1.457956</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.017557</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.212177</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.899042</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.997638</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.217278</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.132408</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-7.369841</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-4.375742</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-8.199329000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-2.3766</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -5884,88 +5844,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173885</v>
+        <v>177159</v>
       </c>
       <c r="C62" t="n">
-        <v>170.550003</v>
+        <v>174.309998</v>
       </c>
       <c r="D62" t="n">
-        <v>105.099998</v>
+        <v>107.360001</v>
       </c>
       <c r="E62" t="n">
-        <v>421.559998</v>
+        <v>425.369995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.099</v>
+        <v>5.0716</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8475</v>
+        <v>5.8255</v>
       </c>
       <c r="H62" t="n">
-        <v>7316.149902</v>
+        <v>7437.629883</v>
       </c>
       <c r="I62" t="n">
-        <v>24442.939453</v>
+        <v>25122.179688</v>
       </c>
       <c r="J62" t="n">
-        <v>51594.140625</v>
+        <v>52208.058594</v>
       </c>
       <c r="K62" t="n">
-        <v>4136.799805</v>
+        <v>4109.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>83.41999800000001</v>
+        <v>84.839996</v>
       </c>
       <c r="M62" t="n">
-        <v>89.889999</v>
+        <v>90.25</v>
       </c>
       <c r="N62" t="n">
-        <v>1193.25</v>
+        <v>1188.5</v>
       </c>
       <c r="O62" t="n">
-        <v>473.5</v>
+        <v>466.25</v>
       </c>
       <c r="P62" t="n">
-        <v>1.081826</v>
+        <v>2.985049</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.887311</v>
+        <v>3.111502</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.667165</v>
+        <v>-0.574183</v>
       </c>
       <c r="S62" t="n">
-        <v>-3.234247</v>
+        <v>-2.359692</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.597654</v>
+        <v>-2.12643</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.177257</v>
+        <v>-1.549054</v>
       </c>
       <c r="V62" t="n">
-        <v>-2.443008</v>
+        <v>-0.823137</v>
       </c>
       <c r="W62" t="n">
-        <v>-6.755169</v>
+        <v>-4.164006</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.385837</v>
+        <v>-0.212428</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.831289</v>
+        <v>2.160131</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.028774</v>
+        <v>22.071937</v>
       </c>
       <c r="AA62" t="n">
-        <v>23.272081</v>
+        <v>23.765774</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.850235</v>
+        <v>6.424894</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.718353</v>
+        <v>12.961841</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -569,30 +569,50 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="B2" t="n">
-        <v>121801</v>
+        <v>118781</v>
       </c>
       <c r="C2" t="n">
-        <v>117.110001</v>
+        <v>114.080002</v>
       </c>
       <c r="D2" t="n">
-        <v>141.800003</v>
+        <v>136.330002</v>
       </c>
       <c r="E2" t="n">
-        <v>250.350006</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>254</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.1829</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.1119</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4522.680176</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15259.240234</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35360.730469</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1815</v>
+      </c>
+      <c r="L2" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>72.989998</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1298.75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>534</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -610,5323 +630,5291 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B3" t="n">
-        <v>118781</v>
+        <v>110979</v>
       </c>
       <c r="C3" t="n">
-        <v>114.080002</v>
+        <v>106.489998</v>
       </c>
       <c r="D3" t="n">
-        <v>136.330002</v>
+        <v>127.400002</v>
       </c>
       <c r="E3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1829</v>
+        <v>5.4143</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1119</v>
+        <v>6.2785</v>
       </c>
       <c r="H3" t="n">
-        <v>4522.680176</v>
+        <v>4307.540039</v>
       </c>
       <c r="I3" t="n">
-        <v>15259.240234</v>
+        <v>14448.580078</v>
       </c>
       <c r="J3" t="n">
-        <v>35360.730469</v>
+        <v>33843.921875</v>
       </c>
       <c r="K3" t="n">
-        <v>1815</v>
+        <v>1755.300049</v>
       </c>
       <c r="L3" t="n">
-        <v>68.5</v>
+        <v>75.029999</v>
       </c>
       <c r="M3" t="n">
-        <v>72.989998</v>
+        <v>78.519997</v>
       </c>
       <c r="N3" t="n">
-        <v>1298.75</v>
+        <v>1256</v>
       </c>
       <c r="O3" t="n">
-        <v>534</v>
+        <v>536.75</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.479454</v>
+        <v>-6.568391</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.58731</v>
+        <v>-6.653229</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.857547</v>
+        <v>-6.550283</v>
       </c>
       <c r="S3" t="n">
-        <v>1.457956</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>0.393701</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.464682</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.725834</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-4.756917</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-5.312585</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-4.289528</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-3.289254</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.532845</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.576379</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-3.291627</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.514981</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B4" t="n">
-        <v>110979</v>
+        <v>103501</v>
       </c>
       <c r="C4" t="n">
-        <v>106.489998</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>127.400002</v>
+        <v>111.199997</v>
       </c>
       <c r="E4" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4143</v>
+        <v>5.6449</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2785</v>
+        <v>6.593</v>
       </c>
       <c r="H4" t="n">
-        <v>4307.540039</v>
+        <v>4605.379883</v>
       </c>
       <c r="I4" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
       <c r="J4" t="n">
-        <v>33843.921875</v>
+        <v>35819.558594</v>
       </c>
       <c r="K4" t="n">
-        <v>1755.300049</v>
+        <v>1783</v>
       </c>
       <c r="L4" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>78.519997</v>
+        <v>84.379997</v>
       </c>
       <c r="N4" t="n">
-        <v>1256</v>
+        <v>1235.75</v>
       </c>
       <c r="O4" t="n">
-        <v>536.75</v>
+        <v>568.25</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.568391</v>
+        <v>-6.738212</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.653229</v>
+        <v>-6.394964</v>
       </c>
       <c r="R4" t="n">
-        <v>-6.550283</v>
+        <v>-12.715859</v>
       </c>
       <c r="S4" t="n">
-        <v>0.393701</v>
+        <v>10.980392</v>
       </c>
       <c r="T4" t="n">
-        <v>4.464682</v>
+        <v>4.259089</v>
       </c>
       <c r="U4" t="n">
-        <v>2.725834</v>
+        <v>5.009156</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.756917</v>
+        <v>6.914384</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.312585</v>
+        <v>7.265832</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.289528</v>
+        <v>5.837493</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3.289254</v>
+        <v>1.578075</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.532845</v>
+        <v>11.382115</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.576379</v>
+        <v>7.463068</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.291627</v>
+        <v>-1.612261</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.514981</v>
+        <v>5.868654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B5" t="n">
-        <v>103501</v>
+        <v>101915</v>
       </c>
       <c r="C5" t="n">
-        <v>99.68000000000001</v>
+        <v>98.349998</v>
       </c>
       <c r="D5" t="n">
-        <v>111.199997</v>
+        <v>108.800003</v>
       </c>
       <c r="E5" t="n">
-        <v>283</v>
+        <v>280.549988</v>
       </c>
       <c r="F5" t="n">
-        <v>5.6449</v>
+        <v>5.6007</v>
       </c>
       <c r="G5" t="n">
-        <v>6.593</v>
+        <v>6.3223</v>
       </c>
       <c r="H5" t="n">
-        <v>4605.379883</v>
+        <v>4567</v>
       </c>
       <c r="I5" t="n">
-        <v>15498.389648</v>
+        <v>15537.69043</v>
       </c>
       <c r="J5" t="n">
-        <v>35819.558594</v>
+        <v>34483.71875</v>
       </c>
       <c r="K5" t="n">
-        <v>1783</v>
+        <v>1773.599976</v>
       </c>
       <c r="L5" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>84.379997</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1235.75</v>
+        <v>1217.25</v>
       </c>
       <c r="O5" t="n">
-        <v>568.25</v>
+        <v>567</v>
       </c>
       <c r="P5" t="n">
-        <v>-6.738212</v>
+        <v>-1.532352</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.394964</v>
+        <v>-1.334271</v>
       </c>
       <c r="R5" t="n">
-        <v>-12.715859</v>
+        <v>-2.158268</v>
       </c>
       <c r="S5" t="n">
-        <v>10.980392</v>
+        <v>-0.865729</v>
       </c>
       <c r="T5" t="n">
-        <v>4.259089</v>
+        <v>-0.783007</v>
       </c>
       <c r="U5" t="n">
-        <v>5.009156</v>
+        <v>-4.10587</v>
       </c>
       <c r="V5" t="n">
-        <v>6.914384</v>
+        <v>-0.833371</v>
       </c>
       <c r="W5" t="n">
-        <v>7.265832</v>
+        <v>0.25358</v>
       </c>
       <c r="X5" t="n">
-        <v>5.837493</v>
+        <v>-3.729359</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.578075</v>
+        <v>-0.527203</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.382115</v>
+        <v>-20.808902</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.463068</v>
+        <v>-16.366435</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.868654</v>
+        <v>-0.219974</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B6" t="n">
-        <v>101915</v>
+        <v>104822</v>
       </c>
       <c r="C6" t="n">
-        <v>98.349998</v>
+        <v>100.800003</v>
       </c>
       <c r="D6" t="n">
-        <v>108.800003</v>
+        <v>113.300003</v>
       </c>
       <c r="E6" t="n">
-        <v>280.549988</v>
+        <v>293.559998</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6007</v>
+        <v>5.5702</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3223</v>
+        <v>6.3049</v>
       </c>
       <c r="H6" t="n">
-        <v>4567</v>
+        <v>4766.180176</v>
       </c>
       <c r="I6" t="n">
-        <v>15537.69043</v>
+        <v>15644.969727</v>
       </c>
       <c r="J6" t="n">
-        <v>34483.71875</v>
+        <v>36338.300781</v>
       </c>
       <c r="K6" t="n">
-        <v>1773.599976</v>
+        <v>1827.5</v>
       </c>
       <c r="L6" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
       <c r="M6" t="n">
-        <v>70.56999999999999</v>
+        <v>77.779999</v>
       </c>
       <c r="N6" t="n">
-        <v>1217.25</v>
+        <v>1328.75</v>
       </c>
       <c r="O6" t="n">
-        <v>567</v>
+        <v>593.25</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.532352</v>
+        <v>2.852377</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.334271</v>
+        <v>2.491108</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.158268</v>
+        <v>4.136029</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.865729</v>
+        <v>4.637323</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.783007</v>
+        <v>-0.544574</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.10587</v>
+        <v>-0.275213</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.833371</v>
+        <v>4.361291</v>
       </c>
       <c r="W6" t="n">
-        <v>0.25358</v>
+        <v>0.690446</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.729359</v>
+        <v>5.378138</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.527203</v>
+        <v>3.039018</v>
       </c>
       <c r="Z6" t="n">
-        <v>-20.808902</v>
+        <v>13.644604</v>
       </c>
       <c r="AA6" t="n">
-        <v>-16.366435</v>
+        <v>10.216805</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.219974</v>
+        <v>4.62963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B7" t="n">
-        <v>104822</v>
+        <v>112388</v>
       </c>
       <c r="C7" t="n">
-        <v>100.800003</v>
+        <v>107.980003</v>
       </c>
       <c r="D7" t="n">
-        <v>113.300003</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>293.559998</v>
+        <v>260.399994</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5702</v>
+        <v>5.3626</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3049</v>
+        <v>5.9782</v>
       </c>
       <c r="H7" t="n">
-        <v>4766.180176</v>
+        <v>4515.549805</v>
       </c>
       <c r="I7" t="n">
-        <v>15644.969727</v>
+        <v>14239.879883</v>
       </c>
       <c r="J7" t="n">
-        <v>36338.300781</v>
+        <v>35131.859375</v>
       </c>
       <c r="K7" t="n">
-        <v>1827.5</v>
+        <v>1795</v>
       </c>
       <c r="L7" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
       <c r="M7" t="n">
-        <v>77.779999</v>
+        <v>91.209999</v>
       </c>
       <c r="N7" t="n">
-        <v>1328.75</v>
+        <v>1490.5</v>
       </c>
       <c r="O7" t="n">
-        <v>593.25</v>
+        <v>626</v>
       </c>
       <c r="P7" t="n">
-        <v>2.852377</v>
+        <v>7.21795</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.491108</v>
+        <v>7.123016</v>
       </c>
       <c r="R7" t="n">
-        <v>4.136029</v>
+        <v>3.265664</v>
       </c>
       <c r="S7" t="n">
-        <v>4.637323</v>
+        <v>-11.295818</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.544574</v>
+        <v>-3.726978</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.275213</v>
+        <v>-5.181687</v>
       </c>
       <c r="V7" t="n">
-        <v>4.361291</v>
+        <v>-5.258517</v>
       </c>
       <c r="W7" t="n">
-        <v>0.690446</v>
+        <v>-8.981097</v>
       </c>
       <c r="X7" t="n">
-        <v>5.378138</v>
+        <v>-3.320027</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.039018</v>
+        <v>-1.778386</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.644604</v>
+        <v>17.205162</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.216805</v>
+        <v>17.26665</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.62963</v>
+        <v>5.520438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B8" t="n">
-        <v>112388</v>
+        <v>113142</v>
       </c>
       <c r="C8" t="n">
-        <v>107.980003</v>
+        <v>108.900002</v>
       </c>
       <c r="D8" t="n">
-        <v>117</v>
+        <v>111.040001</v>
       </c>
       <c r="E8" t="n">
-        <v>260.399994</v>
+        <v>245.5</v>
       </c>
       <c r="F8" t="n">
-        <v>5.3626</v>
+        <v>5.1594</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9782</v>
+        <v>5.814</v>
       </c>
       <c r="H8" t="n">
-        <v>4515.549805</v>
+        <v>4373.939941</v>
       </c>
       <c r="I8" t="n">
-        <v>14239.879883</v>
+        <v>13751.400391</v>
       </c>
       <c r="J8" t="n">
-        <v>35131.859375</v>
+        <v>33892.601562</v>
       </c>
       <c r="K8" t="n">
-        <v>1795</v>
+        <v>1899.400024</v>
       </c>
       <c r="L8" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
       <c r="M8" t="n">
-        <v>91.209999</v>
+        <v>100.989998</v>
       </c>
       <c r="N8" t="n">
-        <v>1490.5</v>
+        <v>1644.25</v>
       </c>
       <c r="O8" t="n">
-        <v>626</v>
+        <v>697.5</v>
       </c>
       <c r="P8" t="n">
-        <v>7.21795</v>
+        <v>0.67089</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.123016</v>
+        <v>0.852008</v>
       </c>
       <c r="R8" t="n">
-        <v>3.265664</v>
+        <v>-5.094016</v>
       </c>
       <c r="S8" t="n">
-        <v>-11.295818</v>
+        <v>-5.721964</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.726978</v>
+        <v>-3.789204</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.181687</v>
+        <v>-2.746643</v>
       </c>
       <c r="V8" t="n">
-        <v>-5.258517</v>
+        <v>-3.136049</v>
       </c>
       <c r="W8" t="n">
-        <v>-8.981097</v>
+        <v>-3.430362</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.320027</v>
+        <v>-3.527447</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.778386</v>
+        <v>5.816157</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.205162</v>
+        <v>8.587634</v>
       </c>
       <c r="AA8" t="n">
-        <v>17.26665</v>
+        <v>10.722507</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.520438</v>
+        <v>11.421725</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B9" t="n">
-        <v>113142</v>
+        <v>119999</v>
       </c>
       <c r="C9" t="n">
-        <v>108.900002</v>
+        <v>115.599998</v>
       </c>
       <c r="D9" t="n">
-        <v>111.040001</v>
+        <v>120.940002</v>
       </c>
       <c r="E9" t="n">
-        <v>245.5</v>
+        <v>235.649994</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1594</v>
+        <v>4.7697</v>
       </c>
       <c r="G9" t="n">
-        <v>5.814</v>
+        <v>5.3198</v>
       </c>
       <c r="H9" t="n">
-        <v>4373.939941</v>
+        <v>4530.410156</v>
       </c>
       <c r="I9" t="n">
-        <v>13751.400391</v>
+        <v>14220.519531</v>
       </c>
       <c r="J9" t="n">
-        <v>33892.601562</v>
+        <v>34678.351562</v>
       </c>
       <c r="K9" t="n">
-        <v>1899.400024</v>
+        <v>1949.199951</v>
       </c>
       <c r="L9" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
       <c r="M9" t="n">
-        <v>100.989998</v>
+        <v>107.910004</v>
       </c>
       <c r="N9" t="n">
-        <v>1644.25</v>
+        <v>1618.25</v>
       </c>
       <c r="O9" t="n">
-        <v>697.5</v>
+        <v>748.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0.67089</v>
+        <v>6.060526</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.852008</v>
+        <v>6.152431</v>
       </c>
       <c r="R9" t="n">
-        <v>-5.094016</v>
+        <v>8.915706999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.721964</v>
+        <v>-4.012222</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.789204</v>
+        <v>-7.553203</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.746643</v>
+        <v>-8.500176</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.136049</v>
+        <v>3.577329</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.430362</v>
+        <v>3.411428</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.527447</v>
+        <v>2.318353</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.816157</v>
+        <v>2.621877</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.587634</v>
+        <v>4.763892</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.722507</v>
+        <v>6.852169</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.421725</v>
+        <v>7.34767</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B10" t="n">
-        <v>119999</v>
+        <v>107876</v>
       </c>
       <c r="C10" t="n">
-        <v>115.599998</v>
+        <v>103.400002</v>
       </c>
       <c r="D10" t="n">
-        <v>120.940002</v>
+        <v>110.599998</v>
       </c>
       <c r="E10" t="n">
-        <v>235.649994</v>
+        <v>224.100006</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7697</v>
+        <v>4.9378</v>
       </c>
       <c r="G10" t="n">
-        <v>5.3198</v>
+        <v>5.1837</v>
       </c>
       <c r="H10" t="n">
-        <v>4530.410156</v>
+        <v>4131.930176</v>
       </c>
       <c r="I10" t="n">
-        <v>14220.519531</v>
+        <v>12334.639648</v>
       </c>
       <c r="J10" t="n">
-        <v>34678.351562</v>
+        <v>32977.210938</v>
       </c>
       <c r="K10" t="n">
-        <v>1949.199951</v>
+        <v>1909.300049</v>
       </c>
       <c r="L10" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
       <c r="M10" t="n">
-        <v>107.910004</v>
+        <v>109.339996</v>
       </c>
       <c r="N10" t="n">
-        <v>1618.25</v>
+        <v>1708.25</v>
       </c>
       <c r="O10" t="n">
-        <v>748.75</v>
+        <v>818.25</v>
       </c>
       <c r="P10" t="n">
-        <v>6.060526</v>
+        <v>-10.102584</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.152431</v>
+        <v>-10.553631</v>
       </c>
       <c r="R10" t="n">
-        <v>8.915706999999999</v>
+        <v>-8.549697</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.012222</v>
+        <v>-4.901332</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.553203</v>
+        <v>3.524328</v>
       </c>
       <c r="U10" t="n">
-        <v>-8.500176</v>
+        <v>-2.558363</v>
       </c>
       <c r="V10" t="n">
-        <v>3.577329</v>
+        <v>-8.795671</v>
       </c>
       <c r="W10" t="n">
-        <v>3.411428</v>
+        <v>-13.261681</v>
       </c>
       <c r="X10" t="n">
-        <v>2.318353</v>
+        <v>-4.905483</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.621877</v>
+        <v>-2.046989</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.763892</v>
+        <v>4.39769</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.852169</v>
+        <v>1.325172</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.34767</v>
+        <v>9.282137000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B11" t="n">
-        <v>107876</v>
+        <v>111351</v>
       </c>
       <c r="C11" t="n">
-        <v>103.400002</v>
+        <v>107.18</v>
       </c>
       <c r="D11" t="n">
-        <v>110.599998</v>
+        <v>109.300003</v>
       </c>
       <c r="E11" t="n">
-        <v>224.100006</v>
+        <v>214.5</v>
       </c>
       <c r="F11" t="n">
-        <v>4.9378</v>
+        <v>4.7524</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1837</v>
+        <v>5.1176</v>
       </c>
       <c r="H11" t="n">
-        <v>4131.930176</v>
+        <v>4132.149902</v>
       </c>
       <c r="I11" t="n">
-        <v>12334.639648</v>
+        <v>12081.389648</v>
       </c>
       <c r="J11" t="n">
-        <v>32977.210938</v>
+        <v>32990.121094</v>
       </c>
       <c r="K11" t="n">
-        <v>1909.300049</v>
+        <v>1842.699951</v>
       </c>
       <c r="L11" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
       <c r="M11" t="n">
-        <v>109.339996</v>
+        <v>122.839996</v>
       </c>
       <c r="N11" t="n">
-        <v>1708.25</v>
+        <v>1683.25</v>
       </c>
       <c r="O11" t="n">
-        <v>818.25</v>
+        <v>753.5</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.102584</v>
+        <v>3.221291</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.553631</v>
+        <v>3.655705</v>
       </c>
       <c r="R11" t="n">
-        <v>-8.549697</v>
+        <v>-1.175403</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.901332</v>
+        <v>-4.283804</v>
       </c>
       <c r="T11" t="n">
-        <v>3.524328</v>
+        <v>-3.754709</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.558363</v>
+        <v>-1.275153</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.795671</v>
+        <v>0.005318</v>
       </c>
       <c r="W11" t="n">
-        <v>-13.261681</v>
+        <v>-2.053161</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.905483</v>
+        <v>0.039149</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.046989</v>
+        <v>-3.488194</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.39769</v>
+        <v>9.532902</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.325172</v>
+        <v>12.346809</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.282137000000001</v>
+        <v>-7.913229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B12" t="n">
-        <v>111351</v>
+        <v>98542</v>
       </c>
       <c r="C12" t="n">
-        <v>107.18</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>109.300003</v>
+        <v>91.33000199999999</v>
       </c>
       <c r="E12" t="n">
-        <v>214.5</v>
+        <v>216.699997</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7524</v>
+        <v>5.1809</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1176</v>
+        <v>5.4098</v>
       </c>
       <c r="H12" t="n">
-        <v>4132.149902</v>
+        <v>3785.379883</v>
       </c>
       <c r="I12" t="n">
-        <v>12081.389648</v>
+        <v>11028.740234</v>
       </c>
       <c r="J12" t="n">
-        <v>32990.121094</v>
+        <v>30775.429688</v>
       </c>
       <c r="K12" t="n">
-        <v>1842.699951</v>
+        <v>1804.099976</v>
       </c>
       <c r="L12" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
       <c r="M12" t="n">
-        <v>122.839996</v>
+        <v>114.809998</v>
       </c>
       <c r="N12" t="n">
-        <v>1683.25</v>
+        <v>1675</v>
       </c>
       <c r="O12" t="n">
-        <v>753.5</v>
+        <v>743.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.221291</v>
+        <v>-11.503264</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.655705</v>
+        <v>-11.364061</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.175403</v>
+        <v>-16.440989</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.283804</v>
+        <v>1.02564</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.754709</v>
+        <v>9.016501</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.275153</v>
+        <v>5.709709</v>
       </c>
       <c r="V12" t="n">
-        <v>0.005318</v>
+        <v>-8.391999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>-2.053161</v>
+        <v>-8.712982999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>0.039149</v>
+        <v>-6.713196</v>
       </c>
       <c r="Y12" t="n">
-        <v>-3.488194</v>
+        <v>-2.094751</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.532902</v>
+        <v>-7.77012</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.346809</v>
+        <v>-6.536958</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
       <c r="AC12" t="n">
-        <v>-7.913229</v>
+        <v>-1.293962</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B13" t="n">
-        <v>98542</v>
+        <v>103165</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>99.300003</v>
       </c>
       <c r="D13" t="n">
-        <v>91.33000199999999</v>
+        <v>95.650002</v>
       </c>
       <c r="E13" t="n">
-        <v>216.699997</v>
+        <v>234.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1809</v>
+        <v>5.1827</v>
       </c>
       <c r="G13" t="n">
-        <v>5.4098</v>
+        <v>5.2797</v>
       </c>
       <c r="H13" t="n">
-        <v>3785.379883</v>
+        <v>4130.290039</v>
       </c>
       <c r="I13" t="n">
-        <v>11028.740234</v>
+        <v>12390.69043</v>
       </c>
       <c r="J13" t="n">
-        <v>30775.429688</v>
+        <v>32845.128906</v>
       </c>
       <c r="K13" t="n">
-        <v>1804.099976</v>
+        <v>1762.900024</v>
       </c>
       <c r="L13" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
       <c r="M13" t="n">
-        <v>114.809998</v>
+        <v>110.010002</v>
       </c>
       <c r="N13" t="n">
-        <v>1675</v>
+        <v>1637</v>
       </c>
       <c r="O13" t="n">
-        <v>743.75</v>
+        <v>616.25</v>
       </c>
       <c r="P13" t="n">
-        <v>-11.503264</v>
+        <v>4.691401</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.364061</v>
+        <v>4.526319</v>
       </c>
       <c r="R13" t="n">
-        <v>-16.440989</v>
+        <v>4.730099</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02564</v>
+        <v>8.214122</v>
       </c>
       <c r="T13" t="n">
-        <v>9.016501</v>
+        <v>0.034744</v>
       </c>
       <c r="U13" t="n">
-        <v>5.709709</v>
+        <v>-2.404899</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.391999999999999</v>
+        <v>9.111639</v>
       </c>
       <c r="W13" t="n">
-        <v>-8.712982999999999</v>
+        <v>12.3491</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.713196</v>
+        <v>6.725168</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.094751</v>
+        <v>-2.283684</v>
       </c>
       <c r="Z13" t="n">
-        <v>-7.77012</v>
+        <v>-6.751134</v>
       </c>
       <c r="AA13" t="n">
-        <v>-6.536958</v>
+        <v>-4.180817</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.293962</v>
+        <v>-17.142857</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B14" t="n">
-        <v>103165</v>
+        <v>109523</v>
       </c>
       <c r="C14" t="n">
-        <v>99.300003</v>
+        <v>105.830002</v>
       </c>
       <c r="D14" t="n">
-        <v>95.650002</v>
+        <v>106.800003</v>
       </c>
       <c r="E14" t="n">
-        <v>234.5</v>
+        <v>226</v>
       </c>
       <c r="F14" t="n">
-        <v>5.1827</v>
+        <v>5.1219</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2797</v>
+        <v>5.1318</v>
       </c>
       <c r="H14" t="n">
-        <v>4130.290039</v>
+        <v>3955</v>
       </c>
       <c r="I14" t="n">
-        <v>12390.69043</v>
+        <v>11816.200195</v>
       </c>
       <c r="J14" t="n">
-        <v>32845.128906</v>
+        <v>31510.429688</v>
       </c>
       <c r="K14" t="n">
-        <v>1762.900024</v>
+        <v>1712.800049</v>
       </c>
       <c r="L14" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
       <c r="M14" t="n">
-        <v>110.010002</v>
+        <v>96.489998</v>
       </c>
       <c r="N14" t="n">
-        <v>1637</v>
+        <v>1507.5</v>
       </c>
       <c r="O14" t="n">
-        <v>616.25</v>
+        <v>673.75</v>
       </c>
       <c r="P14" t="n">
-        <v>4.691401</v>
+        <v>6.162943</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.526319</v>
+        <v>6.576031</v>
       </c>
       <c r="R14" t="n">
-        <v>4.730099</v>
+        <v>11.657085</v>
       </c>
       <c r="S14" t="n">
-        <v>8.214122</v>
+        <v>-3.624733</v>
       </c>
       <c r="T14" t="n">
-        <v>0.034744</v>
+        <v>-1.173135</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.404899</v>
+        <v>-2.801289</v>
       </c>
       <c r="V14" t="n">
-        <v>9.111639</v>
+        <v>-4.244013</v>
       </c>
       <c r="W14" t="n">
-        <v>12.3491</v>
+        <v>-4.636467</v>
       </c>
       <c r="X14" t="n">
-        <v>6.725168</v>
+        <v>-4.063614</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.283684</v>
+        <v>-2.841907</v>
       </c>
       <c r="Z14" t="n">
-        <v>-6.751134</v>
+        <v>-9.196916999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>-4.180817</v>
+        <v>-12.289795</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
       <c r="AC14" t="n">
-        <v>-17.142857</v>
+        <v>9.330629</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B15" t="n">
-        <v>109523</v>
+        <v>110037</v>
       </c>
       <c r="C15" t="n">
-        <v>105.830002</v>
+        <v>106.459999</v>
       </c>
       <c r="D15" t="n">
-        <v>106.800003</v>
+        <v>105.440002</v>
       </c>
       <c r="E15" t="n">
-        <v>226</v>
+        <v>213.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5.1219</v>
+        <v>5.3962</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1318</v>
+        <v>5.3031</v>
       </c>
       <c r="H15" t="n">
-        <v>3955</v>
+        <v>3585.620117</v>
       </c>
       <c r="I15" t="n">
-        <v>11816.200195</v>
+        <v>10575.620117</v>
       </c>
       <c r="J15" t="n">
-        <v>31510.429688</v>
+        <v>28725.509766</v>
       </c>
       <c r="K15" t="n">
-        <v>1712.800049</v>
+        <v>1662.400024</v>
       </c>
       <c r="L15" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
       <c r="M15" t="n">
-        <v>96.489998</v>
+        <v>87.959999</v>
       </c>
       <c r="N15" t="n">
-        <v>1507.5</v>
+        <v>1364.75</v>
       </c>
       <c r="O15" t="n">
-        <v>673.75</v>
+        <v>677.5</v>
       </c>
       <c r="P15" t="n">
-        <v>6.162943</v>
+        <v>0.469308</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.576031</v>
+        <v>0.595292</v>
       </c>
       <c r="R15" t="n">
-        <v>11.657085</v>
+        <v>-1.273409</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.624733</v>
+        <v>-5.530973</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.173135</v>
+        <v>5.355436</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.801289</v>
+        <v>3.338009</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.244013</v>
+        <v>-9.339567000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>-4.636467</v>
+        <v>-10.498976</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.063614</v>
+        <v>-8.838089</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2.841907</v>
+        <v>-2.942552</v>
       </c>
       <c r="Z15" t="n">
-        <v>-9.196916999999999</v>
+        <v>-11.233953</v>
       </c>
       <c r="AA15" t="n">
-        <v>-12.289795</v>
+        <v>-8.840293000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.330629</v>
+        <v>0.556586</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B16" t="n">
-        <v>110037</v>
+        <v>116037</v>
       </c>
       <c r="C16" t="n">
-        <v>106.459999</v>
+        <v>112.150002</v>
       </c>
       <c r="D16" t="n">
-        <v>105.440002</v>
+        <v>112.5</v>
       </c>
       <c r="E16" t="n">
-        <v>213.5</v>
+        <v>220.240005</v>
       </c>
       <c r="F16" t="n">
-        <v>5.3962</v>
+        <v>5.2885</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3031</v>
+        <v>5.2737</v>
       </c>
       <c r="H16" t="n">
-        <v>3585.620117</v>
+        <v>3871.97998</v>
       </c>
       <c r="I16" t="n">
-        <v>10575.620117</v>
+        <v>10988.150391</v>
       </c>
       <c r="J16" t="n">
-        <v>28725.509766</v>
+        <v>32732.949219</v>
       </c>
       <c r="K16" t="n">
-        <v>1662.400024</v>
+        <v>1635.900024</v>
       </c>
       <c r="L16" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
       <c r="M16" t="n">
-        <v>87.959999</v>
+        <v>94.83000199999999</v>
       </c>
       <c r="N16" t="n">
-        <v>1364.75</v>
+        <v>1407</v>
       </c>
       <c r="O16" t="n">
-        <v>677.5</v>
+        <v>691.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0.469308</v>
+        <v>5.452711</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.595292</v>
+        <v>5.344733</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.273409</v>
+        <v>6.695749</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.530973</v>
+        <v>3.156911</v>
       </c>
       <c r="T16" t="n">
-        <v>5.355436</v>
+        <v>-1.995855</v>
       </c>
       <c r="U16" t="n">
-        <v>3.338009</v>
+        <v>-0.55439</v>
       </c>
       <c r="V16" t="n">
-        <v>-9.339567000000001</v>
+        <v>7.986341</v>
       </c>
       <c r="W16" t="n">
-        <v>-10.498976</v>
+        <v>3.900767</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.838089</v>
+        <v>13.950804</v>
       </c>
       <c r="Y16" t="n">
-        <v>-2.942552</v>
+        <v>-1.594081</v>
       </c>
       <c r="Z16" t="n">
-        <v>-11.233953</v>
+        <v>8.856460999999999</v>
       </c>
       <c r="AA16" t="n">
-        <v>-8.840293000000001</v>
+        <v>7.810372</v>
       </c>
       <c r="AB16" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.556586</v>
+        <v>2.066421</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B17" t="n">
-        <v>116037</v>
+        <v>112486</v>
       </c>
       <c r="C17" t="n">
-        <v>112.150002</v>
+        <v>108.580002</v>
       </c>
       <c r="D17" t="n">
-        <v>112.5</v>
+        <v>99.980003</v>
       </c>
       <c r="E17" t="n">
-        <v>220.240005</v>
+        <v>233.25</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2885</v>
+        <v>5.2682</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2737</v>
+        <v>5.4362</v>
       </c>
       <c r="H17" t="n">
-        <v>3871.97998</v>
+        <v>4080.110107</v>
       </c>
       <c r="I17" t="n">
-        <v>10988.150391</v>
+        <v>11468</v>
       </c>
       <c r="J17" t="n">
-        <v>32732.949219</v>
+        <v>34589.769531</v>
       </c>
       <c r="K17" t="n">
-        <v>1635.900024</v>
+        <v>1746</v>
       </c>
       <c r="L17" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
       <c r="M17" t="n">
-        <v>94.83000199999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>1407</v>
+        <v>1469.5</v>
       </c>
       <c r="O17" t="n">
-        <v>691.5</v>
+        <v>662</v>
       </c>
       <c r="P17" t="n">
-        <v>5.452711</v>
+        <v>-3.060231</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.344733</v>
+        <v>-3.183236</v>
       </c>
       <c r="R17" t="n">
-        <v>6.695749</v>
+        <v>-11.128886</v>
       </c>
       <c r="S17" t="n">
-        <v>3.156911</v>
+        <v>5.90719</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.995855</v>
+        <v>-0.38385</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.55439</v>
+        <v>3.081326</v>
       </c>
       <c r="V17" t="n">
-        <v>7.986341</v>
+        <v>5.375289</v>
       </c>
       <c r="W17" t="n">
-        <v>3.900767</v>
+        <v>4.366973</v>
       </c>
       <c r="X17" t="n">
-        <v>13.950804</v>
+        <v>5.672634</v>
       </c>
       <c r="Y17" t="n">
-        <v>-1.594081</v>
+        <v>6.730239</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.856460999999999</v>
+        <v>-6.910893</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.810372</v>
+        <v>-9.912476</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.066421</v>
+        <v>-4.266088</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B18" t="n">
-        <v>112486</v>
+        <v>110031</v>
       </c>
       <c r="C18" t="n">
-        <v>108.580002</v>
+        <v>105.949997</v>
       </c>
       <c r="D18" t="n">
-        <v>99.980003</v>
+        <v>96.519997</v>
       </c>
       <c r="E18" t="n">
-        <v>233.25</v>
+        <v>225</v>
       </c>
       <c r="F18" t="n">
-        <v>5.2682</v>
+        <v>5.2846</v>
       </c>
       <c r="G18" t="n">
-        <v>5.4362</v>
+        <v>5.633</v>
       </c>
       <c r="H18" t="n">
-        <v>4080.110107</v>
+        <v>3839.5</v>
       </c>
       <c r="I18" t="n">
-        <v>11468</v>
+        <v>10466.480469</v>
       </c>
       <c r="J18" t="n">
-        <v>34589.769531</v>
+        <v>33147.25</v>
       </c>
       <c r="K18" t="n">
-        <v>1746</v>
+        <v>1819.699951</v>
       </c>
       <c r="L18" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
       <c r="M18" t="n">
-        <v>85.43000000000001</v>
+        <v>85.910004</v>
       </c>
       <c r="N18" t="n">
-        <v>1469.5</v>
+        <v>1519.25</v>
       </c>
       <c r="O18" t="n">
-        <v>662</v>
+        <v>678.5</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.060231</v>
+        <v>-2.182494</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.183236</v>
+        <v>-2.422182</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.128886</v>
+        <v>-3.460699</v>
       </c>
       <c r="S18" t="n">
-        <v>5.90719</v>
+        <v>-3.536977</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.38385</v>
+        <v>0.311299</v>
       </c>
       <c r="U18" t="n">
-        <v>3.081326</v>
+        <v>3.620171</v>
       </c>
       <c r="V18" t="n">
-        <v>5.375289</v>
+        <v>-5.897147</v>
       </c>
       <c r="W18" t="n">
-        <v>4.366973</v>
+        <v>-8.733166000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>5.672634</v>
+        <v>-4.170365</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.730239</v>
+        <v>4.221074</v>
       </c>
       <c r="Z18" t="n">
-        <v>-6.910893</v>
+        <v>-0.360026</v>
       </c>
       <c r="AA18" t="n">
-        <v>-9.912476</v>
+        <v>0.561867</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4.266088</v>
+        <v>2.492447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B19" t="n">
-        <v>110031</v>
+        <v>113532</v>
       </c>
       <c r="C19" t="n">
-        <v>105.949997</v>
+        <v>109.839996</v>
       </c>
       <c r="D19" t="n">
-        <v>96.519997</v>
+        <v>99.44000200000001</v>
       </c>
       <c r="E19" t="n">
-        <v>225</v>
+        <v>228.199997</v>
       </c>
       <c r="F19" t="n">
-        <v>5.2846</v>
+        <v>5.1149</v>
       </c>
       <c r="G19" t="n">
-        <v>5.633</v>
+        <v>5.5471</v>
       </c>
       <c r="H19" t="n">
-        <v>3839.5</v>
+        <v>4076.600098</v>
       </c>
       <c r="I19" t="n">
-        <v>10466.480469</v>
+        <v>11584.549805</v>
       </c>
       <c r="J19" t="n">
-        <v>33147.25</v>
+        <v>34086.039062</v>
       </c>
       <c r="K19" t="n">
-        <v>1819.699951</v>
+        <v>1929.5</v>
       </c>
       <c r="L19" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
       <c r="M19" t="n">
-        <v>85.910004</v>
+        <v>84.489998</v>
       </c>
       <c r="N19" t="n">
-        <v>1519.25</v>
+        <v>1538</v>
       </c>
       <c r="O19" t="n">
-        <v>678.5</v>
+        <v>679.75</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.182494</v>
+        <v>3.181831</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.422182</v>
+        <v>3.671543</v>
       </c>
       <c r="R19" t="n">
-        <v>-3.460699</v>
+        <v>3.025286</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.536977</v>
+        <v>1.422221</v>
       </c>
       <c r="T19" t="n">
-        <v>0.311299</v>
+        <v>-3.211211</v>
       </c>
       <c r="U19" t="n">
-        <v>3.620171</v>
+        <v>-1.524939</v>
       </c>
       <c r="V19" t="n">
-        <v>-5.897147</v>
+        <v>6.175286</v>
       </c>
       <c r="W19" t="n">
-        <v>-8.733166000000001</v>
+        <v>10.682381</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.170365</v>
+        <v>2.832178</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.221074</v>
+        <v>6.033964</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.360026</v>
+        <v>-1.731871</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.561867</v>
+        <v>-1.652899</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.492447</v>
+        <v>0.18423</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B20" t="n">
-        <v>113532</v>
+        <v>104932</v>
       </c>
       <c r="C20" t="n">
-        <v>109.839996</v>
+        <v>101.150002</v>
       </c>
       <c r="D20" t="n">
-        <v>99.44000200000001</v>
+        <v>88.360001</v>
       </c>
       <c r="E20" t="n">
-        <v>228.199997</v>
+        <v>229.300003</v>
       </c>
       <c r="F20" t="n">
-        <v>5.1149</v>
+        <v>5.1997</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5471</v>
+        <v>5.514</v>
       </c>
       <c r="H20" t="n">
-        <v>4076.600098</v>
+        <v>3970.149902</v>
       </c>
       <c r="I20" t="n">
-        <v>11584.549805</v>
+        <v>11455.540039</v>
       </c>
       <c r="J20" t="n">
-        <v>34086.039062</v>
+        <v>32656.699219</v>
       </c>
       <c r="K20" t="n">
-        <v>1929.5</v>
+        <v>1828.900024</v>
       </c>
       <c r="L20" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
       <c r="M20" t="n">
-        <v>84.489998</v>
+        <v>83.889999</v>
       </c>
       <c r="N20" t="n">
-        <v>1538</v>
+        <v>1490.5</v>
       </c>
       <c r="O20" t="n">
-        <v>679.75</v>
+        <v>629.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.181831</v>
+        <v>-7.574957</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.671543</v>
+        <v>-7.911503</v>
       </c>
       <c r="R20" t="n">
-        <v>3.025286</v>
+        <v>-11.142399</v>
       </c>
       <c r="S20" t="n">
-        <v>1.422221</v>
+        <v>0.482036</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.211211</v>
+        <v>1.657897</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.524939</v>
+        <v>-0.59671</v>
       </c>
       <c r="V20" t="n">
-        <v>6.175286</v>
+        <v>-2.611249</v>
       </c>
       <c r="W20" t="n">
-        <v>10.682381</v>
+        <v>-1.113636</v>
       </c>
       <c r="X20" t="n">
-        <v>2.832178</v>
+        <v>-4.193329</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.033964</v>
+        <v>-5.213785</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.731871</v>
+        <v>-2.307594</v>
       </c>
       <c r="AA20" t="n">
-        <v>-1.652899</v>
+        <v>-0.710141</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.18423</v>
+        <v>-7.392424</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B21" t="n">
-        <v>104932</v>
+        <v>101882</v>
       </c>
       <c r="C21" t="n">
-        <v>101.150002</v>
+        <v>98.489998</v>
       </c>
       <c r="D21" t="n">
-        <v>88.360001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>229.300003</v>
+        <v>229.75</v>
       </c>
       <c r="F21" t="n">
-        <v>5.1997</v>
+        <v>5.0927</v>
       </c>
       <c r="G21" t="n">
-        <v>5.514</v>
+        <v>5.5518</v>
       </c>
       <c r="H21" t="n">
-        <v>3970.149902</v>
+        <v>4109.310059</v>
       </c>
       <c r="I21" t="n">
-        <v>11455.540039</v>
+        <v>12221.910156</v>
       </c>
       <c r="J21" t="n">
-        <v>32656.699219</v>
+        <v>33274.148438</v>
       </c>
       <c r="K21" t="n">
-        <v>1828.900024</v>
+        <v>1969</v>
       </c>
       <c r="L21" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
       <c r="M21" t="n">
-        <v>83.889999</v>
+        <v>79.769997</v>
       </c>
       <c r="N21" t="n">
-        <v>1490.5</v>
+        <v>1505.5</v>
       </c>
       <c r="O21" t="n">
-        <v>629.5</v>
+        <v>660.5</v>
       </c>
       <c r="P21" t="n">
-        <v>-7.574957</v>
+        <v>-2.906644</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.911503</v>
+        <v>-2.629761</v>
       </c>
       <c r="R21" t="n">
-        <v>-11.142399</v>
+        <v>-0.611137</v>
       </c>
       <c r="S21" t="n">
-        <v>0.482036</v>
+        <v>0.196248</v>
       </c>
       <c r="T21" t="n">
-        <v>1.657897</v>
+        <v>-2.057809</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.59671</v>
+        <v>0.6855250000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.611249</v>
+        <v>3.505161</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.113636</v>
+        <v>6.689952</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.193329</v>
+        <v>1.890728</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5.213785</v>
+        <v>7.660341</v>
       </c>
       <c r="Z21" t="n">
-        <v>-2.307594</v>
+        <v>-1.791051</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.710141</v>
+        <v>-4.911197</v>
       </c>
       <c r="AB21" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.392424</v>
+        <v>4.924543</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B22" t="n">
-        <v>101882</v>
+        <v>104432</v>
       </c>
       <c r="C22" t="n">
-        <v>98.489998</v>
+        <v>100.900002</v>
       </c>
       <c r="D22" t="n">
-        <v>87.81999999999999</v>
+        <v>89</v>
       </c>
       <c r="E22" t="n">
         <v>229.75</v>
       </c>
       <c r="F22" t="n">
-        <v>5.0927</v>
+        <v>4.9762</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5518</v>
+        <v>5.4883</v>
       </c>
       <c r="H22" t="n">
-        <v>4109.310059</v>
+        <v>4169.47998</v>
       </c>
       <c r="I22" t="n">
-        <v>12221.910156</v>
+        <v>12226.580078</v>
       </c>
       <c r="J22" t="n">
-        <v>33274.148438</v>
+        <v>34098.160156</v>
       </c>
       <c r="K22" t="n">
-        <v>1969</v>
+        <v>1990.099976</v>
       </c>
       <c r="L22" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
       <c r="M22" t="n">
-        <v>79.769997</v>
+        <v>79.540001</v>
       </c>
       <c r="N22" t="n">
-        <v>1505.5</v>
+        <v>1444.25</v>
       </c>
       <c r="O22" t="n">
-        <v>660.5</v>
+        <v>636</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.906644</v>
+        <v>2.502896</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.629761</v>
+        <v>2.446953</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.611137</v>
+        <v>1.343658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.196248</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.057809</v>
+        <v>-2.287586</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6855250000000001</v>
+        <v>-1.143772</v>
       </c>
       <c r="V22" t="n">
-        <v>3.505161</v>
+        <v>1.464234</v>
       </c>
       <c r="W22" t="n">
-        <v>6.689952</v>
+        <v>0.038209</v>
       </c>
       <c r="X22" t="n">
-        <v>1.890728</v>
+        <v>2.476432</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.660341</v>
+        <v>1.071609</v>
       </c>
       <c r="Z22" t="n">
-        <v>-1.791051</v>
+        <v>1.466897</v>
       </c>
       <c r="AA22" t="n">
-        <v>-4.911197</v>
+        <v>-0.288324</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.924543</v>
+        <v>-3.709311</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B23" t="n">
-        <v>104432</v>
+        <v>108335</v>
       </c>
       <c r="C23" t="n">
-        <v>100.900002</v>
+        <v>104.839996</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>100.5</v>
       </c>
       <c r="E23" t="n">
-        <v>229.75</v>
+        <v>233.25</v>
       </c>
       <c r="F23" t="n">
-        <v>4.9762</v>
+        <v>5.0348</v>
       </c>
       <c r="G23" t="n">
-        <v>5.4883</v>
+        <v>5.4012</v>
       </c>
       <c r="H23" t="n">
-        <v>4169.47998</v>
+        <v>4179.830078</v>
       </c>
       <c r="I23" t="n">
-        <v>12226.580078</v>
+        <v>12935.290039</v>
       </c>
       <c r="J23" t="n">
-        <v>34098.160156</v>
+        <v>32908.269531</v>
       </c>
       <c r="K23" t="n">
-        <v>1990.099976</v>
+        <v>1963.900024</v>
       </c>
       <c r="L23" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
       <c r="M23" t="n">
-        <v>79.540001</v>
+        <v>72.660004</v>
       </c>
       <c r="N23" t="n">
-        <v>1444.25</v>
+        <v>1299.75</v>
       </c>
       <c r="O23" t="n">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="P23" t="n">
-        <v>2.502896</v>
+        <v>3.73736</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.446953</v>
+        <v>3.904851</v>
       </c>
       <c r="R23" t="n">
-        <v>1.343658</v>
+        <v>12.921348</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.523395</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.287586</v>
+        <v>1.177604</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.143772</v>
+        <v>-1.587013</v>
       </c>
       <c r="V23" t="n">
-        <v>1.464234</v>
+        <v>0.248235</v>
       </c>
       <c r="W23" t="n">
-        <v>0.038209</v>
+        <v>5.796469</v>
       </c>
       <c r="X23" t="n">
-        <v>2.476432</v>
+        <v>-3.489604</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.071609</v>
+        <v>-1.316514</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.466897</v>
+        <v>-11.318055</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.288324</v>
+        <v>-8.649732</v>
       </c>
       <c r="AB23" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.709311</v>
+        <v>-6.603774</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B24" t="n">
-        <v>108335</v>
+        <v>118087</v>
       </c>
       <c r="C24" t="n">
-        <v>104.839996</v>
+        <v>114.169998</v>
       </c>
       <c r="D24" t="n">
-        <v>100.5</v>
+        <v>109.5</v>
       </c>
       <c r="E24" t="n">
-        <v>233.25</v>
+        <v>235.25</v>
       </c>
       <c r="F24" t="n">
-        <v>5.0348</v>
+        <v>4.8556</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4012</v>
+        <v>5.2739</v>
       </c>
       <c r="H24" t="n">
-        <v>4179.830078</v>
+        <v>4450.379883</v>
       </c>
       <c r="I24" t="n">
-        <v>12935.290039</v>
+        <v>13787.919922</v>
       </c>
       <c r="J24" t="n">
-        <v>32908.269531</v>
+        <v>34407.601562</v>
       </c>
       <c r="K24" t="n">
-        <v>1963.900024</v>
+        <v>1921.099976</v>
       </c>
       <c r="L24" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
       <c r="M24" t="n">
-        <v>72.660004</v>
+        <v>74.900002</v>
       </c>
       <c r="N24" t="n">
-        <v>1299.75</v>
+        <v>1557.25</v>
       </c>
       <c r="O24" t="n">
-        <v>594</v>
+        <v>554.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.73736</v>
+        <v>9.001708000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.904851</v>
+        <v>8.899277</v>
       </c>
       <c r="R24" t="n">
-        <v>12.921348</v>
+        <v>8.955223999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>1.523395</v>
+        <v>0.857449</v>
       </c>
       <c r="T24" t="n">
-        <v>1.177604</v>
+        <v>-3.559231</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.587013</v>
+        <v>-2.35688</v>
       </c>
       <c r="V24" t="n">
-        <v>0.248235</v>
+        <v>6.472746</v>
       </c>
       <c r="W24" t="n">
-        <v>5.796469</v>
+        <v>6.591502</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.489604</v>
+        <v>4.556095</v>
       </c>
       <c r="Y24" t="n">
-        <v>-1.316514</v>
+        <v>-2.179339</v>
       </c>
       <c r="Z24" t="n">
-        <v>-11.318055</v>
+        <v>3.745048</v>
       </c>
       <c r="AA24" t="n">
-        <v>-8.649732</v>
+        <v>3.082849</v>
       </c>
       <c r="AB24" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
       <c r="AC24" t="n">
-        <v>-6.603774</v>
+        <v>-6.649832</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B25" t="n">
-        <v>118087</v>
+        <v>121943</v>
       </c>
       <c r="C25" t="n">
-        <v>114.169998</v>
+        <v>117.949997</v>
       </c>
       <c r="D25" t="n">
-        <v>109.5</v>
+        <v>112.900002</v>
       </c>
       <c r="E25" t="n">
-        <v>235.25</v>
+        <v>239.820007</v>
       </c>
       <c r="F25" t="n">
-        <v>4.8556</v>
+        <v>4.7233</v>
       </c>
       <c r="G25" t="n">
-        <v>5.2739</v>
+        <v>5.1895</v>
       </c>
       <c r="H25" t="n">
-        <v>4450.379883</v>
+        <v>4588.959961</v>
       </c>
       <c r="I25" t="n">
-        <v>13787.919922</v>
+        <v>14346.019531</v>
       </c>
       <c r="J25" t="n">
-        <v>34407.601562</v>
+        <v>35559.53125</v>
       </c>
       <c r="K25" t="n">
-        <v>1921.099976</v>
+        <v>1970.5</v>
       </c>
       <c r="L25" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
       <c r="M25" t="n">
-        <v>74.900002</v>
+        <v>85.55999799999999</v>
       </c>
       <c r="N25" t="n">
-        <v>1557.25</v>
+        <v>1445.75</v>
       </c>
       <c r="O25" t="n">
-        <v>554.5</v>
+        <v>504</v>
       </c>
       <c r="P25" t="n">
-        <v>9.001708000000001</v>
+        <v>3.265389</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.899277</v>
+        <v>3.310851</v>
       </c>
       <c r="R25" t="n">
-        <v>8.955223999999999</v>
+        <v>3.105024</v>
       </c>
       <c r="S25" t="n">
-        <v>0.857449</v>
+        <v>1.942617</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.559231</v>
+        <v>-2.724687</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.35688</v>
+        <v>-1.600337</v>
       </c>
       <c r="V25" t="n">
-        <v>6.472746</v>
+        <v>3.113893</v>
       </c>
       <c r="W25" t="n">
-        <v>6.591502</v>
+        <v>4.047743</v>
       </c>
       <c r="X25" t="n">
-        <v>4.556095</v>
+        <v>3.347893</v>
       </c>
       <c r="Y25" t="n">
-        <v>-2.179339</v>
+        <v>2.571445</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.745048</v>
+        <v>15.79842</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.082849</v>
+        <v>14.232304</v>
       </c>
       <c r="AB25" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.649832</v>
+        <v>-9.107303999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B26" t="n">
-        <v>121943</v>
+        <v>115742</v>
       </c>
       <c r="C26" t="n">
-        <v>117.949997</v>
+        <v>112.309998</v>
       </c>
       <c r="D26" t="n">
-        <v>112.900002</v>
+        <v>104.199997</v>
       </c>
       <c r="E26" t="n">
-        <v>239.820007</v>
+        <v>247.649994</v>
       </c>
       <c r="F26" t="n">
-        <v>4.7233</v>
+        <v>4.8884</v>
       </c>
       <c r="G26" t="n">
-        <v>5.1895</v>
+        <v>5.313</v>
       </c>
       <c r="H26" t="n">
-        <v>4588.959961</v>
+        <v>4507.660156</v>
       </c>
       <c r="I26" t="n">
-        <v>14346.019531</v>
+        <v>14034.969727</v>
       </c>
       <c r="J26" t="n">
-        <v>35559.53125</v>
+        <v>34721.910156</v>
       </c>
       <c r="K26" t="n">
-        <v>1970.5</v>
+        <v>1938.199951</v>
       </c>
       <c r="L26" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
       <c r="M26" t="n">
-        <v>85.55999799999999</v>
+        <v>86.860001</v>
       </c>
       <c r="N26" t="n">
-        <v>1445.75</v>
+        <v>1360</v>
       </c>
       <c r="O26" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="P26" t="n">
-        <v>3.265389</v>
+        <v>-5.085163</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.310851</v>
+        <v>-4.781687</v>
       </c>
       <c r="R26" t="n">
-        <v>3.105024</v>
+        <v>-7.705938</v>
       </c>
       <c r="S26" t="n">
-        <v>1.942617</v>
+        <v>3.264943</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.724687</v>
+        <v>3.49544</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.600337</v>
+        <v>2.379812</v>
       </c>
       <c r="V26" t="n">
-        <v>3.113893</v>
+        <v>-1.771639</v>
       </c>
       <c r="W26" t="n">
-        <v>4.047743</v>
+        <v>-2.168196</v>
       </c>
       <c r="X26" t="n">
-        <v>3.347893</v>
+        <v>-2.355546</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.571445</v>
+        <v>-1.63918</v>
       </c>
       <c r="Z26" t="n">
-        <v>15.79842</v>
+        <v>2.237157</v>
       </c>
       <c r="AA26" t="n">
-        <v>14.232304</v>
+        <v>1.519405</v>
       </c>
       <c r="AB26" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
       <c r="AC26" t="n">
-        <v>-9.107303999999999</v>
+        <v>-8.531746</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B27" t="n">
-        <v>115742</v>
+        <v>116565</v>
       </c>
       <c r="C27" t="n">
-        <v>112.309998</v>
+        <v>113.150002</v>
       </c>
       <c r="D27" t="n">
-        <v>104.199997</v>
+        <v>101.639999</v>
       </c>
       <c r="E27" t="n">
-        <v>247.649994</v>
+        <v>238.789993</v>
       </c>
       <c r="F27" t="n">
-        <v>4.8884</v>
+        <v>5.0328</v>
       </c>
       <c r="G27" t="n">
-        <v>5.313</v>
+        <v>5.3197</v>
       </c>
       <c r="H27" t="n">
-        <v>4507.660156</v>
+        <v>4288.049805</v>
       </c>
       <c r="I27" t="n">
-        <v>14034.969727</v>
+        <v>13219.320312</v>
       </c>
       <c r="J27" t="n">
-        <v>34721.910156</v>
+        <v>33507.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1938.199951</v>
+        <v>1848.099976</v>
       </c>
       <c r="L27" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
       <c r="M27" t="n">
-        <v>86.860001</v>
+        <v>95.30999799999999</v>
       </c>
       <c r="N27" t="n">
-        <v>1360</v>
+        <v>1275</v>
       </c>
       <c r="O27" t="n">
-        <v>461</v>
+        <v>476.75</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.085163</v>
+        <v>0.711064</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.781687</v>
+        <v>0.747933</v>
       </c>
       <c r="R27" t="n">
-        <v>-7.705938</v>
+        <v>-2.456812</v>
       </c>
       <c r="S27" t="n">
-        <v>3.264943</v>
+        <v>-3.57763</v>
       </c>
       <c r="T27" t="n">
-        <v>3.49544</v>
+        <v>2.953934</v>
       </c>
       <c r="U27" t="n">
-        <v>2.379812</v>
+        <v>0.126098</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.771639</v>
+        <v>-4.871937</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.168196</v>
+        <v>-5.811551</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.355546</v>
+        <v>-3.497533</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.63918</v>
+        <v>-4.648642</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.237157</v>
+        <v>8.561526000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.519405</v>
+        <v>9.728294999999999</v>
       </c>
       <c r="AB27" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.531746</v>
+        <v>3.416486</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B28" t="n">
-        <v>116565</v>
+        <v>113144</v>
       </c>
       <c r="C28" t="n">
-        <v>113.150002</v>
+        <v>109.620003</v>
       </c>
       <c r="D28" t="n">
-        <v>101.639999</v>
+        <v>94.199997</v>
       </c>
       <c r="E28" t="n">
-        <v>238.789993</v>
+        <v>234</v>
       </c>
       <c r="F28" t="n">
-        <v>5.0328</v>
+        <v>5.0461</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3197</v>
+        <v>5.3537</v>
       </c>
       <c r="H28" t="n">
-        <v>4288.049805</v>
+        <v>4193.799805</v>
       </c>
       <c r="I28" t="n">
-        <v>13219.320312</v>
+        <v>12851.240234</v>
       </c>
       <c r="J28" t="n">
-        <v>33507.5</v>
+        <v>33052.871094</v>
       </c>
       <c r="K28" t="n">
-        <v>1848.099976</v>
+        <v>1985.199951</v>
       </c>
       <c r="L28" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
       <c r="M28" t="n">
-        <v>95.30999799999999</v>
+        <v>87.410004</v>
       </c>
       <c r="N28" t="n">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="O28" t="n">
-        <v>476.75</v>
+        <v>478.75</v>
       </c>
       <c r="P28" t="n">
-        <v>0.711064</v>
+        <v>-2.934843</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.747933</v>
+        <v>-3.119751</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.456812</v>
+        <v>-7.319955</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.57763</v>
+        <v>-2.005944</v>
       </c>
       <c r="T28" t="n">
-        <v>2.953934</v>
+        <v>0.264265</v>
       </c>
       <c r="U28" t="n">
-        <v>0.126098</v>
+        <v>0.639141</v>
       </c>
       <c r="V28" t="n">
-        <v>-4.871937</v>
+        <v>-2.197969</v>
       </c>
       <c r="W28" t="n">
-        <v>-5.811551</v>
+        <v>-2.78441</v>
       </c>
       <c r="X28" t="n">
-        <v>-3.497533</v>
+        <v>-1.356797</v>
       </c>
       <c r="Y28" t="n">
-        <v>-4.648642</v>
+        <v>7.418429</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.561526000000001</v>
+        <v>-10.761102</v>
       </c>
       <c r="AA28" t="n">
-        <v>9.728294999999999</v>
+        <v>-8.288736</v>
       </c>
       <c r="AB28" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.416486</v>
+        <v>0.419507</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B29" t="n">
-        <v>113144</v>
+        <v>127331</v>
       </c>
       <c r="C29" t="n">
-        <v>109.620003</v>
+        <v>123.57</v>
       </c>
       <c r="D29" t="n">
-        <v>94.199997</v>
+        <v>106.349998</v>
       </c>
       <c r="E29" t="n">
-        <v>234</v>
+        <v>249.699997</v>
       </c>
       <c r="F29" t="n">
-        <v>5.0461</v>
+        <v>4.9041</v>
       </c>
       <c r="G29" t="n">
-        <v>5.3537</v>
+        <v>5.3628</v>
       </c>
       <c r="H29" t="n">
-        <v>4193.799805</v>
+        <v>4567.799805</v>
       </c>
       <c r="I29" t="n">
-        <v>12851.240234</v>
+        <v>14226.219727</v>
       </c>
       <c r="J29" t="n">
-        <v>33052.871094</v>
+        <v>35950.890625</v>
       </c>
       <c r="K29" t="n">
-        <v>1985.199951</v>
+        <v>2038.099976</v>
       </c>
       <c r="L29" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
       <c r="M29" t="n">
-        <v>87.410004</v>
+        <v>82.83000199999999</v>
       </c>
       <c r="N29" t="n">
-        <v>1287</v>
+        <v>1342.75</v>
       </c>
       <c r="O29" t="n">
-        <v>478.75</v>
+        <v>461.75</v>
       </c>
       <c r="P29" t="n">
-        <v>-2.934843</v>
+        <v>12.538888</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3.119751</v>
+        <v>12.725777</v>
       </c>
       <c r="R29" t="n">
-        <v>-7.319955</v>
+        <v>12.898091</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.005944</v>
+        <v>6.7094</v>
       </c>
       <c r="T29" t="n">
-        <v>0.264265</v>
+        <v>-2.814058</v>
       </c>
       <c r="U29" t="n">
-        <v>0.639141</v>
+        <v>0.169975</v>
       </c>
       <c r="V29" t="n">
-        <v>-2.197969</v>
+        <v>8.917927000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>-2.78441</v>
+        <v>10.699197</v>
       </c>
       <c r="X29" t="n">
-        <v>-1.356797</v>
+        <v>8.76783</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.418429</v>
+        <v>2.66472</v>
       </c>
       <c r="Z29" t="n">
-        <v>-10.761102</v>
+        <v>-6.245369</v>
       </c>
       <c r="AA29" t="n">
-        <v>-8.288736</v>
+        <v>-5.239677</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.419507</v>
+        <v>-3.550914</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B30" t="n">
-        <v>127331</v>
+        <v>134185</v>
       </c>
       <c r="C30" t="n">
-        <v>123.57</v>
+        <v>130.389999</v>
       </c>
       <c r="D30" t="n">
-        <v>106.349998</v>
+        <v>113.199997</v>
       </c>
       <c r="E30" t="n">
-        <v>249.699997</v>
+        <v>257.609985</v>
       </c>
       <c r="F30" t="n">
-        <v>4.9041</v>
+        <v>4.8502</v>
       </c>
       <c r="G30" t="n">
-        <v>5.3628</v>
+        <v>5.343</v>
       </c>
       <c r="H30" t="n">
-        <v>4567.799805</v>
+        <v>4769.830078</v>
       </c>
       <c r="I30" t="n">
-        <v>14226.219727</v>
+        <v>15011.349609</v>
       </c>
       <c r="J30" t="n">
-        <v>35950.890625</v>
+        <v>37689.539062</v>
       </c>
       <c r="K30" t="n">
-        <v>2038.099976</v>
+        <v>2062.399902</v>
       </c>
       <c r="L30" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
       <c r="M30" t="n">
-        <v>82.83000199999999</v>
+        <v>77.040001</v>
       </c>
       <c r="N30" t="n">
-        <v>1342.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O30" t="n">
-        <v>461.75</v>
+        <v>471.25</v>
       </c>
       <c r="P30" t="n">
-        <v>12.538888</v>
+        <v>5.382821</v>
       </c>
       <c r="Q30" t="n">
-        <v>12.725777</v>
+        <v>5.519139</v>
       </c>
       <c r="R30" t="n">
-        <v>12.898091</v>
+        <v>6.440995</v>
       </c>
       <c r="S30" t="n">
-        <v>6.7094</v>
+        <v>3.167797</v>
       </c>
       <c r="T30" t="n">
-        <v>-2.814058</v>
+        <v>-1.099076</v>
       </c>
       <c r="U30" t="n">
-        <v>0.169975</v>
+        <v>-0.369214</v>
       </c>
       <c r="V30" t="n">
-        <v>8.917927000000001</v>
+        <v>4.422923</v>
       </c>
       <c r="W30" t="n">
-        <v>10.699197</v>
+        <v>5.518893</v>
       </c>
       <c r="X30" t="n">
-        <v>8.76783</v>
+        <v>4.836176</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.66472</v>
+        <v>1.192283</v>
       </c>
       <c r="Z30" t="n">
-        <v>-6.245369</v>
+        <v>-5.674036</v>
       </c>
       <c r="AA30" t="n">
-        <v>-5.239677</v>
+        <v>-6.990222</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.550914</v>
+        <v>2.05739</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B31" t="n">
-        <v>134185</v>
+        <v>127752</v>
       </c>
       <c r="C31" t="n">
-        <v>130.389999</v>
+        <v>123.949997</v>
       </c>
       <c r="D31" t="n">
-        <v>113.199997</v>
+        <v>106.370003</v>
       </c>
       <c r="E31" t="n">
-        <v>257.609985</v>
+        <v>266.619995</v>
       </c>
       <c r="F31" t="n">
-        <v>4.8502</v>
+        <v>4.9503</v>
       </c>
       <c r="G31" t="n">
-        <v>5.343</v>
+        <v>5.3604</v>
       </c>
       <c r="H31" t="n">
-        <v>4769.830078</v>
+        <v>4845.649902</v>
       </c>
       <c r="I31" t="n">
-        <v>15011.349609</v>
+        <v>15164.009766</v>
       </c>
       <c r="J31" t="n">
-        <v>37689.539062</v>
+        <v>38150.300781</v>
       </c>
       <c r="K31" t="n">
-        <v>2062.399902</v>
+        <v>2048.399902</v>
       </c>
       <c r="L31" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
       <c r="M31" t="n">
-        <v>77.040001</v>
+        <v>81.709999</v>
       </c>
       <c r="N31" t="n">
-        <v>1293.5</v>
+        <v>1222.25</v>
       </c>
       <c r="O31" t="n">
-        <v>471.25</v>
+        <v>448.25</v>
       </c>
       <c r="P31" t="n">
-        <v>5.382821</v>
+        <v>-4.794128</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.519139</v>
+        <v>-4.939031</v>
       </c>
       <c r="R31" t="n">
-        <v>6.440995</v>
+        <v>-6.033564</v>
       </c>
       <c r="S31" t="n">
-        <v>3.167797</v>
+        <v>3.497539</v>
       </c>
       <c r="T31" t="n">
-        <v>-1.099076</v>
+        <v>2.063833</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.369214</v>
+        <v>0.325665</v>
       </c>
       <c r="V31" t="n">
-        <v>4.422923</v>
+        <v>1.589571</v>
       </c>
       <c r="W31" t="n">
-        <v>5.518893</v>
+        <v>1.016965</v>
       </c>
       <c r="X31" t="n">
-        <v>4.836176</v>
+        <v>1.222519</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.192283</v>
+        <v>-0.678821</v>
       </c>
       <c r="Z31" t="n">
-        <v>-5.674036</v>
+        <v>5.861824</v>
       </c>
       <c r="AA31" t="n">
-        <v>-6.990222</v>
+        <v>6.061784</v>
       </c>
       <c r="AB31" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.05739</v>
+        <v>-4.880637</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B32" t="n">
-        <v>127752</v>
+        <v>129020</v>
       </c>
       <c r="C32" t="n">
-        <v>123.949997</v>
+        <v>125.25</v>
       </c>
       <c r="D32" t="n">
-        <v>106.370003</v>
+        <v>106.5</v>
       </c>
       <c r="E32" t="n">
-        <v>266.619995</v>
+        <v>281.100006</v>
       </c>
       <c r="F32" t="n">
-        <v>4.9503</v>
+        <v>4.9673</v>
       </c>
       <c r="G32" t="n">
-        <v>5.3604</v>
+        <v>5.381</v>
       </c>
       <c r="H32" t="n">
-        <v>4845.649902</v>
+        <v>5096.27002</v>
       </c>
       <c r="I32" t="n">
-        <v>15164.009766</v>
+        <v>16091.919922</v>
       </c>
       <c r="J32" t="n">
-        <v>38150.300781</v>
+        <v>38996.390625</v>
       </c>
       <c r="K32" t="n">
-        <v>2048.399902</v>
+        <v>2045.699951</v>
       </c>
       <c r="L32" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
       <c r="M32" t="n">
-        <v>81.709999</v>
+        <v>83.620003</v>
       </c>
       <c r="N32" t="n">
-        <v>1222.25</v>
+        <v>1128.25</v>
       </c>
       <c r="O32" t="n">
-        <v>448.25</v>
+        <v>415.75</v>
       </c>
       <c r="P32" t="n">
-        <v>-4.794128</v>
+        <v>0.992548</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4.939031</v>
+        <v>1.048812</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.033564</v>
+        <v>0.122212</v>
       </c>
       <c r="S32" t="n">
-        <v>3.497539</v>
+        <v>5.430955</v>
       </c>
       <c r="T32" t="n">
-        <v>2.063833</v>
+        <v>0.343408</v>
       </c>
       <c r="U32" t="n">
-        <v>0.325665</v>
+        <v>0.384297</v>
       </c>
       <c r="V32" t="n">
-        <v>1.589571</v>
+        <v>5.172064</v>
       </c>
       <c r="W32" t="n">
-        <v>1.016965</v>
+        <v>6.119161</v>
       </c>
       <c r="X32" t="n">
-        <v>1.222519</v>
+        <v>2.21778</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.678821</v>
+        <v>-0.131808</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.861824</v>
+        <v>3.177329</v>
       </c>
       <c r="AA32" t="n">
-        <v>6.061784</v>
+        <v>2.33754</v>
       </c>
       <c r="AB32" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
       <c r="AC32" t="n">
-        <v>-4.880637</v>
+        <v>-7.250418</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B33" t="n">
-        <v>129020</v>
+        <v>128106</v>
       </c>
       <c r="C33" t="n">
-        <v>125.25</v>
+        <v>124.330002</v>
       </c>
       <c r="D33" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="E33" t="n">
-        <v>281.100006</v>
+        <v>292.600006</v>
       </c>
       <c r="F33" t="n">
-        <v>4.9673</v>
+        <v>5.0141</v>
       </c>
       <c r="G33" t="n">
-        <v>5.381</v>
+        <v>5.4065</v>
       </c>
       <c r="H33" t="n">
-        <v>5096.27002</v>
+        <v>5254.350098</v>
       </c>
       <c r="I33" t="n">
-        <v>16091.919922</v>
+        <v>16379.459961</v>
       </c>
       <c r="J33" t="n">
-        <v>38996.390625</v>
+        <v>39807.371094</v>
       </c>
       <c r="K33" t="n">
-        <v>2045.699951</v>
+        <v>2217.399902</v>
       </c>
       <c r="L33" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
       <c r="M33" t="n">
-        <v>83.620003</v>
+        <v>87.480003</v>
       </c>
       <c r="N33" t="n">
-        <v>1128.25</v>
+        <v>1191.5</v>
       </c>
       <c r="O33" t="n">
-        <v>415.75</v>
+        <v>442</v>
       </c>
       <c r="P33" t="n">
-        <v>0.992548</v>
+        <v>-0.708417</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.048812</v>
+        <v>-0.734529</v>
       </c>
       <c r="R33" t="n">
-        <v>0.122212</v>
+        <v>2.347418</v>
       </c>
       <c r="S33" t="n">
-        <v>5.430955</v>
+        <v>4.091071</v>
       </c>
       <c r="T33" t="n">
-        <v>0.343408</v>
+        <v>0.942164</v>
       </c>
       <c r="U33" t="n">
-        <v>0.384297</v>
+        <v>0.473886</v>
       </c>
       <c r="V33" t="n">
-        <v>5.172064</v>
+        <v>3.101878</v>
       </c>
       <c r="W33" t="n">
-        <v>6.119161</v>
+        <v>1.78686</v>
       </c>
       <c r="X33" t="n">
-        <v>2.21778</v>
+        <v>2.07963</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.131808</v>
+        <v>8.393212999999999</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.177329</v>
+        <v>6.273953</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.33754</v>
+        <v>4.616121</v>
       </c>
       <c r="AB33" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
       <c r="AC33" t="n">
-        <v>-7.250418</v>
+        <v>6.313891</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B34" t="n">
-        <v>128106</v>
+        <v>125924</v>
       </c>
       <c r="C34" t="n">
-        <v>124.330002</v>
+        <v>122.379997</v>
       </c>
       <c r="D34" t="n">
-        <v>109</v>
+        <v>100.5</v>
       </c>
       <c r="E34" t="n">
-        <v>292.600006</v>
+        <v>291</v>
       </c>
       <c r="F34" t="n">
-        <v>5.0141</v>
+        <v>5.117</v>
       </c>
       <c r="G34" t="n">
-        <v>5.4065</v>
+        <v>5.4794</v>
       </c>
       <c r="H34" t="n">
-        <v>5254.350098</v>
+        <v>5035.689941</v>
       </c>
       <c r="I34" t="n">
-        <v>16379.459961</v>
+        <v>15657.820312</v>
       </c>
       <c r="J34" t="n">
-        <v>39807.371094</v>
+        <v>37815.921875</v>
       </c>
       <c r="K34" t="n">
-        <v>2217.399902</v>
+        <v>2291.399902</v>
       </c>
       <c r="L34" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>87.480003</v>
+        <v>87.860001</v>
       </c>
       <c r="N34" t="n">
-        <v>1191.5</v>
+        <v>1145.5</v>
       </c>
       <c r="O34" t="n">
-        <v>442</v>
+        <v>439.5</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.708417</v>
+        <v>-1.703277</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.734529</v>
+        <v>-1.56841</v>
       </c>
       <c r="R34" t="n">
-        <v>2.347418</v>
+        <v>-7.798165</v>
       </c>
       <c r="S34" t="n">
-        <v>4.091071</v>
+        <v>-0.546824</v>
       </c>
       <c r="T34" t="n">
-        <v>0.942164</v>
+        <v>2.052213</v>
       </c>
       <c r="U34" t="n">
-        <v>0.473886</v>
+        <v>1.348382</v>
       </c>
       <c r="V34" t="n">
-        <v>3.101878</v>
+        <v>-4.161507</v>
       </c>
       <c r="W34" t="n">
-        <v>1.78686</v>
+        <v>-4.40576</v>
       </c>
       <c r="X34" t="n">
-        <v>2.07963</v>
+        <v>-5.002715</v>
       </c>
       <c r="Y34" t="n">
-        <v>8.393212999999999</v>
+        <v>3.337242</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.273953</v>
+        <v>-1.49092</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.616121</v>
+        <v>0.434382</v>
       </c>
       <c r="AB34" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
       <c r="AC34" t="n">
-        <v>6.313891</v>
+        <v>-0.565611</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B35" t="n">
-        <v>125924</v>
+        <v>122098</v>
       </c>
       <c r="C35" t="n">
-        <v>122.379997</v>
+        <v>118.660004</v>
       </c>
       <c r="D35" t="n">
-        <v>100.5</v>
+        <v>96.870003</v>
       </c>
       <c r="E35" t="n">
-        <v>291</v>
+        <v>308.200012</v>
       </c>
       <c r="F35" t="n">
-        <v>5.117</v>
+        <v>5.2021</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4794</v>
+        <v>5.6311</v>
       </c>
       <c r="H35" t="n">
-        <v>5035.689941</v>
+        <v>5277.509766</v>
       </c>
       <c r="I35" t="n">
-        <v>15657.820312</v>
+        <v>16735.019531</v>
       </c>
       <c r="J35" t="n">
-        <v>37815.921875</v>
+        <v>38686.320312</v>
       </c>
       <c r="K35" t="n">
-        <v>2291.399902</v>
+        <v>2322.899902</v>
       </c>
       <c r="L35" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
       <c r="M35" t="n">
-        <v>87.860001</v>
+        <v>81.620003</v>
       </c>
       <c r="N35" t="n">
-        <v>1145.5</v>
+        <v>1205</v>
       </c>
       <c r="O35" t="n">
-        <v>439.5</v>
+        <v>446.25</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.703277</v>
+        <v>-3.038341</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1.56841</v>
+        <v>-3.039707</v>
       </c>
       <c r="R35" t="n">
-        <v>-7.798165</v>
+        <v>-3.611938</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.546824</v>
+        <v>5.910657</v>
       </c>
       <c r="T35" t="n">
-        <v>2.052213</v>
+        <v>1.663078</v>
       </c>
       <c r="U35" t="n">
-        <v>1.348382</v>
+        <v>2.768552</v>
       </c>
       <c r="V35" t="n">
-        <v>-4.161507</v>
+        <v>4.802119</v>
       </c>
       <c r="W35" t="n">
-        <v>-4.40576</v>
+        <v>6.879624</v>
       </c>
       <c r="X35" t="n">
-        <v>-5.002715</v>
+        <v>2.301672</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.337242</v>
+        <v>1.374705</v>
       </c>
       <c r="Z35" t="n">
-        <v>-1.49092</v>
+        <v>-6.02954</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.434382</v>
+        <v>-7.102206</v>
       </c>
       <c r="AB35" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.565611</v>
+        <v>1.535836</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B36" t="n">
-        <v>122098</v>
+        <v>123907</v>
       </c>
       <c r="C36" t="n">
-        <v>118.660004</v>
+        <v>120.379997</v>
       </c>
       <c r="D36" t="n">
-        <v>96.870003</v>
+        <v>96.449997</v>
       </c>
       <c r="E36" t="n">
-        <v>308.200012</v>
+        <v>339.829987</v>
       </c>
       <c r="F36" t="n">
-        <v>5.2021</v>
+        <v>5.5005</v>
       </c>
       <c r="G36" t="n">
-        <v>5.6311</v>
+        <v>5.8909</v>
       </c>
       <c r="H36" t="n">
-        <v>5277.509766</v>
+        <v>5460.47998</v>
       </c>
       <c r="I36" t="n">
-        <v>16735.019531</v>
+        <v>17732.599609</v>
       </c>
       <c r="J36" t="n">
-        <v>38686.320312</v>
+        <v>39118.859375</v>
       </c>
       <c r="K36" t="n">
-        <v>2322.899902</v>
+        <v>2327.699951</v>
       </c>
       <c r="L36" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
       <c r="M36" t="n">
-        <v>81.620003</v>
+        <v>86.410004</v>
       </c>
       <c r="N36" t="n">
-        <v>1205</v>
+        <v>1150.5</v>
       </c>
       <c r="O36" t="n">
-        <v>446.25</v>
+        <v>397.25</v>
       </c>
       <c r="P36" t="n">
-        <v>-3.038341</v>
+        <v>1.481597</v>
       </c>
       <c r="Q36" t="n">
-        <v>-3.039707</v>
+        <v>1.449514</v>
       </c>
       <c r="R36" t="n">
-        <v>-3.611938</v>
+        <v>-0.433577</v>
       </c>
       <c r="S36" t="n">
-        <v>5.910657</v>
+        <v>10.262808</v>
       </c>
       <c r="T36" t="n">
-        <v>1.663078</v>
+        <v>5.736153</v>
       </c>
       <c r="U36" t="n">
-        <v>2.768552</v>
+        <v>4.613663</v>
       </c>
       <c r="V36" t="n">
-        <v>4.802119</v>
+        <v>3.46698</v>
       </c>
       <c r="W36" t="n">
-        <v>6.879624</v>
+        <v>5.961033</v>
       </c>
       <c r="X36" t="n">
-        <v>2.301672</v>
+        <v>1.118067</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.374705</v>
+        <v>0.20664</v>
       </c>
       <c r="Z36" t="n">
-        <v>-6.02954</v>
+        <v>5.909863</v>
       </c>
       <c r="AA36" t="n">
-        <v>-7.102206</v>
+        <v>5.868661</v>
       </c>
       <c r="AB36" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.535836</v>
+        <v>-10.980392</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B37" t="n">
-        <v>123907</v>
+        <v>127652</v>
       </c>
       <c r="C37" t="n">
-        <v>120.379997</v>
+        <v>124.040001</v>
       </c>
       <c r="D37" t="n">
-        <v>96.449997</v>
+        <v>98.5</v>
       </c>
       <c r="E37" t="n">
-        <v>339.829987</v>
+        <v>347.700012</v>
       </c>
       <c r="F37" t="n">
-        <v>5.5005</v>
+        <v>5.6111</v>
       </c>
       <c r="G37" t="n">
-        <v>5.8909</v>
+        <v>6.0695</v>
       </c>
       <c r="H37" t="n">
-        <v>5460.47998</v>
+        <v>5522.299805</v>
       </c>
       <c r="I37" t="n">
-        <v>17732.599609</v>
+        <v>17599.400391</v>
       </c>
       <c r="J37" t="n">
-        <v>39118.859375</v>
+        <v>40842.789062</v>
       </c>
       <c r="K37" t="n">
-        <v>2327.699951</v>
+        <v>2426.5</v>
       </c>
       <c r="L37" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
       <c r="M37" t="n">
-        <v>86.410004</v>
+        <v>80.720001</v>
       </c>
       <c r="N37" t="n">
-        <v>1150.5</v>
+        <v>1028.5</v>
       </c>
       <c r="O37" t="n">
-        <v>397.25</v>
+        <v>382.75</v>
       </c>
       <c r="P37" t="n">
-        <v>1.481597</v>
+        <v>3.022428</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.449514</v>
+        <v>3.040375</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.433577</v>
+        <v>2.125457</v>
       </c>
       <c r="S37" t="n">
-        <v>10.262808</v>
+        <v>2.315871</v>
       </c>
       <c r="T37" t="n">
-        <v>5.736153</v>
+        <v>2.010726</v>
       </c>
       <c r="U37" t="n">
-        <v>4.613663</v>
+        <v>3.031792</v>
       </c>
       <c r="V37" t="n">
-        <v>3.46698</v>
+        <v>1.132132</v>
       </c>
       <c r="W37" t="n">
-        <v>5.961033</v>
+        <v>-0.751154</v>
       </c>
       <c r="X37" t="n">
-        <v>1.118067</v>
+        <v>4.406902</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.20664</v>
+        <v>4.244535</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.909863</v>
+        <v>-4.451799</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.868661</v>
+        <v>-6.584889</v>
       </c>
       <c r="AB37" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
       <c r="AC37" t="n">
-        <v>-10.980392</v>
+        <v>-3.650094</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B38" t="n">
-        <v>127652</v>
+        <v>136004</v>
       </c>
       <c r="C38" t="n">
-        <v>124.040001</v>
+        <v>132.600006</v>
       </c>
       <c r="D38" t="n">
-        <v>98.5</v>
+        <v>102.769997</v>
       </c>
       <c r="E38" t="n">
-        <v>347.700012</v>
+        <v>354.850006</v>
       </c>
       <c r="F38" t="n">
-        <v>5.6111</v>
+        <v>5.6277</v>
       </c>
       <c r="G38" t="n">
-        <v>6.0695</v>
+        <v>6.2224</v>
       </c>
       <c r="H38" t="n">
-        <v>5522.299805</v>
+        <v>5648.399902</v>
       </c>
       <c r="I38" t="n">
-        <v>17599.400391</v>
+        <v>17713.619141</v>
       </c>
       <c r="J38" t="n">
-        <v>40842.789062</v>
+        <v>41563.078125</v>
       </c>
       <c r="K38" t="n">
-        <v>2426.5</v>
+        <v>2493.800049</v>
       </c>
       <c r="L38" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
       <c r="M38" t="n">
-        <v>80.720001</v>
+        <v>78.800003</v>
       </c>
       <c r="N38" t="n">
-        <v>1028.5</v>
+        <v>982</v>
       </c>
       <c r="O38" t="n">
-        <v>382.75</v>
+        <v>378</v>
       </c>
       <c r="P38" t="n">
-        <v>3.022428</v>
+        <v>6.542788</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.040375</v>
+        <v>6.901004</v>
       </c>
       <c r="R38" t="n">
-        <v>2.125457</v>
+        <v>4.335022</v>
       </c>
       <c r="S38" t="n">
-        <v>2.315871</v>
+        <v>2.056369</v>
       </c>
       <c r="T38" t="n">
-        <v>2.010726</v>
+        <v>0.295836</v>
       </c>
       <c r="U38" t="n">
-        <v>3.031792</v>
+        <v>2.519157</v>
       </c>
       <c r="V38" t="n">
-        <v>1.132132</v>
+        <v>2.283471</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.751154</v>
+        <v>0.648992</v>
       </c>
       <c r="X38" t="n">
-        <v>4.406902</v>
+        <v>1.763565</v>
       </c>
       <c r="Y38" t="n">
-        <v>4.244535</v>
+        <v>2.773544</v>
       </c>
       <c r="Z38" t="n">
-        <v>-4.451799</v>
+        <v>-5.596201</v>
       </c>
       <c r="AA38" t="n">
-        <v>-6.584889</v>
+        <v>-2.37859</v>
       </c>
       <c r="AB38" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
       <c r="AC38" t="n">
-        <v>-3.650094</v>
+        <v>-1.241019</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B39" t="n">
-        <v>136004</v>
+        <v>131816</v>
       </c>
       <c r="C39" t="n">
-        <v>132.600006</v>
+        <v>128.429993</v>
       </c>
       <c r="D39" t="n">
-        <v>102.769997</v>
+        <v>97.959999</v>
       </c>
       <c r="E39" t="n">
-        <v>354.850006</v>
+        <v>349.799988</v>
       </c>
       <c r="F39" t="n">
-        <v>5.6277</v>
+        <v>5.4332</v>
       </c>
       <c r="G39" t="n">
-        <v>6.2224</v>
+        <v>6.0652</v>
       </c>
       <c r="H39" t="n">
-        <v>5648.399902</v>
+        <v>5762.47998</v>
       </c>
       <c r="I39" t="n">
-        <v>17713.619141</v>
+        <v>18189.169922</v>
       </c>
       <c r="J39" t="n">
-        <v>41563.078125</v>
+        <v>42330.148438</v>
       </c>
       <c r="K39" t="n">
-        <v>2493.800049</v>
+        <v>2636.100098</v>
       </c>
       <c r="L39" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
       <c r="M39" t="n">
-        <v>78.800003</v>
+        <v>71.769997</v>
       </c>
       <c r="N39" t="n">
-        <v>982</v>
+        <v>1057</v>
       </c>
       <c r="O39" t="n">
-        <v>378</v>
+        <v>424.75</v>
       </c>
       <c r="P39" t="n">
-        <v>6.542788</v>
+        <v>-3.079321</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.901004</v>
+        <v>-3.144806</v>
       </c>
       <c r="R39" t="n">
-        <v>4.335022</v>
+        <v>-4.680352</v>
       </c>
       <c r="S39" t="n">
-        <v>2.056369</v>
+        <v>-1.423142</v>
       </c>
       <c r="T39" t="n">
-        <v>0.295836</v>
+        <v>-3.456118</v>
       </c>
       <c r="U39" t="n">
-        <v>2.519157</v>
+        <v>-2.526362</v>
       </c>
       <c r="V39" t="n">
-        <v>2.283471</v>
+        <v>2.019688</v>
       </c>
       <c r="W39" t="n">
-        <v>0.648992</v>
+        <v>2.684662</v>
       </c>
       <c r="X39" t="n">
-        <v>1.763565</v>
+        <v>1.845557</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.773544</v>
+        <v>5.706153</v>
       </c>
       <c r="Z39" t="n">
-        <v>-5.596201</v>
+        <v>-7.314758</v>
       </c>
       <c r="AA39" t="n">
-        <v>-2.37859</v>
+        <v>-8.921328000000001</v>
       </c>
       <c r="AB39" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
       <c r="AC39" t="n">
-        <v>-1.241019</v>
+        <v>12.367725</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B40" t="n">
-        <v>131816</v>
+        <v>129713</v>
       </c>
       <c r="C40" t="n">
-        <v>128.429993</v>
+        <v>126.260002</v>
       </c>
       <c r="D40" t="n">
-        <v>97.959999</v>
+        <v>97.25</v>
       </c>
       <c r="E40" t="n">
-        <v>349.799988</v>
+        <v>368.579987</v>
       </c>
       <c r="F40" t="n">
-        <v>5.4332</v>
+        <v>5.7623</v>
       </c>
       <c r="G40" t="n">
-        <v>6.0652</v>
+        <v>6.2522</v>
       </c>
       <c r="H40" t="n">
-        <v>5762.47998</v>
+        <v>5705.450195</v>
       </c>
       <c r="I40" t="n">
-        <v>18189.169922</v>
+        <v>18095.150391</v>
       </c>
       <c r="J40" t="n">
-        <v>42330.148438</v>
+        <v>41763.460938</v>
       </c>
       <c r="K40" t="n">
-        <v>2636.100098</v>
+        <v>2738.300049</v>
       </c>
       <c r="L40" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
       <c r="M40" t="n">
-        <v>71.769997</v>
+        <v>73.160004</v>
       </c>
       <c r="N40" t="n">
-        <v>1057</v>
+        <v>982.5</v>
       </c>
       <c r="O40" t="n">
-        <v>424.75</v>
+        <v>410.75</v>
       </c>
       <c r="P40" t="n">
-        <v>-3.079321</v>
+        <v>-1.595406</v>
       </c>
       <c r="Q40" t="n">
-        <v>-3.144806</v>
+        <v>-1.689629</v>
       </c>
       <c r="R40" t="n">
-        <v>-4.680352</v>
+        <v>-0.724785</v>
       </c>
       <c r="S40" t="n">
-        <v>-1.423142</v>
+        <v>5.368782</v>
       </c>
       <c r="T40" t="n">
-        <v>-3.456118</v>
+        <v>6.057206</v>
       </c>
       <c r="U40" t="n">
-        <v>-2.526362</v>
+        <v>3.083168</v>
       </c>
       <c r="V40" t="n">
-        <v>2.019688</v>
+        <v>-0.9896740000000001</v>
       </c>
       <c r="W40" t="n">
-        <v>2.684662</v>
+        <v>-0.516898</v>
       </c>
       <c r="X40" t="n">
-        <v>1.845557</v>
+        <v>-1.338733</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.706153</v>
+        <v>3.876937</v>
       </c>
       <c r="Z40" t="n">
-        <v>-7.314758</v>
+        <v>1.59895</v>
       </c>
       <c r="AA40" t="n">
-        <v>-8.921328000000001</v>
+        <v>1.936752</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
       <c r="AC40" t="n">
-        <v>12.367725</v>
+        <v>-3.296057</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B41" t="n">
-        <v>129713</v>
+        <v>125668</v>
       </c>
       <c r="C41" t="n">
-        <v>126.260002</v>
+        <v>122.32</v>
       </c>
       <c r="D41" t="n">
-        <v>97.25</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>368.579987</v>
+        <v>402.850006</v>
       </c>
       <c r="F41" t="n">
-        <v>5.7623</v>
+        <v>6.0139</v>
       </c>
       <c r="G41" t="n">
-        <v>6.2522</v>
+        <v>6.345178</v>
       </c>
       <c r="H41" t="n">
-        <v>5705.450195</v>
+        <v>6032.379883</v>
       </c>
       <c r="I41" t="n">
-        <v>18095.150391</v>
+        <v>19218.169922</v>
       </c>
       <c r="J41" t="n">
-        <v>41763.460938</v>
+        <v>44910.648438</v>
       </c>
       <c r="K41" t="n">
-        <v>2738.300049</v>
+        <v>2657</v>
       </c>
       <c r="L41" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
       <c r="M41" t="n">
-        <v>73.160004</v>
+        <v>72.94000200000001</v>
       </c>
       <c r="N41" t="n">
-        <v>982.5</v>
+        <v>989.5</v>
       </c>
       <c r="O41" t="n">
-        <v>410.75</v>
+        <v>423</v>
       </c>
       <c r="P41" t="n">
-        <v>-1.595406</v>
+        <v>-3.118423</v>
       </c>
       <c r="Q41" t="n">
-        <v>-1.689629</v>
+        <v>-3.120547</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.724785</v>
+        <v>-4.041131</v>
       </c>
       <c r="S41" t="n">
-        <v>5.368782</v>
+        <v>9.297851</v>
       </c>
       <c r="T41" t="n">
-        <v>6.057206</v>
+        <v>4.366308</v>
       </c>
       <c r="U41" t="n">
-        <v>3.083168</v>
+        <v>1.487125</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.9896740000000001</v>
+        <v>5.73013</v>
       </c>
       <c r="W41" t="n">
-        <v>-0.516898</v>
+        <v>6.206191</v>
       </c>
       <c r="X41" t="n">
-        <v>-1.338733</v>
+        <v>7.535744</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.876937</v>
+        <v>-2.968997</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.59895</v>
+        <v>-1.819235</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.936752</v>
+        <v>-0.300712</v>
       </c>
       <c r="AB41" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
       <c r="AC41" t="n">
-        <v>-3.296057</v>
+        <v>2.982349</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B42" t="n">
-        <v>125668</v>
+        <v>120283</v>
       </c>
       <c r="C42" t="n">
-        <v>122.32</v>
+        <v>117.269997</v>
       </c>
       <c r="D42" t="n">
-        <v>93.31999999999999</v>
+        <v>85.949997</v>
       </c>
       <c r="E42" t="n">
-        <v>402.850006</v>
+        <v>407.700012</v>
       </c>
       <c r="F42" t="n">
-        <v>6.0139</v>
+        <v>6.1779</v>
       </c>
       <c r="G42" t="n">
-        <v>6.345178</v>
+        <v>6.422608</v>
       </c>
       <c r="H42" t="n">
-        <v>6032.379883</v>
+        <v>5881.629883</v>
       </c>
       <c r="I42" t="n">
-        <v>19218.169922</v>
+        <v>19310.789062</v>
       </c>
       <c r="J42" t="n">
-        <v>44910.648438</v>
+        <v>42544.21875</v>
       </c>
       <c r="K42" t="n">
-        <v>2657</v>
+        <v>2629.199951</v>
       </c>
       <c r="L42" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
       <c r="M42" t="n">
-        <v>72.94000200000001</v>
+        <v>74.639999</v>
       </c>
       <c r="N42" t="n">
-        <v>989.5</v>
+        <v>998.25</v>
       </c>
       <c r="O42" t="n">
-        <v>423</v>
+        <v>458.5</v>
       </c>
       <c r="P42" t="n">
-        <v>-3.118423</v>
+        <v>-4.2851</v>
       </c>
       <c r="Q42" t="n">
-        <v>-3.120547</v>
+        <v>-4.128518</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.041131</v>
+        <v>-7.89756</v>
       </c>
       <c r="S42" t="n">
-        <v>9.297851</v>
+        <v>1.203924</v>
       </c>
       <c r="T42" t="n">
-        <v>4.366308</v>
+        <v>2.727016</v>
       </c>
       <c r="U42" t="n">
-        <v>1.487125</v>
+        <v>1.220293</v>
       </c>
       <c r="V42" t="n">
-        <v>5.73013</v>
+        <v>-2.499014</v>
       </c>
       <c r="W42" t="n">
-        <v>6.206191</v>
+        <v>0.481935</v>
       </c>
       <c r="X42" t="n">
-        <v>7.535744</v>
+        <v>-5.269195</v>
       </c>
       <c r="Y42" t="n">
-        <v>-2.968997</v>
+        <v>-1.046295</v>
       </c>
       <c r="Z42" t="n">
-        <v>-1.819235</v>
+        <v>5.47059</v>
       </c>
       <c r="AA42" t="n">
-        <v>-0.300712</v>
+        <v>2.330678</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.982349</v>
+        <v>8.392435000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B43" t="n">
-        <v>120283</v>
+        <v>126135</v>
       </c>
       <c r="C43" t="n">
-        <v>117.269997</v>
+        <v>123</v>
       </c>
       <c r="D43" t="n">
-        <v>85.949997</v>
+        <v>91.400002</v>
       </c>
       <c r="E43" t="n">
-        <v>407.700012</v>
+        <v>394.149994</v>
       </c>
       <c r="F43" t="n">
-        <v>6.1779</v>
+        <v>5.8745</v>
       </c>
       <c r="G43" t="n">
-        <v>6.422608</v>
+        <v>6.101281</v>
       </c>
       <c r="H43" t="n">
-        <v>5881.629883</v>
+        <v>6040.529785</v>
       </c>
       <c r="I43" t="n">
-        <v>19310.789062</v>
+        <v>19627.439453</v>
       </c>
       <c r="J43" t="n">
-        <v>42544.21875</v>
+        <v>44544.660156</v>
       </c>
       <c r="K43" t="n">
-        <v>2629.199951</v>
+        <v>2812.5</v>
       </c>
       <c r="L43" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
       <c r="M43" t="n">
-        <v>74.639999</v>
+        <v>76.760002</v>
       </c>
       <c r="N43" t="n">
-        <v>998.25</v>
+        <v>1042</v>
       </c>
       <c r="O43" t="n">
-        <v>458.5</v>
+        <v>482</v>
       </c>
       <c r="P43" t="n">
-        <v>-4.2851</v>
+        <v>4.865193</v>
       </c>
       <c r="Q43" t="n">
-        <v>-4.128518</v>
+        <v>4.886163</v>
       </c>
       <c r="R43" t="n">
-        <v>-7.89756</v>
+        <v>6.340901</v>
       </c>
       <c r="S43" t="n">
-        <v>1.203924</v>
+        <v>-3.323527</v>
       </c>
       <c r="T43" t="n">
-        <v>2.727016</v>
+        <v>-4.911055</v>
       </c>
       <c r="U43" t="n">
-        <v>1.220293</v>
+        <v>-5.003057</v>
       </c>
       <c r="V43" t="n">
-        <v>-2.499014</v>
+        <v>2.70163</v>
       </c>
       <c r="W43" t="n">
-        <v>0.481935</v>
+        <v>1.639759</v>
       </c>
       <c r="X43" t="n">
-        <v>-5.269195</v>
+        <v>4.702029</v>
       </c>
       <c r="Y43" t="n">
-        <v>-1.046295</v>
+        <v>6.971704</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.47059</v>
+        <v>1.129389</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.330678</v>
+        <v>2.840304</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.392435000000001</v>
+        <v>5.125409</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B44" t="n">
-        <v>126135</v>
+        <v>122799</v>
       </c>
       <c r="C44" t="n">
-        <v>123</v>
+        <v>120.010002</v>
       </c>
       <c r="D44" t="n">
-        <v>91.400002</v>
+        <v>87.599998</v>
       </c>
       <c r="E44" t="n">
-        <v>394.149994</v>
+        <v>392.700012</v>
       </c>
       <c r="F44" t="n">
-        <v>5.8745</v>
+        <v>5.839</v>
       </c>
       <c r="G44" t="n">
-        <v>6.101281</v>
+        <v>6.064281</v>
       </c>
       <c r="H44" t="n">
-        <v>6040.529785</v>
+        <v>5954.5</v>
       </c>
       <c r="I44" t="n">
-        <v>19627.439453</v>
+        <v>18847.279297</v>
       </c>
       <c r="J44" t="n">
-        <v>44544.660156</v>
+        <v>43840.910156</v>
       </c>
       <c r="K44" t="n">
-        <v>2812.5</v>
+        <v>2836.800049</v>
       </c>
       <c r="L44" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
       <c r="M44" t="n">
-        <v>76.760002</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>1042</v>
+        <v>1011.5</v>
       </c>
       <c r="O44" t="n">
-        <v>482</v>
+        <v>453.5</v>
       </c>
       <c r="P44" t="n">
-        <v>4.865193</v>
+        <v>-2.644785</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.886163</v>
+        <v>-2.430893</v>
       </c>
       <c r="R44" t="n">
-        <v>6.340901</v>
+        <v>-4.157553</v>
       </c>
       <c r="S44" t="n">
-        <v>-3.323527</v>
+        <v>-0.367876</v>
       </c>
       <c r="T44" t="n">
-        <v>-4.911055</v>
+        <v>-0.604299</v>
       </c>
       <c r="U44" t="n">
-        <v>-5.003057</v>
+        <v>-0.606433</v>
       </c>
       <c r="V44" t="n">
-        <v>2.70163</v>
+        <v>-1.424209</v>
       </c>
       <c r="W44" t="n">
-        <v>1.639759</v>
+        <v>-3.974844</v>
       </c>
       <c r="X44" t="n">
-        <v>4.702029</v>
+        <v>-1.579875</v>
       </c>
       <c r="Y44" t="n">
-        <v>6.971704</v>
+        <v>0.864002</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.129389</v>
+        <v>-3.819105</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.840304</v>
+        <v>-4.66389</v>
       </c>
       <c r="AB44" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.125409</v>
+        <v>-5.912863</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B45" t="n">
-        <v>122799</v>
+        <v>130260</v>
       </c>
       <c r="C45" t="n">
-        <v>120.010002</v>
+        <v>127.300003</v>
       </c>
       <c r="D45" t="n">
-        <v>87.599998</v>
+        <v>93.41999800000001</v>
       </c>
       <c r="E45" t="n">
-        <v>392.700012</v>
+        <v>358.700012</v>
       </c>
       <c r="F45" t="n">
-        <v>5.839</v>
+        <v>5.7581</v>
       </c>
       <c r="G45" t="n">
-        <v>6.064281</v>
+        <v>6.22665</v>
       </c>
       <c r="H45" t="n">
-        <v>5954.5</v>
+        <v>5611.850098</v>
       </c>
       <c r="I45" t="n">
-        <v>18847.279297</v>
+        <v>17299.289062</v>
       </c>
       <c r="J45" t="n">
-        <v>43840.910156</v>
+        <v>42001.761719</v>
       </c>
       <c r="K45" t="n">
-        <v>2836.800049</v>
+        <v>3122.800049</v>
       </c>
       <c r="L45" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
       <c r="M45" t="n">
-        <v>73.18000000000001</v>
+        <v>74.739998</v>
       </c>
       <c r="N45" t="n">
-        <v>1011.5</v>
+        <v>1014.75</v>
       </c>
       <c r="O45" t="n">
-        <v>453.5</v>
+        <v>457.25</v>
       </c>
       <c r="P45" t="n">
-        <v>-2.644785</v>
+        <v>6.075782</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2.430893</v>
+        <v>6.074494</v>
       </c>
       <c r="R45" t="n">
-        <v>-4.157553</v>
+        <v>6.643835</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.367876</v>
+        <v>-8.658008000000001</v>
       </c>
       <c r="T45" t="n">
-        <v>-0.604299</v>
+        <v>-1.385514</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.606433</v>
+        <v>2.677469</v>
       </c>
       <c r="V45" t="n">
-        <v>-1.424209</v>
+        <v>-5.75447</v>
       </c>
       <c r="W45" t="n">
-        <v>-3.974844</v>
+        <v>-8.213335000000001</v>
       </c>
       <c r="X45" t="n">
-        <v>-1.579875</v>
+        <v>-4.195051</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.864002</v>
+        <v>10.081782</v>
       </c>
       <c r="Z45" t="n">
-        <v>-3.819105</v>
+        <v>2.465598</v>
       </c>
       <c r="AA45" t="n">
-        <v>-4.66389</v>
+        <v>2.131727</v>
       </c>
       <c r="AB45" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
       <c r="AC45" t="n">
-        <v>-5.912863</v>
+        <v>0.826902</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B46" t="n">
-        <v>130260</v>
+        <v>135067</v>
       </c>
       <c r="C46" t="n">
-        <v>127.300003</v>
+        <v>131.630005</v>
       </c>
       <c r="D46" t="n">
-        <v>93.41999800000001</v>
+        <v>101.5</v>
       </c>
       <c r="E46" t="n">
-        <v>358.700012</v>
+        <v>354.350006</v>
       </c>
       <c r="F46" t="n">
-        <v>5.7581</v>
+        <v>5.62</v>
       </c>
       <c r="G46" t="n">
-        <v>6.22665</v>
+        <v>6.393862</v>
       </c>
       <c r="H46" t="n">
-        <v>5611.850098</v>
+        <v>5569.060059</v>
       </c>
       <c r="I46" t="n">
-        <v>17299.289062</v>
+        <v>17446.339844</v>
       </c>
       <c r="J46" t="n">
-        <v>42001.761719</v>
+        <v>40669.359375</v>
       </c>
       <c r="K46" t="n">
-        <v>3122.800049</v>
+        <v>3305</v>
       </c>
       <c r="L46" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
       <c r="M46" t="n">
-        <v>74.739998</v>
+        <v>63.119999</v>
       </c>
       <c r="N46" t="n">
-        <v>1014.75</v>
+        <v>1034.75</v>
       </c>
       <c r="O46" t="n">
-        <v>457.25</v>
+        <v>467.25</v>
       </c>
       <c r="P46" t="n">
-        <v>6.075782</v>
+        <v>3.690312</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.074494</v>
+        <v>3.401415</v>
       </c>
       <c r="R46" t="n">
-        <v>6.643835</v>
+        <v>8.649114000000001</v>
       </c>
       <c r="S46" t="n">
-        <v>-8.658008000000001</v>
+        <v>-1.212714</v>
       </c>
       <c r="T46" t="n">
-        <v>-1.385514</v>
+        <v>-2.398363</v>
       </c>
       <c r="U46" t="n">
-        <v>2.677469</v>
+        <v>2.685417</v>
       </c>
       <c r="V46" t="n">
-        <v>-5.75447</v>
+        <v>-0.762494</v>
       </c>
       <c r="W46" t="n">
-        <v>-8.213335000000001</v>
+        <v>0.850039</v>
       </c>
       <c r="X46" t="n">
-        <v>-4.195051</v>
+        <v>-3.172253</v>
       </c>
       <c r="Y46" t="n">
-        <v>10.081782</v>
+        <v>5.834506</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.465598</v>
+        <v>-18.564639</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.131727</v>
+        <v>-15.547229</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.826902</v>
+        <v>2.186987</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B47" t="n">
-        <v>135067</v>
+        <v>137027</v>
       </c>
       <c r="C47" t="n">
-        <v>131.630005</v>
+        <v>133.990005</v>
       </c>
       <c r="D47" t="n">
-        <v>101.5</v>
+        <v>107.639999</v>
       </c>
       <c r="E47" t="n">
-        <v>354.350006</v>
+        <v>378.799988</v>
       </c>
       <c r="F47" t="n">
-        <v>5.62</v>
+        <v>5.6651</v>
       </c>
       <c r="G47" t="n">
-        <v>6.393862</v>
+        <v>6.43915</v>
       </c>
       <c r="H47" t="n">
-        <v>5569.060059</v>
+        <v>5911.689941</v>
       </c>
       <c r="I47" t="n">
-        <v>17446.339844</v>
+        <v>19113.769531</v>
       </c>
       <c r="J47" t="n">
-        <v>40669.359375</v>
+        <v>42270.070312</v>
       </c>
       <c r="K47" t="n">
-        <v>3305</v>
+        <v>3288.899902</v>
       </c>
       <c r="L47" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
       <c r="M47" t="n">
-        <v>63.119999</v>
+        <v>63.900002</v>
       </c>
       <c r="N47" t="n">
-        <v>1034.75</v>
+        <v>1041.75</v>
       </c>
       <c r="O47" t="n">
-        <v>467.25</v>
+        <v>444</v>
       </c>
       <c r="P47" t="n">
-        <v>3.690312</v>
+        <v>1.451132</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.401415</v>
+        <v>1.792905</v>
       </c>
       <c r="R47" t="n">
-        <v>8.649114000000001</v>
+        <v>6.04926</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.212714</v>
+        <v>6.899952</v>
       </c>
       <c r="T47" t="n">
-        <v>-2.398363</v>
+        <v>0.802495</v>
       </c>
       <c r="U47" t="n">
-        <v>2.685417</v>
+        <v>0.708306</v>
       </c>
       <c r="V47" t="n">
-        <v>-0.762494</v>
+        <v>6.152383</v>
       </c>
       <c r="W47" t="n">
-        <v>0.850039</v>
+        <v>9.557475999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>-3.172253</v>
+        <v>3.935914</v>
       </c>
       <c r="Y47" t="n">
-        <v>5.834506</v>
+        <v>-0.487144</v>
       </c>
       <c r="Z47" t="n">
-        <v>-18.564639</v>
+        <v>4.432231</v>
       </c>
       <c r="AA47" t="n">
-        <v>-15.547229</v>
+        <v>1.235746</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.186987</v>
+        <v>-4.975923</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B48" t="n">
-        <v>137027</v>
+        <v>138855</v>
       </c>
       <c r="C48" t="n">
-        <v>133.990005</v>
+        <v>135.850006</v>
       </c>
       <c r="D48" t="n">
-        <v>107.639999</v>
+        <v>109.029999</v>
       </c>
       <c r="E48" t="n">
-        <v>378.799988</v>
+        <v>377.850006</v>
       </c>
       <c r="F48" t="n">
-        <v>5.6651</v>
+        <v>5.4784</v>
       </c>
       <c r="G48" t="n">
-        <v>6.43915</v>
+        <v>6.418485</v>
       </c>
       <c r="H48" t="n">
-        <v>5911.689941</v>
+        <v>6204.950195</v>
       </c>
       <c r="I48" t="n">
-        <v>19113.769531</v>
+        <v>20369.730469</v>
       </c>
       <c r="J48" t="n">
-        <v>42270.070312</v>
+        <v>44094.769531</v>
       </c>
       <c r="K48" t="n">
-        <v>3288.899902</v>
+        <v>3294.399902</v>
       </c>
       <c r="L48" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
       <c r="M48" t="n">
-        <v>63.900002</v>
+        <v>67.610001</v>
       </c>
       <c r="N48" t="n">
-        <v>1041.75</v>
+        <v>1024.25</v>
       </c>
       <c r="O48" t="n">
-        <v>444</v>
+        <v>420.5</v>
       </c>
       <c r="P48" t="n">
-        <v>1.451132</v>
+        <v>1.334044</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.792905</v>
+        <v>1.388164</v>
       </c>
       <c r="R48" t="n">
-        <v>6.04926</v>
+        <v>1.291341</v>
       </c>
       <c r="S48" t="n">
-        <v>6.899952</v>
+        <v>-0.250787</v>
       </c>
       <c r="T48" t="n">
-        <v>0.802495</v>
+        <v>-3.295615</v>
       </c>
       <c r="U48" t="n">
-        <v>0.708306</v>
+        <v>-0.320923</v>
       </c>
       <c r="V48" t="n">
-        <v>6.152383</v>
+        <v>4.960684</v>
       </c>
       <c r="W48" t="n">
-        <v>9.557475999999999</v>
+        <v>6.570975</v>
       </c>
       <c r="X48" t="n">
-        <v>3.935914</v>
+        <v>4.316764</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.487144</v>
+        <v>0.167229</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.432231</v>
+        <v>7.106431</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.235746</v>
+        <v>5.805945</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
       <c r="AC48" t="n">
-        <v>-4.975923</v>
+        <v>-5.292793</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B49" t="n">
-        <v>138855</v>
+        <v>133071</v>
       </c>
       <c r="C49" t="n">
-        <v>135.850006</v>
+        <v>129.880005</v>
       </c>
       <c r="D49" t="n">
-        <v>109.029999</v>
+        <v>101.919998</v>
       </c>
       <c r="E49" t="n">
-        <v>377.850006</v>
+        <v>398.01001</v>
       </c>
       <c r="F49" t="n">
-        <v>5.4784</v>
+        <v>5.5754</v>
       </c>
       <c r="G49" t="n">
-        <v>6.418485</v>
+        <v>6.365372</v>
       </c>
       <c r="H49" t="n">
-        <v>6204.950195</v>
+        <v>6339.390137</v>
       </c>
       <c r="I49" t="n">
-        <v>20369.730469</v>
+        <v>21122.449219</v>
       </c>
       <c r="J49" t="n">
-        <v>44094.769531</v>
+        <v>44130.980469</v>
       </c>
       <c r="K49" t="n">
-        <v>3294.399902</v>
+        <v>3293.199951</v>
       </c>
       <c r="L49" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
       <c r="M49" t="n">
-        <v>67.610001</v>
+        <v>72.529999</v>
       </c>
       <c r="N49" t="n">
-        <v>1024.25</v>
+        <v>961.75</v>
       </c>
       <c r="O49" t="n">
-        <v>420.5</v>
+        <v>394</v>
       </c>
       <c r="P49" t="n">
-        <v>1.334044</v>
+        <v>-4.165496</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.388164</v>
+        <v>-4.394554</v>
       </c>
       <c r="R49" t="n">
-        <v>1.291341</v>
+        <v>-6.521142</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.250787</v>
+        <v>5.335451</v>
       </c>
       <c r="T49" t="n">
-        <v>-3.295615</v>
+        <v>1.770583</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.320923</v>
+        <v>-0.8275</v>
       </c>
       <c r="V49" t="n">
-        <v>4.960684</v>
+        <v>2.166656</v>
       </c>
       <c r="W49" t="n">
-        <v>6.570975</v>
+        <v>3.695281</v>
       </c>
       <c r="X49" t="n">
-        <v>4.316764</v>
+        <v>0.082121</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.167229</v>
+        <v>-0.036424</v>
       </c>
       <c r="Z49" t="n">
-        <v>7.106431</v>
+        <v>6.373831</v>
       </c>
       <c r="AA49" t="n">
-        <v>5.805945</v>
+        <v>7.277027</v>
       </c>
       <c r="AB49" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
       <c r="AC49" t="n">
-        <v>-5.292793</v>
+        <v>-6.302021</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B50" t="n">
-        <v>133071</v>
+        <v>141422</v>
       </c>
       <c r="C50" t="n">
-        <v>129.880005</v>
+        <v>138.5</v>
       </c>
       <c r="D50" t="n">
-        <v>101.919998</v>
+        <v>107.43</v>
       </c>
       <c r="E50" t="n">
-        <v>398.01001</v>
+        <v>393.850006</v>
       </c>
       <c r="F50" t="n">
-        <v>5.5754</v>
+        <v>5.413</v>
       </c>
       <c r="G50" t="n">
-        <v>6.365372</v>
+        <v>6.317119</v>
       </c>
       <c r="H50" t="n">
-        <v>6339.390137</v>
+        <v>6460.259766</v>
       </c>
       <c r="I50" t="n">
-        <v>21122.449219</v>
+        <v>21455.550781</v>
       </c>
       <c r="J50" t="n">
-        <v>44130.980469</v>
+        <v>45544.878906</v>
       </c>
       <c r="K50" t="n">
-        <v>3293.199951</v>
+        <v>3473.699951</v>
       </c>
       <c r="L50" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
       <c r="M50" t="n">
-        <v>72.529999</v>
+        <v>68.120003</v>
       </c>
       <c r="N50" t="n">
-        <v>961.75</v>
+        <v>1036.75</v>
       </c>
       <c r="O50" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P50" t="n">
-        <v>-4.165496</v>
+        <v>6.275597</v>
       </c>
       <c r="Q50" t="n">
-        <v>-4.394554</v>
+        <v>6.636892</v>
       </c>
       <c r="R50" t="n">
-        <v>-6.521142</v>
+        <v>5.406203</v>
       </c>
       <c r="S50" t="n">
-        <v>5.335451</v>
+        <v>-1.045201</v>
       </c>
       <c r="T50" t="n">
-        <v>1.770583</v>
+        <v>-2.912791</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.8275</v>
+        <v>-0.758056</v>
       </c>
       <c r="V50" t="n">
-        <v>2.166656</v>
+        <v>1.906644</v>
       </c>
       <c r="W50" t="n">
-        <v>3.695281</v>
+        <v>1.577003</v>
       </c>
       <c r="X50" t="n">
-        <v>0.082121</v>
+        <v>3.203868</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.036424</v>
+        <v>5.480991</v>
       </c>
       <c r="Z50" t="n">
-        <v>6.373831</v>
+        <v>-7.580133</v>
       </c>
       <c r="AA50" t="n">
-        <v>7.277027</v>
+        <v>-6.080237</v>
       </c>
       <c r="AB50" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
       <c r="AC50" t="n">
-        <v>-6.302021</v>
+        <v>1.015228</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B51" t="n">
-        <v>141422</v>
+        <v>146237</v>
       </c>
       <c r="C51" t="n">
-        <v>138.5</v>
+        <v>143.240005</v>
       </c>
       <c r="D51" t="n">
-        <v>107.43</v>
+        <v>109.669998</v>
       </c>
       <c r="E51" t="n">
-        <v>393.850006</v>
+        <v>399.799988</v>
       </c>
       <c r="F51" t="n">
-        <v>5.413</v>
+        <v>5.3217</v>
       </c>
       <c r="G51" t="n">
-        <v>6.317119</v>
+        <v>6.238303</v>
       </c>
       <c r="H51" t="n">
-        <v>6460.259766</v>
+        <v>6688.459961</v>
       </c>
       <c r="I51" t="n">
-        <v>21455.550781</v>
+        <v>22660.009766</v>
       </c>
       <c r="J51" t="n">
-        <v>45544.878906</v>
+        <v>46397.890625</v>
       </c>
       <c r="K51" t="n">
-        <v>3473.699951</v>
+        <v>3840.800049</v>
       </c>
       <c r="L51" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
       <c r="M51" t="n">
-        <v>68.120003</v>
+        <v>67.019997</v>
       </c>
       <c r="N51" t="n">
-        <v>1036.75</v>
+        <v>1001.75</v>
       </c>
       <c r="O51" t="n">
-        <v>398</v>
+        <v>415.5</v>
       </c>
       <c r="P51" t="n">
-        <v>6.275597</v>
+        <v>3.404704</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.636892</v>
+        <v>3.422387</v>
       </c>
       <c r="R51" t="n">
-        <v>5.406203</v>
+        <v>2.085077</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.045201</v>
+        <v>1.510723</v>
       </c>
       <c r="T51" t="n">
-        <v>-2.912791</v>
+        <v>-1.68668</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.758056</v>
+        <v>-1.247656</v>
       </c>
       <c r="V51" t="n">
-        <v>1.906644</v>
+        <v>3.532369</v>
       </c>
       <c r="W51" t="n">
-        <v>1.577003</v>
+        <v>5.613741</v>
       </c>
       <c r="X51" t="n">
-        <v>3.203868</v>
+        <v>1.872904</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.480991</v>
+        <v>10.567985</v>
       </c>
       <c r="Z51" t="n">
-        <v>-7.580133</v>
+        <v>-2.562105</v>
       </c>
       <c r="AA51" t="n">
-        <v>-6.080237</v>
+        <v>-1.614806</v>
       </c>
       <c r="AB51" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.015228</v>
+        <v>4.396985</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B52" t="n">
-        <v>146237</v>
+        <v>149540</v>
       </c>
       <c r="C52" t="n">
-        <v>143.240005</v>
+        <v>146.410004</v>
       </c>
       <c r="D52" t="n">
-        <v>109.669998</v>
+        <v>110.059998</v>
       </c>
       <c r="E52" t="n">
-        <v>399.799988</v>
+        <v>413.329987</v>
       </c>
       <c r="F52" t="n">
-        <v>5.3217</v>
+        <v>5.382</v>
       </c>
       <c r="G52" t="n">
-        <v>6.238303</v>
+        <v>6.222775</v>
       </c>
       <c r="H52" t="n">
-        <v>6688.459961</v>
+        <v>6840.200195</v>
       </c>
       <c r="I52" t="n">
-        <v>22660.009766</v>
+        <v>23724.960938</v>
       </c>
       <c r="J52" t="n">
-        <v>46397.890625</v>
+        <v>47562.871094</v>
       </c>
       <c r="K52" t="n">
-        <v>3840.800049</v>
+        <v>3982.199951</v>
       </c>
       <c r="L52" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
       <c r="M52" t="n">
-        <v>67.019997</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>1001.75</v>
+        <v>1099.75</v>
       </c>
       <c r="O52" t="n">
-        <v>415.5</v>
+        <v>431.5</v>
       </c>
       <c r="P52" t="n">
-        <v>3.404704</v>
+        <v>2.258662</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.422387</v>
+        <v>2.213068</v>
       </c>
       <c r="R52" t="n">
-        <v>2.085077</v>
+        <v>0.355612</v>
       </c>
       <c r="S52" t="n">
-        <v>1.510723</v>
+        <v>3.384192</v>
       </c>
       <c r="T52" t="n">
-        <v>-1.68668</v>
+        <v>1.133094</v>
       </c>
       <c r="U52" t="n">
-        <v>-1.247656</v>
+        <v>-0.248917</v>
       </c>
       <c r="V52" t="n">
-        <v>3.532369</v>
+        <v>2.268687</v>
       </c>
       <c r="W52" t="n">
-        <v>5.613741</v>
+        <v>4.699694</v>
       </c>
       <c r="X52" t="n">
-        <v>1.872904</v>
+        <v>2.510848</v>
       </c>
       <c r="Y52" t="n">
-        <v>10.567985</v>
+        <v>3.681522</v>
       </c>
       <c r="Z52" t="n">
-        <v>-2.562105</v>
+        <v>-2.228635</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.614806</v>
+        <v>-2.909575</v>
       </c>
       <c r="AB52" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
       <c r="AC52" t="n">
-        <v>4.396985</v>
+        <v>3.850782</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B53" t="n">
-        <v>149540</v>
+        <v>159072</v>
       </c>
       <c r="C53" t="n">
-        <v>146.410004</v>
+        <v>155.850006</v>
       </c>
       <c r="D53" t="n">
-        <v>110.059998</v>
+        <v>116.489998</v>
       </c>
       <c r="E53" t="n">
-        <v>413.329987</v>
+        <v>411.089996</v>
       </c>
       <c r="F53" t="n">
-        <v>5.382</v>
+        <v>5.3554</v>
       </c>
       <c r="G53" t="n">
-        <v>6.222775</v>
+        <v>6.207325</v>
       </c>
       <c r="H53" t="n">
-        <v>6840.200195</v>
+        <v>6849.089844</v>
       </c>
       <c r="I53" t="n">
-        <v>23724.960938</v>
+        <v>23365.689453</v>
       </c>
       <c r="J53" t="n">
-        <v>47562.871094</v>
+        <v>47716.421875</v>
       </c>
       <c r="K53" t="n">
-        <v>3982.199951</v>
+        <v>4218.299805</v>
       </c>
       <c r="L53" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
       <c r="M53" t="n">
-        <v>65.06999999999999</v>
+        <v>63.200001</v>
       </c>
       <c r="N53" t="n">
-        <v>1099.75</v>
+        <v>1137.75</v>
       </c>
       <c r="O53" t="n">
-        <v>431.5</v>
+        <v>435.5</v>
       </c>
       <c r="P53" t="n">
-        <v>2.258662</v>
+        <v>6.374214</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.213068</v>
+        <v>6.447649</v>
       </c>
       <c r="R53" t="n">
-        <v>0.355612</v>
+        <v>5.842268</v>
       </c>
       <c r="S53" t="n">
-        <v>3.384192</v>
+        <v>-0.541938</v>
       </c>
       <c r="T53" t="n">
-        <v>1.133094</v>
+        <v>-0.494238</v>
       </c>
       <c r="U53" t="n">
-        <v>-0.248917</v>
+        <v>-0.248282</v>
       </c>
       <c r="V53" t="n">
-        <v>2.268687</v>
+        <v>0.129962</v>
       </c>
       <c r="W53" t="n">
-        <v>4.699694</v>
+        <v>-1.514319</v>
       </c>
       <c r="X53" t="n">
-        <v>2.510848</v>
+        <v>0.322837</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.681522</v>
+        <v>5.92888</v>
       </c>
       <c r="Z53" t="n">
-        <v>-2.228635</v>
+        <v>-3.984914</v>
       </c>
       <c r="AA53" t="n">
-        <v>-2.909575</v>
+        <v>-2.873827</v>
       </c>
       <c r="AB53" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.850782</v>
+        <v>0.926999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B54" t="n">
-        <v>159072</v>
+        <v>161125</v>
       </c>
       <c r="C54" t="n">
-        <v>155.850006</v>
+        <v>158</v>
       </c>
       <c r="D54" t="n">
-        <v>116.489998</v>
+        <v>112.449997</v>
       </c>
       <c r="E54" t="n">
-        <v>411.089996</v>
+        <v>424.200012</v>
       </c>
       <c r="F54" t="n">
-        <v>5.3554</v>
+        <v>5.4762</v>
       </c>
       <c r="G54" t="n">
-        <v>6.207325</v>
+        <v>6.426735</v>
       </c>
       <c r="H54" t="n">
-        <v>6849.089844</v>
+        <v>6845.5</v>
       </c>
       <c r="I54" t="n">
-        <v>23365.689453</v>
+        <v>23241.990234</v>
       </c>
       <c r="J54" t="n">
-        <v>47716.421875</v>
+        <v>48063.289062</v>
       </c>
       <c r="K54" t="n">
-        <v>4218.299805</v>
+        <v>4325.600098</v>
       </c>
       <c r="L54" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
       <c r="M54" t="n">
-        <v>63.200001</v>
+        <v>60.849998</v>
       </c>
       <c r="N54" t="n">
-        <v>1137.75</v>
+        <v>1030.5</v>
       </c>
       <c r="O54" t="n">
-        <v>435.5</v>
+        <v>440.25</v>
       </c>
       <c r="P54" t="n">
-        <v>6.374214</v>
+        <v>1.290611</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.447649</v>
+        <v>1.379528</v>
       </c>
       <c r="R54" t="n">
-        <v>5.842268</v>
+        <v>-3.46811</v>
       </c>
       <c r="S54" t="n">
-        <v>-0.541938</v>
+        <v>3.189087</v>
       </c>
       <c r="T54" t="n">
-        <v>-0.494238</v>
+        <v>2.255667</v>
       </c>
       <c r="U54" t="n">
-        <v>-0.248282</v>
+        <v>3.534694</v>
       </c>
       <c r="V54" t="n">
-        <v>0.129962</v>
+        <v>-0.052413</v>
       </c>
       <c r="W54" t="n">
-        <v>-1.514319</v>
+        <v>-0.529405</v>
       </c>
       <c r="X54" t="n">
-        <v>0.322837</v>
+        <v>0.726935</v>
       </c>
       <c r="Y54" t="n">
-        <v>5.92888</v>
+        <v>2.543686</v>
       </c>
       <c r="Z54" t="n">
-        <v>-3.984914</v>
+        <v>-1.929976</v>
       </c>
       <c r="AA54" t="n">
-        <v>-2.873827</v>
+        <v>-3.718358</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.926999</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B55" t="n">
-        <v>161125</v>
+        <v>181364</v>
       </c>
       <c r="C55" t="n">
-        <v>158</v>
+        <v>178.199997</v>
       </c>
       <c r="D55" t="n">
-        <v>112.449997</v>
+        <v>123.800003</v>
       </c>
       <c r="E55" t="n">
-        <v>424.200012</v>
+        <v>410.649994</v>
       </c>
       <c r="F55" t="n">
-        <v>5.4762</v>
+        <v>5.1892</v>
       </c>
       <c r="G55" t="n">
-        <v>6.426735</v>
+        <v>6.203474</v>
       </c>
       <c r="H55" t="n">
-        <v>6845.5</v>
+        <v>6939.029785</v>
       </c>
       <c r="I55" t="n">
-        <v>23241.990234</v>
+        <v>23461.820312</v>
       </c>
       <c r="J55" t="n">
-        <v>48063.289062</v>
+        <v>48892.46875</v>
       </c>
       <c r="K55" t="n">
-        <v>4325.600098</v>
+        <v>4713.899902</v>
       </c>
       <c r="L55" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
       <c r="M55" t="n">
-        <v>60.849998</v>
+        <v>70.69000200000001</v>
       </c>
       <c r="N55" t="n">
-        <v>1030.5</v>
+        <v>1064.25</v>
       </c>
       <c r="O55" t="n">
-        <v>440.25</v>
+        <v>428.25</v>
       </c>
       <c r="P55" t="n">
-        <v>1.290611</v>
+        <v>12.561055</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.379528</v>
+        <v>12.784808</v>
       </c>
       <c r="R55" t="n">
-        <v>-3.46811</v>
+        <v>10.093381</v>
       </c>
       <c r="S55" t="n">
-        <v>3.189087</v>
+        <v>-3.194252</v>
       </c>
       <c r="T55" t="n">
-        <v>2.255667</v>
+        <v>-5.240864</v>
       </c>
       <c r="U55" t="n">
-        <v>3.534694</v>
+        <v>-3.473939</v>
       </c>
       <c r="V55" t="n">
-        <v>-0.052413</v>
+        <v>1.366296</v>
       </c>
       <c r="W55" t="n">
-        <v>-0.529405</v>
+        <v>0.945832</v>
       </c>
       <c r="X55" t="n">
-        <v>0.726935</v>
+        <v>1.725183</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.543686</v>
+        <v>8.976785</v>
       </c>
       <c r="Z55" t="n">
-        <v>-1.929976</v>
+        <v>13.566704</v>
       </c>
       <c r="AA55" t="n">
-        <v>-3.718358</v>
+        <v>16.170919</v>
       </c>
       <c r="AB55" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.0907</v>
+        <v>-2.725724</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B56" t="n">
-        <v>181364</v>
+        <v>188787</v>
       </c>
       <c r="C56" t="n">
-        <v>178.199997</v>
+        <v>185.160004</v>
       </c>
       <c r="D56" t="n">
-        <v>123.800003</v>
+        <v>126.379997</v>
       </c>
       <c r="E56" t="n">
-        <v>410.649994</v>
+        <v>396.75</v>
       </c>
       <c r="F56" t="n">
-        <v>5.1892</v>
+        <v>5.1366</v>
       </c>
       <c r="G56" t="n">
-        <v>6.203474</v>
+        <v>6.056935</v>
       </c>
       <c r="H56" t="n">
-        <v>6939.029785</v>
+        <v>6878.879883</v>
       </c>
       <c r="I56" t="n">
-        <v>23461.820312</v>
+        <v>22668.210938</v>
       </c>
       <c r="J56" t="n">
-        <v>48892.46875</v>
+        <v>48977.921875</v>
       </c>
       <c r="K56" t="n">
-        <v>4713.899902</v>
+        <v>5230.5</v>
       </c>
       <c r="L56" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
       <c r="M56" t="n">
-        <v>70.69000200000001</v>
+        <v>72.480003</v>
       </c>
       <c r="N56" t="n">
-        <v>1064.25</v>
+        <v>1157.25</v>
       </c>
       <c r="O56" t="n">
-        <v>428.25</v>
+        <v>438.75</v>
       </c>
       <c r="P56" t="n">
-        <v>12.561055</v>
+        <v>4.092874</v>
       </c>
       <c r="Q56" t="n">
-        <v>12.784808</v>
+        <v>3.905728</v>
       </c>
       <c r="R56" t="n">
-        <v>10.093381</v>
+        <v>2.084002</v>
       </c>
       <c r="S56" t="n">
-        <v>-3.194252</v>
+        <v>-3.384876</v>
       </c>
       <c r="T56" t="n">
-        <v>-5.240864</v>
+        <v>-1.013642</v>
       </c>
       <c r="U56" t="n">
-        <v>-3.473939</v>
+        <v>-2.362212</v>
       </c>
       <c r="V56" t="n">
-        <v>1.366296</v>
+        <v>-0.866834</v>
       </c>
       <c r="W56" t="n">
-        <v>0.945832</v>
+        <v>-3.382557</v>
       </c>
       <c r="X56" t="n">
-        <v>1.725183</v>
+        <v>0.174778</v>
       </c>
       <c r="Y56" t="n">
-        <v>8.976785</v>
+        <v>10.959081</v>
       </c>
       <c r="Z56" t="n">
-        <v>13.566704</v>
+        <v>2.775644</v>
       </c>
       <c r="AA56" t="n">
-        <v>16.170919</v>
+        <v>2.532184</v>
       </c>
       <c r="AB56" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
       <c r="AC56" t="n">
-        <v>-2.725724</v>
+        <v>2.451839</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B57" t="n">
-        <v>188787</v>
+        <v>187462</v>
       </c>
       <c r="C57" t="n">
-        <v>185.160004</v>
+        <v>184.279999</v>
       </c>
       <c r="D57" t="n">
-        <v>126.379997</v>
+        <v>120</v>
       </c>
       <c r="E57" t="n">
-        <v>396.75</v>
+        <v>380.149994</v>
       </c>
       <c r="F57" t="n">
-        <v>5.1366</v>
+        <v>5.264</v>
       </c>
       <c r="G57" t="n">
-        <v>6.056935</v>
+        <v>6.027728</v>
       </c>
       <c r="H57" t="n">
-        <v>6878.879883</v>
+        <v>6528.52002</v>
       </c>
       <c r="I57" t="n">
-        <v>22668.210938</v>
+        <v>21590.630859</v>
       </c>
       <c r="J57" t="n">
-        <v>48977.921875</v>
+        <v>46341.511719</v>
       </c>
       <c r="K57" t="n">
-        <v>5230.5</v>
+        <v>4647.600098</v>
       </c>
       <c r="L57" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
       <c r="M57" t="n">
-        <v>72.480003</v>
+        <v>118.349998</v>
       </c>
       <c r="N57" t="n">
-        <v>1157.25</v>
+        <v>1171</v>
       </c>
       <c r="O57" t="n">
-        <v>438.75</v>
+        <v>457.75</v>
       </c>
       <c r="P57" t="n">
-        <v>4.092874</v>
+        <v>-0.7018489999999999</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.905728</v>
+        <v>-0.475267</v>
       </c>
       <c r="R57" t="n">
-        <v>2.084002</v>
+        <v>-5.048265</v>
       </c>
       <c r="S57" t="n">
-        <v>-3.384876</v>
+        <v>-4.183996</v>
       </c>
       <c r="T57" t="n">
-        <v>-1.013642</v>
+        <v>2.480238</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.362212</v>
+        <v>-0.482204</v>
       </c>
       <c r="V57" t="n">
-        <v>-0.866834</v>
+        <v>-5.093269</v>
       </c>
       <c r="W57" t="n">
-        <v>-3.382557</v>
+        <v>-4.753706</v>
       </c>
       <c r="X57" t="n">
-        <v>0.174778</v>
+        <v>-5.382854</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.959081</v>
+        <v>-11.144248</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.775644</v>
+        <v>51.268282</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.532184</v>
+        <v>63.286414</v>
       </c>
       <c r="AB57" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.451839</v>
+        <v>4.330484</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B58" t="n">
-        <v>187462</v>
+        <v>187318</v>
       </c>
       <c r="C58" t="n">
-        <v>184.279999</v>
+        <v>184.089996</v>
       </c>
       <c r="D58" t="n">
-        <v>120</v>
+        <v>115.760002</v>
       </c>
       <c r="E58" t="n">
-        <v>380.149994</v>
+        <v>402.5</v>
       </c>
       <c r="F58" t="n">
-        <v>5.264</v>
+        <v>5.0175</v>
       </c>
       <c r="G58" t="n">
-        <v>6.027728</v>
+        <v>5.858231</v>
       </c>
       <c r="H58" t="n">
-        <v>6528.52002</v>
+        <v>7209.009766</v>
       </c>
       <c r="I58" t="n">
-        <v>21590.630859</v>
+        <v>24892.310547</v>
       </c>
       <c r="J58" t="n">
-        <v>46341.511719</v>
+        <v>49652.140625</v>
       </c>
       <c r="K58" t="n">
-        <v>4647.600098</v>
+        <v>4614.700195</v>
       </c>
       <c r="L58" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
       <c r="M58" t="n">
-        <v>118.349998</v>
+        <v>114.010002</v>
       </c>
       <c r="N58" t="n">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="O58" t="n">
-        <v>457.75</v>
+        <v>464.75</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.7018489999999999</v>
+        <v>-0.076816</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.475267</v>
+        <v>-0.103105</v>
       </c>
       <c r="R58" t="n">
-        <v>-5.048265</v>
+        <v>-3.533332</v>
       </c>
       <c r="S58" t="n">
-        <v>-4.183996</v>
+        <v>5.87926</v>
       </c>
       <c r="T58" t="n">
-        <v>2.480238</v>
+        <v>-4.682751</v>
       </c>
       <c r="U58" t="n">
-        <v>-0.482204</v>
+        <v>-2.811955</v>
       </c>
       <c r="V58" t="n">
-        <v>-5.093269</v>
+        <v>10.423339</v>
       </c>
       <c r="W58" t="n">
-        <v>-4.753706</v>
+        <v>15.292187</v>
       </c>
       <c r="X58" t="n">
-        <v>-5.382854</v>
+        <v>7.143981</v>
       </c>
       <c r="Y58" t="n">
-        <v>-11.144248</v>
+        <v>-0.70789</v>
       </c>
       <c r="Z58" t="n">
-        <v>51.268282</v>
+        <v>3.639774</v>
       </c>
       <c r="AA58" t="n">
-        <v>63.286414</v>
+        <v>-3.667086</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.330484</v>
+        <v>1.529219</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B59" t="n">
-        <v>187318</v>
+        <v>173788</v>
       </c>
       <c r="C59" t="n">
-        <v>184.089996</v>
+        <v>170.75</v>
       </c>
       <c r="D59" t="n">
-        <v>115.760002</v>
+        <v>110.989998</v>
       </c>
       <c r="E59" t="n">
-        <v>402.5</v>
+        <v>430.399994</v>
       </c>
       <c r="F59" t="n">
-        <v>5.0175</v>
+        <v>5.0517</v>
       </c>
       <c r="G59" t="n">
-        <v>5.858231</v>
+        <v>5.882353</v>
       </c>
       <c r="H59" t="n">
-        <v>7209.009766</v>
+        <v>7580.060059</v>
       </c>
       <c r="I59" t="n">
-        <v>24892.310547</v>
+        <v>26972.619141</v>
       </c>
       <c r="J59" t="n">
-        <v>49652.140625</v>
+        <v>51032.460938</v>
       </c>
       <c r="K59" t="n">
-        <v>4614.700195</v>
+        <v>4560.5</v>
       </c>
       <c r="L59" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
       <c r="M59" t="n">
-        <v>114.010002</v>
+        <v>92.050003</v>
       </c>
       <c r="N59" t="n">
-        <v>1182</v>
+        <v>1186.75</v>
       </c>
       <c r="O59" t="n">
-        <v>464.75</v>
+        <v>446.75</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.076816</v>
+        <v>-7.223011</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.103105</v>
+        <v>-7.246454</v>
       </c>
       <c r="R59" t="n">
-        <v>-3.533332</v>
+        <v>-4.120598</v>
       </c>
       <c r="S59" t="n">
-        <v>5.87926</v>
+        <v>6.931676</v>
       </c>
       <c r="T59" t="n">
-        <v>-4.682751</v>
+        <v>0.6816179999999999</v>
       </c>
       <c r="U59" t="n">
-        <v>-2.811955</v>
+        <v>0.411758</v>
       </c>
       <c r="V59" t="n">
-        <v>10.423339</v>
+        <v>5.147036</v>
       </c>
       <c r="W59" t="n">
-        <v>15.292187</v>
+        <v>8.357234</v>
       </c>
       <c r="X59" t="n">
-        <v>7.143981</v>
+        <v>2.779981</v>
       </c>
       <c r="Y59" t="n">
-        <v>-0.70789</v>
+        <v>-1.174512</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.639774</v>
+        <v>-16.855429</v>
       </c>
       <c r="AA59" t="n">
-        <v>-3.667086</v>
+        <v>-19.261467</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.529219</v>
+        <v>-3.87305</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B60" t="n">
-        <v>173788</v>
+        <v>172024</v>
       </c>
       <c r="C60" t="n">
-        <v>170.75</v>
+        <v>169.050003</v>
       </c>
       <c r="D60" t="n">
-        <v>110.989998</v>
+        <v>107.980003</v>
       </c>
       <c r="E60" t="n">
-        <v>430.399994</v>
+        <v>435.649994</v>
       </c>
       <c r="F60" t="n">
-        <v>5.0517</v>
+        <v>5.181787</v>
       </c>
       <c r="G60" t="n">
-        <v>5.882353</v>
+        <v>5.91716</v>
       </c>
       <c r="H60" t="n">
-        <v>7580.060059</v>
+        <v>7499.359863</v>
       </c>
       <c r="I60" t="n">
-        <v>26972.619141</v>
+        <v>26213.720703</v>
       </c>
       <c r="J60" t="n">
-        <v>51032.460938</v>
+        <v>52319.199219</v>
       </c>
       <c r="K60" t="n">
-        <v>4560.5</v>
+        <v>4022.899902</v>
       </c>
       <c r="L60" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
       <c r="M60" t="n">
-        <v>92.050003</v>
+        <v>72.91999800000001</v>
       </c>
       <c r="N60" t="n">
-        <v>1186.75</v>
+        <v>1116.75</v>
       </c>
       <c r="O60" t="n">
-        <v>446.75</v>
+        <v>412.75</v>
       </c>
       <c r="P60" t="n">
-        <v>-7.223011</v>
+        <v>-1.01503</v>
       </c>
       <c r="Q60" t="n">
-        <v>-7.246454</v>
+        <v>-0.995606</v>
       </c>
       <c r="R60" t="n">
-        <v>-4.120598</v>
+        <v>-2.711951</v>
       </c>
       <c r="S60" t="n">
-        <v>6.931676</v>
+        <v>1.219796</v>
       </c>
       <c r="T60" t="n">
-        <v>0.6816179999999999</v>
+        <v>2.575111</v>
       </c>
       <c r="U60" t="n">
-        <v>0.411758</v>
+        <v>0.591722</v>
       </c>
       <c r="V60" t="n">
-        <v>5.147036</v>
+        <v>-1.064638</v>
       </c>
       <c r="W60" t="n">
-        <v>8.357234</v>
+        <v>-2.813588</v>
       </c>
       <c r="X60" t="n">
-        <v>2.779981</v>
+        <v>2.521411</v>
       </c>
       <c r="Y60" t="n">
-        <v>-1.174512</v>
+        <v>-11.788183</v>
       </c>
       <c r="Z60" t="n">
-        <v>-16.855429</v>
+        <v>-20.44414</v>
       </c>
       <c r="AA60" t="n">
-        <v>-19.261467</v>
+        <v>-20.782188</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
       <c r="AC60" t="n">
-        <v>-3.87305</v>
+        <v>-7.61052</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>172024</v>
+        <v>177999</v>
       </c>
       <c r="C61" t="n">
-        <v>169.050003</v>
+        <v>175.020004</v>
       </c>
       <c r="D61" t="n">
-        <v>107.980003</v>
+        <v>107.25</v>
       </c>
       <c r="E61" t="n">
-        <v>435.649994</v>
+        <v>428.390015</v>
       </c>
       <c r="F61" t="n">
-        <v>5.181787</v>
+        <v>5.0781</v>
       </c>
       <c r="G61" t="n">
-        <v>5.91716</v>
+        <v>5.8536</v>
       </c>
       <c r="H61" t="n">
-        <v>7499.359863</v>
+        <v>7489.720215</v>
       </c>
       <c r="I61" t="n">
-        <v>26213.720703</v>
+        <v>25373.849609</v>
       </c>
       <c r="J61" t="n">
-        <v>52319.199219</v>
+        <v>52485.03125</v>
       </c>
       <c r="K61" t="n">
-        <v>4022.899902</v>
+        <v>4049.100098</v>
       </c>
       <c r="L61" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
       <c r="M61" t="n">
-        <v>72.91999800000001</v>
+        <v>90.120003</v>
       </c>
       <c r="N61" t="n">
-        <v>1116.75</v>
+        <v>1172</v>
       </c>
       <c r="O61" t="n">
-        <v>412.75</v>
+        <v>440.75</v>
       </c>
       <c r="P61" t="n">
-        <v>-1.01503</v>
+        <v>3.473353</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.995606</v>
+        <v>3.5315</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.711951</v>
+        <v>-0.676054</v>
       </c>
       <c r="S61" t="n">
-        <v>1.219796</v>
+        <v>-1.666471</v>
       </c>
       <c r="T61" t="n">
-        <v>2.575111</v>
+        <v>-2.000986</v>
       </c>
       <c r="U61" t="n">
-        <v>0.591722</v>
+        <v>-1.074164</v>
       </c>
       <c r="V61" t="n">
-        <v>-1.064638</v>
+        <v>-0.12854</v>
       </c>
       <c r="W61" t="n">
-        <v>-2.813588</v>
+        <v>-3.203937</v>
       </c>
       <c r="X61" t="n">
-        <v>2.521411</v>
+        <v>0.316962</v>
       </c>
       <c r="Y61" t="n">
-        <v>-11.788183</v>
+        <v>0.651276</v>
       </c>
       <c r="Z61" t="n">
-        <v>-20.44414</v>
+        <v>21.827335</v>
       </c>
       <c r="AA61" t="n">
-        <v>-20.782188</v>
+        <v>23.5875</v>
       </c>
       <c r="AB61" t="n">
-        <v>-5.898462</v>
+        <v>4.947392</v>
       </c>
       <c r="AC61" t="n">
-        <v>-7.61052</v>
+        <v>6.783767</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B62" t="n">
-        <v>177159</v>
-      </c>
-      <c r="C62" t="n">
-        <v>174.309998</v>
-      </c>
-      <c r="D62" t="n">
-        <v>107.360001</v>
-      </c>
-      <c r="E62" t="n">
-        <v>425.369995</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>5.0716</v>
-      </c>
-      <c r="G62" t="n">
-        <v>5.8255</v>
-      </c>
-      <c r="H62" t="n">
-        <v>7437.629883</v>
-      </c>
-      <c r="I62" t="n">
-        <v>25122.179688</v>
-      </c>
-      <c r="J62" t="n">
-        <v>52208.058594</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4109.799805</v>
-      </c>
-      <c r="L62" t="n">
-        <v>84.839996</v>
-      </c>
-      <c r="M62" t="n">
-        <v>90.25</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1188.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>466.25</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2.985049</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>3.111502</v>
-      </c>
-      <c r="R62" t="n">
-        <v>-0.574183</v>
-      </c>
-      <c r="S62" t="n">
-        <v>-2.359692</v>
-      </c>
+        <v>5.0747</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>-2.12643</v>
-      </c>
-      <c r="U62" t="n">
-        <v>-1.549054</v>
-      </c>
-      <c r="V62" t="n">
-        <v>-0.823137</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-4.164006</v>
-      </c>
-      <c r="X62" t="n">
-        <v>-0.212428</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.160131</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>22.071937</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>23.765774</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>6.424894</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>12.961841</v>
-      </c>
+        <v>-0.06696100000000001</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5822,7 +5822,7 @@
         <v>52485.03125</v>
       </c>
       <c r="K61" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="L61" t="n">
         <v>84.66999800000001</v>
@@ -5831,10 +5831,10 @@
         <v>90.120003</v>
       </c>
       <c r="N61" t="n">
-        <v>1172</v>
+        <v>1187.5</v>
       </c>
       <c r="O61" t="n">
-        <v>440.75</v>
+        <v>464</v>
       </c>
       <c r="P61" t="n">
         <v>3.473353</v>
@@ -5864,7 +5864,7 @@
         <v>0.316962</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.651276</v>
+        <v>2.090534</v>
       </c>
       <c r="Z61" t="n">
         <v>21.827335</v>
@@ -5873,10 +5873,10 @@
         <v>23.5875</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.947392</v>
+        <v>6.335348</v>
       </c>
       <c r="AC61" t="n">
-        <v>6.783767</v>
+        <v>12.416717</v>
       </c>
     </row>
     <row r="62">

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5810,7 +5810,7 @@
         <v>5.0781</v>
       </c>
       <c r="G61" t="n">
-        <v>5.8536</v>
+        <v>5.847953</v>
       </c>
       <c r="H61" t="n">
         <v>7489.720215</v>
@@ -5822,7 +5822,7 @@
         <v>52485.03125</v>
       </c>
       <c r="K61" t="n">
-        <v>4107</v>
+        <v>4049.100098</v>
       </c>
       <c r="L61" t="n">
         <v>84.66999800000001</v>
@@ -5831,10 +5831,10 @@
         <v>90.120003</v>
       </c>
       <c r="N61" t="n">
-        <v>1187.5</v>
+        <v>1172</v>
       </c>
       <c r="O61" t="n">
-        <v>464</v>
+        <v>440.75</v>
       </c>
       <c r="P61" t="n">
         <v>3.473353</v>
@@ -5852,7 +5852,7 @@
         <v>-2.000986</v>
       </c>
       <c r="U61" t="n">
-        <v>-1.074164</v>
+        <v>-1.169601</v>
       </c>
       <c r="V61" t="n">
         <v>-0.12854</v>
@@ -5864,7 +5864,7 @@
         <v>0.316962</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.090534</v>
+        <v>0.651276</v>
       </c>
       <c r="Z61" t="n">
         <v>21.827335</v>
@@ -5873,10 +5873,10 @@
         <v>23.5875</v>
       </c>
       <c r="AB61" t="n">
-        <v>6.335348</v>
+        <v>4.947392</v>
       </c>
       <c r="AC61" t="n">
-        <v>12.416717</v>
+        <v>6.783767</v>
       </c>
     </row>
     <row r="62">
@@ -5888,33 +5888,57 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>5.0747</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
+        <v>5.0598</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5.8308</v>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>4101.899902</v>
+      </c>
+      <c r="L62" t="n">
+        <v>78.849998</v>
+      </c>
+      <c r="M62" t="n">
+        <v>82.839996</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1179.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>461.5</v>
+      </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>-0.06696100000000001</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>-0.360372</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-0.293313</v>
+      </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
+      <c r="Y62" t="n">
+        <v>1.303989</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-6.873745</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>-8.078125</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.661263</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>4.707884</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -592,9 +592,7 @@
       <c r="H2" t="n">
         <v>4522.680176</v>
       </c>
-      <c r="I2" t="n">
-        <v>15259.240234</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>35360.730469</v>
       </c>
@@ -653,9 +651,7 @@
       <c r="H3" t="n">
         <v>4307.540039</v>
       </c>
-      <c r="I3" t="n">
-        <v>14448.580078</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>33843.921875</v>
       </c>
@@ -695,9 +691,7 @@
       <c r="V3" t="n">
         <v>-4.756917</v>
       </c>
-      <c r="W3" t="n">
-        <v>-5.312585</v>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>-4.289528</v>
       </c>
@@ -742,9 +736,7 @@
       <c r="H4" t="n">
         <v>4605.379883</v>
       </c>
-      <c r="I4" t="n">
-        <v>15498.389648</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>35819.558594</v>
       </c>
@@ -784,9 +776,7 @@
       <c r="V4" t="n">
         <v>6.914384</v>
       </c>
-      <c r="W4" t="n">
-        <v>7.265832</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>5.837493</v>
       </c>
@@ -831,9 +821,7 @@
       <c r="H5" t="n">
         <v>4567</v>
       </c>
-      <c r="I5" t="n">
-        <v>15537.69043</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>34483.71875</v>
       </c>
@@ -873,9 +861,7 @@
       <c r="V5" t="n">
         <v>-0.833371</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.25358</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>-3.729359</v>
       </c>
@@ -920,9 +906,7 @@
       <c r="H6" t="n">
         <v>4766.180176</v>
       </c>
-      <c r="I6" t="n">
-        <v>15644.969727</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>36338.300781</v>
       </c>
@@ -962,9 +946,7 @@
       <c r="V6" t="n">
         <v>4.361291</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.690446</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>5.378138</v>
       </c>
@@ -1009,9 +991,7 @@
       <c r="H7" t="n">
         <v>4515.549805</v>
       </c>
-      <c r="I7" t="n">
-        <v>14239.879883</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>35131.859375</v>
       </c>
@@ -1051,9 +1031,7 @@
       <c r="V7" t="n">
         <v>-5.258517</v>
       </c>
-      <c r="W7" t="n">
-        <v>-8.981097</v>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>-3.320027</v>
       </c>
@@ -1098,9 +1076,7 @@
       <c r="H8" t="n">
         <v>4373.939941</v>
       </c>
-      <c r="I8" t="n">
-        <v>13751.400391</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>33892.601562</v>
       </c>
@@ -1140,9 +1116,7 @@
       <c r="V8" t="n">
         <v>-3.136049</v>
       </c>
-      <c r="W8" t="n">
-        <v>-3.430362</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>-3.527447</v>
       </c>
@@ -1187,9 +1161,7 @@
       <c r="H9" t="n">
         <v>4530.410156</v>
       </c>
-      <c r="I9" t="n">
-        <v>14220.519531</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>34678.351562</v>
       </c>
@@ -1229,9 +1201,7 @@
       <c r="V9" t="n">
         <v>3.577329</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.411428</v>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>2.318353</v>
       </c>
@@ -1276,9 +1246,7 @@
       <c r="H10" t="n">
         <v>4131.930176</v>
       </c>
-      <c r="I10" t="n">
-        <v>12334.639648</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>32977.210938</v>
       </c>
@@ -1318,9 +1286,7 @@
       <c r="V10" t="n">
         <v>-8.795671</v>
       </c>
-      <c r="W10" t="n">
-        <v>-13.261681</v>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-4.905483</v>
       </c>
@@ -1365,9 +1331,7 @@
       <c r="H11" t="n">
         <v>4132.149902</v>
       </c>
-      <c r="I11" t="n">
-        <v>12081.389648</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>32990.121094</v>
       </c>
@@ -1407,9 +1371,7 @@
       <c r="V11" t="n">
         <v>0.005318</v>
       </c>
-      <c r="W11" t="n">
-        <v>-2.053161</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>0.039149</v>
       </c>
@@ -1454,9 +1416,7 @@
       <c r="H12" t="n">
         <v>3785.379883</v>
       </c>
-      <c r="I12" t="n">
-        <v>11028.740234</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>30775.429688</v>
       </c>
@@ -1496,9 +1456,7 @@
       <c r="V12" t="n">
         <v>-8.391999999999999</v>
       </c>
-      <c r="W12" t="n">
-        <v>-8.712982999999999</v>
-      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>-6.713196</v>
       </c>
@@ -1543,9 +1501,7 @@
       <c r="H13" t="n">
         <v>4130.290039</v>
       </c>
-      <c r="I13" t="n">
-        <v>12390.69043</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>32845.128906</v>
       </c>
@@ -1585,9 +1541,7 @@
       <c r="V13" t="n">
         <v>9.111639</v>
       </c>
-      <c r="W13" t="n">
-        <v>12.3491</v>
-      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>6.725168</v>
       </c>
@@ -1632,9 +1586,7 @@
       <c r="H14" t="n">
         <v>3955</v>
       </c>
-      <c r="I14" t="n">
-        <v>11816.200195</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>31510.429688</v>
       </c>
@@ -1674,9 +1626,7 @@
       <c r="V14" t="n">
         <v>-4.244013</v>
       </c>
-      <c r="W14" t="n">
-        <v>-4.636467</v>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>-4.063614</v>
       </c>
@@ -1721,9 +1671,7 @@
       <c r="H15" t="n">
         <v>3585.620117</v>
       </c>
-      <c r="I15" t="n">
-        <v>10575.620117</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>28725.509766</v>
       </c>
@@ -1763,9 +1711,7 @@
       <c r="V15" t="n">
         <v>-9.339567000000001</v>
       </c>
-      <c r="W15" t="n">
-        <v>-10.498976</v>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>-8.838089</v>
       </c>
@@ -1810,9 +1756,7 @@
       <c r="H16" t="n">
         <v>3871.97998</v>
       </c>
-      <c r="I16" t="n">
-        <v>10988.150391</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>32732.949219</v>
       </c>
@@ -1852,9 +1796,7 @@
       <c r="V16" t="n">
         <v>7.986341</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.900767</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>13.950804</v>
       </c>
@@ -1899,9 +1841,7 @@
       <c r="H17" t="n">
         <v>4080.110107</v>
       </c>
-      <c r="I17" t="n">
-        <v>11468</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>34589.769531</v>
       </c>
@@ -1941,9 +1881,7 @@
       <c r="V17" t="n">
         <v>5.375289</v>
       </c>
-      <c r="W17" t="n">
-        <v>4.366973</v>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>5.672634</v>
       </c>
@@ -1988,9 +1926,7 @@
       <c r="H18" t="n">
         <v>3839.5</v>
       </c>
-      <c r="I18" t="n">
-        <v>10466.480469</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>33147.25</v>
       </c>
@@ -2030,9 +1966,7 @@
       <c r="V18" t="n">
         <v>-5.897147</v>
       </c>
-      <c r="W18" t="n">
-        <v>-8.733166000000001</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>-4.170365</v>
       </c>
@@ -2077,9 +2011,7 @@
       <c r="H19" t="n">
         <v>4076.600098</v>
       </c>
-      <c r="I19" t="n">
-        <v>11584.549805</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>34086.039062</v>
       </c>
@@ -2119,9 +2051,7 @@
       <c r="V19" t="n">
         <v>6.175286</v>
       </c>
-      <c r="W19" t="n">
-        <v>10.682381</v>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>2.832178</v>
       </c>
@@ -2166,9 +2096,7 @@
       <c r="H20" t="n">
         <v>3970.149902</v>
       </c>
-      <c r="I20" t="n">
-        <v>11455.540039</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>32656.699219</v>
       </c>
@@ -2208,9 +2136,7 @@
       <c r="V20" t="n">
         <v>-2.611249</v>
       </c>
-      <c r="W20" t="n">
-        <v>-1.113636</v>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-4.193329</v>
       </c>
@@ -2255,9 +2181,7 @@
       <c r="H21" t="n">
         <v>4109.310059</v>
       </c>
-      <c r="I21" t="n">
-        <v>12221.910156</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>33274.148438</v>
       </c>
@@ -2297,9 +2221,7 @@
       <c r="V21" t="n">
         <v>3.505161</v>
       </c>
-      <c r="W21" t="n">
-        <v>6.689952</v>
-      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>1.890728</v>
       </c>
@@ -2344,9 +2266,7 @@
       <c r="H22" t="n">
         <v>4169.47998</v>
       </c>
-      <c r="I22" t="n">
-        <v>12226.580078</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>34098.160156</v>
       </c>
@@ -2386,9 +2306,7 @@
       <c r="V22" t="n">
         <v>1.464234</v>
       </c>
-      <c r="W22" t="n">
-        <v>0.038209</v>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>2.476432</v>
       </c>
@@ -2433,9 +2351,7 @@
       <c r="H23" t="n">
         <v>4179.830078</v>
       </c>
-      <c r="I23" t="n">
-        <v>12935.290039</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>32908.269531</v>
       </c>
@@ -2475,9 +2391,7 @@
       <c r="V23" t="n">
         <v>0.248235</v>
       </c>
-      <c r="W23" t="n">
-        <v>5.796469</v>
-      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>-3.489604</v>
       </c>
@@ -2522,9 +2436,7 @@
       <c r="H24" t="n">
         <v>4450.379883</v>
       </c>
-      <c r="I24" t="n">
-        <v>13787.919922</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>34407.601562</v>
       </c>
@@ -2564,9 +2476,7 @@
       <c r="V24" t="n">
         <v>6.472746</v>
       </c>
-      <c r="W24" t="n">
-        <v>6.591502</v>
-      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>4.556095</v>
       </c>
@@ -2611,9 +2521,7 @@
       <c r="H25" t="n">
         <v>4588.959961</v>
       </c>
-      <c r="I25" t="n">
-        <v>14346.019531</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>35559.53125</v>
       </c>
@@ -2653,9 +2561,7 @@
       <c r="V25" t="n">
         <v>3.113893</v>
       </c>
-      <c r="W25" t="n">
-        <v>4.047743</v>
-      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>3.347893</v>
       </c>
@@ -2700,9 +2606,7 @@
       <c r="H26" t="n">
         <v>4507.660156</v>
       </c>
-      <c r="I26" t="n">
-        <v>14034.969727</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>34721.910156</v>
       </c>
@@ -2742,9 +2646,7 @@
       <c r="V26" t="n">
         <v>-1.771639</v>
       </c>
-      <c r="W26" t="n">
-        <v>-2.168196</v>
-      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
         <v>-2.355546</v>
       </c>
@@ -2789,9 +2691,7 @@
       <c r="H27" t="n">
         <v>4288.049805</v>
       </c>
-      <c r="I27" t="n">
-        <v>13219.320312</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>33507.5</v>
       </c>
@@ -2831,9 +2731,7 @@
       <c r="V27" t="n">
         <v>-4.871937</v>
       </c>
-      <c r="W27" t="n">
-        <v>-5.811551</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>-3.497533</v>
       </c>
@@ -2878,9 +2776,7 @@
       <c r="H28" t="n">
         <v>4193.799805</v>
       </c>
-      <c r="I28" t="n">
-        <v>12851.240234</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>33052.871094</v>
       </c>
@@ -2920,9 +2816,7 @@
       <c r="V28" t="n">
         <v>-2.197969</v>
       </c>
-      <c r="W28" t="n">
-        <v>-2.78441</v>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>-1.356797</v>
       </c>
@@ -2967,9 +2861,7 @@
       <c r="H29" t="n">
         <v>4567.799805</v>
       </c>
-      <c r="I29" t="n">
-        <v>14226.219727</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>35950.890625</v>
       </c>
@@ -3009,9 +2901,7 @@
       <c r="V29" t="n">
         <v>8.917927000000001</v>
       </c>
-      <c r="W29" t="n">
-        <v>10.699197</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>8.76783</v>
       </c>
@@ -3056,9 +2946,7 @@
       <c r="H30" t="n">
         <v>4769.830078</v>
       </c>
-      <c r="I30" t="n">
-        <v>15011.349609</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>37689.539062</v>
       </c>
@@ -3098,9 +2986,7 @@
       <c r="V30" t="n">
         <v>4.422923</v>
       </c>
-      <c r="W30" t="n">
-        <v>5.518893</v>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>4.836176</v>
       </c>
@@ -3145,9 +3031,7 @@
       <c r="H31" t="n">
         <v>4845.649902</v>
       </c>
-      <c r="I31" t="n">
-        <v>15164.009766</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>38150.300781</v>
       </c>
@@ -3187,9 +3071,7 @@
       <c r="V31" t="n">
         <v>1.589571</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.016965</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>1.222519</v>
       </c>
@@ -3234,9 +3116,7 @@
       <c r="H32" t="n">
         <v>5096.27002</v>
       </c>
-      <c r="I32" t="n">
-        <v>16091.919922</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>38996.390625</v>
       </c>
@@ -3276,9 +3156,7 @@
       <c r="V32" t="n">
         <v>5.172064</v>
       </c>
-      <c r="W32" t="n">
-        <v>6.119161</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
         <v>2.21778</v>
       </c>
@@ -3323,9 +3201,7 @@
       <c r="H33" t="n">
         <v>5254.350098</v>
       </c>
-      <c r="I33" t="n">
-        <v>16379.459961</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>39807.371094</v>
       </c>
@@ -3365,9 +3241,7 @@
       <c r="V33" t="n">
         <v>3.101878</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.78686</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>2.07963</v>
       </c>
@@ -3412,9 +3286,7 @@
       <c r="H34" t="n">
         <v>5035.689941</v>
       </c>
-      <c r="I34" t="n">
-        <v>15657.820312</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>37815.921875</v>
       </c>
@@ -3454,9 +3326,7 @@
       <c r="V34" t="n">
         <v>-4.161507</v>
       </c>
-      <c r="W34" t="n">
-        <v>-4.40576</v>
-      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-5.002715</v>
       </c>
@@ -3501,9 +3371,7 @@
       <c r="H35" t="n">
         <v>5277.509766</v>
       </c>
-      <c r="I35" t="n">
-        <v>16735.019531</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>38686.320312</v>
       </c>
@@ -3543,9 +3411,7 @@
       <c r="V35" t="n">
         <v>4.802119</v>
       </c>
-      <c r="W35" t="n">
-        <v>6.879624</v>
-      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>2.301672</v>
       </c>
@@ -3590,9 +3456,7 @@
       <c r="H36" t="n">
         <v>5460.47998</v>
       </c>
-      <c r="I36" t="n">
-        <v>17732.599609</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>39118.859375</v>
       </c>
@@ -3632,9 +3496,7 @@
       <c r="V36" t="n">
         <v>3.46698</v>
       </c>
-      <c r="W36" t="n">
-        <v>5.961033</v>
-      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>1.118067</v>
       </c>
@@ -3679,9 +3541,7 @@
       <c r="H37" t="n">
         <v>5522.299805</v>
       </c>
-      <c r="I37" t="n">
-        <v>17599.400391</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
         <v>40842.789062</v>
       </c>
@@ -3721,9 +3581,7 @@
       <c r="V37" t="n">
         <v>1.132132</v>
       </c>
-      <c r="W37" t="n">
-        <v>-0.751154</v>
-      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>4.406902</v>
       </c>
@@ -3768,9 +3626,7 @@
       <c r="H38" t="n">
         <v>5648.399902</v>
       </c>
-      <c r="I38" t="n">
-        <v>17713.619141</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>41563.078125</v>
       </c>
@@ -3810,9 +3666,7 @@
       <c r="V38" t="n">
         <v>2.283471</v>
       </c>
-      <c r="W38" t="n">
-        <v>0.648992</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>1.763565</v>
       </c>
@@ -3857,9 +3711,7 @@
       <c r="H39" t="n">
         <v>5762.47998</v>
       </c>
-      <c r="I39" t="n">
-        <v>18189.169922</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>42330.148438</v>
       </c>
@@ -3899,9 +3751,7 @@
       <c r="V39" t="n">
         <v>2.019688</v>
       </c>
-      <c r="W39" t="n">
-        <v>2.684662</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>1.845557</v>
       </c>
@@ -3946,9 +3796,7 @@
       <c r="H40" t="n">
         <v>5705.450195</v>
       </c>
-      <c r="I40" t="n">
-        <v>18095.150391</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>41763.460938</v>
       </c>
@@ -3988,9 +3836,7 @@
       <c r="V40" t="n">
         <v>-0.9896740000000001</v>
       </c>
-      <c r="W40" t="n">
-        <v>-0.516898</v>
-      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-1.338733</v>
       </c>
@@ -4035,9 +3881,7 @@
       <c r="H41" t="n">
         <v>6032.379883</v>
       </c>
-      <c r="I41" t="n">
-        <v>19218.169922</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>44910.648438</v>
       </c>
@@ -4077,9 +3921,7 @@
       <c r="V41" t="n">
         <v>5.73013</v>
       </c>
-      <c r="W41" t="n">
-        <v>6.206191</v>
-      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>7.535744</v>
       </c>
@@ -4124,9 +3966,7 @@
       <c r="H42" t="n">
         <v>5881.629883</v>
       </c>
-      <c r="I42" t="n">
-        <v>19310.789062</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>42544.21875</v>
       </c>
@@ -4166,9 +4006,7 @@
       <c r="V42" t="n">
         <v>-2.499014</v>
       </c>
-      <c r="W42" t="n">
-        <v>0.481935</v>
-      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>-5.269195</v>
       </c>
@@ -4213,9 +4051,7 @@
       <c r="H43" t="n">
         <v>6040.529785</v>
       </c>
-      <c r="I43" t="n">
-        <v>19627.439453</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>44544.660156</v>
       </c>
@@ -4255,9 +4091,7 @@
       <c r="V43" t="n">
         <v>2.70163</v>
       </c>
-      <c r="W43" t="n">
-        <v>1.639759</v>
-      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>4.702029</v>
       </c>
@@ -4302,9 +4136,7 @@
       <c r="H44" t="n">
         <v>5954.5</v>
       </c>
-      <c r="I44" t="n">
-        <v>18847.279297</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>43840.910156</v>
       </c>
@@ -4344,9 +4176,7 @@
       <c r="V44" t="n">
         <v>-1.424209</v>
       </c>
-      <c r="W44" t="n">
-        <v>-3.974844</v>
-      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-1.579875</v>
       </c>
@@ -4391,9 +4221,7 @@
       <c r="H45" t="n">
         <v>5611.850098</v>
       </c>
-      <c r="I45" t="n">
-        <v>17299.289062</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>42001.761719</v>
       </c>
@@ -4433,9 +4261,7 @@
       <c r="V45" t="n">
         <v>-5.75447</v>
       </c>
-      <c r="W45" t="n">
-        <v>-8.213335000000001</v>
-      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>-4.195051</v>
       </c>
@@ -4480,9 +4306,7 @@
       <c r="H46" t="n">
         <v>5569.060059</v>
       </c>
-      <c r="I46" t="n">
-        <v>17446.339844</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>40669.359375</v>
       </c>
@@ -4522,9 +4346,7 @@
       <c r="V46" t="n">
         <v>-0.762494</v>
       </c>
-      <c r="W46" t="n">
-        <v>0.850039</v>
-      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-3.172253</v>
       </c>
@@ -4569,9 +4391,7 @@
       <c r="H47" t="n">
         <v>5911.689941</v>
       </c>
-      <c r="I47" t="n">
-        <v>19113.769531</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>42270.070312</v>
       </c>
@@ -4611,9 +4431,7 @@
       <c r="V47" t="n">
         <v>6.152383</v>
       </c>
-      <c r="W47" t="n">
-        <v>9.557475999999999</v>
-      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>3.935914</v>
       </c>
@@ -4658,9 +4476,7 @@
       <c r="H48" t="n">
         <v>6204.950195</v>
       </c>
-      <c r="I48" t="n">
-        <v>20369.730469</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>44094.769531</v>
       </c>
@@ -4700,9 +4516,7 @@
       <c r="V48" t="n">
         <v>4.960684</v>
       </c>
-      <c r="W48" t="n">
-        <v>6.570975</v>
-      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>4.316764</v>
       </c>
@@ -4747,9 +4561,7 @@
       <c r="H49" t="n">
         <v>6339.390137</v>
       </c>
-      <c r="I49" t="n">
-        <v>21122.449219</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>44130.980469</v>
       </c>
@@ -4789,9 +4601,7 @@
       <c r="V49" t="n">
         <v>2.166656</v>
       </c>
-      <c r="W49" t="n">
-        <v>3.695281</v>
-      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>0.082121</v>
       </c>
@@ -4836,9 +4646,7 @@
       <c r="H50" t="n">
         <v>6460.259766</v>
       </c>
-      <c r="I50" t="n">
-        <v>21455.550781</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>45544.878906</v>
       </c>
@@ -4878,9 +4686,7 @@
       <c r="V50" t="n">
         <v>1.906644</v>
       </c>
-      <c r="W50" t="n">
-        <v>1.577003</v>
-      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>3.203868</v>
       </c>
@@ -4925,9 +4731,7 @@
       <c r="H51" t="n">
         <v>6688.459961</v>
       </c>
-      <c r="I51" t="n">
-        <v>22660.009766</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>46397.890625</v>
       </c>
@@ -4967,9 +4771,7 @@
       <c r="V51" t="n">
         <v>3.532369</v>
       </c>
-      <c r="W51" t="n">
-        <v>5.613741</v>
-      </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>1.872904</v>
       </c>
@@ -5014,9 +4816,7 @@
       <c r="H52" t="n">
         <v>6840.200195</v>
       </c>
-      <c r="I52" t="n">
-        <v>23724.960938</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>47562.871094</v>
       </c>
@@ -5056,9 +4856,7 @@
       <c r="V52" t="n">
         <v>2.268687</v>
       </c>
-      <c r="W52" t="n">
-        <v>4.699694</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>2.510848</v>
       </c>
@@ -5103,9 +4901,7 @@
       <c r="H53" t="n">
         <v>6849.089844</v>
       </c>
-      <c r="I53" t="n">
-        <v>23365.689453</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>47716.421875</v>
       </c>
@@ -5145,9 +4941,7 @@
       <c r="V53" t="n">
         <v>0.129962</v>
       </c>
-      <c r="W53" t="n">
-        <v>-1.514319</v>
-      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>0.322837</v>
       </c>
@@ -5192,9 +4986,7 @@
       <c r="H54" t="n">
         <v>6845.5</v>
       </c>
-      <c r="I54" t="n">
-        <v>23241.990234</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>48063.289062</v>
       </c>
@@ -5234,9 +5026,7 @@
       <c r="V54" t="n">
         <v>-0.052413</v>
       </c>
-      <c r="W54" t="n">
-        <v>-0.529405</v>
-      </c>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>0.726935</v>
       </c>
@@ -5281,9 +5071,7 @@
       <c r="H55" t="n">
         <v>6939.029785</v>
       </c>
-      <c r="I55" t="n">
-        <v>23461.820312</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>48892.46875</v>
       </c>
@@ -5323,9 +5111,7 @@
       <c r="V55" t="n">
         <v>1.366296</v>
       </c>
-      <c r="W55" t="n">
-        <v>0.945832</v>
-      </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>1.725183</v>
       </c>
@@ -5370,9 +5156,7 @@
       <c r="H56" t="n">
         <v>6878.879883</v>
       </c>
-      <c r="I56" t="n">
-        <v>22668.210938</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>48977.921875</v>
       </c>
@@ -5412,9 +5196,7 @@
       <c r="V56" t="n">
         <v>-0.866834</v>
       </c>
-      <c r="W56" t="n">
-        <v>-3.382557</v>
-      </c>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>0.174778</v>
       </c>
@@ -5459,9 +5241,7 @@
       <c r="H57" t="n">
         <v>6528.52002</v>
       </c>
-      <c r="I57" t="n">
-        <v>21590.630859</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>46341.511719</v>
       </c>
@@ -5501,9 +5281,7 @@
       <c r="V57" t="n">
         <v>-5.093269</v>
       </c>
-      <c r="W57" t="n">
-        <v>-4.753706</v>
-      </c>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>-5.382854</v>
       </c>
@@ -5548,9 +5326,7 @@
       <c r="H58" t="n">
         <v>7209.009766</v>
       </c>
-      <c r="I58" t="n">
-        <v>24892.310547</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>49652.140625</v>
       </c>
@@ -5590,9 +5366,7 @@
       <c r="V58" t="n">
         <v>10.423339</v>
       </c>
-      <c r="W58" t="n">
-        <v>15.292187</v>
-      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>7.143981</v>
       </c>
@@ -5637,9 +5411,7 @@
       <c r="H59" t="n">
         <v>7580.060059</v>
       </c>
-      <c r="I59" t="n">
-        <v>26972.619141</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>51032.460938</v>
       </c>
@@ -5679,9 +5451,7 @@
       <c r="V59" t="n">
         <v>5.147036</v>
       </c>
-      <c r="W59" t="n">
-        <v>8.357234</v>
-      </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>2.779981</v>
       </c>
@@ -5726,9 +5496,7 @@
       <c r="H60" t="n">
         <v>7499.359863</v>
       </c>
-      <c r="I60" t="n">
-        <v>26213.720703</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>52319.199219</v>
       </c>
@@ -5768,9 +5536,7 @@
       <c r="V60" t="n">
         <v>-1.064638</v>
       </c>
-      <c r="W60" t="n">
-        <v>-2.813588</v>
-      </c>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>2.521411</v>
       </c>
@@ -5815,9 +5581,7 @@
       <c r="H61" t="n">
         <v>7489.720215</v>
       </c>
-      <c r="I61" t="n">
-        <v>25373.849609</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>52485.03125</v>
       </c>
@@ -5857,9 +5621,7 @@
       <c r="V61" t="n">
         <v>-0.12854</v>
       </c>
-      <c r="W61" t="n">
-        <v>-3.203937</v>
-      </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>0.316962</v>
       </c>
@@ -5883,61 +5645,73 @@
       <c r="A62" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>178000</v>
+      </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
-        <v>5.0598</v>
+        <v>5.0743</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8308</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>5.8596</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7600.5</v>
+      </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>53178.410156</v>
+      </c>
       <c r="K62" t="n">
-        <v>4101.899902</v>
+        <v>4133.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>78.849998</v>
+        <v>77.480003</v>
       </c>
       <c r="M62" t="n">
-        <v>82.839996</v>
+        <v>81.370003</v>
       </c>
       <c r="N62" t="n">
-        <v>1179.75</v>
+        <v>1182.25</v>
       </c>
       <c r="O62" t="n">
-        <v>461.5</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
+        <v>469.25</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.000562</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="n">
-        <v>-0.360372</v>
+        <v>-0.074839</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.293313</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
+        <v>0.199168</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.479091</v>
+      </c>
       <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>1.321098</v>
+      </c>
       <c r="Y62" t="n">
-        <v>1.303989</v>
+        <v>2.091816</v>
       </c>
       <c r="Z62" t="n">
-        <v>-6.873745</v>
+        <v>-8.491785999999999</v>
       </c>
       <c r="AA62" t="n">
-        <v>-8.078125</v>
+        <v>-9.709275999999999</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.661263</v>
+        <v>0.874573</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.707884</v>
+        <v>6.466251</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -592,7 +592,9 @@
       <c r="H2" t="n">
         <v>4522.680176</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>15259.240234</v>
+      </c>
       <c r="J2" t="n">
         <v>35360.730469</v>
       </c>
@@ -651,7 +653,9 @@
       <c r="H3" t="n">
         <v>4307.540039</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>14448.580078</v>
+      </c>
       <c r="J3" t="n">
         <v>33843.921875</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="V3" t="n">
         <v>-4.756917</v>
       </c>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>-5.312585</v>
+      </c>
       <c r="X3" t="n">
         <v>-4.289528</v>
       </c>
@@ -736,7 +742,9 @@
       <c r="H4" t="n">
         <v>4605.379883</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>15498.389648</v>
+      </c>
       <c r="J4" t="n">
         <v>35819.558594</v>
       </c>
@@ -776,7 +784,9 @@
       <c r="V4" t="n">
         <v>6.914384</v>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>7.265832</v>
+      </c>
       <c r="X4" t="n">
         <v>5.837493</v>
       </c>
@@ -821,7 +831,9 @@
       <c r="H5" t="n">
         <v>4567</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>15537.69043</v>
+      </c>
       <c r="J5" t="n">
         <v>34483.71875</v>
       </c>
@@ -861,7 +873,9 @@
       <c r="V5" t="n">
         <v>-0.833371</v>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0.25358</v>
+      </c>
       <c r="X5" t="n">
         <v>-3.729359</v>
       </c>
@@ -906,7 +920,9 @@
       <c r="H6" t="n">
         <v>4766.180176</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>15644.969727</v>
+      </c>
       <c r="J6" t="n">
         <v>36338.300781</v>
       </c>
@@ -946,7 +962,9 @@
       <c r="V6" t="n">
         <v>4.361291</v>
       </c>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0.690446</v>
+      </c>
       <c r="X6" t="n">
         <v>5.378138</v>
       </c>
@@ -991,7 +1009,9 @@
       <c r="H7" t="n">
         <v>4515.549805</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>14239.879883</v>
+      </c>
       <c r="J7" t="n">
         <v>35131.859375</v>
       </c>
@@ -1031,7 +1051,9 @@
       <c r="V7" t="n">
         <v>-5.258517</v>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>-8.981097</v>
+      </c>
       <c r="X7" t="n">
         <v>-3.320027</v>
       </c>
@@ -1076,7 +1098,9 @@
       <c r="H8" t="n">
         <v>4373.939941</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>13751.400391</v>
+      </c>
       <c r="J8" t="n">
         <v>33892.601562</v>
       </c>
@@ -1116,7 +1140,9 @@
       <c r="V8" t="n">
         <v>-3.136049</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>-3.430362</v>
+      </c>
       <c r="X8" t="n">
         <v>-3.527447</v>
       </c>
@@ -1161,7 +1187,9 @@
       <c r="H9" t="n">
         <v>4530.410156</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>14220.519531</v>
+      </c>
       <c r="J9" t="n">
         <v>34678.351562</v>
       </c>
@@ -1201,7 +1229,9 @@
       <c r="V9" t="n">
         <v>3.577329</v>
       </c>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>3.411428</v>
+      </c>
       <c r="X9" t="n">
         <v>2.318353</v>
       </c>
@@ -1246,7 +1276,9 @@
       <c r="H10" t="n">
         <v>4131.930176</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>12334.639648</v>
+      </c>
       <c r="J10" t="n">
         <v>32977.210938</v>
       </c>
@@ -1286,7 +1318,9 @@
       <c r="V10" t="n">
         <v>-8.795671</v>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>-13.261681</v>
+      </c>
       <c r="X10" t="n">
         <v>-4.905483</v>
       </c>
@@ -1331,7 +1365,9 @@
       <c r="H11" t="n">
         <v>4132.149902</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>12081.389648</v>
+      </c>
       <c r="J11" t="n">
         <v>32990.121094</v>
       </c>
@@ -1371,7 +1407,9 @@
       <c r="V11" t="n">
         <v>0.005318</v>
       </c>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>-2.053161</v>
+      </c>
       <c r="X11" t="n">
         <v>0.039149</v>
       </c>
@@ -1416,7 +1454,9 @@
       <c r="H12" t="n">
         <v>3785.379883</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>11028.740234</v>
+      </c>
       <c r="J12" t="n">
         <v>30775.429688</v>
       </c>
@@ -1456,7 +1496,9 @@
       <c r="V12" t="n">
         <v>-8.391999999999999</v>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>-8.712982999999999</v>
+      </c>
       <c r="X12" t="n">
         <v>-6.713196</v>
       </c>
@@ -1501,7 +1543,9 @@
       <c r="H13" t="n">
         <v>4130.290039</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>12390.69043</v>
+      </c>
       <c r="J13" t="n">
         <v>32845.128906</v>
       </c>
@@ -1541,7 +1585,9 @@
       <c r="V13" t="n">
         <v>9.111639</v>
       </c>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>12.3491</v>
+      </c>
       <c r="X13" t="n">
         <v>6.725168</v>
       </c>
@@ -1586,7 +1632,9 @@
       <c r="H14" t="n">
         <v>3955</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>11816.200195</v>
+      </c>
       <c r="J14" t="n">
         <v>31510.429688</v>
       </c>
@@ -1626,7 +1674,9 @@
       <c r="V14" t="n">
         <v>-4.244013</v>
       </c>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>-4.636467</v>
+      </c>
       <c r="X14" t="n">
         <v>-4.063614</v>
       </c>
@@ -1671,7 +1721,9 @@
       <c r="H15" t="n">
         <v>3585.620117</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>10575.620117</v>
+      </c>
       <c r="J15" t="n">
         <v>28725.509766</v>
       </c>
@@ -1711,7 +1763,9 @@
       <c r="V15" t="n">
         <v>-9.339567000000001</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>-10.498976</v>
+      </c>
       <c r="X15" t="n">
         <v>-8.838089</v>
       </c>
@@ -1756,7 +1810,9 @@
       <c r="H16" t="n">
         <v>3871.97998</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>10988.150391</v>
+      </c>
       <c r="J16" t="n">
         <v>32732.949219</v>
       </c>
@@ -1796,7 +1852,9 @@
       <c r="V16" t="n">
         <v>7.986341</v>
       </c>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>3.900767</v>
+      </c>
       <c r="X16" t="n">
         <v>13.950804</v>
       </c>
@@ -1841,7 +1899,9 @@
       <c r="H17" t="n">
         <v>4080.110107</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>11468</v>
+      </c>
       <c r="J17" t="n">
         <v>34589.769531</v>
       </c>
@@ -1881,7 +1941,9 @@
       <c r="V17" t="n">
         <v>5.375289</v>
       </c>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>4.366973</v>
+      </c>
       <c r="X17" t="n">
         <v>5.672634</v>
       </c>
@@ -1926,7 +1988,9 @@
       <c r="H18" t="n">
         <v>3839.5</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>10466.480469</v>
+      </c>
       <c r="J18" t="n">
         <v>33147.25</v>
       </c>
@@ -1966,7 +2030,9 @@
       <c r="V18" t="n">
         <v>-5.897147</v>
       </c>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-8.733166000000001</v>
+      </c>
       <c r="X18" t="n">
         <v>-4.170365</v>
       </c>
@@ -2011,7 +2077,9 @@
       <c r="H19" t="n">
         <v>4076.600098</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>11584.549805</v>
+      </c>
       <c r="J19" t="n">
         <v>34086.039062</v>
       </c>
@@ -2051,7 +2119,9 @@
       <c r="V19" t="n">
         <v>6.175286</v>
       </c>
-      <c r="W19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>10.682381</v>
+      </c>
       <c r="X19" t="n">
         <v>2.832178</v>
       </c>
@@ -2096,7 +2166,9 @@
       <c r="H20" t="n">
         <v>3970.149902</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>11455.540039</v>
+      </c>
       <c r="J20" t="n">
         <v>32656.699219</v>
       </c>
@@ -2136,7 +2208,9 @@
       <c r="V20" t="n">
         <v>-2.611249</v>
       </c>
-      <c r="W20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>-1.113636</v>
+      </c>
       <c r="X20" t="n">
         <v>-4.193329</v>
       </c>
@@ -2181,7 +2255,9 @@
       <c r="H21" t="n">
         <v>4109.310059</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>12221.910156</v>
+      </c>
       <c r="J21" t="n">
         <v>33274.148438</v>
       </c>
@@ -2221,7 +2297,9 @@
       <c r="V21" t="n">
         <v>3.505161</v>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>6.689952</v>
+      </c>
       <c r="X21" t="n">
         <v>1.890728</v>
       </c>
@@ -2266,7 +2344,9 @@
       <c r="H22" t="n">
         <v>4169.47998</v>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>12226.580078</v>
+      </c>
       <c r="J22" t="n">
         <v>34098.160156</v>
       </c>
@@ -2306,7 +2386,9 @@
       <c r="V22" t="n">
         <v>1.464234</v>
       </c>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0.038209</v>
+      </c>
       <c r="X22" t="n">
         <v>2.476432</v>
       </c>
@@ -2351,7 +2433,9 @@
       <c r="H23" t="n">
         <v>4179.830078</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>12935.290039</v>
+      </c>
       <c r="J23" t="n">
         <v>32908.269531</v>
       </c>
@@ -2391,7 +2475,9 @@
       <c r="V23" t="n">
         <v>0.248235</v>
       </c>
-      <c r="W23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>5.796469</v>
+      </c>
       <c r="X23" t="n">
         <v>-3.489604</v>
       </c>
@@ -2436,7 +2522,9 @@
       <c r="H24" t="n">
         <v>4450.379883</v>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>13787.919922</v>
+      </c>
       <c r="J24" t="n">
         <v>34407.601562</v>
       </c>
@@ -2476,7 +2564,9 @@
       <c r="V24" t="n">
         <v>6.472746</v>
       </c>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>6.591502</v>
+      </c>
       <c r="X24" t="n">
         <v>4.556095</v>
       </c>
@@ -2521,7 +2611,9 @@
       <c r="H25" t="n">
         <v>4588.959961</v>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>14346.019531</v>
+      </c>
       <c r="J25" t="n">
         <v>35559.53125</v>
       </c>
@@ -2561,7 +2653,9 @@
       <c r="V25" t="n">
         <v>3.113893</v>
       </c>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>4.047743</v>
+      </c>
       <c r="X25" t="n">
         <v>3.347893</v>
       </c>
@@ -2606,7 +2700,9 @@
       <c r="H26" t="n">
         <v>4507.660156</v>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>14034.969727</v>
+      </c>
       <c r="J26" t="n">
         <v>34721.910156</v>
       </c>
@@ -2646,7 +2742,9 @@
       <c r="V26" t="n">
         <v>-1.771639</v>
       </c>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-2.168196</v>
+      </c>
       <c r="X26" t="n">
         <v>-2.355546</v>
       </c>
@@ -2691,7 +2789,9 @@
       <c r="H27" t="n">
         <v>4288.049805</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>13219.320312</v>
+      </c>
       <c r="J27" t="n">
         <v>33507.5</v>
       </c>
@@ -2731,7 +2831,9 @@
       <c r="V27" t="n">
         <v>-4.871937</v>
       </c>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-5.811551</v>
+      </c>
       <c r="X27" t="n">
         <v>-3.497533</v>
       </c>
@@ -2776,7 +2878,9 @@
       <c r="H28" t="n">
         <v>4193.799805</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12851.240234</v>
+      </c>
       <c r="J28" t="n">
         <v>33052.871094</v>
       </c>
@@ -2816,7 +2920,9 @@
       <c r="V28" t="n">
         <v>-2.197969</v>
       </c>
-      <c r="W28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-2.78441</v>
+      </c>
       <c r="X28" t="n">
         <v>-1.356797</v>
       </c>
@@ -2861,7 +2967,9 @@
       <c r="H29" t="n">
         <v>4567.799805</v>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>14226.219727</v>
+      </c>
       <c r="J29" t="n">
         <v>35950.890625</v>
       </c>
@@ -2901,7 +3009,9 @@
       <c r="V29" t="n">
         <v>8.917927000000001</v>
       </c>
-      <c r="W29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>10.699197</v>
+      </c>
       <c r="X29" t="n">
         <v>8.76783</v>
       </c>
@@ -2946,7 +3056,9 @@
       <c r="H30" t="n">
         <v>4769.830078</v>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>15011.349609</v>
+      </c>
       <c r="J30" t="n">
         <v>37689.539062</v>
       </c>
@@ -2986,7 +3098,9 @@
       <c r="V30" t="n">
         <v>4.422923</v>
       </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>5.518893</v>
+      </c>
       <c r="X30" t="n">
         <v>4.836176</v>
       </c>
@@ -3031,7 +3145,9 @@
       <c r="H31" t="n">
         <v>4845.649902</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>15164.009766</v>
+      </c>
       <c r="J31" t="n">
         <v>38150.300781</v>
       </c>
@@ -3071,7 +3187,9 @@
       <c r="V31" t="n">
         <v>1.589571</v>
       </c>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>1.016965</v>
+      </c>
       <c r="X31" t="n">
         <v>1.222519</v>
       </c>
@@ -3116,7 +3234,9 @@
       <c r="H32" t="n">
         <v>5096.27002</v>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>16091.919922</v>
+      </c>
       <c r="J32" t="n">
         <v>38996.390625</v>
       </c>
@@ -3156,7 +3276,9 @@
       <c r="V32" t="n">
         <v>5.172064</v>
       </c>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>6.119161</v>
+      </c>
       <c r="X32" t="n">
         <v>2.21778</v>
       </c>
@@ -3201,7 +3323,9 @@
       <c r="H33" t="n">
         <v>5254.350098</v>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>16379.459961</v>
+      </c>
       <c r="J33" t="n">
         <v>39807.371094</v>
       </c>
@@ -3241,7 +3365,9 @@
       <c r="V33" t="n">
         <v>3.101878</v>
       </c>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="n">
+        <v>1.78686</v>
+      </c>
       <c r="X33" t="n">
         <v>2.07963</v>
       </c>
@@ -3286,7 +3412,9 @@
       <c r="H34" t="n">
         <v>5035.689941</v>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>15657.820312</v>
+      </c>
       <c r="J34" t="n">
         <v>37815.921875</v>
       </c>
@@ -3326,7 +3454,9 @@
       <c r="V34" t="n">
         <v>-4.161507</v>
       </c>
-      <c r="W34" t="inlineStr"/>
+      <c r="W34" t="n">
+        <v>-4.40576</v>
+      </c>
       <c r="X34" t="n">
         <v>-5.002715</v>
       </c>
@@ -3371,7 +3501,9 @@
       <c r="H35" t="n">
         <v>5277.509766</v>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>16735.019531</v>
+      </c>
       <c r="J35" t="n">
         <v>38686.320312</v>
       </c>
@@ -3411,7 +3543,9 @@
       <c r="V35" t="n">
         <v>4.802119</v>
       </c>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>6.879624</v>
+      </c>
       <c r="X35" t="n">
         <v>2.301672</v>
       </c>
@@ -3456,7 +3590,9 @@
       <c r="H36" t="n">
         <v>5460.47998</v>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>17732.599609</v>
+      </c>
       <c r="J36" t="n">
         <v>39118.859375</v>
       </c>
@@ -3496,7 +3632,9 @@
       <c r="V36" t="n">
         <v>3.46698</v>
       </c>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>5.961033</v>
+      </c>
       <c r="X36" t="n">
         <v>1.118067</v>
       </c>
@@ -3541,7 +3679,9 @@
       <c r="H37" t="n">
         <v>5522.299805</v>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>17599.400391</v>
+      </c>
       <c r="J37" t="n">
         <v>40842.789062</v>
       </c>
@@ -3581,7 +3721,9 @@
       <c r="V37" t="n">
         <v>1.132132</v>
       </c>
-      <c r="W37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>-0.751154</v>
+      </c>
       <c r="X37" t="n">
         <v>4.406902</v>
       </c>
@@ -3626,7 +3768,9 @@
       <c r="H38" t="n">
         <v>5648.399902</v>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>17713.619141</v>
+      </c>
       <c r="J38" t="n">
         <v>41563.078125</v>
       </c>
@@ -3666,7 +3810,9 @@
       <c r="V38" t="n">
         <v>2.283471</v>
       </c>
-      <c r="W38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>0.648992</v>
+      </c>
       <c r="X38" t="n">
         <v>1.763565</v>
       </c>
@@ -3711,7 +3857,9 @@
       <c r="H39" t="n">
         <v>5762.47998</v>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>18189.169922</v>
+      </c>
       <c r="J39" t="n">
         <v>42330.148438</v>
       </c>
@@ -3751,7 +3899,9 @@
       <c r="V39" t="n">
         <v>2.019688</v>
       </c>
-      <c r="W39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>2.684662</v>
+      </c>
       <c r="X39" t="n">
         <v>1.845557</v>
       </c>
@@ -3796,7 +3946,9 @@
       <c r="H40" t="n">
         <v>5705.450195</v>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>18095.150391</v>
+      </c>
       <c r="J40" t="n">
         <v>41763.460938</v>
       </c>
@@ -3836,7 +3988,9 @@
       <c r="V40" t="n">
         <v>-0.9896740000000001</v>
       </c>
-      <c r="W40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>-0.516898</v>
+      </c>
       <c r="X40" t="n">
         <v>-1.338733</v>
       </c>
@@ -3881,7 +4035,9 @@
       <c r="H41" t="n">
         <v>6032.379883</v>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>19218.169922</v>
+      </c>
       <c r="J41" t="n">
         <v>44910.648438</v>
       </c>
@@ -3921,7 +4077,9 @@
       <c r="V41" t="n">
         <v>5.73013</v>
       </c>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>6.206191</v>
+      </c>
       <c r="X41" t="n">
         <v>7.535744</v>
       </c>
@@ -3966,7 +4124,9 @@
       <c r="H42" t="n">
         <v>5881.629883</v>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>19310.789062</v>
+      </c>
       <c r="J42" t="n">
         <v>42544.21875</v>
       </c>
@@ -4006,7 +4166,9 @@
       <c r="V42" t="n">
         <v>-2.499014</v>
       </c>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>0.481935</v>
+      </c>
       <c r="X42" t="n">
         <v>-5.269195</v>
       </c>
@@ -4051,7 +4213,9 @@
       <c r="H43" t="n">
         <v>6040.529785</v>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>19627.439453</v>
+      </c>
       <c r="J43" t="n">
         <v>44544.660156</v>
       </c>
@@ -4091,7 +4255,9 @@
       <c r="V43" t="n">
         <v>2.70163</v>
       </c>
-      <c r="W43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>1.639759</v>
+      </c>
       <c r="X43" t="n">
         <v>4.702029</v>
       </c>
@@ -4136,7 +4302,9 @@
       <c r="H44" t="n">
         <v>5954.5</v>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>18847.279297</v>
+      </c>
       <c r="J44" t="n">
         <v>43840.910156</v>
       </c>
@@ -4176,7 +4344,9 @@
       <c r="V44" t="n">
         <v>-1.424209</v>
       </c>
-      <c r="W44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>-3.974844</v>
+      </c>
       <c r="X44" t="n">
         <v>-1.579875</v>
       </c>
@@ -4221,7 +4391,9 @@
       <c r="H45" t="n">
         <v>5611.850098</v>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>17299.289062</v>
+      </c>
       <c r="J45" t="n">
         <v>42001.761719</v>
       </c>
@@ -4261,7 +4433,9 @@
       <c r="V45" t="n">
         <v>-5.75447</v>
       </c>
-      <c r="W45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>-8.213335000000001</v>
+      </c>
       <c r="X45" t="n">
         <v>-4.195051</v>
       </c>
@@ -4306,7 +4480,9 @@
       <c r="H46" t="n">
         <v>5569.060059</v>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>17446.339844</v>
+      </c>
       <c r="J46" t="n">
         <v>40669.359375</v>
       </c>
@@ -4346,7 +4522,9 @@
       <c r="V46" t="n">
         <v>-0.762494</v>
       </c>
-      <c r="W46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>0.850039</v>
+      </c>
       <c r="X46" t="n">
         <v>-3.172253</v>
       </c>
@@ -4391,7 +4569,9 @@
       <c r="H47" t="n">
         <v>5911.689941</v>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>19113.769531</v>
+      </c>
       <c r="J47" t="n">
         <v>42270.070312</v>
       </c>
@@ -4431,7 +4611,9 @@
       <c r="V47" t="n">
         <v>6.152383</v>
       </c>
-      <c r="W47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>9.557475999999999</v>
+      </c>
       <c r="X47" t="n">
         <v>3.935914</v>
       </c>
@@ -4476,7 +4658,9 @@
       <c r="H48" t="n">
         <v>6204.950195</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>20369.730469</v>
+      </c>
       <c r="J48" t="n">
         <v>44094.769531</v>
       </c>
@@ -4516,7 +4700,9 @@
       <c r="V48" t="n">
         <v>4.960684</v>
       </c>
-      <c r="W48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>6.570975</v>
+      </c>
       <c r="X48" t="n">
         <v>4.316764</v>
       </c>
@@ -4561,7 +4747,9 @@
       <c r="H49" t="n">
         <v>6339.390137</v>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>21122.449219</v>
+      </c>
       <c r="J49" t="n">
         <v>44130.980469</v>
       </c>
@@ -4601,7 +4789,9 @@
       <c r="V49" t="n">
         <v>2.166656</v>
       </c>
-      <c r="W49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>3.695281</v>
+      </c>
       <c r="X49" t="n">
         <v>0.082121</v>
       </c>
@@ -4646,7 +4836,9 @@
       <c r="H50" t="n">
         <v>6460.259766</v>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>21455.550781</v>
+      </c>
       <c r="J50" t="n">
         <v>45544.878906</v>
       </c>
@@ -4686,7 +4878,9 @@
       <c r="V50" t="n">
         <v>1.906644</v>
       </c>
-      <c r="W50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>1.577003</v>
+      </c>
       <c r="X50" t="n">
         <v>3.203868</v>
       </c>
@@ -4731,7 +4925,9 @@
       <c r="H51" t="n">
         <v>6688.459961</v>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>22660.009766</v>
+      </c>
       <c r="J51" t="n">
         <v>46397.890625</v>
       </c>
@@ -4771,7 +4967,9 @@
       <c r="V51" t="n">
         <v>3.532369</v>
       </c>
-      <c r="W51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>5.613741</v>
+      </c>
       <c r="X51" t="n">
         <v>1.872904</v>
       </c>
@@ -4816,7 +5014,9 @@
       <c r="H52" t="n">
         <v>6840.200195</v>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>23724.960938</v>
+      </c>
       <c r="J52" t="n">
         <v>47562.871094</v>
       </c>
@@ -4856,7 +5056,9 @@
       <c r="V52" t="n">
         <v>2.268687</v>
       </c>
-      <c r="W52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>4.699694</v>
+      </c>
       <c r="X52" t="n">
         <v>2.510848</v>
       </c>
@@ -4901,7 +5103,9 @@
       <c r="H53" t="n">
         <v>6849.089844</v>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>23365.689453</v>
+      </c>
       <c r="J53" t="n">
         <v>47716.421875</v>
       </c>
@@ -4941,7 +5145,9 @@
       <c r="V53" t="n">
         <v>0.129962</v>
       </c>
-      <c r="W53" t="inlineStr"/>
+      <c r="W53" t="n">
+        <v>-1.514319</v>
+      </c>
       <c r="X53" t="n">
         <v>0.322837</v>
       </c>
@@ -4986,7 +5192,9 @@
       <c r="H54" t="n">
         <v>6845.5</v>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>23241.990234</v>
+      </c>
       <c r="J54" t="n">
         <v>48063.289062</v>
       </c>
@@ -5026,7 +5234,9 @@
       <c r="V54" t="n">
         <v>-0.052413</v>
       </c>
-      <c r="W54" t="inlineStr"/>
+      <c r="W54" t="n">
+        <v>-0.529405</v>
+      </c>
       <c r="X54" t="n">
         <v>0.726935</v>
       </c>
@@ -5071,7 +5281,9 @@
       <c r="H55" t="n">
         <v>6939.029785</v>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>23461.820312</v>
+      </c>
       <c r="J55" t="n">
         <v>48892.46875</v>
       </c>
@@ -5111,7 +5323,9 @@
       <c r="V55" t="n">
         <v>1.366296</v>
       </c>
-      <c r="W55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>0.945832</v>
+      </c>
       <c r="X55" t="n">
         <v>1.725183</v>
       </c>
@@ -5156,7 +5370,9 @@
       <c r="H56" t="n">
         <v>6878.879883</v>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>22668.210938</v>
+      </c>
       <c r="J56" t="n">
         <v>48977.921875</v>
       </c>
@@ -5196,7 +5412,9 @@
       <c r="V56" t="n">
         <v>-0.866834</v>
       </c>
-      <c r="W56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>-3.382557</v>
+      </c>
       <c r="X56" t="n">
         <v>0.174778</v>
       </c>
@@ -5241,7 +5459,9 @@
       <c r="H57" t="n">
         <v>6528.52002</v>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>21590.630859</v>
+      </c>
       <c r="J57" t="n">
         <v>46341.511719</v>
       </c>
@@ -5281,7 +5501,9 @@
       <c r="V57" t="n">
         <v>-5.093269</v>
       </c>
-      <c r="W57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>-4.753706</v>
+      </c>
       <c r="X57" t="n">
         <v>-5.382854</v>
       </c>
@@ -5326,7 +5548,9 @@
       <c r="H58" t="n">
         <v>7209.009766</v>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>24892.310547</v>
+      </c>
       <c r="J58" t="n">
         <v>49652.140625</v>
       </c>
@@ -5366,7 +5590,9 @@
       <c r="V58" t="n">
         <v>10.423339</v>
       </c>
-      <c r="W58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>15.292187</v>
+      </c>
       <c r="X58" t="n">
         <v>7.143981</v>
       </c>
@@ -5411,7 +5637,9 @@
       <c r="H59" t="n">
         <v>7580.060059</v>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>26972.619141</v>
+      </c>
       <c r="J59" t="n">
         <v>51032.460938</v>
       </c>
@@ -5451,7 +5679,9 @@
       <c r="V59" t="n">
         <v>5.147036</v>
       </c>
-      <c r="W59" t="inlineStr"/>
+      <c r="W59" t="n">
+        <v>8.357234</v>
+      </c>
       <c r="X59" t="n">
         <v>2.779981</v>
       </c>
@@ -5496,7 +5726,9 @@
       <c r="H60" t="n">
         <v>7499.359863</v>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>26213.720703</v>
+      </c>
       <c r="J60" t="n">
         <v>52319.199219</v>
       </c>
@@ -5536,7 +5768,9 @@
       <c r="V60" t="n">
         <v>-1.064638</v>
       </c>
-      <c r="W60" t="inlineStr"/>
+      <c r="W60" t="n">
+        <v>-2.813588</v>
+      </c>
       <c r="X60" t="n">
         <v>2.521411</v>
       </c>
@@ -5581,7 +5815,9 @@
       <c r="H61" t="n">
         <v>7489.720215</v>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>25373.849609</v>
+      </c>
       <c r="J61" t="n">
         <v>52485.03125</v>
       </c>
@@ -5621,7 +5857,9 @@
       <c r="V61" t="n">
         <v>-0.12854</v>
       </c>
-      <c r="W61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>-3.203937</v>
+      </c>
       <c r="X61" t="n">
         <v>0.316962</v>
       </c>
@@ -5646,72 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>178000</v>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+        <v>177895</v>
+      </c>
+      <c r="C62" t="n">
+        <v>174.899994</v>
+      </c>
+      <c r="D62" t="n">
+        <v>108.379997</v>
+      </c>
+      <c r="E62" t="n">
+        <v>435.829987</v>
+      </c>
       <c r="F62" t="n">
-        <v>5.0743</v>
+        <v>5.1397</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8596</v>
+        <v>5.9358</v>
       </c>
       <c r="H62" t="n">
-        <v>7600.5</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
+        <v>7736.52002</v>
+      </c>
+      <c r="I62" t="n">
+        <v>26584.990234</v>
+      </c>
       <c r="J62" t="n">
-        <v>53178.410156</v>
+        <v>54085.878906</v>
       </c>
       <c r="K62" t="n">
-        <v>4133.799805</v>
+        <v>4246.5</v>
       </c>
       <c r="L62" t="n">
-        <v>77.480003</v>
+        <v>76.19000200000001</v>
       </c>
       <c r="M62" t="n">
-        <v>81.370003</v>
+        <v>80.279999</v>
       </c>
       <c r="N62" t="n">
-        <v>1182.25</v>
+        <v>1167.75</v>
       </c>
       <c r="O62" t="n">
-        <v>469.25</v>
+        <v>459.25</v>
       </c>
       <c r="P62" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+        <v>-0.058427</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-0.06857000000000001</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.05361</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1.736729</v>
+      </c>
       <c r="T62" t="n">
-        <v>-0.074839</v>
+        <v>1.213047</v>
       </c>
       <c r="U62" t="n">
-        <v>0.199168</v>
+        <v>1.502188</v>
       </c>
       <c r="V62" t="n">
-        <v>1.479091</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
+        <v>3.295181</v>
+      </c>
+      <c r="W62" t="n">
+        <v>4.773184</v>
+      </c>
       <c r="X62" t="n">
-        <v>1.321098</v>
+        <v>3.050103</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.091816</v>
+        <v>4.875155</v>
       </c>
       <c r="Z62" t="n">
-        <v>-8.491785999999999</v>
+        <v>-10.015349</v>
       </c>
       <c r="AA62" t="n">
-        <v>-9.709275999999999</v>
+        <v>-10.918779</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.874573</v>
+        <v>-0.362628</v>
       </c>
       <c r="AC62" t="n">
-        <v>6.466251</v>
+        <v>4.197391</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>177895</v>
+        <v>177726</v>
       </c>
       <c r="C62" t="n">
-        <v>174.899994</v>
+        <v>174.699997</v>
       </c>
       <c r="D62" t="n">
-        <v>108.379997</v>
+        <v>107.790001</v>
       </c>
       <c r="E62" t="n">
-        <v>435.829987</v>
+        <v>446.51001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1397</v>
+        <v>5.1165</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9358</v>
+        <v>5.9151</v>
       </c>
       <c r="H62" t="n">
-        <v>7736.52002</v>
+        <v>7723.549805</v>
       </c>
       <c r="I62" t="n">
-        <v>26584.990234</v>
+        <v>26363.439453</v>
       </c>
       <c r="J62" t="n">
-        <v>54085.878906</v>
+        <v>54349.121094</v>
       </c>
       <c r="K62" t="n">
-        <v>4246.5</v>
+        <v>4312.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>76.19000200000001</v>
+        <v>76.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>80.279999</v>
+        <v>80.55999799999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1167.75</v>
+        <v>1174</v>
       </c>
       <c r="O62" t="n">
-        <v>459.25</v>
+        <v>460.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.058427</v>
+        <v>-0.153372</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.06857000000000001</v>
+        <v>-0.18284</v>
       </c>
       <c r="R62" t="n">
-        <v>1.05361</v>
+        <v>0.503497</v>
       </c>
       <c r="S62" t="n">
-        <v>1.736729</v>
+        <v>4.229789</v>
       </c>
       <c r="T62" t="n">
-        <v>1.213047</v>
+        <v>0.756182</v>
       </c>
       <c r="U62" t="n">
-        <v>1.502188</v>
+        <v>1.148218</v>
       </c>
       <c r="V62" t="n">
-        <v>3.295181</v>
+        <v>3.122007</v>
       </c>
       <c r="W62" t="n">
-        <v>4.773184</v>
+        <v>3.900038</v>
       </c>
       <c r="X62" t="n">
-        <v>3.050103</v>
+        <v>3.55166</v>
       </c>
       <c r="Y62" t="n">
-        <v>4.875155</v>
+        <v>6.512551</v>
       </c>
       <c r="Z62" t="n">
-        <v>-10.015349</v>
+        <v>-10.086218</v>
       </c>
       <c r="AA62" t="n">
-        <v>-10.918779</v>
+        <v>-10.608084</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.362628</v>
+        <v>0.170648</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.197391</v>
+        <v>4.480998</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>177726</v>
+        <v>175546</v>
       </c>
       <c r="C62" t="n">
-        <v>174.699997</v>
+        <v>172.039993</v>
       </c>
       <c r="D62" t="n">
-        <v>107.790001</v>
+        <v>105.910004</v>
       </c>
       <c r="E62" t="n">
-        <v>446.51001</v>
+        <v>443.950012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1165</v>
+        <v>5.1014</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9151</v>
+        <v>5.8811</v>
       </c>
       <c r="H62" t="n">
-        <v>7723.549805</v>
+        <v>7709.959961</v>
       </c>
       <c r="I62" t="n">
-        <v>26363.439453</v>
+        <v>26348.349609</v>
       </c>
       <c r="J62" t="n">
-        <v>54349.121094</v>
+        <v>53885.101562</v>
       </c>
       <c r="K62" t="n">
-        <v>4312.799805</v>
+        <v>4375.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>76.129997</v>
+        <v>76.879997</v>
       </c>
       <c r="M62" t="n">
-        <v>80.55999799999999</v>
+        <v>81.839996</v>
       </c>
       <c r="N62" t="n">
-        <v>1174</v>
+        <v>1182.25</v>
       </c>
       <c r="O62" t="n">
-        <v>460.5</v>
+        <v>465.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.153372</v>
+        <v>-1.378098</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.18284</v>
+        <v>-1.702669</v>
       </c>
       <c r="R62" t="n">
-        <v>0.503497</v>
+        <v>-1.249414</v>
       </c>
       <c r="S62" t="n">
-        <v>4.229789</v>
+        <v>3.632204</v>
       </c>
       <c r="T62" t="n">
-        <v>0.756182</v>
+        <v>0.458827</v>
       </c>
       <c r="U62" t="n">
-        <v>1.148218</v>
+        <v>0.566819</v>
       </c>
       <c r="V62" t="n">
-        <v>3.122007</v>
+        <v>2.94056</v>
       </c>
       <c r="W62" t="n">
-        <v>3.900038</v>
+        <v>3.840568</v>
       </c>
       <c r="X62" t="n">
-        <v>3.55166</v>
+        <v>2.667561</v>
       </c>
       <c r="Y62" t="n">
-        <v>6.512551</v>
+        <v>8.068452000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>-10.086218</v>
+        <v>-9.200426</v>
       </c>
       <c r="AA62" t="n">
-        <v>-10.608084</v>
+        <v>-9.187756</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.170648</v>
+        <v>0.874573</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.480998</v>
+        <v>5.558707</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>175546</v>
+        <v>172513</v>
       </c>
       <c r="C62" t="n">
-        <v>172.039993</v>
+        <v>169.369995</v>
       </c>
       <c r="D62" t="n">
-        <v>105.910004</v>
+        <v>104.699997</v>
       </c>
       <c r="E62" t="n">
-        <v>443.950012</v>
+        <v>444.350006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1014</v>
+        <v>5.0842</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8811</v>
+        <v>5.8734</v>
       </c>
       <c r="H62" t="n">
-        <v>7709.959961</v>
+        <v>7757.640137</v>
       </c>
       <c r="I62" t="n">
-        <v>26348.349609</v>
+        <v>26690.619141</v>
       </c>
       <c r="J62" t="n">
-        <v>53885.101562</v>
+        <v>54036.929688</v>
       </c>
       <c r="K62" t="n">
-        <v>4375.799805</v>
+        <v>4340.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>76.879997</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>81.839996</v>
+        <v>83.550003</v>
       </c>
       <c r="N62" t="n">
-        <v>1182.25</v>
+        <v>1156.5</v>
       </c>
       <c r="O62" t="n">
-        <v>465.25</v>
+        <v>439</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.378098</v>
+        <v>-3.08204</v>
       </c>
       <c r="Q62" t="n">
-        <v>-1.702669</v>
+        <v>-3.228208</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.249414</v>
+        <v>-2.377625</v>
       </c>
       <c r="S62" t="n">
-        <v>3.632204</v>
+        <v>3.725575</v>
       </c>
       <c r="T62" t="n">
-        <v>0.458827</v>
+        <v>0.120118</v>
       </c>
       <c r="U62" t="n">
-        <v>0.566819</v>
+        <v>0.43515</v>
       </c>
       <c r="V62" t="n">
-        <v>2.94056</v>
+        <v>3.577169</v>
       </c>
       <c r="W62" t="n">
-        <v>3.840568</v>
+        <v>5.189475</v>
       </c>
       <c r="X62" t="n">
-        <v>2.667561</v>
+        <v>2.95684</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.068452000000001</v>
+        <v>7.201603</v>
       </c>
       <c r="Z62" t="n">
-        <v>-9.200426</v>
+        <v>-7.66505</v>
       </c>
       <c r="AA62" t="n">
-        <v>-9.187756</v>
+        <v>-7.290279</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.874573</v>
+        <v>-1.322526</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.558707</v>
+        <v>-0.39705</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5911,7 +5911,7 @@
         <v>54036.929688</v>
       </c>
       <c r="K62" t="n">
-        <v>4340.700195</v>
+        <v>4399.700195</v>
       </c>
       <c r="L62" t="n">
         <v>78.18000000000001</v>
@@ -5920,10 +5920,10 @@
         <v>83.550003</v>
       </c>
       <c r="N62" t="n">
-        <v>1156.5</v>
+        <v>1176.25</v>
       </c>
       <c r="O62" t="n">
-        <v>439</v>
+        <v>461.5</v>
       </c>
       <c r="P62" t="n">
         <v>-3.08204</v>
@@ -5953,7 +5953,7 @@
         <v>2.95684</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.201603</v>
+        <v>8.658716</v>
       </c>
       <c r="Z62" t="n">
         <v>-7.66505</v>
@@ -5962,10 +5962,10 @@
         <v>-7.290279</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.322526</v>
+        <v>0.362628</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.39705</v>
+        <v>4.707884</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>444.350006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0842</v>
+        <v>5.0848</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8734</v>
+        <v>5.8753</v>
       </c>
       <c r="H62" t="n">
         <v>7757.640137</v>
@@ -5911,19 +5911,19 @@
         <v>54036.929688</v>
       </c>
       <c r="K62" t="n">
-        <v>4399.700195</v>
+        <v>4395.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>78.18000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="M62" t="n">
-        <v>83.550003</v>
+        <v>84.949997</v>
       </c>
       <c r="N62" t="n">
-        <v>1176.25</v>
+        <v>1183.25</v>
       </c>
       <c r="O62" t="n">
-        <v>461.5</v>
+        <v>463.75</v>
       </c>
       <c r="P62" t="n">
         <v>-3.08204</v>
@@ -5938,10 +5938,10 @@
         <v>3.725575</v>
       </c>
       <c r="T62" t="n">
-        <v>0.120118</v>
+        <v>0.13193</v>
       </c>
       <c r="U62" t="n">
-        <v>0.43515</v>
+        <v>0.467635</v>
       </c>
       <c r="V62" t="n">
         <v>3.577169</v>
@@ -5953,19 +5953,19 @@
         <v>2.95684</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.658716</v>
+        <v>8.559929</v>
       </c>
       <c r="Z62" t="n">
-        <v>-7.66505</v>
+        <v>-6.106057</v>
       </c>
       <c r="AA62" t="n">
-        <v>-7.290279</v>
+        <v>-5.736802</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.362628</v>
+        <v>0.959898</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.707884</v>
+        <v>5.218378</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,85 +5884,85 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>172513</v>
+        <v>172180</v>
       </c>
       <c r="C62" t="n">
-        <v>169.369995</v>
+        <v>169.270004</v>
       </c>
       <c r="D62" t="n">
-        <v>104.699997</v>
+        <v>103.519997</v>
       </c>
       <c r="E62" t="n">
-        <v>444.350006</v>
+        <v>446.850006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0848</v>
+        <v>5.1133</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8753</v>
+        <v>5.8987</v>
       </c>
       <c r="H62" t="n">
-        <v>7757.640137</v>
+        <v>7753.109863</v>
       </c>
       <c r="I62" t="n">
-        <v>26690.619141</v>
+        <v>26605.359375</v>
       </c>
       <c r="J62" t="n">
-        <v>54036.929688</v>
+        <v>53975.980469</v>
       </c>
       <c r="K62" t="n">
-        <v>4395.700195</v>
+        <v>4436.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>79.5</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>84.949997</v>
+        <v>89.19000200000001</v>
       </c>
       <c r="N62" t="n">
-        <v>1183.25</v>
+        <v>1180.75</v>
       </c>
       <c r="O62" t="n">
         <v>463.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-3.08204</v>
+        <v>-3.269119</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3.228208</v>
+        <v>-3.285339</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.377625</v>
+        <v>-3.477859</v>
       </c>
       <c r="S62" t="n">
-        <v>3.725575</v>
+        <v>4.309155</v>
       </c>
       <c r="T62" t="n">
-        <v>0.13193</v>
+        <v>0.6931659999999999</v>
       </c>
       <c r="U62" t="n">
-        <v>0.467635</v>
+        <v>0.867781</v>
       </c>
       <c r="V62" t="n">
-        <v>3.577169</v>
+        <v>3.516682</v>
       </c>
       <c r="W62" t="n">
-        <v>5.189475</v>
+        <v>4.85346</v>
       </c>
       <c r="X62" t="n">
-        <v>2.95684</v>
+        <v>2.840713</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.559929</v>
+        <v>9.570028000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>-6.106057</v>
+        <v>-1.169243</v>
       </c>
       <c r="AA62" t="n">
-        <v>-5.736802</v>
+        <v>-1.031958</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.959898</v>
+        <v>0.746587</v>
       </c>
       <c r="AC62" t="n">
         <v>5.218378</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,7 +5884,7 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>172180</v>
+        <v>167875</v>
       </c>
       <c r="C62" t="n">
         <v>169.270004</v>
@@ -5896,37 +5896,37 @@
         <v>446.850006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1133</v>
+        <v>5.1716</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8987</v>
+        <v>5.9654</v>
       </c>
       <c r="H62" t="n">
-        <v>7753.109863</v>
+        <v>7728.200195</v>
       </c>
       <c r="I62" t="n">
-        <v>26605.359375</v>
+        <v>26445.449219</v>
       </c>
       <c r="J62" t="n">
-        <v>53975.980469</v>
+        <v>53791.851562</v>
       </c>
       <c r="K62" t="n">
-        <v>4436.600098</v>
+        <v>4469</v>
       </c>
       <c r="L62" t="n">
-        <v>83.68000000000001</v>
+        <v>83.519997</v>
       </c>
       <c r="M62" t="n">
-        <v>89.19000200000001</v>
+        <v>89.220001</v>
       </c>
       <c r="N62" t="n">
-        <v>1180.75</v>
+        <v>1175.25</v>
       </c>
       <c r="O62" t="n">
-        <v>463.75</v>
+        <v>465.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-3.269119</v>
+        <v>-5.687672</v>
       </c>
       <c r="Q62" t="n">
         <v>-3.285339</v>
@@ -5938,34 +5938,34 @@
         <v>4.309155</v>
       </c>
       <c r="T62" t="n">
-        <v>0.6931659999999999</v>
+        <v>1.841233</v>
       </c>
       <c r="U62" t="n">
-        <v>0.867781</v>
+        <v>2.00835</v>
       </c>
       <c r="V62" t="n">
-        <v>3.516682</v>
+        <v>3.184097</v>
       </c>
       <c r="W62" t="n">
-        <v>4.85346</v>
+        <v>4.223244</v>
       </c>
       <c r="X62" t="n">
-        <v>2.840713</v>
+        <v>2.489891</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.570028000000001</v>
+        <v>10.370203</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.169243</v>
+        <v>-1.358216</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.031958</v>
+        <v>-0.9986699999999999</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.746587</v>
+        <v>0.277304</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.218378</v>
+        <v>5.67215</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>167875</v>
+        <v>167491</v>
       </c>
       <c r="C62" t="n">
-        <v>169.270004</v>
+        <v>165.050003</v>
       </c>
       <c r="D62" t="n">
-        <v>103.519997</v>
+        <v>101.199997</v>
       </c>
       <c r="E62" t="n">
-        <v>446.850006</v>
+        <v>450.350006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1716</v>
+        <v>5.1612</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9654</v>
+        <v>5.9514</v>
       </c>
       <c r="H62" t="n">
-        <v>7728.200195</v>
+        <v>7748.5</v>
       </c>
       <c r="I62" t="n">
-        <v>26445.449219</v>
+        <v>26588.490234</v>
       </c>
       <c r="J62" t="n">
-        <v>53791.851562</v>
+        <v>53770.269531</v>
       </c>
       <c r="K62" t="n">
-        <v>4469</v>
+        <v>4450.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>83.519997</v>
+        <v>81.459999</v>
       </c>
       <c r="M62" t="n">
-        <v>89.220001</v>
+        <v>87.220001</v>
       </c>
       <c r="N62" t="n">
-        <v>1175.25</v>
+        <v>1184.5</v>
       </c>
       <c r="O62" t="n">
-        <v>465.75</v>
+        <v>478.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.687672</v>
+        <v>-5.903404</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3.285339</v>
+        <v>-5.696492</v>
       </c>
       <c r="R62" t="n">
-        <v>-3.477859</v>
+        <v>-5.641028</v>
       </c>
       <c r="S62" t="n">
-        <v>4.309155</v>
+        <v>5.126168</v>
       </c>
       <c r="T62" t="n">
-        <v>1.841233</v>
+        <v>1.636436</v>
       </c>
       <c r="U62" t="n">
-        <v>2.00835</v>
+        <v>1.768943</v>
       </c>
       <c r="V62" t="n">
-        <v>3.184097</v>
+        <v>3.455133</v>
       </c>
       <c r="W62" t="n">
-        <v>4.223244</v>
+        <v>4.786978</v>
       </c>
       <c r="X62" t="n">
-        <v>2.489891</v>
+        <v>2.448771</v>
       </c>
       <c r="Y62" t="n">
-        <v>10.370203</v>
+        <v>9.910838999999999</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.358216</v>
+        <v>-3.791188</v>
       </c>
       <c r="AA62" t="n">
-        <v>-0.9986699999999999</v>
+        <v>-3.217933</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.277304</v>
+        <v>1.066553</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.67215</v>
+        <v>8.508224999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5813,13 +5813,13 @@
         <v>5.847953</v>
       </c>
       <c r="H61" t="n">
-        <v>7489.720215</v>
+        <v>7437.629883</v>
       </c>
       <c r="I61" t="n">
         <v>25373.849609</v>
       </c>
       <c r="J61" t="n">
-        <v>52485.03125</v>
+        <v>52208.058594</v>
       </c>
       <c r="K61" t="n">
         <v>4049.100098</v>
@@ -5855,13 +5855,13 @@
         <v>-1.169601</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.12854</v>
+        <v>-0.823137</v>
       </c>
       <c r="W61" t="n">
         <v>-3.203937</v>
       </c>
       <c r="X61" t="n">
-        <v>0.316962</v>
+        <v>-0.212428</v>
       </c>
       <c r="Y61" t="n">
         <v>0.651276</v>
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>167491</v>
+        <v>167101</v>
       </c>
       <c r="C62" t="n">
-        <v>165.050003</v>
+        <v>164.669998</v>
       </c>
       <c r="D62" t="n">
-        <v>101.199997</v>
+        <v>100.769997</v>
       </c>
       <c r="E62" t="n">
-        <v>450.350006</v>
+        <v>452.440002</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1612</v>
+        <v>5.189</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9514</v>
+        <v>5.9962</v>
       </c>
       <c r="H62" t="n">
-        <v>7748.5</v>
+        <v>7798.990234</v>
       </c>
       <c r="I62" t="n">
-        <v>26588.490234</v>
+        <v>26803.029297</v>
       </c>
       <c r="J62" t="n">
-        <v>53770.269531</v>
+        <v>53839.988281</v>
       </c>
       <c r="K62" t="n">
-        <v>4450.399902</v>
+        <v>4407.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>81.459999</v>
+        <v>81.699997</v>
       </c>
       <c r="M62" t="n">
-        <v>87.220001</v>
+        <v>87.160004</v>
       </c>
       <c r="N62" t="n">
-        <v>1184.5</v>
+        <v>1186.5</v>
       </c>
       <c r="O62" t="n">
-        <v>478.25</v>
+        <v>476</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.903404</v>
+        <v>-6.122506</v>
       </c>
       <c r="Q62" t="n">
-        <v>-5.696492</v>
+        <v>-5.913613</v>
       </c>
       <c r="R62" t="n">
-        <v>-5.641028</v>
+        <v>-6.041961</v>
       </c>
       <c r="S62" t="n">
-        <v>5.126168</v>
+        <v>5.61404</v>
       </c>
       <c r="T62" t="n">
-        <v>1.636436</v>
+        <v>2.183886</v>
       </c>
       <c r="U62" t="n">
-        <v>1.768943</v>
+        <v>2.535028</v>
       </c>
       <c r="V62" t="n">
-        <v>3.455133</v>
+        <v>4.858542</v>
       </c>
       <c r="W62" t="n">
-        <v>4.786978</v>
+        <v>5.632491</v>
       </c>
       <c r="X62" t="n">
-        <v>2.448771</v>
+        <v>3.12582</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.910838999999999</v>
+        <v>8.861223000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>-3.791188</v>
+        <v>-3.507737</v>
       </c>
       <c r="AA62" t="n">
-        <v>-3.217933</v>
+        <v>-3.284508</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.066553</v>
+        <v>1.237201</v>
       </c>
       <c r="AC62" t="n">
-        <v>8.508224999999999</v>
+        <v>7.997731</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5795,7 +5795,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>177999</v>
+        <v>177159</v>
       </c>
       <c r="C61" t="n">
         <v>175.020004</v>
@@ -5816,7 +5816,7 @@
         <v>7437.629883</v>
       </c>
       <c r="I61" t="n">
-        <v>25373.849609</v>
+        <v>25122.179688</v>
       </c>
       <c r="J61" t="n">
         <v>52208.058594</v>
@@ -5837,7 +5837,7 @@
         <v>440.75</v>
       </c>
       <c r="P61" t="n">
-        <v>3.473353</v>
+        <v>2.985049</v>
       </c>
       <c r="Q61" t="n">
         <v>3.5315</v>
@@ -5858,7 +5858,7 @@
         <v>-0.823137</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.203937</v>
+        <v>-4.164006</v>
       </c>
       <c r="X61" t="n">
         <v>-0.212428</v>
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>167101</v>
+        <v>166934</v>
       </c>
       <c r="C62" t="n">
-        <v>164.669998</v>
+        <v>164.149994</v>
       </c>
       <c r="D62" t="n">
-        <v>100.769997</v>
+        <v>100.970001</v>
       </c>
       <c r="E62" t="n">
-        <v>452.440002</v>
+        <v>457</v>
       </c>
       <c r="F62" t="n">
-        <v>5.189</v>
+        <v>5.2132</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9962</v>
+        <v>6.0459</v>
       </c>
       <c r="H62" t="n">
-        <v>7798.990234</v>
+        <v>7785.759766</v>
       </c>
       <c r="I62" t="n">
-        <v>26803.029297</v>
+        <v>26729.160156</v>
       </c>
       <c r="J62" t="n">
-        <v>53839.988281</v>
+        <v>53732.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4407.899902</v>
+        <v>4380.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>81.699997</v>
+        <v>82.400002</v>
       </c>
       <c r="M62" t="n">
-        <v>87.160004</v>
+        <v>88.519997</v>
       </c>
       <c r="N62" t="n">
-        <v>1186.5</v>
+        <v>1173.75</v>
       </c>
       <c r="O62" t="n">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="P62" t="n">
-        <v>-6.122506</v>
+        <v>-5.771651</v>
       </c>
       <c r="Q62" t="n">
-        <v>-5.913613</v>
+        <v>-6.210725</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.041961</v>
+        <v>-5.855477</v>
       </c>
       <c r="S62" t="n">
-        <v>5.61404</v>
+        <v>6.67849</v>
       </c>
       <c r="T62" t="n">
-        <v>2.183886</v>
+        <v>2.660442</v>
       </c>
       <c r="U62" t="n">
-        <v>2.535028</v>
+        <v>3.384894</v>
       </c>
       <c r="V62" t="n">
-        <v>4.858542</v>
+        <v>4.680656</v>
       </c>
       <c r="W62" t="n">
-        <v>5.632491</v>
+        <v>6.39666</v>
       </c>
       <c r="X62" t="n">
-        <v>3.12582</v>
+        <v>2.919763</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.861223000000001</v>
+        <v>8.18206</v>
       </c>
       <c r="Z62" t="n">
-        <v>-3.507737</v>
+        <v>-2.680993</v>
       </c>
       <c r="AA62" t="n">
-        <v>-3.284508</v>
+        <v>-1.775417</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.237201</v>
+        <v>0.149317</v>
       </c>
       <c r="AC62" t="n">
-        <v>7.997731</v>
+        <v>4.140669</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5795,7 +5795,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
       <c r="C61" t="n">
         <v>175.020004</v>
@@ -5813,13 +5813,13 @@
         <v>5.847953</v>
       </c>
       <c r="H61" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
       <c r="I61" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
       <c r="J61" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
       <c r="K61" t="n">
         <v>4049.100098</v>
@@ -5837,7 +5837,7 @@
         <v>440.75</v>
       </c>
       <c r="P61" t="n">
-        <v>2.985049</v>
+        <v>3.473353</v>
       </c>
       <c r="Q61" t="n">
         <v>3.5315</v>
@@ -5855,13 +5855,13 @@
         <v>-1.169601</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.823137</v>
+        <v>-0.12854</v>
       </c>
       <c r="W61" t="n">
-        <v>-4.164006</v>
+        <v>-3.203937</v>
       </c>
       <c r="X61" t="n">
-        <v>-0.212428</v>
+        <v>0.316962</v>
       </c>
       <c r="Y61" t="n">
         <v>0.651276</v>
@@ -5887,13 +5887,13 @@
         <v>166934</v>
       </c>
       <c r="C62" t="n">
-        <v>164.149994</v>
+        <v>163.899994</v>
       </c>
       <c r="D62" t="n">
-        <v>100.970001</v>
+        <v>100.120003</v>
       </c>
       <c r="E62" t="n">
-        <v>457</v>
+        <v>458.100006</v>
       </c>
       <c r="F62" t="n">
         <v>5.2132</v>
@@ -5911,7 +5911,7 @@
         <v>53732.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4380.399902</v>
+        <v>4437.299805</v>
       </c>
       <c r="L62" t="n">
         <v>82.400002</v>
@@ -5920,22 +5920,22 @@
         <v>88.519997</v>
       </c>
       <c r="N62" t="n">
-        <v>1173.75</v>
+        <v>1192.5</v>
       </c>
       <c r="O62" t="n">
-        <v>459</v>
+        <v>483.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.771651</v>
+        <v>-6.216327</v>
       </c>
       <c r="Q62" t="n">
-        <v>-6.210725</v>
+        <v>-6.353565</v>
       </c>
       <c r="R62" t="n">
-        <v>-5.855477</v>
+        <v>-6.648016</v>
       </c>
       <c r="S62" t="n">
-        <v>6.67849</v>
+        <v>6.935267</v>
       </c>
       <c r="T62" t="n">
         <v>2.660442</v>
@@ -5944,16 +5944,16 @@
         <v>3.384894</v>
       </c>
       <c r="V62" t="n">
-        <v>4.680656</v>
+        <v>3.952612</v>
       </c>
       <c r="W62" t="n">
-        <v>6.39666</v>
+        <v>5.341367</v>
       </c>
       <c r="X62" t="n">
-        <v>2.919763</v>
+        <v>2.376637</v>
       </c>
       <c r="Y62" t="n">
-        <v>8.18206</v>
+        <v>9.587308</v>
       </c>
       <c r="Z62" t="n">
         <v>-2.680993</v>
@@ -5962,10 +5962,10 @@
         <v>-1.775417</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.149317</v>
+        <v>1.749147</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.140669</v>
+        <v>9.642655</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>458.100006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2132</v>
+        <v>5.2265</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0459</v>
+        <v>6.0614</v>
       </c>
       <c r="H62" t="n">
         <v>7785.759766</v>
@@ -5911,19 +5911,19 @@
         <v>53732.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4437.299805</v>
+        <v>4452.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>82.400002</v>
+        <v>83.050003</v>
       </c>
       <c r="M62" t="n">
-        <v>88.519997</v>
+        <v>89.480003</v>
       </c>
       <c r="N62" t="n">
-        <v>1192.5</v>
+        <v>1198.75</v>
       </c>
       <c r="O62" t="n">
-        <v>483.25</v>
+        <v>486</v>
       </c>
       <c r="P62" t="n">
         <v>-6.216327</v>
@@ -5938,10 +5938,10 @@
         <v>6.935267</v>
       </c>
       <c r="T62" t="n">
-        <v>2.660442</v>
+        <v>2.922349</v>
       </c>
       <c r="U62" t="n">
-        <v>3.384894</v>
+        <v>3.649946</v>
       </c>
       <c r="V62" t="n">
         <v>3.952612</v>
@@ -5953,19 +5953,19 @@
         <v>2.376637</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.587308</v>
+        <v>9.952828999999999</v>
       </c>
       <c r="Z62" t="n">
-        <v>-2.680993</v>
+        <v>-1.913305</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.775417</v>
+        <v>-0.710164</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.749147</v>
+        <v>2.282423</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.642655</v>
+        <v>10.266591</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5795,7 +5795,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>177999</v>
+        <v>177159</v>
       </c>
       <c r="C61" t="n">
         <v>175.020004</v>
@@ -5813,10 +5813,10 @@
         <v>5.847953</v>
       </c>
       <c r="H61" t="n">
-        <v>7489.720215</v>
+        <v>7437.629883</v>
       </c>
       <c r="I61" t="n">
-        <v>25373.849609</v>
+        <v>25122.179688</v>
       </c>
       <c r="J61" t="n">
         <v>52485.03125</v>
@@ -5837,7 +5837,7 @@
         <v>440.75</v>
       </c>
       <c r="P61" t="n">
-        <v>3.473353</v>
+        <v>2.985049</v>
       </c>
       <c r="Q61" t="n">
         <v>3.5315</v>
@@ -5855,10 +5855,10 @@
         <v>-1.169601</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.12854</v>
+        <v>-0.823137</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.203937</v>
+        <v>-4.164006</v>
       </c>
       <c r="X61" t="n">
         <v>0.316962</v>
@@ -5896,10 +5896,10 @@
         <v>458.100006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2265</v>
+        <v>5.2</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0614</v>
+        <v>6.0196</v>
       </c>
       <c r="H62" t="n">
         <v>7785.759766</v>
@@ -5911,22 +5911,22 @@
         <v>53732.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4452.100098</v>
+        <v>4451.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>83.050003</v>
+        <v>84.370003</v>
       </c>
       <c r="M62" t="n">
-        <v>89.480003</v>
+        <v>91.129997</v>
       </c>
       <c r="N62" t="n">
-        <v>1198.75</v>
+        <v>1225</v>
       </c>
       <c r="O62" t="n">
-        <v>486</v>
+        <v>492.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-6.216327</v>
+        <v>-5.771651</v>
       </c>
       <c r="Q62" t="n">
         <v>-6.353565</v>
@@ -5938,34 +5938,34 @@
         <v>6.935267</v>
       </c>
       <c r="T62" t="n">
-        <v>2.922349</v>
+        <v>2.400496</v>
       </c>
       <c r="U62" t="n">
-        <v>3.649946</v>
+        <v>2.935165</v>
       </c>
       <c r="V62" t="n">
-        <v>3.952612</v>
+        <v>4.680656</v>
       </c>
       <c r="W62" t="n">
-        <v>5.341367</v>
+        <v>6.39666</v>
       </c>
       <c r="X62" t="n">
         <v>2.376637</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.952828999999999</v>
+        <v>9.935536000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.913305</v>
+        <v>-0.354311</v>
       </c>
       <c r="AA62" t="n">
-        <v>-0.710164</v>
+        <v>1.120722</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.282423</v>
+        <v>4.522184</v>
       </c>
       <c r="AC62" t="n">
-        <v>10.266591</v>
+        <v>11.798071</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5819,7 +5819,7 @@
         <v>25122.179688</v>
       </c>
       <c r="J61" t="n">
-        <v>52485.03125</v>
+        <v>52208.058594</v>
       </c>
       <c r="K61" t="n">
         <v>4049.100098</v>
@@ -5861,7 +5861,7 @@
         <v>-4.164006</v>
       </c>
       <c r="X61" t="n">
-        <v>0.316962</v>
+        <v>-0.212428</v>
       </c>
       <c r="Y61" t="n">
         <v>0.651276</v>
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>166934</v>
+        <v>166335</v>
       </c>
       <c r="C62" t="n">
-        <v>163.899994</v>
+        <v>163.800003</v>
       </c>
       <c r="D62" t="n">
-        <v>100.120003</v>
+        <v>100</v>
       </c>
       <c r="E62" t="n">
-        <v>458.100006</v>
+        <v>453.890015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2</v>
+        <v>5.2196</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0196</v>
+        <v>6.0607</v>
       </c>
       <c r="H62" t="n">
-        <v>7785.759766</v>
+        <v>7691.759766</v>
       </c>
       <c r="I62" t="n">
-        <v>26729.160156</v>
+        <v>26289.710938</v>
       </c>
       <c r="J62" t="n">
-        <v>53732.410156</v>
+        <v>53343.398438</v>
       </c>
       <c r="K62" t="n">
-        <v>4451.399902</v>
+        <v>4422.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>84.370003</v>
+        <v>85.019997</v>
       </c>
       <c r="M62" t="n">
-        <v>91.129997</v>
+        <v>92.010002</v>
       </c>
       <c r="N62" t="n">
-        <v>1225</v>
+        <v>1227.25</v>
       </c>
       <c r="O62" t="n">
-        <v>492.75</v>
+        <v>490.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.771651</v>
+        <v>-6.109766</v>
       </c>
       <c r="Q62" t="n">
-        <v>-6.353565</v>
+        <v>-6.410696</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.648016</v>
+        <v>-6.759907</v>
       </c>
       <c r="S62" t="n">
-        <v>6.935267</v>
+        <v>5.95252</v>
       </c>
       <c r="T62" t="n">
-        <v>2.400496</v>
+        <v>2.786475</v>
       </c>
       <c r="U62" t="n">
-        <v>2.935165</v>
+        <v>3.637976</v>
       </c>
       <c r="V62" t="n">
-        <v>4.680656</v>
+        <v>3.416813</v>
       </c>
       <c r="W62" t="n">
-        <v>6.39666</v>
+        <v>4.647412</v>
       </c>
       <c r="X62" t="n">
-        <v>2.376637</v>
+        <v>2.174645</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.935536000000001</v>
+        <v>9.216856</v>
       </c>
       <c r="Z62" t="n">
-        <v>-0.354311</v>
+        <v>0.413368</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.120722</v>
+        <v>2.097203</v>
       </c>
       <c r="AB62" t="n">
-        <v>4.522184</v>
+        <v>4.714164</v>
       </c>
       <c r="AC62" t="n">
-        <v>11.798071</v>
+        <v>11.230856</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5795,7 +5795,7 @@
         <v>46234</v>
       </c>
       <c r="B61" t="n">
-        <v>177159</v>
+        <v>177999</v>
       </c>
       <c r="C61" t="n">
         <v>175.020004</v>
@@ -5813,13 +5813,13 @@
         <v>5.847953</v>
       </c>
       <c r="H61" t="n">
-        <v>7437.629883</v>
+        <v>7489.720215</v>
       </c>
       <c r="I61" t="n">
-        <v>25122.179688</v>
+        <v>25373.849609</v>
       </c>
       <c r="J61" t="n">
-        <v>52208.058594</v>
+        <v>52485.03125</v>
       </c>
       <c r="K61" t="n">
         <v>4049.100098</v>
@@ -5837,7 +5837,7 @@
         <v>440.75</v>
       </c>
       <c r="P61" t="n">
-        <v>2.985049</v>
+        <v>3.473353</v>
       </c>
       <c r="Q61" t="n">
         <v>3.5315</v>
@@ -5855,13 +5855,13 @@
         <v>-1.169601</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.823137</v>
+        <v>-0.12854</v>
       </c>
       <c r="W61" t="n">
-        <v>-4.164006</v>
+        <v>-3.203937</v>
       </c>
       <c r="X61" t="n">
-        <v>-0.212428</v>
+        <v>0.316962</v>
       </c>
       <c r="Y61" t="n">
         <v>0.651276</v>
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>166335</v>
+        <v>167830</v>
       </c>
       <c r="C62" t="n">
-        <v>163.800003</v>
+        <v>163.550003</v>
       </c>
       <c r="D62" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E62" t="n">
-        <v>453.890015</v>
+        <v>453.25</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2196</v>
+        <v>5.1681</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0607</v>
+        <v>6.0502</v>
       </c>
       <c r="H62" t="n">
-        <v>7691.759766</v>
+        <v>7707.97998</v>
       </c>
       <c r="I62" t="n">
-        <v>26289.710938</v>
+        <v>26331.089844</v>
       </c>
       <c r="J62" t="n">
-        <v>53343.398438</v>
+        <v>53463.050781</v>
       </c>
       <c r="K62" t="n">
-        <v>4422.299805</v>
+        <v>4543.5</v>
       </c>
       <c r="L62" t="n">
-        <v>85.019997</v>
+        <v>86.589996</v>
       </c>
       <c r="M62" t="n">
-        <v>92.010002</v>
+        <v>93.849998</v>
       </c>
       <c r="N62" t="n">
-        <v>1227.25</v>
+        <v>1241.5</v>
       </c>
       <c r="O62" t="n">
-        <v>490.25</v>
+        <v>502</v>
       </c>
       <c r="P62" t="n">
-        <v>-6.109766</v>
+        <v>-5.712953</v>
       </c>
       <c r="Q62" t="n">
-        <v>-6.410696</v>
+        <v>-6.553537</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.759907</v>
+        <v>-7.692308</v>
       </c>
       <c r="S62" t="n">
-        <v>5.95252</v>
+        <v>5.80312</v>
       </c>
       <c r="T62" t="n">
-        <v>2.786475</v>
+        <v>1.77231</v>
       </c>
       <c r="U62" t="n">
-        <v>3.637976</v>
+        <v>3.458426</v>
       </c>
       <c r="V62" t="n">
-        <v>3.416813</v>
+        <v>2.914124</v>
       </c>
       <c r="W62" t="n">
-        <v>4.647412</v>
+        <v>3.772546</v>
       </c>
       <c r="X62" t="n">
-        <v>2.174645</v>
+        <v>1.863426</v>
       </c>
       <c r="Y62" t="n">
-        <v>9.216856</v>
+        <v>12.210118</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.413368</v>
+        <v>2.267625</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.097203</v>
+        <v>4.138921</v>
       </c>
       <c r="AB62" t="n">
-        <v>4.714164</v>
+        <v>5.930034</v>
       </c>
       <c r="AC62" t="n">
-        <v>11.230856</v>
+        <v>13.896767</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,85 +5884,85 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>167830</v>
+        <v>167927</v>
       </c>
       <c r="C62" t="n">
-        <v>163.550003</v>
+        <v>165</v>
       </c>
       <c r="D62" t="n">
-        <v>99</v>
+        <v>99.94000200000001</v>
       </c>
       <c r="E62" t="n">
-        <v>453.25</v>
+        <v>450.299988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1681</v>
+        <v>5.1931</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0502</v>
+        <v>6.0795</v>
       </c>
       <c r="H62" t="n">
-        <v>7707.97998</v>
+        <v>7641.160156</v>
       </c>
       <c r="I62" t="n">
-        <v>26331.089844</v>
+        <v>26067.169922</v>
       </c>
       <c r="J62" t="n">
-        <v>53463.050781</v>
+        <v>52759.210938</v>
       </c>
       <c r="K62" t="n">
-        <v>4543.5</v>
+        <v>4640.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>86.589996</v>
+        <v>87.25</v>
       </c>
       <c r="M62" t="n">
-        <v>93.849998</v>
+        <v>94.05999799999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1241.5</v>
+        <v>1231.75</v>
       </c>
       <c r="O62" t="n">
         <v>502</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.712953</v>
+        <v>-5.658459</v>
       </c>
       <c r="Q62" t="n">
-        <v>-6.553537</v>
+        <v>-5.725062</v>
       </c>
       <c r="R62" t="n">
-        <v>-7.692308</v>
+        <v>-6.815849</v>
       </c>
       <c r="S62" t="n">
-        <v>5.80312</v>
+        <v>5.114492</v>
       </c>
       <c r="T62" t="n">
-        <v>1.77231</v>
+        <v>2.264622</v>
       </c>
       <c r="U62" t="n">
-        <v>3.458426</v>
+        <v>3.95946</v>
       </c>
       <c r="V62" t="n">
-        <v>2.914124</v>
+        <v>2.021971</v>
       </c>
       <c r="W62" t="n">
-        <v>3.772546</v>
+        <v>2.732421</v>
       </c>
       <c r="X62" t="n">
-        <v>1.863426</v>
+        <v>0.522396</v>
       </c>
       <c r="Y62" t="n">
-        <v>12.210118</v>
+        <v>14.610656</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.267625</v>
+        <v>3.047126</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.138921</v>
+        <v>4.371943</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.930034</v>
+        <v>5.098123</v>
       </c>
       <c r="AC62" t="n">
         <v>13.896767</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>167927</v>
+        <v>171031.734375</v>
       </c>
       <c r="C62" t="n">
         <v>165</v>
       </c>
       <c r="D62" t="n">
-        <v>99.94000200000001</v>
+        <v>99.25</v>
       </c>
       <c r="E62" t="n">
-        <v>450.299988</v>
+        <v>448</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1931</v>
+        <v>5.1366</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0795</v>
+        <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>7641.160156</v>
+        <v>7674.370117</v>
       </c>
       <c r="I62" t="n">
-        <v>26067.169922</v>
+        <v>26180.460938</v>
       </c>
       <c r="J62" t="n">
-        <v>52759.210938</v>
+        <v>53277.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4640.700195</v>
+        <v>4624.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>87.25</v>
+        <v>87.05999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>94.05999799999999</v>
+        <v>94.389999</v>
       </c>
       <c r="N62" t="n">
-        <v>1231.75</v>
+        <v>1225</v>
       </c>
       <c r="O62" t="n">
-        <v>502</v>
+        <v>483.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.658459</v>
+        <v>-3.914216</v>
       </c>
       <c r="Q62" t="n">
         <v>-5.725062</v>
       </c>
       <c r="R62" t="n">
-        <v>-6.815849</v>
+        <v>-7.459207</v>
       </c>
       <c r="S62" t="n">
-        <v>5.114492</v>
+        <v>4.577601</v>
       </c>
       <c r="T62" t="n">
-        <v>2.264622</v>
+        <v>1.152002</v>
       </c>
       <c r="U62" t="n">
-        <v>3.95946</v>
+        <v>2.600007</v>
       </c>
       <c r="V62" t="n">
-        <v>2.021971</v>
+        <v>2.465378</v>
       </c>
       <c r="W62" t="n">
-        <v>2.732421</v>
+        <v>3.178908</v>
       </c>
       <c r="X62" t="n">
-        <v>0.522396</v>
+        <v>1.508964</v>
       </c>
       <c r="Y62" t="n">
-        <v>14.610656</v>
+        <v>14.200686</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.047126</v>
+        <v>2.822723</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.371943</v>
+        <v>4.738123</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.098123</v>
+        <v>4.522184</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.896767</v>
+        <v>9.756098</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -601,9 +601,7 @@
       <c r="K2" t="n">
         <v>1815</v>
       </c>
-      <c r="L2" t="n">
-        <v>68.5</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>72.989998</v>
       </c>
@@ -662,9 +660,7 @@
       <c r="K3" t="n">
         <v>1755.300049</v>
       </c>
-      <c r="L3" t="n">
-        <v>75.029999</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>78.519997</v>
       </c>
@@ -704,9 +700,7 @@
       <c r="Y3" t="n">
         <v>-3.289254</v>
       </c>
-      <c r="Z3" t="n">
-        <v>9.532845</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>7.576379</v>
       </c>
@@ -751,9 +745,7 @@
       <c r="K4" t="n">
         <v>1783</v>
       </c>
-      <c r="L4" t="n">
-        <v>83.56999999999999</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>84.379997</v>
       </c>
@@ -793,9 +785,7 @@
       <c r="Y4" t="n">
         <v>1.578075</v>
       </c>
-      <c r="Z4" t="n">
-        <v>11.382115</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>7.463068</v>
       </c>
@@ -840,9 +830,7 @@
       <c r="K5" t="n">
         <v>1773.599976</v>
       </c>
-      <c r="L5" t="n">
-        <v>66.18000000000001</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>70.56999999999999</v>
       </c>
@@ -882,9 +870,7 @@
       <c r="Y5" t="n">
         <v>-0.527203</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-20.808902</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>-16.366435</v>
       </c>
@@ -929,9 +915,7 @@
       <c r="K6" t="n">
         <v>1827.5</v>
       </c>
-      <c r="L6" t="n">
-        <v>75.209999</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>77.779999</v>
       </c>
@@ -971,9 +955,7 @@
       <c r="Y6" t="n">
         <v>3.039018</v>
       </c>
-      <c r="Z6" t="n">
-        <v>13.644604</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>10.216805</v>
       </c>
@@ -1018,9 +1000,7 @@
       <c r="K7" t="n">
         <v>1795</v>
       </c>
-      <c r="L7" t="n">
-        <v>88.150002</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>91.209999</v>
       </c>
@@ -1060,9 +1040,7 @@
       <c r="Y7" t="n">
         <v>-1.778386</v>
       </c>
-      <c r="Z7" t="n">
-        <v>17.205162</v>
-      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>17.26665</v>
       </c>
@@ -1107,9 +1085,7 @@
       <c r="K8" t="n">
         <v>1899.400024</v>
       </c>
-      <c r="L8" t="n">
-        <v>95.720001</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>100.989998</v>
       </c>
@@ -1149,9 +1125,7 @@
       <c r="Y8" t="n">
         <v>5.816157</v>
       </c>
-      <c r="Z8" t="n">
-        <v>8.587634</v>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>10.722507</v>
       </c>
@@ -1196,9 +1170,7 @@
       <c r="K9" t="n">
         <v>1949.199951</v>
       </c>
-      <c r="L9" t="n">
-        <v>100.279999</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>107.910004</v>
       </c>
@@ -1238,9 +1210,7 @@
       <c r="Y9" t="n">
         <v>2.621877</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.763892</v>
-      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
         <v>6.852169</v>
       </c>
@@ -1285,9 +1255,7 @@
       <c r="K10" t="n">
         <v>1909.300049</v>
       </c>
-      <c r="L10" t="n">
-        <v>104.690002</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>109.339996</v>
       </c>
@@ -1327,9 +1295,7 @@
       <c r="Y10" t="n">
         <v>-2.046989</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4.39769</v>
-      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>1.325172</v>
       </c>
@@ -1374,9 +1340,7 @@
       <c r="K11" t="n">
         <v>1842.699951</v>
       </c>
-      <c r="L11" t="n">
-        <v>114.669998</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>122.839996</v>
       </c>
@@ -1416,9 +1380,7 @@
       <c r="Y11" t="n">
         <v>-3.488194</v>
       </c>
-      <c r="Z11" t="n">
-        <v>9.532902</v>
-      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
         <v>12.346809</v>
       </c>
@@ -1463,9 +1425,7 @@
       <c r="K12" t="n">
         <v>1804.099976</v>
       </c>
-      <c r="L12" t="n">
-        <v>105.760002</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>114.809998</v>
       </c>
@@ -1505,9 +1465,7 @@
       <c r="Y12" t="n">
         <v>-2.094751</v>
       </c>
-      <c r="Z12" t="n">
-        <v>-7.77012</v>
-      </c>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
         <v>-6.536958</v>
       </c>
@@ -1552,9 +1510,7 @@
       <c r="K13" t="n">
         <v>1762.900024</v>
       </c>
-      <c r="L13" t="n">
-        <v>98.620003</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>110.010002</v>
       </c>
@@ -1594,9 +1550,7 @@
       <c r="Y13" t="n">
         <v>-2.283684</v>
       </c>
-      <c r="Z13" t="n">
-        <v>-6.751134</v>
-      </c>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
         <v>-4.180817</v>
       </c>
@@ -1641,9 +1595,7 @@
       <c r="K14" t="n">
         <v>1712.800049</v>
       </c>
-      <c r="L14" t="n">
-        <v>89.550003</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>96.489998</v>
       </c>
@@ -1683,9 +1635,7 @@
       <c r="Y14" t="n">
         <v>-2.841907</v>
       </c>
-      <c r="Z14" t="n">
-        <v>-9.196916999999999</v>
-      </c>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
         <v>-12.289795</v>
       </c>
@@ -1730,9 +1680,7 @@
       <c r="K15" t="n">
         <v>1662.400024</v>
       </c>
-      <c r="L15" t="n">
-        <v>79.489998</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>87.959999</v>
       </c>
@@ -1772,9 +1720,7 @@
       <c r="Y15" t="n">
         <v>-2.942552</v>
       </c>
-      <c r="Z15" t="n">
-        <v>-11.233953</v>
-      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>-8.840293000000001</v>
       </c>
@@ -1819,9 +1765,7 @@
       <c r="K16" t="n">
         <v>1635.900024</v>
       </c>
-      <c r="L16" t="n">
-        <v>86.529999</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>94.83000199999999</v>
       </c>
@@ -1861,9 +1805,7 @@
       <c r="Y16" t="n">
         <v>-1.594081</v>
       </c>
-      <c r="Z16" t="n">
-        <v>8.856460999999999</v>
-      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
         <v>7.810372</v>
       </c>
@@ -1908,9 +1850,7 @@
       <c r="K17" t="n">
         <v>1746</v>
       </c>
-      <c r="L17" t="n">
-        <v>80.550003</v>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>85.43000000000001</v>
       </c>
@@ -1950,9 +1890,7 @@
       <c r="Y17" t="n">
         <v>6.730239</v>
       </c>
-      <c r="Z17" t="n">
-        <v>-6.910893</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
         <v>-9.912476</v>
       </c>
@@ -1997,9 +1935,7 @@
       <c r="K18" t="n">
         <v>1819.699951</v>
       </c>
-      <c r="L18" t="n">
-        <v>80.260002</v>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>85.910004</v>
       </c>
@@ -2039,9 +1975,7 @@
       <c r="Y18" t="n">
         <v>4.221074</v>
       </c>
-      <c r="Z18" t="n">
-        <v>-0.360026</v>
-      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
         <v>0.561867</v>
       </c>
@@ -2086,9 +2020,7 @@
       <c r="K19" t="n">
         <v>1929.5</v>
       </c>
-      <c r="L19" t="n">
-        <v>78.870003</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>84.489998</v>
       </c>
@@ -2128,9 +2060,7 @@
       <c r="Y19" t="n">
         <v>6.033964</v>
       </c>
-      <c r="Z19" t="n">
-        <v>-1.731871</v>
-      </c>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
         <v>-1.652899</v>
       </c>
@@ -2175,9 +2105,7 @@
       <c r="K20" t="n">
         <v>1828.900024</v>
       </c>
-      <c r="L20" t="n">
-        <v>77.050003</v>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>83.889999</v>
       </c>
@@ -2217,9 +2145,7 @@
       <c r="Y20" t="n">
         <v>-5.213785</v>
       </c>
-      <c r="Z20" t="n">
-        <v>-2.307594</v>
-      </c>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
         <v>-0.710141</v>
       </c>
@@ -2264,9 +2190,7 @@
       <c r="K21" t="n">
         <v>1969</v>
       </c>
-      <c r="L21" t="n">
-        <v>75.66999800000001</v>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>79.769997</v>
       </c>
@@ -2306,9 +2230,7 @@
       <c r="Y21" t="n">
         <v>7.660341</v>
       </c>
-      <c r="Z21" t="n">
-        <v>-1.791051</v>
-      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
         <v>-4.911197</v>
       </c>
@@ -2353,9 +2275,7 @@
       <c r="K22" t="n">
         <v>1990.099976</v>
       </c>
-      <c r="L22" t="n">
-        <v>76.779999</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>79.540001</v>
       </c>
@@ -2395,9 +2315,7 @@
       <c r="Y22" t="n">
         <v>1.071609</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.466897</v>
-      </c>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
         <v>-0.288324</v>
       </c>
@@ -2442,9 +2360,7 @@
       <c r="K23" t="n">
         <v>1963.900024</v>
       </c>
-      <c r="L23" t="n">
-        <v>68.089996</v>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>72.660004</v>
       </c>
@@ -2484,9 +2400,7 @@
       <c r="Y23" t="n">
         <v>-1.316514</v>
       </c>
-      <c r="Z23" t="n">
-        <v>-11.318055</v>
-      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
         <v>-8.649732</v>
       </c>
@@ -2531,9 +2445,7 @@
       <c r="K24" t="n">
         <v>1921.099976</v>
       </c>
-      <c r="L24" t="n">
-        <v>70.639999</v>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>74.900002</v>
       </c>
@@ -2573,9 +2485,7 @@
       <c r="Y24" t="n">
         <v>-2.179339</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.745048</v>
-      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
         <v>3.082849</v>
       </c>
@@ -2620,9 +2530,7 @@
       <c r="K25" t="n">
         <v>1970.5</v>
       </c>
-      <c r="L25" t="n">
-        <v>81.800003</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>85.55999799999999</v>
       </c>
@@ -2662,9 +2570,7 @@
       <c r="Y25" t="n">
         <v>2.571445</v>
       </c>
-      <c r="Z25" t="n">
-        <v>15.79842</v>
-      </c>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
         <v>14.232304</v>
       </c>
@@ -2709,9 +2615,7 @@
       <c r="K26" t="n">
         <v>1938.199951</v>
       </c>
-      <c r="L26" t="n">
-        <v>83.629997</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>86.860001</v>
       </c>
@@ -2751,9 +2655,7 @@
       <c r="Y26" t="n">
         <v>-1.63918</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2.237157</v>
-      </c>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
         <v>1.519405</v>
       </c>
@@ -2798,9 +2700,7 @@
       <c r="K27" t="n">
         <v>1848.099976</v>
       </c>
-      <c r="L27" t="n">
-        <v>90.790001</v>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>95.30999799999999</v>
       </c>
@@ -2840,9 +2740,7 @@
       <c r="Y27" t="n">
         <v>-4.648642</v>
       </c>
-      <c r="Z27" t="n">
-        <v>8.561526000000001</v>
-      </c>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
         <v>9.728294999999999</v>
       </c>
@@ -2887,9 +2785,7 @@
       <c r="K28" t="n">
         <v>1985.199951</v>
       </c>
-      <c r="L28" t="n">
-        <v>81.019997</v>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>87.410004</v>
       </c>
@@ -2929,9 +2825,7 @@
       <c r="Y28" t="n">
         <v>7.418429</v>
       </c>
-      <c r="Z28" t="n">
-        <v>-10.761102</v>
-      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
         <v>-8.288736</v>
       </c>
@@ -2976,9 +2870,7 @@
       <c r="K29" t="n">
         <v>2038.099976</v>
       </c>
-      <c r="L29" t="n">
-        <v>75.959999</v>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>82.83000199999999</v>
       </c>
@@ -3018,9 +2910,7 @@
       <c r="Y29" t="n">
         <v>2.66472</v>
       </c>
-      <c r="Z29" t="n">
-        <v>-6.245369</v>
-      </c>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
         <v>-5.239677</v>
       </c>
@@ -3065,9 +2955,7 @@
       <c r="K30" t="n">
         <v>2062.399902</v>
       </c>
-      <c r="L30" t="n">
-        <v>71.650002</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>77.040001</v>
       </c>
@@ -3107,9 +2995,7 @@
       <c r="Y30" t="n">
         <v>1.192283</v>
       </c>
-      <c r="Z30" t="n">
-        <v>-5.674036</v>
-      </c>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
         <v>-6.990222</v>
       </c>
@@ -3154,9 +3040,7 @@
       <c r="K31" t="n">
         <v>2048.399902</v>
       </c>
-      <c r="L31" t="n">
-        <v>75.849998</v>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>81.709999</v>
       </c>
@@ -3196,9 +3080,7 @@
       <c r="Y31" t="n">
         <v>-0.678821</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5.861824</v>
-      </c>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
         <v>6.061784</v>
       </c>
@@ -3243,9 +3125,7 @@
       <c r="K32" t="n">
         <v>2045.699951</v>
       </c>
-      <c r="L32" t="n">
-        <v>78.260002</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>83.620003</v>
       </c>
@@ -3285,9 +3165,7 @@
       <c r="Y32" t="n">
         <v>-0.131808</v>
       </c>
-      <c r="Z32" t="n">
-        <v>3.177329</v>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
         <v>2.33754</v>
       </c>
@@ -3332,9 +3210,7 @@
       <c r="K33" t="n">
         <v>2217.399902</v>
       </c>
-      <c r="L33" t="n">
-        <v>83.16999800000001</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>87.480003</v>
       </c>
@@ -3374,9 +3250,7 @@
       <c r="Y33" t="n">
         <v>8.393212999999999</v>
       </c>
-      <c r="Z33" t="n">
-        <v>6.273953</v>
-      </c>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
         <v>4.616121</v>
       </c>
@@ -3421,9 +3295,7 @@
       <c r="K34" t="n">
         <v>2291.399902</v>
       </c>
-      <c r="L34" t="n">
-        <v>81.93000000000001</v>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>87.860001</v>
       </c>
@@ -3463,9 +3335,7 @@
       <c r="Y34" t="n">
         <v>3.337242</v>
       </c>
-      <c r="Z34" t="n">
-        <v>-1.49092</v>
-      </c>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
         <v>0.434382</v>
       </c>
@@ -3510,9 +3380,7 @@
       <c r="K35" t="n">
         <v>2322.899902</v>
       </c>
-      <c r="L35" t="n">
-        <v>76.989998</v>
-      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>81.620003</v>
       </c>
@@ -3552,9 +3420,7 @@
       <c r="Y35" t="n">
         <v>1.374705</v>
       </c>
-      <c r="Z35" t="n">
-        <v>-6.02954</v>
-      </c>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
         <v>-7.102206</v>
       </c>
@@ -3599,9 +3465,7 @@
       <c r="K36" t="n">
         <v>2327.699951</v>
       </c>
-      <c r="L36" t="n">
-        <v>81.540001</v>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>86.410004</v>
       </c>
@@ -3641,9 +3505,7 @@
       <c r="Y36" t="n">
         <v>0.20664</v>
       </c>
-      <c r="Z36" t="n">
-        <v>5.909863</v>
-      </c>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
         <v>5.868661</v>
       </c>
@@ -3688,9 +3550,7 @@
       <c r="K37" t="n">
         <v>2426.5</v>
       </c>
-      <c r="L37" t="n">
-        <v>77.910004</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>80.720001</v>
       </c>
@@ -3730,9 +3590,7 @@
       <c r="Y37" t="n">
         <v>4.244535</v>
       </c>
-      <c r="Z37" t="n">
-        <v>-4.451799</v>
-      </c>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
         <v>-6.584889</v>
       </c>
@@ -3777,9 +3635,7 @@
       <c r="K38" t="n">
         <v>2493.800049</v>
       </c>
-      <c r="L38" t="n">
-        <v>73.550003</v>
-      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>78.800003</v>
       </c>
@@ -3819,9 +3675,7 @@
       <c r="Y38" t="n">
         <v>2.773544</v>
       </c>
-      <c r="Z38" t="n">
-        <v>-5.596201</v>
-      </c>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
         <v>-2.37859</v>
       </c>
@@ -3866,9 +3720,7 @@
       <c r="K39" t="n">
         <v>2636.100098</v>
       </c>
-      <c r="L39" t="n">
-        <v>68.16999800000001</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>71.769997</v>
       </c>
@@ -3908,9 +3760,7 @@
       <c r="Y39" t="n">
         <v>5.706153</v>
       </c>
-      <c r="Z39" t="n">
-        <v>-7.314758</v>
-      </c>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
         <v>-8.921328000000001</v>
       </c>
@@ -3955,9 +3805,7 @@
       <c r="K40" t="n">
         <v>2738.300049</v>
       </c>
-      <c r="L40" t="n">
-        <v>69.260002</v>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>73.160004</v>
       </c>
@@ -3997,9 +3845,7 @@
       <c r="Y40" t="n">
         <v>3.876937</v>
       </c>
-      <c r="Z40" t="n">
-        <v>1.59895</v>
-      </c>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
         <v>1.936752</v>
       </c>
@@ -4044,9 +3890,7 @@
       <c r="K41" t="n">
         <v>2657</v>
       </c>
-      <c r="L41" t="n">
-        <v>68</v>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>72.94000200000001</v>
       </c>
@@ -4086,9 +3930,7 @@
       <c r="Y41" t="n">
         <v>-2.968997</v>
       </c>
-      <c r="Z41" t="n">
-        <v>-1.819235</v>
-      </c>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
         <v>-0.300712</v>
       </c>
@@ -4133,9 +3975,7 @@
       <c r="K42" t="n">
         <v>2629.199951</v>
       </c>
-      <c r="L42" t="n">
-        <v>71.720001</v>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>74.639999</v>
       </c>
@@ -4175,9 +4015,7 @@
       <c r="Y42" t="n">
         <v>-1.046295</v>
       </c>
-      <c r="Z42" t="n">
-        <v>5.47059</v>
-      </c>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="n">
         <v>2.330678</v>
       </c>
@@ -4222,9 +4060,7 @@
       <c r="K43" t="n">
         <v>2812.5</v>
       </c>
-      <c r="L43" t="n">
-        <v>72.529999</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>76.760002</v>
       </c>
@@ -4264,9 +4100,7 @@
       <c r="Y43" t="n">
         <v>6.971704</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1.129389</v>
-      </c>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
         <v>2.840304</v>
       </c>
@@ -4311,9 +4145,7 @@
       <c r="K44" t="n">
         <v>2836.800049</v>
       </c>
-      <c r="L44" t="n">
-        <v>69.760002</v>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>73.18000000000001</v>
       </c>
@@ -4353,9 +4185,7 @@
       <c r="Y44" t="n">
         <v>0.864002</v>
       </c>
-      <c r="Z44" t="n">
-        <v>-3.819105</v>
-      </c>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="n">
         <v>-4.66389</v>
       </c>
@@ -4400,9 +4230,7 @@
       <c r="K45" t="n">
         <v>3122.800049</v>
       </c>
-      <c r="L45" t="n">
-        <v>71.480003</v>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>74.739998</v>
       </c>
@@ -4442,9 +4270,7 @@
       <c r="Y45" t="n">
         <v>10.081782</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.465598</v>
-      </c>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="n">
         <v>2.131727</v>
       </c>
@@ -4489,9 +4315,7 @@
       <c r="K46" t="n">
         <v>3305</v>
       </c>
-      <c r="L46" t="n">
-        <v>58.209999</v>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>63.119999</v>
       </c>
@@ -4531,9 +4355,7 @@
       <c r="Y46" t="n">
         <v>5.834506</v>
       </c>
-      <c r="Z46" t="n">
-        <v>-18.564639</v>
-      </c>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="n">
         <v>-15.547229</v>
       </c>
@@ -4578,9 +4400,7 @@
       <c r="K47" t="n">
         <v>3288.899902</v>
       </c>
-      <c r="L47" t="n">
-        <v>60.790001</v>
-      </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>63.900002</v>
       </c>
@@ -4620,9 +4440,7 @@
       <c r="Y47" t="n">
         <v>-0.487144</v>
       </c>
-      <c r="Z47" t="n">
-        <v>4.432231</v>
-      </c>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
         <v>1.235746</v>
       </c>
@@ -4667,9 +4485,7 @@
       <c r="K48" t="n">
         <v>3294.399902</v>
       </c>
-      <c r="L48" t="n">
-        <v>65.110001</v>
-      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>67.610001</v>
       </c>
@@ -4709,9 +4525,7 @@
       <c r="Y48" t="n">
         <v>0.167229</v>
       </c>
-      <c r="Z48" t="n">
-        <v>7.106431</v>
-      </c>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="n">
         <v>5.805945</v>
       </c>
@@ -4756,9 +4570,7 @@
       <c r="K49" t="n">
         <v>3293.199951</v>
       </c>
-      <c r="L49" t="n">
-        <v>69.260002</v>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>72.529999</v>
       </c>
@@ -4798,9 +4610,7 @@
       <c r="Y49" t="n">
         <v>-0.036424</v>
       </c>
-      <c r="Z49" t="n">
-        <v>6.373831</v>
-      </c>
+      <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="n">
         <v>7.277027</v>
       </c>
@@ -4845,9 +4655,7 @@
       <c r="K50" t="n">
         <v>3473.699951</v>
       </c>
-      <c r="L50" t="n">
-        <v>64.010002</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>68.120003</v>
       </c>
@@ -4887,9 +4695,7 @@
       <c r="Y50" t="n">
         <v>5.480991</v>
       </c>
-      <c r="Z50" t="n">
-        <v>-7.580133</v>
-      </c>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="n">
         <v>-6.080237</v>
       </c>
@@ -4934,9 +4740,7 @@
       <c r="K51" t="n">
         <v>3840.800049</v>
       </c>
-      <c r="L51" t="n">
-        <v>62.369999</v>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>67.019997</v>
       </c>
@@ -4976,9 +4780,7 @@
       <c r="Y51" t="n">
         <v>10.567985</v>
       </c>
-      <c r="Z51" t="n">
-        <v>-2.562105</v>
-      </c>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
         <v>-1.614806</v>
       </c>
@@ -5023,9 +4825,7 @@
       <c r="K52" t="n">
         <v>3982.199951</v>
       </c>
-      <c r="L52" t="n">
-        <v>60.98</v>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>65.06999999999999</v>
       </c>
@@ -5065,9 +4865,7 @@
       <c r="Y52" t="n">
         <v>3.681522</v>
       </c>
-      <c r="Z52" t="n">
-        <v>-2.228635</v>
-      </c>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="n">
         <v>-2.909575</v>
       </c>
@@ -5112,9 +4910,7 @@
       <c r="K53" t="n">
         <v>4218.299805</v>
       </c>
-      <c r="L53" t="n">
-        <v>58.549999</v>
-      </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>63.200001</v>
       </c>
@@ -5154,9 +4950,7 @@
       <c r="Y53" t="n">
         <v>5.92888</v>
       </c>
-      <c r="Z53" t="n">
-        <v>-3.984914</v>
-      </c>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="n">
         <v>-2.873827</v>
       </c>
@@ -5201,9 +4995,7 @@
       <c r="K54" t="n">
         <v>4325.600098</v>
       </c>
-      <c r="L54" t="n">
-        <v>57.419998</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>60.849998</v>
       </c>
@@ -5243,9 +5035,7 @@
       <c r="Y54" t="n">
         <v>2.543686</v>
       </c>
-      <c r="Z54" t="n">
-        <v>-1.929976</v>
-      </c>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="n">
         <v>-3.718358</v>
       </c>
@@ -5290,9 +5080,7 @@
       <c r="K55" t="n">
         <v>4713.899902</v>
       </c>
-      <c r="L55" t="n">
-        <v>65.209999</v>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>70.69000200000001</v>
       </c>
@@ -5332,9 +5120,7 @@
       <c r="Y55" t="n">
         <v>8.976785</v>
       </c>
-      <c r="Z55" t="n">
-        <v>13.566704</v>
-      </c>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="n">
         <v>16.170919</v>
       </c>
@@ -5379,9 +5165,7 @@
       <c r="K56" t="n">
         <v>5230.5</v>
       </c>
-      <c r="L56" t="n">
-        <v>67.019997</v>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>72.480003</v>
       </c>
@@ -5421,9 +5205,7 @@
       <c r="Y56" t="n">
         <v>10.959081</v>
       </c>
-      <c r="Z56" t="n">
-        <v>2.775644</v>
-      </c>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="n">
         <v>2.532184</v>
       </c>
@@ -5468,9 +5250,7 @@
       <c r="K57" t="n">
         <v>4647.600098</v>
       </c>
-      <c r="L57" t="n">
-        <v>101.379997</v>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>118.349998</v>
       </c>
@@ -5510,9 +5290,7 @@
       <c r="Y57" t="n">
         <v>-11.144248</v>
       </c>
-      <c r="Z57" t="n">
-        <v>51.268282</v>
-      </c>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="n">
         <v>63.286414</v>
       </c>
@@ -5557,9 +5335,7 @@
       <c r="K58" t="n">
         <v>4614.700195</v>
       </c>
-      <c r="L58" t="n">
-        <v>105.07</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>114.010002</v>
       </c>
@@ -5599,9 +5375,7 @@
       <c r="Y58" t="n">
         <v>-0.70789</v>
       </c>
-      <c r="Z58" t="n">
-        <v>3.639774</v>
-      </c>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="n">
         <v>-3.667086</v>
       </c>
@@ -5646,9 +5420,7 @@
       <c r="K59" t="n">
         <v>4560.5</v>
       </c>
-      <c r="L59" t="n">
-        <v>87.360001</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>92.050003</v>
       </c>
@@ -5688,9 +5460,7 @@
       <c r="Y59" t="n">
         <v>-1.174512</v>
       </c>
-      <c r="Z59" t="n">
-        <v>-16.855429</v>
-      </c>
+      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="n">
         <v>-19.261467</v>
       </c>
@@ -5735,9 +5505,7 @@
       <c r="K60" t="n">
         <v>4022.899902</v>
       </c>
-      <c r="L60" t="n">
-        <v>69.5</v>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>72.91999800000001</v>
       </c>
@@ -5777,9 +5545,7 @@
       <c r="Y60" t="n">
         <v>-11.788183</v>
       </c>
-      <c r="Z60" t="n">
-        <v>-20.44414</v>
-      </c>
+      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="n">
         <v>-20.782188</v>
       </c>
@@ -5824,9 +5590,7 @@
       <c r="K61" t="n">
         <v>4049.100098</v>
       </c>
-      <c r="L61" t="n">
-        <v>84.66999800000001</v>
-      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>90.120003</v>
       </c>
@@ -5866,9 +5630,7 @@
       <c r="Y61" t="n">
         <v>0.651276</v>
       </c>
-      <c r="Z61" t="n">
-        <v>21.827335</v>
-      </c>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="n">
         <v>23.5875</v>
       </c>
@@ -5887,13 +5649,13 @@
         <v>171031.734375</v>
       </c>
       <c r="C62" t="n">
-        <v>165</v>
+        <v>168.330002</v>
       </c>
       <c r="D62" t="n">
-        <v>99.25</v>
+        <v>102.25</v>
       </c>
       <c r="E62" t="n">
-        <v>448</v>
+        <v>445.850006</v>
       </c>
       <c r="F62" t="n">
         <v>5.1366</v>
@@ -5911,7 +5673,7 @@
         <v>53277.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4624.100098</v>
+        <v>4680.600098</v>
       </c>
       <c r="L62" t="n">
         <v>87.05999799999999</v>
@@ -5920,22 +5682,22 @@
         <v>94.389999</v>
       </c>
       <c r="N62" t="n">
-        <v>1225</v>
+        <v>1239.5</v>
       </c>
       <c r="O62" t="n">
-        <v>483.75</v>
+        <v>508.5</v>
       </c>
       <c r="P62" t="n">
         <v>-3.914216</v>
       </c>
       <c r="Q62" t="n">
-        <v>-5.725062</v>
+        <v>-3.822422</v>
       </c>
       <c r="R62" t="n">
-        <v>-7.459207</v>
+        <v>-4.662005</v>
       </c>
       <c r="S62" t="n">
-        <v>4.577601</v>
+        <v>4.075723</v>
       </c>
       <c r="T62" t="n">
         <v>1.152002</v>
@@ -5953,19 +5715,17 @@
         <v>1.508964</v>
       </c>
       <c r="Y62" t="n">
-        <v>14.200686</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>2.822723</v>
-      </c>
+        <v>15.596058</v>
+      </c>
+      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="n">
         <v>4.738123</v>
       </c>
       <c r="AB62" t="n">
-        <v>4.522184</v>
+        <v>5.759386</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.756098</v>
+        <v>15.371526</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -601,7 +601,9 @@
       <c r="K2" t="n">
         <v>1815</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>68.5</v>
+      </c>
       <c r="M2" t="n">
         <v>72.989998</v>
       </c>
@@ -660,7 +662,9 @@
       <c r="K3" t="n">
         <v>1755.300049</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>75.029999</v>
+      </c>
       <c r="M3" t="n">
         <v>78.519997</v>
       </c>
@@ -700,7 +704,9 @@
       <c r="Y3" t="n">
         <v>-3.289254</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>9.532845</v>
+      </c>
       <c r="AA3" t="n">
         <v>7.576379</v>
       </c>
@@ -745,7 +751,9 @@
       <c r="K4" t="n">
         <v>1783</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>83.56999999999999</v>
+      </c>
       <c r="M4" t="n">
         <v>84.379997</v>
       </c>
@@ -785,7 +793,9 @@
       <c r="Y4" t="n">
         <v>1.578075</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>11.382115</v>
+      </c>
       <c r="AA4" t="n">
         <v>7.463068</v>
       </c>
@@ -830,7 +840,9 @@
       <c r="K5" t="n">
         <v>1773.599976</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>66.18000000000001</v>
+      </c>
       <c r="M5" t="n">
         <v>70.56999999999999</v>
       </c>
@@ -870,7 +882,9 @@
       <c r="Y5" t="n">
         <v>-0.527203</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-20.808902</v>
+      </c>
       <c r="AA5" t="n">
         <v>-16.366435</v>
       </c>
@@ -915,7 +929,9 @@
       <c r="K6" t="n">
         <v>1827.5</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>75.209999</v>
+      </c>
       <c r="M6" t="n">
         <v>77.779999</v>
       </c>
@@ -955,7 +971,9 @@
       <c r="Y6" t="n">
         <v>3.039018</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>13.644604</v>
+      </c>
       <c r="AA6" t="n">
         <v>10.216805</v>
       </c>
@@ -1000,7 +1018,9 @@
       <c r="K7" t="n">
         <v>1795</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>88.150002</v>
+      </c>
       <c r="M7" t="n">
         <v>91.209999</v>
       </c>
@@ -1040,7 +1060,9 @@
       <c r="Y7" t="n">
         <v>-1.778386</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>17.205162</v>
+      </c>
       <c r="AA7" t="n">
         <v>17.26665</v>
       </c>
@@ -1085,7 +1107,9 @@
       <c r="K8" t="n">
         <v>1899.400024</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>95.720001</v>
+      </c>
       <c r="M8" t="n">
         <v>100.989998</v>
       </c>
@@ -1125,7 +1149,9 @@
       <c r="Y8" t="n">
         <v>5.816157</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>8.587634</v>
+      </c>
       <c r="AA8" t="n">
         <v>10.722507</v>
       </c>
@@ -1170,7 +1196,9 @@
       <c r="K9" t="n">
         <v>1949.199951</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>100.279999</v>
+      </c>
       <c r="M9" t="n">
         <v>107.910004</v>
       </c>
@@ -1210,7 +1238,9 @@
       <c r="Y9" t="n">
         <v>2.621877</v>
       </c>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>4.763892</v>
+      </c>
       <c r="AA9" t="n">
         <v>6.852169</v>
       </c>
@@ -1255,7 +1285,9 @@
       <c r="K10" t="n">
         <v>1909.300049</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>104.690002</v>
+      </c>
       <c r="M10" t="n">
         <v>109.339996</v>
       </c>
@@ -1295,7 +1327,9 @@
       <c r="Y10" t="n">
         <v>-2.046989</v>
       </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>4.39769</v>
+      </c>
       <c r="AA10" t="n">
         <v>1.325172</v>
       </c>
@@ -1340,7 +1374,9 @@
       <c r="K11" t="n">
         <v>1842.699951</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>114.669998</v>
+      </c>
       <c r="M11" t="n">
         <v>122.839996</v>
       </c>
@@ -1380,7 +1416,9 @@
       <c r="Y11" t="n">
         <v>-3.488194</v>
       </c>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>9.532902</v>
+      </c>
       <c r="AA11" t="n">
         <v>12.346809</v>
       </c>
@@ -1425,7 +1463,9 @@
       <c r="K12" t="n">
         <v>1804.099976</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>105.760002</v>
+      </c>
       <c r="M12" t="n">
         <v>114.809998</v>
       </c>
@@ -1465,7 +1505,9 @@
       <c r="Y12" t="n">
         <v>-2.094751</v>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>-7.77012</v>
+      </c>
       <c r="AA12" t="n">
         <v>-6.536958</v>
       </c>
@@ -1510,7 +1552,9 @@
       <c r="K13" t="n">
         <v>1762.900024</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>98.620003</v>
+      </c>
       <c r="M13" t="n">
         <v>110.010002</v>
       </c>
@@ -1550,7 +1594,9 @@
       <c r="Y13" t="n">
         <v>-2.283684</v>
       </c>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>-6.751134</v>
+      </c>
       <c r="AA13" t="n">
         <v>-4.180817</v>
       </c>
@@ -1595,7 +1641,9 @@
       <c r="K14" t="n">
         <v>1712.800049</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>89.550003</v>
+      </c>
       <c r="M14" t="n">
         <v>96.489998</v>
       </c>
@@ -1635,7 +1683,9 @@
       <c r="Y14" t="n">
         <v>-2.841907</v>
       </c>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>-9.196916999999999</v>
+      </c>
       <c r="AA14" t="n">
         <v>-12.289795</v>
       </c>
@@ -1680,7 +1730,9 @@
       <c r="K15" t="n">
         <v>1662.400024</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>79.489998</v>
+      </c>
       <c r="M15" t="n">
         <v>87.959999</v>
       </c>
@@ -1720,7 +1772,9 @@
       <c r="Y15" t="n">
         <v>-2.942552</v>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>-11.233953</v>
+      </c>
       <c r="AA15" t="n">
         <v>-8.840293000000001</v>
       </c>
@@ -1765,7 +1819,9 @@
       <c r="K16" t="n">
         <v>1635.900024</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>86.529999</v>
+      </c>
       <c r="M16" t="n">
         <v>94.83000199999999</v>
       </c>
@@ -1805,7 +1861,9 @@
       <c r="Y16" t="n">
         <v>-1.594081</v>
       </c>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>8.856460999999999</v>
+      </c>
       <c r="AA16" t="n">
         <v>7.810372</v>
       </c>
@@ -1850,7 +1908,9 @@
       <c r="K17" t="n">
         <v>1746</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>80.550003</v>
+      </c>
       <c r="M17" t="n">
         <v>85.43000000000001</v>
       </c>
@@ -1890,7 +1950,9 @@
       <c r="Y17" t="n">
         <v>6.730239</v>
       </c>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>-6.910893</v>
+      </c>
       <c r="AA17" t="n">
         <v>-9.912476</v>
       </c>
@@ -1935,7 +1997,9 @@
       <c r="K18" t="n">
         <v>1819.699951</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>80.260002</v>
+      </c>
       <c r="M18" t="n">
         <v>85.910004</v>
       </c>
@@ -1975,7 +2039,9 @@
       <c r="Y18" t="n">
         <v>4.221074</v>
       </c>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>-0.360026</v>
+      </c>
       <c r="AA18" t="n">
         <v>0.561867</v>
       </c>
@@ -2020,7 +2086,9 @@
       <c r="K19" t="n">
         <v>1929.5</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>78.870003</v>
+      </c>
       <c r="M19" t="n">
         <v>84.489998</v>
       </c>
@@ -2060,7 +2128,9 @@
       <c r="Y19" t="n">
         <v>6.033964</v>
       </c>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>-1.731871</v>
+      </c>
       <c r="AA19" t="n">
         <v>-1.652899</v>
       </c>
@@ -2105,7 +2175,9 @@
       <c r="K20" t="n">
         <v>1828.900024</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>77.050003</v>
+      </c>
       <c r="M20" t="n">
         <v>83.889999</v>
       </c>
@@ -2145,7 +2217,9 @@
       <c r="Y20" t="n">
         <v>-5.213785</v>
       </c>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>-2.307594</v>
+      </c>
       <c r="AA20" t="n">
         <v>-0.710141</v>
       </c>
@@ -2190,7 +2264,9 @@
       <c r="K21" t="n">
         <v>1969</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>75.66999800000001</v>
+      </c>
       <c r="M21" t="n">
         <v>79.769997</v>
       </c>
@@ -2230,7 +2306,9 @@
       <c r="Y21" t="n">
         <v>7.660341</v>
       </c>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>-1.791051</v>
+      </c>
       <c r="AA21" t="n">
         <v>-4.911197</v>
       </c>
@@ -2275,7 +2353,9 @@
       <c r="K22" t="n">
         <v>1990.099976</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>76.779999</v>
+      </c>
       <c r="M22" t="n">
         <v>79.540001</v>
       </c>
@@ -2315,7 +2395,9 @@
       <c r="Y22" t="n">
         <v>1.071609</v>
       </c>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>1.466897</v>
+      </c>
       <c r="AA22" t="n">
         <v>-0.288324</v>
       </c>
@@ -2360,7 +2442,9 @@
       <c r="K23" t="n">
         <v>1963.900024</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>68.089996</v>
+      </c>
       <c r="M23" t="n">
         <v>72.660004</v>
       </c>
@@ -2400,7 +2484,9 @@
       <c r="Y23" t="n">
         <v>-1.316514</v>
       </c>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>-11.318055</v>
+      </c>
       <c r="AA23" t="n">
         <v>-8.649732</v>
       </c>
@@ -2445,7 +2531,9 @@
       <c r="K24" t="n">
         <v>1921.099976</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>70.639999</v>
+      </c>
       <c r="M24" t="n">
         <v>74.900002</v>
       </c>
@@ -2485,7 +2573,9 @@
       <c r="Y24" t="n">
         <v>-2.179339</v>
       </c>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>3.745048</v>
+      </c>
       <c r="AA24" t="n">
         <v>3.082849</v>
       </c>
@@ -2530,7 +2620,9 @@
       <c r="K25" t="n">
         <v>1970.5</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>81.800003</v>
+      </c>
       <c r="M25" t="n">
         <v>85.55999799999999</v>
       </c>
@@ -2570,7 +2662,9 @@
       <c r="Y25" t="n">
         <v>2.571445</v>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>15.79842</v>
+      </c>
       <c r="AA25" t="n">
         <v>14.232304</v>
       </c>
@@ -2615,7 +2709,9 @@
       <c r="K26" t="n">
         <v>1938.199951</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>83.629997</v>
+      </c>
       <c r="M26" t="n">
         <v>86.860001</v>
       </c>
@@ -2655,7 +2751,9 @@
       <c r="Y26" t="n">
         <v>-1.63918</v>
       </c>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>2.237157</v>
+      </c>
       <c r="AA26" t="n">
         <v>1.519405</v>
       </c>
@@ -2700,7 +2798,9 @@
       <c r="K27" t="n">
         <v>1848.099976</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>90.790001</v>
+      </c>
       <c r="M27" t="n">
         <v>95.30999799999999</v>
       </c>
@@ -2740,7 +2840,9 @@
       <c r="Y27" t="n">
         <v>-4.648642</v>
       </c>
-      <c r="Z27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>8.561526000000001</v>
+      </c>
       <c r="AA27" t="n">
         <v>9.728294999999999</v>
       </c>
@@ -2785,7 +2887,9 @@
       <c r="K28" t="n">
         <v>1985.199951</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>81.019997</v>
+      </c>
       <c r="M28" t="n">
         <v>87.410004</v>
       </c>
@@ -2825,7 +2929,9 @@
       <c r="Y28" t="n">
         <v>7.418429</v>
       </c>
-      <c r="Z28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>-10.761102</v>
+      </c>
       <c r="AA28" t="n">
         <v>-8.288736</v>
       </c>
@@ -2870,7 +2976,9 @@
       <c r="K29" t="n">
         <v>2038.099976</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>75.959999</v>
+      </c>
       <c r="M29" t="n">
         <v>82.83000199999999</v>
       </c>
@@ -2910,7 +3018,9 @@
       <c r="Y29" t="n">
         <v>2.66472</v>
       </c>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>-6.245369</v>
+      </c>
       <c r="AA29" t="n">
         <v>-5.239677</v>
       </c>
@@ -2955,7 +3065,9 @@
       <c r="K30" t="n">
         <v>2062.399902</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>71.650002</v>
+      </c>
       <c r="M30" t="n">
         <v>77.040001</v>
       </c>
@@ -2995,7 +3107,9 @@
       <c r="Y30" t="n">
         <v>1.192283</v>
       </c>
-      <c r="Z30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>-5.674036</v>
+      </c>
       <c r="AA30" t="n">
         <v>-6.990222</v>
       </c>
@@ -3040,7 +3154,9 @@
       <c r="K31" t="n">
         <v>2048.399902</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>75.849998</v>
+      </c>
       <c r="M31" t="n">
         <v>81.709999</v>
       </c>
@@ -3080,7 +3196,9 @@
       <c r="Y31" t="n">
         <v>-0.678821</v>
       </c>
-      <c r="Z31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>5.861824</v>
+      </c>
       <c r="AA31" t="n">
         <v>6.061784</v>
       </c>
@@ -3125,7 +3243,9 @@
       <c r="K32" t="n">
         <v>2045.699951</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>78.260002</v>
+      </c>
       <c r="M32" t="n">
         <v>83.620003</v>
       </c>
@@ -3165,7 +3285,9 @@
       <c r="Y32" t="n">
         <v>-0.131808</v>
       </c>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>3.177329</v>
+      </c>
       <c r="AA32" t="n">
         <v>2.33754</v>
       </c>
@@ -3210,7 +3332,9 @@
       <c r="K33" t="n">
         <v>2217.399902</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>83.16999800000001</v>
+      </c>
       <c r="M33" t="n">
         <v>87.480003</v>
       </c>
@@ -3250,7 +3374,9 @@
       <c r="Y33" t="n">
         <v>8.393212999999999</v>
       </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>6.273953</v>
+      </c>
       <c r="AA33" t="n">
         <v>4.616121</v>
       </c>
@@ -3295,7 +3421,9 @@
       <c r="K34" t="n">
         <v>2291.399902</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>81.93000000000001</v>
+      </c>
       <c r="M34" t="n">
         <v>87.860001</v>
       </c>
@@ -3335,7 +3463,9 @@
       <c r="Y34" t="n">
         <v>3.337242</v>
       </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>-1.49092</v>
+      </c>
       <c r="AA34" t="n">
         <v>0.434382</v>
       </c>
@@ -3380,7 +3510,9 @@
       <c r="K35" t="n">
         <v>2322.899902</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>76.989998</v>
+      </c>
       <c r="M35" t="n">
         <v>81.620003</v>
       </c>
@@ -3420,7 +3552,9 @@
       <c r="Y35" t="n">
         <v>1.374705</v>
       </c>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>-6.02954</v>
+      </c>
       <c r="AA35" t="n">
         <v>-7.102206</v>
       </c>
@@ -3465,7 +3599,9 @@
       <c r="K36" t="n">
         <v>2327.699951</v>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>81.540001</v>
+      </c>
       <c r="M36" t="n">
         <v>86.410004</v>
       </c>
@@ -3505,7 +3641,9 @@
       <c r="Y36" t="n">
         <v>0.20664</v>
       </c>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>5.909863</v>
+      </c>
       <c r="AA36" t="n">
         <v>5.868661</v>
       </c>
@@ -3550,7 +3688,9 @@
       <c r="K37" t="n">
         <v>2426.5</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>77.910004</v>
+      </c>
       <c r="M37" t="n">
         <v>80.720001</v>
       </c>
@@ -3590,7 +3730,9 @@
       <c r="Y37" t="n">
         <v>4.244535</v>
       </c>
-      <c r="Z37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>-4.451799</v>
+      </c>
       <c r="AA37" t="n">
         <v>-6.584889</v>
       </c>
@@ -3635,7 +3777,9 @@
       <c r="K38" t="n">
         <v>2493.800049</v>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>73.550003</v>
+      </c>
       <c r="M38" t="n">
         <v>78.800003</v>
       </c>
@@ -3675,7 +3819,9 @@
       <c r="Y38" t="n">
         <v>2.773544</v>
       </c>
-      <c r="Z38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>-5.596201</v>
+      </c>
       <c r="AA38" t="n">
         <v>-2.37859</v>
       </c>
@@ -3720,7 +3866,9 @@
       <c r="K39" t="n">
         <v>2636.100098</v>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>68.16999800000001</v>
+      </c>
       <c r="M39" t="n">
         <v>71.769997</v>
       </c>
@@ -3760,7 +3908,9 @@
       <c r="Y39" t="n">
         <v>5.706153</v>
       </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Z39" t="n">
+        <v>-7.314758</v>
+      </c>
       <c r="AA39" t="n">
         <v>-8.921328000000001</v>
       </c>
@@ -3805,7 +3955,9 @@
       <c r="K40" t="n">
         <v>2738.300049</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>69.260002</v>
+      </c>
       <c r="M40" t="n">
         <v>73.160004</v>
       </c>
@@ -3845,7 +3997,9 @@
       <c r="Y40" t="n">
         <v>3.876937</v>
       </c>
-      <c r="Z40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>1.59895</v>
+      </c>
       <c r="AA40" t="n">
         <v>1.936752</v>
       </c>
@@ -3890,7 +4044,9 @@
       <c r="K41" t="n">
         <v>2657</v>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>68</v>
+      </c>
       <c r="M41" t="n">
         <v>72.94000200000001</v>
       </c>
@@ -3930,7 +4086,9 @@
       <c r="Y41" t="n">
         <v>-2.968997</v>
       </c>
-      <c r="Z41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>-1.819235</v>
+      </c>
       <c r="AA41" t="n">
         <v>-0.300712</v>
       </c>
@@ -3975,7 +4133,9 @@
       <c r="K42" t="n">
         <v>2629.199951</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>71.720001</v>
+      </c>
       <c r="M42" t="n">
         <v>74.639999</v>
       </c>
@@ -4015,7 +4175,9 @@
       <c r="Y42" t="n">
         <v>-1.046295</v>
       </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>5.47059</v>
+      </c>
       <c r="AA42" t="n">
         <v>2.330678</v>
       </c>
@@ -4060,7 +4222,9 @@
       <c r="K43" t="n">
         <v>2812.5</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>72.529999</v>
+      </c>
       <c r="M43" t="n">
         <v>76.760002</v>
       </c>
@@ -4100,7 +4264,9 @@
       <c r="Y43" t="n">
         <v>6.971704</v>
       </c>
-      <c r="Z43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>1.129389</v>
+      </c>
       <c r="AA43" t="n">
         <v>2.840304</v>
       </c>
@@ -4145,7 +4311,9 @@
       <c r="K44" t="n">
         <v>2836.800049</v>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>69.760002</v>
+      </c>
       <c r="M44" t="n">
         <v>73.18000000000001</v>
       </c>
@@ -4185,7 +4353,9 @@
       <c r="Y44" t="n">
         <v>0.864002</v>
       </c>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>-3.819105</v>
+      </c>
       <c r="AA44" t="n">
         <v>-4.66389</v>
       </c>
@@ -4230,7 +4400,9 @@
       <c r="K45" t="n">
         <v>3122.800049</v>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>71.480003</v>
+      </c>
       <c r="M45" t="n">
         <v>74.739998</v>
       </c>
@@ -4270,7 +4442,9 @@
       <c r="Y45" t="n">
         <v>10.081782</v>
       </c>
-      <c r="Z45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>2.465598</v>
+      </c>
       <c r="AA45" t="n">
         <v>2.131727</v>
       </c>
@@ -4315,7 +4489,9 @@
       <c r="K46" t="n">
         <v>3305</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>58.209999</v>
+      </c>
       <c r="M46" t="n">
         <v>63.119999</v>
       </c>
@@ -4355,7 +4531,9 @@
       <c r="Y46" t="n">
         <v>5.834506</v>
       </c>
-      <c r="Z46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>-18.564639</v>
+      </c>
       <c r="AA46" t="n">
         <v>-15.547229</v>
       </c>
@@ -4400,7 +4578,9 @@
       <c r="K47" t="n">
         <v>3288.899902</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>60.790001</v>
+      </c>
       <c r="M47" t="n">
         <v>63.900002</v>
       </c>
@@ -4440,7 +4620,9 @@
       <c r="Y47" t="n">
         <v>-0.487144</v>
       </c>
-      <c r="Z47" t="inlineStr"/>
+      <c r="Z47" t="n">
+        <v>4.432231</v>
+      </c>
       <c r="AA47" t="n">
         <v>1.235746</v>
       </c>
@@ -4485,7 +4667,9 @@
       <c r="K48" t="n">
         <v>3294.399902</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>65.110001</v>
+      </c>
       <c r="M48" t="n">
         <v>67.610001</v>
       </c>
@@ -4525,7 +4709,9 @@
       <c r="Y48" t="n">
         <v>0.167229</v>
       </c>
-      <c r="Z48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>7.106431</v>
+      </c>
       <c r="AA48" t="n">
         <v>5.805945</v>
       </c>
@@ -4570,7 +4756,9 @@
       <c r="K49" t="n">
         <v>3293.199951</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>69.260002</v>
+      </c>
       <c r="M49" t="n">
         <v>72.529999</v>
       </c>
@@ -4610,7 +4798,9 @@
       <c r="Y49" t="n">
         <v>-0.036424</v>
       </c>
-      <c r="Z49" t="inlineStr"/>
+      <c r="Z49" t="n">
+        <v>6.373831</v>
+      </c>
       <c r="AA49" t="n">
         <v>7.277027</v>
       </c>
@@ -4655,7 +4845,9 @@
       <c r="K50" t="n">
         <v>3473.699951</v>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>64.010002</v>
+      </c>
       <c r="M50" t="n">
         <v>68.120003</v>
       </c>
@@ -4695,7 +4887,9 @@
       <c r="Y50" t="n">
         <v>5.480991</v>
       </c>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Z50" t="n">
+        <v>-7.580133</v>
+      </c>
       <c r="AA50" t="n">
         <v>-6.080237</v>
       </c>
@@ -4740,7 +4934,9 @@
       <c r="K51" t="n">
         <v>3840.800049</v>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>62.369999</v>
+      </c>
       <c r="M51" t="n">
         <v>67.019997</v>
       </c>
@@ -4780,7 +4976,9 @@
       <c r="Y51" t="n">
         <v>10.567985</v>
       </c>
-      <c r="Z51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>-2.562105</v>
+      </c>
       <c r="AA51" t="n">
         <v>-1.614806</v>
       </c>
@@ -4825,7 +5023,9 @@
       <c r="K52" t="n">
         <v>3982.199951</v>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>60.98</v>
+      </c>
       <c r="M52" t="n">
         <v>65.06999999999999</v>
       </c>
@@ -4865,7 +5065,9 @@
       <c r="Y52" t="n">
         <v>3.681522</v>
       </c>
-      <c r="Z52" t="inlineStr"/>
+      <c r="Z52" t="n">
+        <v>-2.228635</v>
+      </c>
       <c r="AA52" t="n">
         <v>-2.909575</v>
       </c>
@@ -4910,7 +5112,9 @@
       <c r="K53" t="n">
         <v>4218.299805</v>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>58.549999</v>
+      </c>
       <c r="M53" t="n">
         <v>63.200001</v>
       </c>
@@ -4950,7 +5154,9 @@
       <c r="Y53" t="n">
         <v>5.92888</v>
       </c>
-      <c r="Z53" t="inlineStr"/>
+      <c r="Z53" t="n">
+        <v>-3.984914</v>
+      </c>
       <c r="AA53" t="n">
         <v>-2.873827</v>
       </c>
@@ -4995,7 +5201,9 @@
       <c r="K54" t="n">
         <v>4325.600098</v>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>57.419998</v>
+      </c>
       <c r="M54" t="n">
         <v>60.849998</v>
       </c>
@@ -5035,7 +5243,9 @@
       <c r="Y54" t="n">
         <v>2.543686</v>
       </c>
-      <c r="Z54" t="inlineStr"/>
+      <c r="Z54" t="n">
+        <v>-1.929976</v>
+      </c>
       <c r="AA54" t="n">
         <v>-3.718358</v>
       </c>
@@ -5080,7 +5290,9 @@
       <c r="K55" t="n">
         <v>4713.899902</v>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>65.209999</v>
+      </c>
       <c r="M55" t="n">
         <v>70.69000200000001</v>
       </c>
@@ -5120,7 +5332,9 @@
       <c r="Y55" t="n">
         <v>8.976785</v>
       </c>
-      <c r="Z55" t="inlineStr"/>
+      <c r="Z55" t="n">
+        <v>13.566704</v>
+      </c>
       <c r="AA55" t="n">
         <v>16.170919</v>
       </c>
@@ -5165,7 +5379,9 @@
       <c r="K56" t="n">
         <v>5230.5</v>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>67.019997</v>
+      </c>
       <c r="M56" t="n">
         <v>72.480003</v>
       </c>
@@ -5205,7 +5421,9 @@
       <c r="Y56" t="n">
         <v>10.959081</v>
       </c>
-      <c r="Z56" t="inlineStr"/>
+      <c r="Z56" t="n">
+        <v>2.775644</v>
+      </c>
       <c r="AA56" t="n">
         <v>2.532184</v>
       </c>
@@ -5250,7 +5468,9 @@
       <c r="K57" t="n">
         <v>4647.600098</v>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>101.379997</v>
+      </c>
       <c r="M57" t="n">
         <v>118.349998</v>
       </c>
@@ -5290,7 +5510,9 @@
       <c r="Y57" t="n">
         <v>-11.144248</v>
       </c>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>51.268282</v>
+      </c>
       <c r="AA57" t="n">
         <v>63.286414</v>
       </c>
@@ -5335,7 +5557,9 @@
       <c r="K58" t="n">
         <v>4614.700195</v>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>105.07</v>
+      </c>
       <c r="M58" t="n">
         <v>114.010002</v>
       </c>
@@ -5375,7 +5599,9 @@
       <c r="Y58" t="n">
         <v>-0.70789</v>
       </c>
-      <c r="Z58" t="inlineStr"/>
+      <c r="Z58" t="n">
+        <v>3.639774</v>
+      </c>
       <c r="AA58" t="n">
         <v>-3.667086</v>
       </c>
@@ -5420,7 +5646,9 @@
       <c r="K59" t="n">
         <v>4560.5</v>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>87.360001</v>
+      </c>
       <c r="M59" t="n">
         <v>92.050003</v>
       </c>
@@ -5460,7 +5688,9 @@
       <c r="Y59" t="n">
         <v>-1.174512</v>
       </c>
-      <c r="Z59" t="inlineStr"/>
+      <c r="Z59" t="n">
+        <v>-16.855429</v>
+      </c>
       <c r="AA59" t="n">
         <v>-19.261467</v>
       </c>
@@ -5505,7 +5735,9 @@
       <c r="K60" t="n">
         <v>4022.899902</v>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>69.5</v>
+      </c>
       <c r="M60" t="n">
         <v>72.91999800000001</v>
       </c>
@@ -5545,7 +5777,9 @@
       <c r="Y60" t="n">
         <v>-11.788183</v>
       </c>
-      <c r="Z60" t="inlineStr"/>
+      <c r="Z60" t="n">
+        <v>-20.44414</v>
+      </c>
       <c r="AA60" t="n">
         <v>-20.782188</v>
       </c>
@@ -5590,7 +5824,9 @@
       <c r="K61" t="n">
         <v>4049.100098</v>
       </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>84.66999800000001</v>
+      </c>
       <c r="M61" t="n">
         <v>90.120003</v>
       </c>
@@ -5630,7 +5866,9 @@
       <c r="Y61" t="n">
         <v>0.651276</v>
       </c>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="n">
+        <v>21.827335</v>
+      </c>
       <c r="AA61" t="n">
         <v>23.5875</v>
       </c>
@@ -5646,7 +5884,7 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>171031.734375</v>
+        <v>170448.875</v>
       </c>
       <c r="C62" t="n">
         <v>168.330002</v>
@@ -5661,7 +5899,7 @@
         <v>5.1366</v>
       </c>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>5.9925</v>
       </c>
       <c r="H62" t="n">
         <v>7674.370117</v>
@@ -5673,22 +5911,22 @@
         <v>53277.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4680.600098</v>
+        <v>4700.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>87.05999799999999</v>
+        <v>85.040001</v>
       </c>
       <c r="M62" t="n">
-        <v>94.389999</v>
+        <v>92.779999</v>
       </c>
       <c r="N62" t="n">
-        <v>1239.5</v>
+        <v>1237.25</v>
       </c>
       <c r="O62" t="n">
-        <v>508.5</v>
+        <v>522.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-3.914216</v>
+        <v>-4.241667</v>
       </c>
       <c r="Q62" t="n">
         <v>-3.822422</v>
@@ -5703,7 +5941,7 @@
         <v>1.152002</v>
       </c>
       <c r="U62" t="n">
-        <v>2.600007</v>
+        <v>2.471754</v>
       </c>
       <c r="V62" t="n">
         <v>2.465378</v>
@@ -5715,17 +5953,19 @@
         <v>1.508964</v>
       </c>
       <c r="Y62" t="n">
-        <v>15.596058</v>
-      </c>
-      <c r="Z62" t="inlineStr"/>
+        <v>16.094927</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.436994</v>
+      </c>
       <c r="AA62" t="n">
-        <v>4.738123</v>
+        <v>2.951616</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.759386</v>
+        <v>5.567406</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.371526</v>
+        <v>18.54793</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,7 +5884,7 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>170448.875</v>
+        <v>171907</v>
       </c>
       <c r="C62" t="n">
         <v>168.330002</v>
@@ -5896,37 +5896,37 @@
         <v>445.850006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1366</v>
+        <v>5.154</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9925</v>
+        <v>6.0109</v>
       </c>
       <c r="H62" t="n">
-        <v>7674.370117</v>
+        <v>7652.859863</v>
       </c>
       <c r="I62" t="n">
-        <v>26180.460938</v>
+        <v>25980.189453</v>
       </c>
       <c r="J62" t="n">
-        <v>53277.011719</v>
+        <v>53417.160156</v>
       </c>
       <c r="K62" t="n">
-        <v>4700.799805</v>
+        <v>4693.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>85.040001</v>
+        <v>82.540001</v>
       </c>
       <c r="M62" t="n">
-        <v>92.779999</v>
+        <v>88.019997</v>
       </c>
       <c r="N62" t="n">
-        <v>1237.25</v>
+        <v>1218.25</v>
       </c>
       <c r="O62" t="n">
-        <v>522.5</v>
+        <v>514.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-4.241667</v>
+        <v>-3.422491</v>
       </c>
       <c r="Q62" t="n">
         <v>-3.822422</v>
@@ -5938,34 +5938,34 @@
         <v>4.075723</v>
       </c>
       <c r="T62" t="n">
-        <v>1.152002</v>
+        <v>1.494646</v>
       </c>
       <c r="U62" t="n">
-        <v>2.471754</v>
+        <v>2.786397</v>
       </c>
       <c r="V62" t="n">
-        <v>2.465378</v>
+        <v>2.178181</v>
       </c>
       <c r="W62" t="n">
-        <v>3.178908</v>
+        <v>2.389625</v>
       </c>
       <c r="X62" t="n">
-        <v>1.508964</v>
+        <v>1.77599</v>
       </c>
       <c r="Y62" t="n">
-        <v>16.094927</v>
+        <v>15.904769</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.436994</v>
+        <v>-2.515646</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.951616</v>
+        <v>-2.330233</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.567406</v>
+        <v>3.946246</v>
       </c>
       <c r="AC62" t="n">
-        <v>18.54793</v>
+        <v>16.67612</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>171907</v>
+        <v>174577</v>
       </c>
       <c r="C62" t="n">
-        <v>168.330002</v>
+        <v>169.009995</v>
       </c>
       <c r="D62" t="n">
-        <v>102.25</v>
+        <v>102.639999</v>
       </c>
       <c r="E62" t="n">
-        <v>445.850006</v>
+        <v>444.700012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.154</v>
+        <v>5.148</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0109</v>
+        <v>6.0044</v>
       </c>
       <c r="H62" t="n">
-        <v>7652.859863</v>
+        <v>7677.279785</v>
       </c>
       <c r="I62" t="n">
-        <v>25980.189453</v>
+        <v>26151.300781</v>
       </c>
       <c r="J62" t="n">
-        <v>53417.160156</v>
+        <v>53577.398438</v>
       </c>
       <c r="K62" t="n">
-        <v>4693.100098</v>
+        <v>4670.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>82.540001</v>
+        <v>80.139999</v>
       </c>
       <c r="M62" t="n">
-        <v>88.019997</v>
+        <v>84.910004</v>
       </c>
       <c r="N62" t="n">
-        <v>1218.25</v>
+        <v>1240.75</v>
       </c>
       <c r="O62" t="n">
-        <v>514.25</v>
+        <v>528</v>
       </c>
       <c r="P62" t="n">
-        <v>-3.422491</v>
+        <v>-1.922483</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3.822422</v>
+        <v>-3.433899</v>
       </c>
       <c r="R62" t="n">
-        <v>-4.662005</v>
+        <v>-4.298369</v>
       </c>
       <c r="S62" t="n">
-        <v>4.075723</v>
+        <v>3.807278</v>
       </c>
       <c r="T62" t="n">
-        <v>1.494646</v>
+        <v>1.37649</v>
       </c>
       <c r="U62" t="n">
-        <v>2.786397</v>
+        <v>2.675243</v>
       </c>
       <c r="V62" t="n">
-        <v>2.178181</v>
+        <v>2.504227</v>
       </c>
       <c r="W62" t="n">
-        <v>2.389625</v>
+        <v>3.063986</v>
       </c>
       <c r="X62" t="n">
-        <v>1.77599</v>
+        <v>2.081293</v>
       </c>
       <c r="Y62" t="n">
-        <v>15.904769</v>
+        <v>15.351562</v>
       </c>
       <c r="Z62" t="n">
-        <v>-2.515646</v>
+        <v>-5.350182</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.330233</v>
+        <v>-5.781179</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.946246</v>
+        <v>5.866041</v>
       </c>
       <c r="AC62" t="n">
-        <v>16.67612</v>
+        <v>19.795803</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>174577</v>
+        <v>175329.453125</v>
       </c>
       <c r="C62" t="n">
-        <v>169.009995</v>
+        <v>172.399994</v>
       </c>
       <c r="D62" t="n">
-        <v>102.639999</v>
+        <v>105.360001</v>
       </c>
       <c r="E62" t="n">
-        <v>444.700012</v>
+        <v>450.690002</v>
       </c>
       <c r="F62" t="n">
-        <v>5.148</v>
+        <v>5.1611</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0044</v>
+        <v>6.013</v>
       </c>
       <c r="H62" t="n">
-        <v>7677.279785</v>
+        <v>7730.990234</v>
       </c>
       <c r="I62" t="n">
-        <v>26151.300781</v>
+        <v>26541.351562</v>
       </c>
       <c r="J62" t="n">
-        <v>53577.398438</v>
+        <v>53569.441406</v>
       </c>
       <c r="K62" t="n">
-        <v>4670.700195</v>
+        <v>4660.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>80.139999</v>
+        <v>83.639999</v>
       </c>
       <c r="M62" t="n">
-        <v>84.910004</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1240.75</v>
+        <v>1263.5</v>
       </c>
       <c r="O62" t="n">
-        <v>528</v>
+        <v>531.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.922483</v>
+        <v>-1.499754</v>
       </c>
       <c r="Q62" t="n">
-        <v>-3.433899</v>
+        <v>-1.496978</v>
       </c>
       <c r="R62" t="n">
-        <v>-4.298369</v>
+        <v>-1.762237</v>
       </c>
       <c r="S62" t="n">
-        <v>3.807278</v>
+        <v>5.205534</v>
       </c>
       <c r="T62" t="n">
-        <v>1.37649</v>
+        <v>1.634464</v>
       </c>
       <c r="U62" t="n">
-        <v>2.675243</v>
+        <v>2.822307</v>
       </c>
       <c r="V62" t="n">
-        <v>2.504227</v>
+        <v>3.221349</v>
       </c>
       <c r="W62" t="n">
-        <v>3.063986</v>
+        <v>4.601202</v>
       </c>
       <c r="X62" t="n">
-        <v>2.081293</v>
+        <v>2.066132</v>
       </c>
       <c r="Y62" t="n">
-        <v>15.351562</v>
+        <v>15.102121</v>
       </c>
       <c r="Z62" t="n">
-        <v>-5.350182</v>
+        <v>-1.216486</v>
       </c>
       <c r="AA62" t="n">
-        <v>-5.781179</v>
+        <v>-1.719932</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.866041</v>
+        <v>7.807167</v>
       </c>
       <c r="AC62" t="n">
-        <v>19.795803</v>
+        <v>20.589904</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>175329.453125</v>
+        <v>175664.625</v>
       </c>
       <c r="C62" t="n">
-        <v>172.399994</v>
+        <v>172.720001</v>
       </c>
       <c r="D62" t="n">
-        <v>105.360001</v>
+        <v>104.580002</v>
       </c>
       <c r="E62" t="n">
-        <v>450.690002</v>
+        <v>452.049988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1611</v>
+        <v>5.1925</v>
       </c>
       <c r="G62" t="n">
-        <v>6.013</v>
+        <v>6.0137</v>
       </c>
       <c r="H62" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="I62" t="n">
-        <v>26541.351562</v>
+        <v>26402.423828</v>
       </c>
       <c r="J62" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="K62" t="n">
-        <v>4660.600098</v>
+        <v>4505.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>83.639999</v>
+        <v>83.400002</v>
       </c>
       <c r="M62" t="n">
-        <v>88.56999999999999</v>
+        <v>88.230003</v>
       </c>
       <c r="N62" t="n">
-        <v>1263.5</v>
+        <v>1287.75</v>
       </c>
       <c r="O62" t="n">
-        <v>531.5</v>
+        <v>536.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.499754</v>
+        <v>-1.311454</v>
       </c>
       <c r="Q62" t="n">
-        <v>-1.496978</v>
+        <v>-1.314137</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.762237</v>
+        <v>-2.489509</v>
       </c>
       <c r="S62" t="n">
-        <v>5.205534</v>
+        <v>5.522998</v>
       </c>
       <c r="T62" t="n">
-        <v>1.634464</v>
+        <v>2.252809</v>
       </c>
       <c r="U62" t="n">
-        <v>2.822307</v>
+        <v>2.834277</v>
       </c>
       <c r="V62" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
       <c r="W62" t="n">
-        <v>4.601202</v>
+        <v>4.053678</v>
       </c>
       <c r="X62" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
       <c r="Y62" t="n">
-        <v>15.102121</v>
+        <v>11.279042</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.216486</v>
+        <v>-1.499937</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.719932</v>
+        <v>-2.097203</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.807167</v>
+        <v>9.87628</v>
       </c>
       <c r="AC62" t="n">
-        <v>20.589904</v>
+        <v>21.667612</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>175664.625</v>
+        <v>175135</v>
       </c>
       <c r="C62" t="n">
-        <v>172.720001</v>
+        <v>172.399994</v>
       </c>
       <c r="D62" t="n">
-        <v>104.580002</v>
+        <v>105.169998</v>
       </c>
       <c r="E62" t="n">
-        <v>452.049988</v>
+        <v>450</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1925</v>
+        <v>5.2054</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0137</v>
+        <v>6.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>7711.759766</v>
+        <v>7730.990234</v>
       </c>
       <c r="I62" t="n">
-        <v>26402.423828</v>
+        <v>26541.349609</v>
       </c>
       <c r="J62" t="n">
-        <v>53559.988281</v>
+        <v>53569.441406</v>
       </c>
       <c r="K62" t="n">
-        <v>4505.799805</v>
+        <v>4609.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>83.400002</v>
+        <v>83.529999</v>
       </c>
       <c r="M62" t="n">
-        <v>88.230003</v>
+        <v>89.699997</v>
       </c>
       <c r="N62" t="n">
-        <v>1287.75</v>
+        <v>1256.5</v>
       </c>
       <c r="O62" t="n">
-        <v>536.25</v>
+        <v>510.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.311454</v>
+        <v>-1.608998</v>
       </c>
       <c r="Q62" t="n">
-        <v>-1.314137</v>
+        <v>-1.496978</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.489509</v>
+        <v>-1.939396</v>
       </c>
       <c r="S62" t="n">
-        <v>5.522998</v>
+        <v>5.044465</v>
       </c>
       <c r="T62" t="n">
-        <v>2.252809</v>
+        <v>2.506839</v>
       </c>
       <c r="U62" t="n">
-        <v>2.834277</v>
+        <v>2.69235</v>
       </c>
       <c r="V62" t="n">
-        <v>2.964591</v>
+        <v>3.221349</v>
       </c>
       <c r="W62" t="n">
-        <v>4.053678</v>
+        <v>4.601194</v>
       </c>
       <c r="X62" t="n">
-        <v>2.048121</v>
+        <v>2.066132</v>
       </c>
       <c r="Y62" t="n">
-        <v>11.279042</v>
+        <v>13.845054</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.499937</v>
+        <v>-1.346403</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.097203</v>
+        <v>-0.466052</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.87628</v>
+        <v>7.209898</v>
       </c>
       <c r="AC62" t="n">
-        <v>21.667612</v>
+        <v>15.768576</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,7 +5884,7 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>175135</v>
+        <v>175665</v>
       </c>
       <c r="C62" t="n">
         <v>172.399994</v>
@@ -5896,37 +5896,37 @@
         <v>450</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2054</v>
+        <v>5.185</v>
       </c>
       <c r="G62" t="n">
         <v>6.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>7730.990234</v>
+        <v>7711.759766</v>
       </c>
       <c r="I62" t="n">
-        <v>26541.349609</v>
+        <v>26402.419922</v>
       </c>
       <c r="J62" t="n">
-        <v>53569.441406</v>
+        <v>53559.988281</v>
       </c>
       <c r="K62" t="n">
-        <v>4609.700195</v>
+        <v>4529.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>83.529999</v>
+        <v>83.400002</v>
       </c>
       <c r="M62" t="n">
-        <v>89.699997</v>
+        <v>88.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1256.5</v>
+        <v>1288</v>
       </c>
       <c r="O62" t="n">
-        <v>510.25</v>
+        <v>536.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.608998</v>
+        <v>-1.311243</v>
       </c>
       <c r="Q62" t="n">
         <v>-1.496978</v>
@@ -5938,34 +5938,34 @@
         <v>5.044465</v>
       </c>
       <c r="T62" t="n">
-        <v>2.506839</v>
+        <v>2.105113</v>
       </c>
       <c r="U62" t="n">
         <v>2.69235</v>
       </c>
       <c r="V62" t="n">
-        <v>3.221349</v>
+        <v>2.964591</v>
       </c>
       <c r="W62" t="n">
-        <v>4.601194</v>
+        <v>4.053663</v>
       </c>
       <c r="X62" t="n">
-        <v>2.066132</v>
+        <v>2.048121</v>
       </c>
       <c r="Y62" t="n">
-        <v>13.845054</v>
+        <v>11.874239</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.346403</v>
+        <v>-1.499937</v>
       </c>
       <c r="AA62" t="n">
-        <v>-0.466052</v>
+        <v>-2.241461</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.209898</v>
+        <v>9.897610999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.768576</v>
+        <v>21.724334</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46265</v>
       </c>
       <c r="B62" t="n">
-        <v>175665</v>
+        <v>177580.765625</v>
       </c>
       <c r="C62" t="n">
-        <v>172.399994</v>
+        <v>174.800003</v>
       </c>
       <c r="D62" t="n">
-        <v>105.169998</v>
+        <v>106.550003</v>
       </c>
       <c r="E62" t="n">
-        <v>450</v>
+        <v>449.230011</v>
       </c>
       <c r="F62" t="n">
-        <v>5.185</v>
+        <v>5.1834</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0054</v>
+        <v>6.0184</v>
       </c>
       <c r="H62" t="n">
-        <v>7711.759766</v>
+        <v>7672.839844</v>
       </c>
       <c r="I62" t="n">
-        <v>26402.419922</v>
+        <v>26289.875</v>
       </c>
       <c r="J62" t="n">
-        <v>53559.988281</v>
+        <v>53199.460938</v>
       </c>
       <c r="K62" t="n">
-        <v>4529.899902</v>
+        <v>4483.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>83.400002</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>88.099998</v>
+        <v>88.269997</v>
       </c>
       <c r="N62" t="n">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="O62" t="n">
-        <v>536.5</v>
+        <v>538</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.311243</v>
+        <v>-0.234964</v>
       </c>
       <c r="Q62" t="n">
-        <v>-1.496978</v>
+        <v>-0.125701</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.939396</v>
+        <v>-0.652678</v>
       </c>
       <c r="S62" t="n">
-        <v>5.044465</v>
+        <v>4.864725</v>
       </c>
       <c r="T62" t="n">
-        <v>2.105113</v>
+        <v>2.073609</v>
       </c>
       <c r="U62" t="n">
-        <v>2.69235</v>
+        <v>2.91465</v>
       </c>
       <c r="V62" t="n">
-        <v>2.964591</v>
+        <v>2.444946</v>
       </c>
       <c r="W62" t="n">
-        <v>4.053663</v>
+        <v>3.610116</v>
       </c>
       <c r="X62" t="n">
-        <v>2.048121</v>
+        <v>1.361207</v>
       </c>
       <c r="Y62" t="n">
-        <v>11.874239</v>
+        <v>10.725835</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.499937</v>
+        <v>1.192869</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.241461</v>
+        <v>-2.052825</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.897610999999999</v>
+        <v>10.068259</v>
       </c>
       <c r="AC62" t="n">
-        <v>21.724334</v>
+        <v>22.064663</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -569,49 +569,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>118781</v>
+        <v>110979</v>
       </c>
       <c r="C2" t="n">
-        <v>114.080002</v>
+        <v>106.489998</v>
       </c>
       <c r="D2" t="n">
-        <v>136.330002</v>
+        <v>127.400002</v>
       </c>
       <c r="E2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1829</v>
+        <v>5.4143</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1119</v>
+        <v>6.2785</v>
       </c>
       <c r="H2" t="n">
-        <v>4522.680176</v>
+        <v>4307.540039</v>
       </c>
       <c r="I2" t="n">
-        <v>15259.240234</v>
+        <v>14448.580078</v>
       </c>
       <c r="J2" t="n">
-        <v>35360.730469</v>
+        <v>33843.921875</v>
       </c>
       <c r="K2" t="n">
-        <v>1815</v>
+        <v>1755.300049</v>
       </c>
       <c r="L2" t="n">
-        <v>68.5</v>
+        <v>75.029999</v>
       </c>
       <c r="M2" t="n">
-        <v>72.989998</v>
+        <v>78.519997</v>
       </c>
       <c r="N2" t="n">
-        <v>1298.75</v>
+        <v>1256</v>
       </c>
       <c r="O2" t="n">
-        <v>534</v>
+        <v>536.75</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -630,5342 +630,5342 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B3" t="n">
-        <v>110979</v>
+        <v>103501</v>
       </c>
       <c r="C3" t="n">
-        <v>106.489998</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>127.400002</v>
+        <v>111.199997</v>
       </c>
       <c r="E3" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4143</v>
+        <v>5.6449</v>
       </c>
       <c r="G3" t="n">
-        <v>6.2785</v>
+        <v>6.593</v>
       </c>
       <c r="H3" t="n">
-        <v>4307.540039</v>
+        <v>4605.379883</v>
       </c>
       <c r="I3" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
       <c r="J3" t="n">
-        <v>33843.921875</v>
+        <v>35819.558594</v>
       </c>
       <c r="K3" t="n">
-        <v>1755.300049</v>
+        <v>1783</v>
       </c>
       <c r="L3" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>78.519997</v>
+        <v>84.379997</v>
       </c>
       <c r="N3" t="n">
-        <v>1256</v>
+        <v>1235.75</v>
       </c>
       <c r="O3" t="n">
-        <v>536.75</v>
+        <v>568.25</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.568391</v>
+        <v>-6.738212</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.653229</v>
+        <v>-6.394964</v>
       </c>
       <c r="R3" t="n">
-        <v>-6.550283</v>
+        <v>-12.715859</v>
       </c>
       <c r="S3" t="n">
-        <v>0.393701</v>
+        <v>10.980392</v>
       </c>
       <c r="T3" t="n">
-        <v>4.464682</v>
+        <v>4.259089</v>
       </c>
       <c r="U3" t="n">
-        <v>2.725834</v>
+        <v>5.009156</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.756917</v>
+        <v>6.914384</v>
       </c>
       <c r="W3" t="n">
-        <v>-5.312585</v>
+        <v>7.265832</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.289528</v>
+        <v>5.837493</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.289254</v>
+        <v>1.578075</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.532845</v>
+        <v>11.382115</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.576379</v>
+        <v>7.463068</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3.291627</v>
+        <v>-1.612261</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.514981</v>
+        <v>5.868654</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B4" t="n">
-        <v>103501</v>
+        <v>101915</v>
       </c>
       <c r="C4" t="n">
-        <v>99.68000000000001</v>
+        <v>98.349998</v>
       </c>
       <c r="D4" t="n">
-        <v>111.199997</v>
+        <v>108.800003</v>
       </c>
       <c r="E4" t="n">
-        <v>283</v>
+        <v>280.549988</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6449</v>
+        <v>5.6007</v>
       </c>
       <c r="G4" t="n">
-        <v>6.593</v>
+        <v>6.3223</v>
       </c>
       <c r="H4" t="n">
-        <v>4605.379883</v>
+        <v>4567</v>
       </c>
       <c r="I4" t="n">
-        <v>15498.389648</v>
+        <v>15537.69043</v>
       </c>
       <c r="J4" t="n">
-        <v>35819.558594</v>
+        <v>34483.71875</v>
       </c>
       <c r="K4" t="n">
-        <v>1783</v>
+        <v>1773.599976</v>
       </c>
       <c r="L4" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>84.379997</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>1235.75</v>
+        <v>1217.25</v>
       </c>
       <c r="O4" t="n">
-        <v>568.25</v>
+        <v>567</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.738212</v>
+        <v>-1.532352</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.394964</v>
+        <v>-1.334271</v>
       </c>
       <c r="R4" t="n">
-        <v>-12.715859</v>
+        <v>-2.158268</v>
       </c>
       <c r="S4" t="n">
-        <v>10.980392</v>
+        <v>-0.865729</v>
       </c>
       <c r="T4" t="n">
-        <v>4.259089</v>
+        <v>-0.783007</v>
       </c>
       <c r="U4" t="n">
-        <v>5.009156</v>
+        <v>-4.10587</v>
       </c>
       <c r="V4" t="n">
-        <v>6.914384</v>
+        <v>-0.833371</v>
       </c>
       <c r="W4" t="n">
-        <v>7.265832</v>
+        <v>0.25358</v>
       </c>
       <c r="X4" t="n">
-        <v>5.837493</v>
+        <v>-3.729359</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.578075</v>
+        <v>-0.527203</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.382115</v>
+        <v>-20.808902</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.463068</v>
+        <v>-16.366435</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.868654</v>
+        <v>-0.219974</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>101915</v>
+        <v>104822</v>
       </c>
       <c r="C5" t="n">
-        <v>98.349998</v>
+        <v>100.800003</v>
       </c>
       <c r="D5" t="n">
-        <v>108.800003</v>
+        <v>113.300003</v>
       </c>
       <c r="E5" t="n">
-        <v>280.549988</v>
+        <v>293.559998</v>
       </c>
       <c r="F5" t="n">
-        <v>5.6007</v>
+        <v>5.5702</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3223</v>
+        <v>6.3049</v>
       </c>
       <c r="H5" t="n">
-        <v>4567</v>
+        <v>4766.180176</v>
       </c>
       <c r="I5" t="n">
-        <v>15537.69043</v>
+        <v>15644.969727</v>
       </c>
       <c r="J5" t="n">
-        <v>34483.71875</v>
+        <v>36338.300781</v>
       </c>
       <c r="K5" t="n">
-        <v>1773.599976</v>
+        <v>1827.5</v>
       </c>
       <c r="L5" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
       <c r="M5" t="n">
-        <v>70.56999999999999</v>
+        <v>77.779999</v>
       </c>
       <c r="N5" t="n">
-        <v>1217.25</v>
+        <v>1328.75</v>
       </c>
       <c r="O5" t="n">
-        <v>567</v>
+        <v>593.25</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.532352</v>
+        <v>2.852377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.334271</v>
+        <v>2.491108</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.158268</v>
+        <v>4.136029</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.865729</v>
+        <v>4.637323</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.783007</v>
+        <v>-0.544574</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.10587</v>
+        <v>-0.275213</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.833371</v>
+        <v>4.361291</v>
       </c>
       <c r="W5" t="n">
-        <v>0.25358</v>
+        <v>0.690446</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.729359</v>
+        <v>5.378138</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.527203</v>
+        <v>3.039018</v>
       </c>
       <c r="Z5" t="n">
-        <v>-20.808902</v>
+        <v>13.644604</v>
       </c>
       <c r="AA5" t="n">
-        <v>-16.366435</v>
+        <v>10.216805</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.219974</v>
+        <v>4.62963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B6" t="n">
-        <v>104822</v>
+        <v>112388</v>
       </c>
       <c r="C6" t="n">
-        <v>100.800003</v>
+        <v>107.980003</v>
       </c>
       <c r="D6" t="n">
-        <v>113.300003</v>
+        <v>117</v>
       </c>
       <c r="E6" t="n">
-        <v>293.559998</v>
+        <v>260.399994</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5702</v>
+        <v>5.3626</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3049</v>
+        <v>5.9782</v>
       </c>
       <c r="H6" t="n">
-        <v>4766.180176</v>
+        <v>4515.549805</v>
       </c>
       <c r="I6" t="n">
-        <v>15644.969727</v>
+        <v>14239.879883</v>
       </c>
       <c r="J6" t="n">
-        <v>36338.300781</v>
+        <v>35131.859375</v>
       </c>
       <c r="K6" t="n">
-        <v>1827.5</v>
+        <v>1795</v>
       </c>
       <c r="L6" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
       <c r="M6" t="n">
-        <v>77.779999</v>
+        <v>91.209999</v>
       </c>
       <c r="N6" t="n">
-        <v>1328.75</v>
+        <v>1490.5</v>
       </c>
       <c r="O6" t="n">
-        <v>593.25</v>
+        <v>626</v>
       </c>
       <c r="P6" t="n">
-        <v>2.852377</v>
+        <v>7.21795</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.491108</v>
+        <v>7.123016</v>
       </c>
       <c r="R6" t="n">
-        <v>4.136029</v>
+        <v>3.265664</v>
       </c>
       <c r="S6" t="n">
-        <v>4.637323</v>
+        <v>-11.295818</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.544574</v>
+        <v>-3.726978</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.275213</v>
+        <v>-5.181687</v>
       </c>
       <c r="V6" t="n">
-        <v>4.361291</v>
+        <v>-5.258517</v>
       </c>
       <c r="W6" t="n">
-        <v>0.690446</v>
+        <v>-8.981097</v>
       </c>
       <c r="X6" t="n">
-        <v>5.378138</v>
+        <v>-3.320027</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.039018</v>
+        <v>-1.778386</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.644604</v>
+        <v>17.205162</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.216805</v>
+        <v>17.26665</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.62963</v>
+        <v>5.520438</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B7" t="n">
-        <v>112388</v>
+        <v>113142</v>
       </c>
       <c r="C7" t="n">
-        <v>107.980003</v>
+        <v>108.900002</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>111.040001</v>
       </c>
       <c r="E7" t="n">
-        <v>260.399994</v>
+        <v>245.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3626</v>
+        <v>5.1594</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9782</v>
+        <v>5.814</v>
       </c>
       <c r="H7" t="n">
-        <v>4515.549805</v>
+        <v>4373.939941</v>
       </c>
       <c r="I7" t="n">
-        <v>14239.879883</v>
+        <v>13751.400391</v>
       </c>
       <c r="J7" t="n">
-        <v>35131.859375</v>
+        <v>33892.601562</v>
       </c>
       <c r="K7" t="n">
-        <v>1795</v>
+        <v>1899.400024</v>
       </c>
       <c r="L7" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
       <c r="M7" t="n">
-        <v>91.209999</v>
+        <v>100.989998</v>
       </c>
       <c r="N7" t="n">
-        <v>1490.5</v>
+        <v>1644.25</v>
       </c>
       <c r="O7" t="n">
-        <v>626</v>
+        <v>697.5</v>
       </c>
       <c r="P7" t="n">
-        <v>7.21795</v>
+        <v>0.67089</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.123016</v>
+        <v>0.852008</v>
       </c>
       <c r="R7" t="n">
-        <v>3.265664</v>
+        <v>-5.094016</v>
       </c>
       <c r="S7" t="n">
-        <v>-11.295818</v>
+        <v>-5.721964</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.726978</v>
+        <v>-3.789204</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.181687</v>
+        <v>-2.746643</v>
       </c>
       <c r="V7" t="n">
-        <v>-5.258517</v>
+        <v>-3.136049</v>
       </c>
       <c r="W7" t="n">
-        <v>-8.981097</v>
+        <v>-3.430362</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.320027</v>
+        <v>-3.527447</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.778386</v>
+        <v>5.816157</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.205162</v>
+        <v>8.587634</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.26665</v>
+        <v>10.722507</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.520438</v>
+        <v>11.421725</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B8" t="n">
-        <v>113142</v>
+        <v>119999</v>
       </c>
       <c r="C8" t="n">
-        <v>108.900002</v>
+        <v>115.599998</v>
       </c>
       <c r="D8" t="n">
-        <v>111.040001</v>
+        <v>120.940002</v>
       </c>
       <c r="E8" t="n">
-        <v>245.5</v>
+        <v>235.649994</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1594</v>
+        <v>4.7697</v>
       </c>
       <c r="G8" t="n">
-        <v>5.814</v>
+        <v>5.3198</v>
       </c>
       <c r="H8" t="n">
-        <v>4373.939941</v>
+        <v>4530.410156</v>
       </c>
       <c r="I8" t="n">
-        <v>13751.400391</v>
+        <v>14220.519531</v>
       </c>
       <c r="J8" t="n">
-        <v>33892.601562</v>
+        <v>34678.351562</v>
       </c>
       <c r="K8" t="n">
-        <v>1899.400024</v>
+        <v>1949.199951</v>
       </c>
       <c r="L8" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
       <c r="M8" t="n">
-        <v>100.989998</v>
+        <v>107.910004</v>
       </c>
       <c r="N8" t="n">
-        <v>1644.25</v>
+        <v>1618.25</v>
       </c>
       <c r="O8" t="n">
-        <v>697.5</v>
+        <v>748.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0.67089</v>
+        <v>6.060526</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.852008</v>
+        <v>6.152431</v>
       </c>
       <c r="R8" t="n">
-        <v>-5.094016</v>
+        <v>8.915706999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.721964</v>
+        <v>-4.012222</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.789204</v>
+        <v>-7.553203</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.746643</v>
+        <v>-8.500176</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.136049</v>
+        <v>3.577329</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.430362</v>
+        <v>3.411428</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.527447</v>
+        <v>2.318353</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.816157</v>
+        <v>2.621877</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.587634</v>
+        <v>4.763892</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.722507</v>
+        <v>6.852169</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.421725</v>
+        <v>7.34767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B9" t="n">
-        <v>119999</v>
+        <v>107876</v>
       </c>
       <c r="C9" t="n">
-        <v>115.599998</v>
+        <v>103.400002</v>
       </c>
       <c r="D9" t="n">
-        <v>120.940002</v>
+        <v>110.599998</v>
       </c>
       <c r="E9" t="n">
-        <v>235.649994</v>
+        <v>224.100006</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7697</v>
+        <v>4.9378</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3198</v>
+        <v>5.1837</v>
       </c>
       <c r="H9" t="n">
-        <v>4530.410156</v>
+        <v>4131.930176</v>
       </c>
       <c r="I9" t="n">
-        <v>14220.519531</v>
+        <v>12334.639648</v>
       </c>
       <c r="J9" t="n">
-        <v>34678.351562</v>
+        <v>32977.210938</v>
       </c>
       <c r="K9" t="n">
-        <v>1949.199951</v>
+        <v>1909.300049</v>
       </c>
       <c r="L9" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
       <c r="M9" t="n">
-        <v>107.910004</v>
+        <v>109.339996</v>
       </c>
       <c r="N9" t="n">
-        <v>1618.25</v>
+        <v>1708.25</v>
       </c>
       <c r="O9" t="n">
-        <v>748.75</v>
+        <v>818.25</v>
       </c>
       <c r="P9" t="n">
-        <v>6.060526</v>
+        <v>-10.102584</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.152431</v>
+        <v>-10.553631</v>
       </c>
       <c r="R9" t="n">
-        <v>8.915706999999999</v>
+        <v>-8.549697</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.012222</v>
+        <v>-4.901332</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.553203</v>
+        <v>3.524328</v>
       </c>
       <c r="U9" t="n">
-        <v>-8.500176</v>
+        <v>-2.558363</v>
       </c>
       <c r="V9" t="n">
-        <v>3.577329</v>
+        <v>-8.795671</v>
       </c>
       <c r="W9" t="n">
-        <v>3.411428</v>
+        <v>-13.261681</v>
       </c>
       <c r="X9" t="n">
-        <v>2.318353</v>
+        <v>-4.905483</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.621877</v>
+        <v>-2.046989</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.763892</v>
+        <v>4.39769</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.852169</v>
+        <v>1.325172</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.34767</v>
+        <v>9.282137000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B10" t="n">
-        <v>107876</v>
+        <v>111351</v>
       </c>
       <c r="C10" t="n">
-        <v>103.400002</v>
+        <v>107.18</v>
       </c>
       <c r="D10" t="n">
-        <v>110.599998</v>
+        <v>109.300003</v>
       </c>
       <c r="E10" t="n">
-        <v>224.100006</v>
+        <v>214.5</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9378</v>
+        <v>4.7524</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1837</v>
+        <v>5.1176</v>
       </c>
       <c r="H10" t="n">
-        <v>4131.930176</v>
+        <v>4132.149902</v>
       </c>
       <c r="I10" t="n">
-        <v>12334.639648</v>
+        <v>12081.389648</v>
       </c>
       <c r="J10" t="n">
-        <v>32977.210938</v>
+        <v>32990.121094</v>
       </c>
       <c r="K10" t="n">
-        <v>1909.300049</v>
+        <v>1842.699951</v>
       </c>
       <c r="L10" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
       <c r="M10" t="n">
-        <v>109.339996</v>
+        <v>122.839996</v>
       </c>
       <c r="N10" t="n">
-        <v>1708.25</v>
+        <v>1683.25</v>
       </c>
       <c r="O10" t="n">
-        <v>818.25</v>
+        <v>753.5</v>
       </c>
       <c r="P10" t="n">
-        <v>-10.102584</v>
+        <v>3.221291</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.553631</v>
+        <v>3.655705</v>
       </c>
       <c r="R10" t="n">
-        <v>-8.549697</v>
+        <v>-1.175403</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.901332</v>
+        <v>-4.283804</v>
       </c>
       <c r="T10" t="n">
-        <v>3.524328</v>
+        <v>-3.754709</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.558363</v>
+        <v>-1.275153</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.795671</v>
+        <v>0.005318</v>
       </c>
       <c r="W10" t="n">
-        <v>-13.261681</v>
+        <v>-2.053161</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.905483</v>
+        <v>0.039149</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.046989</v>
+        <v>-3.488194</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.39769</v>
+        <v>9.532902</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.325172</v>
+        <v>12.346809</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.282137000000001</v>
+        <v>-7.913229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B11" t="n">
-        <v>111351</v>
+        <v>98542</v>
       </c>
       <c r="C11" t="n">
-        <v>107.18</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>109.300003</v>
+        <v>91.33000199999999</v>
       </c>
       <c r="E11" t="n">
-        <v>214.5</v>
+        <v>216.699997</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7524</v>
+        <v>5.1809</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1176</v>
+        <v>5.4098</v>
       </c>
       <c r="H11" t="n">
-        <v>4132.149902</v>
+        <v>3785.379883</v>
       </c>
       <c r="I11" t="n">
-        <v>12081.389648</v>
+        <v>11028.740234</v>
       </c>
       <c r="J11" t="n">
-        <v>32990.121094</v>
+        <v>30775.429688</v>
       </c>
       <c r="K11" t="n">
-        <v>1842.699951</v>
+        <v>1804.099976</v>
       </c>
       <c r="L11" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
       <c r="M11" t="n">
-        <v>122.839996</v>
+        <v>114.809998</v>
       </c>
       <c r="N11" t="n">
-        <v>1683.25</v>
+        <v>1675</v>
       </c>
       <c r="O11" t="n">
-        <v>753.5</v>
+        <v>743.75</v>
       </c>
       <c r="P11" t="n">
-        <v>3.221291</v>
+        <v>-11.503264</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.655705</v>
+        <v>-11.364061</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.175403</v>
+        <v>-16.440989</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.283804</v>
+        <v>1.02564</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.754709</v>
+        <v>9.016501</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.275153</v>
+        <v>5.709709</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005318</v>
+        <v>-8.391999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>-2.053161</v>
+        <v>-8.712982999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>0.039149</v>
+        <v>-6.713196</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.488194</v>
+        <v>-2.094751</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.532902</v>
+        <v>-7.77012</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.346809</v>
+        <v>-6.536958</v>
       </c>
       <c r="AB11" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
       <c r="AC11" t="n">
-        <v>-7.913229</v>
+        <v>-1.293962</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B12" t="n">
-        <v>98542</v>
+        <v>103165</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>99.300003</v>
       </c>
       <c r="D12" t="n">
-        <v>91.33000199999999</v>
+        <v>95.650002</v>
       </c>
       <c r="E12" t="n">
-        <v>216.699997</v>
+        <v>234.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1809</v>
+        <v>5.1827</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4098</v>
+        <v>5.2797</v>
       </c>
       <c r="H12" t="n">
-        <v>3785.379883</v>
+        <v>4130.290039</v>
       </c>
       <c r="I12" t="n">
-        <v>11028.740234</v>
+        <v>12390.69043</v>
       </c>
       <c r="J12" t="n">
-        <v>30775.429688</v>
+        <v>32845.128906</v>
       </c>
       <c r="K12" t="n">
-        <v>1804.099976</v>
+        <v>1762.900024</v>
       </c>
       <c r="L12" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
       <c r="M12" t="n">
-        <v>114.809998</v>
+        <v>110.010002</v>
       </c>
       <c r="N12" t="n">
-        <v>1675</v>
+        <v>1637</v>
       </c>
       <c r="O12" t="n">
-        <v>743.75</v>
+        <v>616.25</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.503264</v>
+        <v>4.691401</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.364061</v>
+        <v>4.526319</v>
       </c>
       <c r="R12" t="n">
-        <v>-16.440989</v>
+        <v>4.730099</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02564</v>
+        <v>8.214122</v>
       </c>
       <c r="T12" t="n">
-        <v>9.016501</v>
+        <v>0.034744</v>
       </c>
       <c r="U12" t="n">
-        <v>5.709709</v>
+        <v>-2.404899</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.391999999999999</v>
+        <v>9.111639</v>
       </c>
       <c r="W12" t="n">
-        <v>-8.712982999999999</v>
+        <v>12.3491</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.713196</v>
+        <v>6.725168</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.094751</v>
+        <v>-2.283684</v>
       </c>
       <c r="Z12" t="n">
-        <v>-7.77012</v>
+        <v>-6.751134</v>
       </c>
       <c r="AA12" t="n">
-        <v>-6.536958</v>
+        <v>-4.180817</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.293962</v>
+        <v>-17.142857</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B13" t="n">
-        <v>103165</v>
+        <v>109523</v>
       </c>
       <c r="C13" t="n">
-        <v>99.300003</v>
+        <v>105.830002</v>
       </c>
       <c r="D13" t="n">
-        <v>95.650002</v>
+        <v>106.800003</v>
       </c>
       <c r="E13" t="n">
-        <v>234.5</v>
+        <v>226</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1827</v>
+        <v>5.1219</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2797</v>
+        <v>5.1318</v>
       </c>
       <c r="H13" t="n">
-        <v>4130.290039</v>
+        <v>3955</v>
       </c>
       <c r="I13" t="n">
-        <v>12390.69043</v>
+        <v>11816.200195</v>
       </c>
       <c r="J13" t="n">
-        <v>32845.128906</v>
+        <v>31510.429688</v>
       </c>
       <c r="K13" t="n">
-        <v>1762.900024</v>
+        <v>1712.800049</v>
       </c>
       <c r="L13" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
       <c r="M13" t="n">
-        <v>110.010002</v>
+        <v>96.489998</v>
       </c>
       <c r="N13" t="n">
-        <v>1637</v>
+        <v>1507.5</v>
       </c>
       <c r="O13" t="n">
-        <v>616.25</v>
+        <v>673.75</v>
       </c>
       <c r="P13" t="n">
-        <v>4.691401</v>
+        <v>6.162943</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.526319</v>
+        <v>6.576031</v>
       </c>
       <c r="R13" t="n">
-        <v>4.730099</v>
+        <v>11.657085</v>
       </c>
       <c r="S13" t="n">
-        <v>8.214122</v>
+        <v>-3.624733</v>
       </c>
       <c r="T13" t="n">
-        <v>0.034744</v>
+        <v>-1.173135</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.404899</v>
+        <v>-2.801289</v>
       </c>
       <c r="V13" t="n">
-        <v>9.111639</v>
+        <v>-4.244013</v>
       </c>
       <c r="W13" t="n">
-        <v>12.3491</v>
+        <v>-4.636467</v>
       </c>
       <c r="X13" t="n">
-        <v>6.725168</v>
+        <v>-4.063614</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.283684</v>
+        <v>-2.841907</v>
       </c>
       <c r="Z13" t="n">
-        <v>-6.751134</v>
+        <v>-9.196916999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>-4.180817</v>
+        <v>-12.289795</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
       <c r="AC13" t="n">
-        <v>-17.142857</v>
+        <v>9.330629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B14" t="n">
-        <v>109523</v>
+        <v>110037</v>
       </c>
       <c r="C14" t="n">
-        <v>105.830002</v>
+        <v>106.459999</v>
       </c>
       <c r="D14" t="n">
-        <v>106.800003</v>
+        <v>105.440002</v>
       </c>
       <c r="E14" t="n">
-        <v>226</v>
+        <v>213.5</v>
       </c>
       <c r="F14" t="n">
-        <v>5.1219</v>
+        <v>5.3962</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1318</v>
+        <v>5.3031</v>
       </c>
       <c r="H14" t="n">
-        <v>3955</v>
+        <v>3585.620117</v>
       </c>
       <c r="I14" t="n">
-        <v>11816.200195</v>
+        <v>10575.620117</v>
       </c>
       <c r="J14" t="n">
-        <v>31510.429688</v>
+        <v>28725.509766</v>
       </c>
       <c r="K14" t="n">
-        <v>1712.800049</v>
+        <v>1662.400024</v>
       </c>
       <c r="L14" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
       <c r="M14" t="n">
-        <v>96.489998</v>
+        <v>87.959999</v>
       </c>
       <c r="N14" t="n">
-        <v>1507.5</v>
+        <v>1364.75</v>
       </c>
       <c r="O14" t="n">
-        <v>673.75</v>
+        <v>677.5</v>
       </c>
       <c r="P14" t="n">
-        <v>6.162943</v>
+        <v>0.469308</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.576031</v>
+        <v>0.595292</v>
       </c>
       <c r="R14" t="n">
-        <v>11.657085</v>
+        <v>-1.273409</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.624733</v>
+        <v>-5.530973</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.173135</v>
+        <v>5.355436</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.801289</v>
+        <v>3.338009</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.244013</v>
+        <v>-9.339567000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-4.636467</v>
+        <v>-10.498976</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.063614</v>
+        <v>-8.838089</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.841907</v>
+        <v>-2.942552</v>
       </c>
       <c r="Z14" t="n">
-        <v>-9.196916999999999</v>
+        <v>-11.233953</v>
       </c>
       <c r="AA14" t="n">
-        <v>-12.289795</v>
+        <v>-8.840293000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.330629</v>
+        <v>0.556586</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B15" t="n">
-        <v>110037</v>
+        <v>116037</v>
       </c>
       <c r="C15" t="n">
-        <v>106.459999</v>
+        <v>112.150002</v>
       </c>
       <c r="D15" t="n">
-        <v>105.440002</v>
+        <v>112.5</v>
       </c>
       <c r="E15" t="n">
-        <v>213.5</v>
+        <v>220.240005</v>
       </c>
       <c r="F15" t="n">
-        <v>5.3962</v>
+        <v>5.2885</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3031</v>
+        <v>5.2737</v>
       </c>
       <c r="H15" t="n">
-        <v>3585.620117</v>
+        <v>3871.97998</v>
       </c>
       <c r="I15" t="n">
-        <v>10575.620117</v>
+        <v>10988.150391</v>
       </c>
       <c r="J15" t="n">
-        <v>28725.509766</v>
+        <v>32732.949219</v>
       </c>
       <c r="K15" t="n">
-        <v>1662.400024</v>
+        <v>1635.900024</v>
       </c>
       <c r="L15" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
       <c r="M15" t="n">
-        <v>87.959999</v>
+        <v>94.83000199999999</v>
       </c>
       <c r="N15" t="n">
-        <v>1364.75</v>
+        <v>1407</v>
       </c>
       <c r="O15" t="n">
-        <v>677.5</v>
+        <v>691.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0.469308</v>
+        <v>5.452711</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.595292</v>
+        <v>5.344733</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.273409</v>
+        <v>6.695749</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.530973</v>
+        <v>3.156911</v>
       </c>
       <c r="T15" t="n">
-        <v>5.355436</v>
+        <v>-1.995855</v>
       </c>
       <c r="U15" t="n">
-        <v>3.338009</v>
+        <v>-0.55439</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.339567000000001</v>
+        <v>7.986341</v>
       </c>
       <c r="W15" t="n">
-        <v>-10.498976</v>
+        <v>3.900767</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.838089</v>
+        <v>13.950804</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2.942552</v>
+        <v>-1.594081</v>
       </c>
       <c r="Z15" t="n">
-        <v>-11.233953</v>
+        <v>8.856460999999999</v>
       </c>
       <c r="AA15" t="n">
-        <v>-8.840293000000001</v>
+        <v>7.810372</v>
       </c>
       <c r="AB15" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.556586</v>
+        <v>2.066421</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B16" t="n">
-        <v>116037</v>
+        <v>112486</v>
       </c>
       <c r="C16" t="n">
-        <v>112.150002</v>
+        <v>108.580002</v>
       </c>
       <c r="D16" t="n">
-        <v>112.5</v>
+        <v>99.980003</v>
       </c>
       <c r="E16" t="n">
-        <v>220.240005</v>
+        <v>233.25</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2885</v>
+        <v>5.2682</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2737</v>
+        <v>5.4362</v>
       </c>
       <c r="H16" t="n">
-        <v>3871.97998</v>
+        <v>4080.110107</v>
       </c>
       <c r="I16" t="n">
-        <v>10988.150391</v>
+        <v>11468</v>
       </c>
       <c r="J16" t="n">
-        <v>32732.949219</v>
+        <v>34589.769531</v>
       </c>
       <c r="K16" t="n">
-        <v>1635.900024</v>
+        <v>1746</v>
       </c>
       <c r="L16" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
       <c r="M16" t="n">
-        <v>94.83000199999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>1407</v>
+        <v>1469.5</v>
       </c>
       <c r="O16" t="n">
-        <v>691.5</v>
+        <v>662</v>
       </c>
       <c r="P16" t="n">
-        <v>5.452711</v>
+        <v>-3.060231</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.344733</v>
+        <v>-3.183236</v>
       </c>
       <c r="R16" t="n">
-        <v>6.695749</v>
+        <v>-11.128886</v>
       </c>
       <c r="S16" t="n">
-        <v>3.156911</v>
+        <v>5.90719</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.995855</v>
+        <v>-0.38385</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.55439</v>
+        <v>3.081326</v>
       </c>
       <c r="V16" t="n">
-        <v>7.986341</v>
+        <v>5.375289</v>
       </c>
       <c r="W16" t="n">
-        <v>3.900767</v>
+        <v>4.366973</v>
       </c>
       <c r="X16" t="n">
-        <v>13.950804</v>
+        <v>5.672634</v>
       </c>
       <c r="Y16" t="n">
-        <v>-1.594081</v>
+        <v>6.730239</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.856460999999999</v>
+        <v>-6.910893</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.810372</v>
+        <v>-9.912476</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.066421</v>
+        <v>-4.266088</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B17" t="n">
-        <v>112486</v>
+        <v>110031</v>
       </c>
       <c r="C17" t="n">
-        <v>108.580002</v>
+        <v>105.949997</v>
       </c>
       <c r="D17" t="n">
-        <v>99.980003</v>
+        <v>96.519997</v>
       </c>
       <c r="E17" t="n">
-        <v>233.25</v>
+        <v>225</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2682</v>
+        <v>5.2846</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4362</v>
+        <v>5.633</v>
       </c>
       <c r="H17" t="n">
-        <v>4080.110107</v>
+        <v>3839.5</v>
       </c>
       <c r="I17" t="n">
-        <v>11468</v>
+        <v>10466.480469</v>
       </c>
       <c r="J17" t="n">
-        <v>34589.769531</v>
+        <v>33147.25</v>
       </c>
       <c r="K17" t="n">
-        <v>1746</v>
+        <v>1819.699951</v>
       </c>
       <c r="L17" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
       <c r="M17" t="n">
-        <v>85.43000000000001</v>
+        <v>85.910004</v>
       </c>
       <c r="N17" t="n">
-        <v>1469.5</v>
+        <v>1519.25</v>
       </c>
       <c r="O17" t="n">
-        <v>662</v>
+        <v>678.5</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.060231</v>
+        <v>-2.182494</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.183236</v>
+        <v>-2.422182</v>
       </c>
       <c r="R17" t="n">
-        <v>-11.128886</v>
+        <v>-3.460699</v>
       </c>
       <c r="S17" t="n">
-        <v>5.90719</v>
+        <v>-3.536977</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.38385</v>
+        <v>0.311299</v>
       </c>
       <c r="U17" t="n">
-        <v>3.081326</v>
+        <v>3.620171</v>
       </c>
       <c r="V17" t="n">
-        <v>5.375289</v>
+        <v>-5.897147</v>
       </c>
       <c r="W17" t="n">
-        <v>4.366973</v>
+        <v>-8.733166000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5.672634</v>
+        <v>-4.170365</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.730239</v>
+        <v>4.221074</v>
       </c>
       <c r="Z17" t="n">
-        <v>-6.910893</v>
+        <v>-0.360026</v>
       </c>
       <c r="AA17" t="n">
-        <v>-9.912476</v>
+        <v>0.561867</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4.266088</v>
+        <v>2.492447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B18" t="n">
-        <v>110031</v>
+        <v>113532</v>
       </c>
       <c r="C18" t="n">
-        <v>105.949997</v>
+        <v>109.839996</v>
       </c>
       <c r="D18" t="n">
-        <v>96.519997</v>
+        <v>99.44000200000001</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>228.199997</v>
       </c>
       <c r="F18" t="n">
-        <v>5.2846</v>
+        <v>5.1149</v>
       </c>
       <c r="G18" t="n">
-        <v>5.633</v>
+        <v>5.5471</v>
       </c>
       <c r="H18" t="n">
-        <v>3839.5</v>
+        <v>4076.600098</v>
       </c>
       <c r="I18" t="n">
-        <v>10466.480469</v>
+        <v>11584.549805</v>
       </c>
       <c r="J18" t="n">
-        <v>33147.25</v>
+        <v>34086.039062</v>
       </c>
       <c r="K18" t="n">
-        <v>1819.699951</v>
+        <v>1929.5</v>
       </c>
       <c r="L18" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
       <c r="M18" t="n">
-        <v>85.910004</v>
+        <v>84.489998</v>
       </c>
       <c r="N18" t="n">
-        <v>1519.25</v>
+        <v>1538</v>
       </c>
       <c r="O18" t="n">
-        <v>678.5</v>
+        <v>679.75</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.182494</v>
+        <v>3.181831</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.422182</v>
+        <v>3.671543</v>
       </c>
       <c r="R18" t="n">
-        <v>-3.460699</v>
+        <v>3.025286</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.536977</v>
+        <v>1.422221</v>
       </c>
       <c r="T18" t="n">
-        <v>0.311299</v>
+        <v>-3.211211</v>
       </c>
       <c r="U18" t="n">
-        <v>3.620171</v>
+        <v>-1.524939</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.897147</v>
+        <v>6.175286</v>
       </c>
       <c r="W18" t="n">
-        <v>-8.733166000000001</v>
+        <v>10.682381</v>
       </c>
       <c r="X18" t="n">
-        <v>-4.170365</v>
+        <v>2.832178</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.221074</v>
+        <v>6.033964</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.360026</v>
+        <v>-1.731871</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.561867</v>
+        <v>-1.652899</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.492447</v>
+        <v>0.18423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B19" t="n">
-        <v>113532</v>
+        <v>104932</v>
       </c>
       <c r="C19" t="n">
-        <v>109.839996</v>
+        <v>101.150002</v>
       </c>
       <c r="D19" t="n">
-        <v>99.44000200000001</v>
+        <v>88.360001</v>
       </c>
       <c r="E19" t="n">
-        <v>228.199997</v>
+        <v>229.300003</v>
       </c>
       <c r="F19" t="n">
-        <v>5.1149</v>
+        <v>5.1997</v>
       </c>
       <c r="G19" t="n">
-        <v>5.5471</v>
+        <v>5.514</v>
       </c>
       <c r="H19" t="n">
-        <v>4076.600098</v>
+        <v>3970.149902</v>
       </c>
       <c r="I19" t="n">
-        <v>11584.549805</v>
+        <v>11455.540039</v>
       </c>
       <c r="J19" t="n">
-        <v>34086.039062</v>
+        <v>32656.699219</v>
       </c>
       <c r="K19" t="n">
-        <v>1929.5</v>
+        <v>1828.900024</v>
       </c>
       <c r="L19" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
       <c r="M19" t="n">
-        <v>84.489998</v>
+        <v>83.889999</v>
       </c>
       <c r="N19" t="n">
-        <v>1538</v>
+        <v>1490.5</v>
       </c>
       <c r="O19" t="n">
-        <v>679.75</v>
+        <v>629.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.181831</v>
+        <v>-7.574957</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.671543</v>
+        <v>-7.911503</v>
       </c>
       <c r="R19" t="n">
-        <v>3.025286</v>
+        <v>-11.142399</v>
       </c>
       <c r="S19" t="n">
-        <v>1.422221</v>
+        <v>0.482036</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.211211</v>
+        <v>1.657897</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.524939</v>
+        <v>-0.59671</v>
       </c>
       <c r="V19" t="n">
-        <v>6.175286</v>
+        <v>-2.611249</v>
       </c>
       <c r="W19" t="n">
-        <v>10.682381</v>
+        <v>-1.113636</v>
       </c>
       <c r="X19" t="n">
-        <v>2.832178</v>
+        <v>-4.193329</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.033964</v>
+        <v>-5.213785</v>
       </c>
       <c r="Z19" t="n">
-        <v>-1.731871</v>
+        <v>-2.307594</v>
       </c>
       <c r="AA19" t="n">
-        <v>-1.652899</v>
+        <v>-0.710141</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.18423</v>
+        <v>-7.392424</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B20" t="n">
-        <v>104932</v>
+        <v>101882</v>
       </c>
       <c r="C20" t="n">
-        <v>101.150002</v>
+        <v>98.489998</v>
       </c>
       <c r="D20" t="n">
-        <v>88.360001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>229.300003</v>
+        <v>229.75</v>
       </c>
       <c r="F20" t="n">
-        <v>5.1997</v>
+        <v>5.0927</v>
       </c>
       <c r="G20" t="n">
-        <v>5.514</v>
+        <v>5.5518</v>
       </c>
       <c r="H20" t="n">
-        <v>3970.149902</v>
+        <v>4109.310059</v>
       </c>
       <c r="I20" t="n">
-        <v>11455.540039</v>
+        <v>12221.910156</v>
       </c>
       <c r="J20" t="n">
-        <v>32656.699219</v>
+        <v>33274.148438</v>
       </c>
       <c r="K20" t="n">
-        <v>1828.900024</v>
+        <v>1969</v>
       </c>
       <c r="L20" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
       <c r="M20" t="n">
-        <v>83.889999</v>
+        <v>79.769997</v>
       </c>
       <c r="N20" t="n">
-        <v>1490.5</v>
+        <v>1505.5</v>
       </c>
       <c r="O20" t="n">
-        <v>629.5</v>
+        <v>660.5</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.574957</v>
+        <v>-2.906644</v>
       </c>
       <c r="Q20" t="n">
-        <v>-7.911503</v>
+        <v>-2.629761</v>
       </c>
       <c r="R20" t="n">
-        <v>-11.142399</v>
+        <v>-0.611137</v>
       </c>
       <c r="S20" t="n">
-        <v>0.482036</v>
+        <v>0.196248</v>
       </c>
       <c r="T20" t="n">
-        <v>1.657897</v>
+        <v>-2.057809</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.59671</v>
+        <v>0.6855250000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.611249</v>
+        <v>3.505161</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.113636</v>
+        <v>6.689952</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.193329</v>
+        <v>1.890728</v>
       </c>
       <c r="Y20" t="n">
-        <v>-5.213785</v>
+        <v>7.660341</v>
       </c>
       <c r="Z20" t="n">
-        <v>-2.307594</v>
+        <v>-1.791051</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.710141</v>
+        <v>-4.911197</v>
       </c>
       <c r="AB20" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
       <c r="AC20" t="n">
-        <v>-7.392424</v>
+        <v>4.924543</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B21" t="n">
-        <v>101882</v>
+        <v>104432</v>
       </c>
       <c r="C21" t="n">
-        <v>98.489998</v>
+        <v>100.900002</v>
       </c>
       <c r="D21" t="n">
-        <v>87.81999999999999</v>
+        <v>89</v>
       </c>
       <c r="E21" t="n">
         <v>229.75</v>
       </c>
       <c r="F21" t="n">
-        <v>5.0927</v>
+        <v>4.9762</v>
       </c>
       <c r="G21" t="n">
-        <v>5.5518</v>
+        <v>5.4883</v>
       </c>
       <c r="H21" t="n">
-        <v>4109.310059</v>
+        <v>4169.47998</v>
       </c>
       <c r="I21" t="n">
-        <v>12221.910156</v>
+        <v>12226.580078</v>
       </c>
       <c r="J21" t="n">
-        <v>33274.148438</v>
+        <v>34098.160156</v>
       </c>
       <c r="K21" t="n">
-        <v>1969</v>
+        <v>1990.099976</v>
       </c>
       <c r="L21" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
       <c r="M21" t="n">
-        <v>79.769997</v>
+        <v>79.540001</v>
       </c>
       <c r="N21" t="n">
-        <v>1505.5</v>
+        <v>1444.25</v>
       </c>
       <c r="O21" t="n">
-        <v>660.5</v>
+        <v>636</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.906644</v>
+        <v>2.502896</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.629761</v>
+        <v>2.446953</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.611137</v>
+        <v>1.343658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.196248</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.057809</v>
+        <v>-2.287586</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6855250000000001</v>
+        <v>-1.143772</v>
       </c>
       <c r="V21" t="n">
-        <v>3.505161</v>
+        <v>1.464234</v>
       </c>
       <c r="W21" t="n">
-        <v>6.689952</v>
+        <v>0.038209</v>
       </c>
       <c r="X21" t="n">
-        <v>1.890728</v>
+        <v>2.476432</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.660341</v>
+        <v>1.071609</v>
       </c>
       <c r="Z21" t="n">
-        <v>-1.791051</v>
+        <v>1.466897</v>
       </c>
       <c r="AA21" t="n">
-        <v>-4.911197</v>
+        <v>-0.288324</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.924543</v>
+        <v>-3.709311</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B22" t="n">
-        <v>104432</v>
+        <v>108335</v>
       </c>
       <c r="C22" t="n">
-        <v>100.900002</v>
+        <v>104.839996</v>
       </c>
       <c r="D22" t="n">
-        <v>89</v>
+        <v>100.5</v>
       </c>
       <c r="E22" t="n">
-        <v>229.75</v>
+        <v>233.25</v>
       </c>
       <c r="F22" t="n">
-        <v>4.9762</v>
+        <v>5.0348</v>
       </c>
       <c r="G22" t="n">
-        <v>5.4883</v>
+        <v>5.4012</v>
       </c>
       <c r="H22" t="n">
-        <v>4169.47998</v>
+        <v>4179.830078</v>
       </c>
       <c r="I22" t="n">
-        <v>12226.580078</v>
+        <v>12935.290039</v>
       </c>
       <c r="J22" t="n">
-        <v>34098.160156</v>
+        <v>32908.269531</v>
       </c>
       <c r="K22" t="n">
-        <v>1990.099976</v>
+        <v>1963.900024</v>
       </c>
       <c r="L22" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
       <c r="M22" t="n">
-        <v>79.540001</v>
+        <v>72.660004</v>
       </c>
       <c r="N22" t="n">
-        <v>1444.25</v>
+        <v>1299.75</v>
       </c>
       <c r="O22" t="n">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="P22" t="n">
-        <v>2.502896</v>
+        <v>3.73736</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.446953</v>
+        <v>3.904851</v>
       </c>
       <c r="R22" t="n">
-        <v>1.343658</v>
+        <v>12.921348</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.523395</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.287586</v>
+        <v>1.177604</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.143772</v>
+        <v>-1.587013</v>
       </c>
       <c r="V22" t="n">
-        <v>1.464234</v>
+        <v>0.248235</v>
       </c>
       <c r="W22" t="n">
-        <v>0.038209</v>
+        <v>5.796469</v>
       </c>
       <c r="X22" t="n">
-        <v>2.476432</v>
+        <v>-3.489604</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.071609</v>
+        <v>-1.316514</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.466897</v>
+        <v>-11.318055</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.288324</v>
+        <v>-8.649732</v>
       </c>
       <c r="AB22" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
       <c r="AC22" t="n">
-        <v>-3.709311</v>
+        <v>-6.603774</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B23" t="n">
-        <v>108335</v>
+        <v>118087</v>
       </c>
       <c r="C23" t="n">
-        <v>104.839996</v>
+        <v>114.169998</v>
       </c>
       <c r="D23" t="n">
-        <v>100.5</v>
+        <v>109.5</v>
       </c>
       <c r="E23" t="n">
-        <v>233.25</v>
+        <v>235.25</v>
       </c>
       <c r="F23" t="n">
-        <v>5.0348</v>
+        <v>4.8556</v>
       </c>
       <c r="G23" t="n">
-        <v>5.4012</v>
+        <v>5.2739</v>
       </c>
       <c r="H23" t="n">
-        <v>4179.830078</v>
+        <v>4450.379883</v>
       </c>
       <c r="I23" t="n">
-        <v>12935.290039</v>
+        <v>13787.919922</v>
       </c>
       <c r="J23" t="n">
-        <v>32908.269531</v>
+        <v>34407.601562</v>
       </c>
       <c r="K23" t="n">
-        <v>1963.900024</v>
+        <v>1921.099976</v>
       </c>
       <c r="L23" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
       <c r="M23" t="n">
-        <v>72.660004</v>
+        <v>74.900002</v>
       </c>
       <c r="N23" t="n">
-        <v>1299.75</v>
+        <v>1557.25</v>
       </c>
       <c r="O23" t="n">
-        <v>594</v>
+        <v>554.5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.73736</v>
+        <v>9.001708000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.904851</v>
+        <v>8.899277</v>
       </c>
       <c r="R23" t="n">
-        <v>12.921348</v>
+        <v>8.955223999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>1.523395</v>
+        <v>0.857449</v>
       </c>
       <c r="T23" t="n">
-        <v>1.177604</v>
+        <v>-3.559231</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.587013</v>
+        <v>-2.35688</v>
       </c>
       <c r="V23" t="n">
-        <v>0.248235</v>
+        <v>6.472746</v>
       </c>
       <c r="W23" t="n">
-        <v>5.796469</v>
+        <v>6.591502</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.489604</v>
+        <v>4.556095</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.316514</v>
+        <v>-2.179339</v>
       </c>
       <c r="Z23" t="n">
-        <v>-11.318055</v>
+        <v>3.745048</v>
       </c>
       <c r="AA23" t="n">
-        <v>-8.649732</v>
+        <v>3.082849</v>
       </c>
       <c r="AB23" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.603774</v>
+        <v>-6.649832</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B24" t="n">
-        <v>118087</v>
+        <v>121943</v>
       </c>
       <c r="C24" t="n">
-        <v>114.169998</v>
+        <v>117.949997</v>
       </c>
       <c r="D24" t="n">
-        <v>109.5</v>
+        <v>112.900002</v>
       </c>
       <c r="E24" t="n">
-        <v>235.25</v>
+        <v>239.820007</v>
       </c>
       <c r="F24" t="n">
-        <v>4.8556</v>
+        <v>4.7233</v>
       </c>
       <c r="G24" t="n">
-        <v>5.2739</v>
+        <v>5.1895</v>
       </c>
       <c r="H24" t="n">
-        <v>4450.379883</v>
+        <v>4588.959961</v>
       </c>
       <c r="I24" t="n">
-        <v>13787.919922</v>
+        <v>14346.019531</v>
       </c>
       <c r="J24" t="n">
-        <v>34407.601562</v>
+        <v>35559.53125</v>
       </c>
       <c r="K24" t="n">
-        <v>1921.099976</v>
+        <v>1970.5</v>
       </c>
       <c r="L24" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
       <c r="M24" t="n">
-        <v>74.900002</v>
+        <v>85.55999799999999</v>
       </c>
       <c r="N24" t="n">
-        <v>1557.25</v>
+        <v>1445.75</v>
       </c>
       <c r="O24" t="n">
-        <v>554.5</v>
+        <v>504</v>
       </c>
       <c r="P24" t="n">
-        <v>9.001708000000001</v>
+        <v>3.265389</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.899277</v>
+        <v>3.310851</v>
       </c>
       <c r="R24" t="n">
-        <v>8.955223999999999</v>
+        <v>3.105024</v>
       </c>
       <c r="S24" t="n">
-        <v>0.857449</v>
+        <v>1.942617</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.559231</v>
+        <v>-2.724687</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.35688</v>
+        <v>-1.600337</v>
       </c>
       <c r="V24" t="n">
-        <v>6.472746</v>
+        <v>3.113893</v>
       </c>
       <c r="W24" t="n">
-        <v>6.591502</v>
+        <v>4.047743</v>
       </c>
       <c r="X24" t="n">
-        <v>4.556095</v>
+        <v>3.347893</v>
       </c>
       <c r="Y24" t="n">
-        <v>-2.179339</v>
+        <v>2.571445</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.745048</v>
+        <v>15.79842</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.082849</v>
+        <v>14.232304</v>
       </c>
       <c r="AB24" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
       <c r="AC24" t="n">
-        <v>-6.649832</v>
+        <v>-9.107303999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B25" t="n">
-        <v>121943</v>
+        <v>115742</v>
       </c>
       <c r="C25" t="n">
-        <v>117.949997</v>
+        <v>112.309998</v>
       </c>
       <c r="D25" t="n">
-        <v>112.900002</v>
+        <v>104.199997</v>
       </c>
       <c r="E25" t="n">
-        <v>239.820007</v>
+        <v>247.649994</v>
       </c>
       <c r="F25" t="n">
-        <v>4.7233</v>
+        <v>4.8884</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1895</v>
+        <v>5.313</v>
       </c>
       <c r="H25" t="n">
-        <v>4588.959961</v>
+        <v>4507.660156</v>
       </c>
       <c r="I25" t="n">
-        <v>14346.019531</v>
+        <v>14034.969727</v>
       </c>
       <c r="J25" t="n">
-        <v>35559.53125</v>
+        <v>34721.910156</v>
       </c>
       <c r="K25" t="n">
-        <v>1970.5</v>
+        <v>1938.199951</v>
       </c>
       <c r="L25" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
       <c r="M25" t="n">
-        <v>85.55999799999999</v>
+        <v>86.860001</v>
       </c>
       <c r="N25" t="n">
-        <v>1445.75</v>
+        <v>1360</v>
       </c>
       <c r="O25" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="P25" t="n">
-        <v>3.265389</v>
+        <v>-5.085163</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.310851</v>
+        <v>-4.781687</v>
       </c>
       <c r="R25" t="n">
-        <v>3.105024</v>
+        <v>-7.705938</v>
       </c>
       <c r="S25" t="n">
-        <v>1.942617</v>
+        <v>3.264943</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.724687</v>
+        <v>3.49544</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.600337</v>
+        <v>2.379812</v>
       </c>
       <c r="V25" t="n">
-        <v>3.113893</v>
+        <v>-1.771639</v>
       </c>
       <c r="W25" t="n">
-        <v>4.047743</v>
+        <v>-2.168196</v>
       </c>
       <c r="X25" t="n">
-        <v>3.347893</v>
+        <v>-2.355546</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.571445</v>
+        <v>-1.63918</v>
       </c>
       <c r="Z25" t="n">
-        <v>15.79842</v>
+        <v>2.237157</v>
       </c>
       <c r="AA25" t="n">
-        <v>14.232304</v>
+        <v>1.519405</v>
       </c>
       <c r="AB25" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
       <c r="AC25" t="n">
-        <v>-9.107303999999999</v>
+        <v>-8.531746</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B26" t="n">
-        <v>115742</v>
+        <v>116565</v>
       </c>
       <c r="C26" t="n">
-        <v>112.309998</v>
+        <v>113.150002</v>
       </c>
       <c r="D26" t="n">
-        <v>104.199997</v>
+        <v>101.639999</v>
       </c>
       <c r="E26" t="n">
-        <v>247.649994</v>
+        <v>238.789993</v>
       </c>
       <c r="F26" t="n">
-        <v>4.8884</v>
+        <v>5.0328</v>
       </c>
       <c r="G26" t="n">
-        <v>5.313</v>
+        <v>5.3197</v>
       </c>
       <c r="H26" t="n">
-        <v>4507.660156</v>
+        <v>4288.049805</v>
       </c>
       <c r="I26" t="n">
-        <v>14034.969727</v>
+        <v>13219.320312</v>
       </c>
       <c r="J26" t="n">
-        <v>34721.910156</v>
+        <v>33507.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1938.199951</v>
+        <v>1848.099976</v>
       </c>
       <c r="L26" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
       <c r="M26" t="n">
-        <v>86.860001</v>
+        <v>95.30999799999999</v>
       </c>
       <c r="N26" t="n">
-        <v>1360</v>
+        <v>1275</v>
       </c>
       <c r="O26" t="n">
-        <v>461</v>
+        <v>476.75</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.085163</v>
+        <v>0.711064</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.781687</v>
+        <v>0.747933</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.705938</v>
+        <v>-2.456812</v>
       </c>
       <c r="S26" t="n">
-        <v>3.264943</v>
+        <v>-3.57763</v>
       </c>
       <c r="T26" t="n">
-        <v>3.49544</v>
+        <v>2.953934</v>
       </c>
       <c r="U26" t="n">
-        <v>2.379812</v>
+        <v>0.126098</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.771639</v>
+        <v>-4.871937</v>
       </c>
       <c r="W26" t="n">
-        <v>-2.168196</v>
+        <v>-5.811551</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.355546</v>
+        <v>-3.497533</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.63918</v>
+        <v>-4.648642</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.237157</v>
+        <v>8.561526000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.519405</v>
+        <v>9.728294999999999</v>
       </c>
       <c r="AB26" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>-8.531746</v>
+        <v>3.416486</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B27" t="n">
-        <v>116565</v>
+        <v>113144</v>
       </c>
       <c r="C27" t="n">
-        <v>113.150002</v>
+        <v>109.620003</v>
       </c>
       <c r="D27" t="n">
-        <v>101.639999</v>
+        <v>94.199997</v>
       </c>
       <c r="E27" t="n">
-        <v>238.789993</v>
+        <v>234</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0328</v>
+        <v>5.0461</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3197</v>
+        <v>5.3537</v>
       </c>
       <c r="H27" t="n">
-        <v>4288.049805</v>
+        <v>4193.799805</v>
       </c>
       <c r="I27" t="n">
-        <v>13219.320312</v>
+        <v>12851.240234</v>
       </c>
       <c r="J27" t="n">
-        <v>33507.5</v>
+        <v>33052.871094</v>
       </c>
       <c r="K27" t="n">
-        <v>1848.099976</v>
+        <v>1985.199951</v>
       </c>
       <c r="L27" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
       <c r="M27" t="n">
-        <v>95.30999799999999</v>
+        <v>87.410004</v>
       </c>
       <c r="N27" t="n">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="O27" t="n">
-        <v>476.75</v>
+        <v>478.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0.711064</v>
+        <v>-2.934843</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.747933</v>
+        <v>-3.119751</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.456812</v>
+        <v>-7.319955</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.57763</v>
+        <v>-2.005944</v>
       </c>
       <c r="T27" t="n">
-        <v>2.953934</v>
+        <v>0.264265</v>
       </c>
       <c r="U27" t="n">
-        <v>0.126098</v>
+        <v>0.639141</v>
       </c>
       <c r="V27" t="n">
-        <v>-4.871937</v>
+        <v>-2.197969</v>
       </c>
       <c r="W27" t="n">
-        <v>-5.811551</v>
+        <v>-2.78441</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.497533</v>
+        <v>-1.356797</v>
       </c>
       <c r="Y27" t="n">
-        <v>-4.648642</v>
+        <v>7.418429</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.561526000000001</v>
+        <v>-10.761102</v>
       </c>
       <c r="AA27" t="n">
-        <v>9.728294999999999</v>
+        <v>-8.288736</v>
       </c>
       <c r="AB27" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.416486</v>
+        <v>0.419507</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B28" t="n">
-        <v>113144</v>
+        <v>127331</v>
       </c>
       <c r="C28" t="n">
-        <v>109.620003</v>
+        <v>123.57</v>
       </c>
       <c r="D28" t="n">
-        <v>94.199997</v>
+        <v>106.349998</v>
       </c>
       <c r="E28" t="n">
-        <v>234</v>
+        <v>249.699997</v>
       </c>
       <c r="F28" t="n">
-        <v>5.0461</v>
+        <v>4.9041</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3537</v>
+        <v>5.3628</v>
       </c>
       <c r="H28" t="n">
-        <v>4193.799805</v>
+        <v>4567.799805</v>
       </c>
       <c r="I28" t="n">
-        <v>12851.240234</v>
+        <v>14226.219727</v>
       </c>
       <c r="J28" t="n">
-        <v>33052.871094</v>
+        <v>35950.890625</v>
       </c>
       <c r="K28" t="n">
-        <v>1985.199951</v>
+        <v>2038.099976</v>
       </c>
       <c r="L28" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
       <c r="M28" t="n">
-        <v>87.410004</v>
+        <v>82.83000199999999</v>
       </c>
       <c r="N28" t="n">
-        <v>1287</v>
+        <v>1342.75</v>
       </c>
       <c r="O28" t="n">
-        <v>478.75</v>
+        <v>461.75</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.934843</v>
+        <v>12.538888</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.119751</v>
+        <v>12.725777</v>
       </c>
       <c r="R28" t="n">
-        <v>-7.319955</v>
+        <v>12.898091</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.005944</v>
+        <v>6.7094</v>
       </c>
       <c r="T28" t="n">
-        <v>0.264265</v>
+        <v>-2.814058</v>
       </c>
       <c r="U28" t="n">
-        <v>0.639141</v>
+        <v>0.169975</v>
       </c>
       <c r="V28" t="n">
-        <v>-2.197969</v>
+        <v>8.917927000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>-2.78441</v>
+        <v>10.699197</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.356797</v>
+        <v>8.76783</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.418429</v>
+        <v>2.66472</v>
       </c>
       <c r="Z28" t="n">
-        <v>-10.761102</v>
+        <v>-6.245369</v>
       </c>
       <c r="AA28" t="n">
-        <v>-8.288736</v>
+        <v>-5.239677</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.419507</v>
+        <v>-3.550914</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B29" t="n">
-        <v>127331</v>
+        <v>134185</v>
       </c>
       <c r="C29" t="n">
-        <v>123.57</v>
+        <v>130.389999</v>
       </c>
       <c r="D29" t="n">
-        <v>106.349998</v>
+        <v>113.199997</v>
       </c>
       <c r="E29" t="n">
-        <v>249.699997</v>
+        <v>257.609985</v>
       </c>
       <c r="F29" t="n">
-        <v>4.9041</v>
+        <v>4.8502</v>
       </c>
       <c r="G29" t="n">
-        <v>5.3628</v>
+        <v>5.343</v>
       </c>
       <c r="H29" t="n">
-        <v>4567.799805</v>
+        <v>4769.830078</v>
       </c>
       <c r="I29" t="n">
-        <v>14226.219727</v>
+        <v>15011.349609</v>
       </c>
       <c r="J29" t="n">
-        <v>35950.890625</v>
+        <v>37689.539062</v>
       </c>
       <c r="K29" t="n">
-        <v>2038.099976</v>
+        <v>2062.399902</v>
       </c>
       <c r="L29" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
       <c r="M29" t="n">
-        <v>82.83000199999999</v>
+        <v>77.040001</v>
       </c>
       <c r="N29" t="n">
-        <v>1342.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O29" t="n">
-        <v>461.75</v>
+        <v>471.25</v>
       </c>
       <c r="P29" t="n">
-        <v>12.538888</v>
+        <v>5.382821</v>
       </c>
       <c r="Q29" t="n">
-        <v>12.725777</v>
+        <v>5.519139</v>
       </c>
       <c r="R29" t="n">
-        <v>12.898091</v>
+        <v>6.440995</v>
       </c>
       <c r="S29" t="n">
-        <v>6.7094</v>
+        <v>3.167797</v>
       </c>
       <c r="T29" t="n">
-        <v>-2.814058</v>
+        <v>-1.099076</v>
       </c>
       <c r="U29" t="n">
-        <v>0.169975</v>
+        <v>-0.369214</v>
       </c>
       <c r="V29" t="n">
-        <v>8.917927000000001</v>
+        <v>4.422923</v>
       </c>
       <c r="W29" t="n">
-        <v>10.699197</v>
+        <v>5.518893</v>
       </c>
       <c r="X29" t="n">
-        <v>8.76783</v>
+        <v>4.836176</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.66472</v>
+        <v>1.192283</v>
       </c>
       <c r="Z29" t="n">
-        <v>-6.245369</v>
+        <v>-5.674036</v>
       </c>
       <c r="AA29" t="n">
-        <v>-5.239677</v>
+        <v>-6.990222</v>
       </c>
       <c r="AB29" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.550914</v>
+        <v>2.05739</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B30" t="n">
-        <v>134185</v>
+        <v>127752</v>
       </c>
       <c r="C30" t="n">
-        <v>130.389999</v>
+        <v>123.949997</v>
       </c>
       <c r="D30" t="n">
-        <v>113.199997</v>
+        <v>106.370003</v>
       </c>
       <c r="E30" t="n">
-        <v>257.609985</v>
+        <v>266.619995</v>
       </c>
       <c r="F30" t="n">
-        <v>4.8502</v>
+        <v>4.9503</v>
       </c>
       <c r="G30" t="n">
-        <v>5.343</v>
+        <v>5.3604</v>
       </c>
       <c r="H30" t="n">
-        <v>4769.830078</v>
+        <v>4845.649902</v>
       </c>
       <c r="I30" t="n">
-        <v>15011.349609</v>
+        <v>15164.009766</v>
       </c>
       <c r="J30" t="n">
-        <v>37689.539062</v>
+        <v>38150.300781</v>
       </c>
       <c r="K30" t="n">
-        <v>2062.399902</v>
+        <v>2048.399902</v>
       </c>
       <c r="L30" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
       <c r="M30" t="n">
-        <v>77.040001</v>
+        <v>81.709999</v>
       </c>
       <c r="N30" t="n">
-        <v>1293.5</v>
+        <v>1222.25</v>
       </c>
       <c r="O30" t="n">
-        <v>471.25</v>
+        <v>448.25</v>
       </c>
       <c r="P30" t="n">
-        <v>5.382821</v>
+        <v>-4.794128</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.519139</v>
+        <v>-4.939031</v>
       </c>
       <c r="R30" t="n">
-        <v>6.440995</v>
+        <v>-6.033564</v>
       </c>
       <c r="S30" t="n">
-        <v>3.167797</v>
+        <v>3.497539</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.099076</v>
+        <v>2.063833</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.369214</v>
+        <v>0.325665</v>
       </c>
       <c r="V30" t="n">
-        <v>4.422923</v>
+        <v>1.589571</v>
       </c>
       <c r="W30" t="n">
-        <v>5.518893</v>
+        <v>1.016965</v>
       </c>
       <c r="X30" t="n">
-        <v>4.836176</v>
+        <v>1.222519</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.192283</v>
+        <v>-0.678821</v>
       </c>
       <c r="Z30" t="n">
-        <v>-5.674036</v>
+        <v>5.861824</v>
       </c>
       <c r="AA30" t="n">
-        <v>-6.990222</v>
+        <v>6.061784</v>
       </c>
       <c r="AB30" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.05739</v>
+        <v>-4.880637</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B31" t="n">
-        <v>127752</v>
+        <v>129020</v>
       </c>
       <c r="C31" t="n">
-        <v>123.949997</v>
+        <v>125.25</v>
       </c>
       <c r="D31" t="n">
-        <v>106.370003</v>
+        <v>106.5</v>
       </c>
       <c r="E31" t="n">
-        <v>266.619995</v>
+        <v>281.100006</v>
       </c>
       <c r="F31" t="n">
-        <v>4.9503</v>
+        <v>4.9673</v>
       </c>
       <c r="G31" t="n">
-        <v>5.3604</v>
+        <v>5.381</v>
       </c>
       <c r="H31" t="n">
-        <v>4845.649902</v>
+        <v>5096.27002</v>
       </c>
       <c r="I31" t="n">
-        <v>15164.009766</v>
+        <v>16091.919922</v>
       </c>
       <c r="J31" t="n">
-        <v>38150.300781</v>
+        <v>38996.390625</v>
       </c>
       <c r="K31" t="n">
-        <v>2048.399902</v>
+        <v>2045.699951</v>
       </c>
       <c r="L31" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
       <c r="M31" t="n">
-        <v>81.709999</v>
+        <v>83.620003</v>
       </c>
       <c r="N31" t="n">
-        <v>1222.25</v>
+        <v>1128.25</v>
       </c>
       <c r="O31" t="n">
-        <v>448.25</v>
+        <v>415.75</v>
       </c>
       <c r="P31" t="n">
-        <v>-4.794128</v>
+        <v>0.992548</v>
       </c>
       <c r="Q31" t="n">
-        <v>-4.939031</v>
+        <v>1.048812</v>
       </c>
       <c r="R31" t="n">
-        <v>-6.033564</v>
+        <v>0.122212</v>
       </c>
       <c r="S31" t="n">
-        <v>3.497539</v>
+        <v>5.430955</v>
       </c>
       <c r="T31" t="n">
-        <v>2.063833</v>
+        <v>0.343408</v>
       </c>
       <c r="U31" t="n">
-        <v>0.325665</v>
+        <v>0.384297</v>
       </c>
       <c r="V31" t="n">
-        <v>1.589571</v>
+        <v>5.172064</v>
       </c>
       <c r="W31" t="n">
-        <v>1.016965</v>
+        <v>6.119161</v>
       </c>
       <c r="X31" t="n">
-        <v>1.222519</v>
+        <v>2.21778</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.678821</v>
+        <v>-0.131808</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.861824</v>
+        <v>3.177329</v>
       </c>
       <c r="AA31" t="n">
-        <v>6.061784</v>
+        <v>2.33754</v>
       </c>
       <c r="AB31" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
       <c r="AC31" t="n">
-        <v>-4.880637</v>
+        <v>-7.250418</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B32" t="n">
-        <v>129020</v>
+        <v>128106</v>
       </c>
       <c r="C32" t="n">
-        <v>125.25</v>
+        <v>124.330002</v>
       </c>
       <c r="D32" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="E32" t="n">
-        <v>281.100006</v>
+        <v>292.600006</v>
       </c>
       <c r="F32" t="n">
-        <v>4.9673</v>
+        <v>5.0141</v>
       </c>
       <c r="G32" t="n">
-        <v>5.381</v>
+        <v>5.4065</v>
       </c>
       <c r="H32" t="n">
-        <v>5096.27002</v>
+        <v>5254.350098</v>
       </c>
       <c r="I32" t="n">
-        <v>16091.919922</v>
+        <v>16379.459961</v>
       </c>
       <c r="J32" t="n">
-        <v>38996.390625</v>
+        <v>39807.371094</v>
       </c>
       <c r="K32" t="n">
-        <v>2045.699951</v>
+        <v>2217.399902</v>
       </c>
       <c r="L32" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
       <c r="M32" t="n">
-        <v>83.620003</v>
+        <v>87.480003</v>
       </c>
       <c r="N32" t="n">
-        <v>1128.25</v>
+        <v>1191.5</v>
       </c>
       <c r="O32" t="n">
-        <v>415.75</v>
+        <v>442</v>
       </c>
       <c r="P32" t="n">
-        <v>0.992548</v>
+        <v>-0.708417</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.048812</v>
+        <v>-0.734529</v>
       </c>
       <c r="R32" t="n">
-        <v>0.122212</v>
+        <v>2.347418</v>
       </c>
       <c r="S32" t="n">
-        <v>5.430955</v>
+        <v>4.091071</v>
       </c>
       <c r="T32" t="n">
-        <v>0.343408</v>
+        <v>0.942164</v>
       </c>
       <c r="U32" t="n">
-        <v>0.384297</v>
+        <v>0.473886</v>
       </c>
       <c r="V32" t="n">
-        <v>5.172064</v>
+        <v>3.101878</v>
       </c>
       <c r="W32" t="n">
-        <v>6.119161</v>
+        <v>1.78686</v>
       </c>
       <c r="X32" t="n">
-        <v>2.21778</v>
+        <v>2.07963</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.131808</v>
+        <v>8.393212999999999</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.177329</v>
+        <v>6.273953</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.33754</v>
+        <v>4.616121</v>
       </c>
       <c r="AB32" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
       <c r="AC32" t="n">
-        <v>-7.250418</v>
+        <v>6.313891</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B33" t="n">
-        <v>128106</v>
+        <v>125924</v>
       </c>
       <c r="C33" t="n">
-        <v>124.330002</v>
+        <v>122.379997</v>
       </c>
       <c r="D33" t="n">
-        <v>109</v>
+        <v>100.5</v>
       </c>
       <c r="E33" t="n">
-        <v>292.600006</v>
+        <v>291</v>
       </c>
       <c r="F33" t="n">
-        <v>5.0141</v>
+        <v>5.117</v>
       </c>
       <c r="G33" t="n">
-        <v>5.4065</v>
+        <v>5.4794</v>
       </c>
       <c r="H33" t="n">
-        <v>5254.350098</v>
+        <v>5035.689941</v>
       </c>
       <c r="I33" t="n">
-        <v>16379.459961</v>
+        <v>15657.820312</v>
       </c>
       <c r="J33" t="n">
-        <v>39807.371094</v>
+        <v>37815.921875</v>
       </c>
       <c r="K33" t="n">
-        <v>2217.399902</v>
+        <v>2291.399902</v>
       </c>
       <c r="L33" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>87.480003</v>
+        <v>87.860001</v>
       </c>
       <c r="N33" t="n">
-        <v>1191.5</v>
+        <v>1145.5</v>
       </c>
       <c r="O33" t="n">
-        <v>442</v>
+        <v>439.5</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.708417</v>
+        <v>-1.703277</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.734529</v>
+        <v>-1.56841</v>
       </c>
       <c r="R33" t="n">
-        <v>2.347418</v>
+        <v>-7.798165</v>
       </c>
       <c r="S33" t="n">
-        <v>4.091071</v>
+        <v>-0.546824</v>
       </c>
       <c r="T33" t="n">
-        <v>0.942164</v>
+        <v>2.052213</v>
       </c>
       <c r="U33" t="n">
-        <v>0.473886</v>
+        <v>1.348382</v>
       </c>
       <c r="V33" t="n">
-        <v>3.101878</v>
+        <v>-4.161507</v>
       </c>
       <c r="W33" t="n">
-        <v>1.78686</v>
+        <v>-4.40576</v>
       </c>
       <c r="X33" t="n">
-        <v>2.07963</v>
+        <v>-5.002715</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.393212999999999</v>
+        <v>3.337242</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.273953</v>
+        <v>-1.49092</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.616121</v>
+        <v>0.434382</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.313891</v>
+        <v>-0.565611</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B34" t="n">
-        <v>125924</v>
+        <v>122098</v>
       </c>
       <c r="C34" t="n">
-        <v>122.379997</v>
+        <v>118.660004</v>
       </c>
       <c r="D34" t="n">
-        <v>100.5</v>
+        <v>96.870003</v>
       </c>
       <c r="E34" t="n">
-        <v>291</v>
+        <v>308.200012</v>
       </c>
       <c r="F34" t="n">
-        <v>5.117</v>
+        <v>5.2021</v>
       </c>
       <c r="G34" t="n">
-        <v>5.4794</v>
+        <v>5.6311</v>
       </c>
       <c r="H34" t="n">
-        <v>5035.689941</v>
+        <v>5277.509766</v>
       </c>
       <c r="I34" t="n">
-        <v>15657.820312</v>
+        <v>16735.019531</v>
       </c>
       <c r="J34" t="n">
-        <v>37815.921875</v>
+        <v>38686.320312</v>
       </c>
       <c r="K34" t="n">
-        <v>2291.399902</v>
+        <v>2322.899902</v>
       </c>
       <c r="L34" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
       <c r="M34" t="n">
-        <v>87.860001</v>
+        <v>81.620003</v>
       </c>
       <c r="N34" t="n">
-        <v>1145.5</v>
+        <v>1205</v>
       </c>
       <c r="O34" t="n">
-        <v>439.5</v>
+        <v>446.25</v>
       </c>
       <c r="P34" t="n">
-        <v>-1.703277</v>
+        <v>-3.038341</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.56841</v>
+        <v>-3.039707</v>
       </c>
       <c r="R34" t="n">
-        <v>-7.798165</v>
+        <v>-3.611938</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.546824</v>
+        <v>5.910657</v>
       </c>
       <c r="T34" t="n">
-        <v>2.052213</v>
+        <v>1.663078</v>
       </c>
       <c r="U34" t="n">
-        <v>1.348382</v>
+        <v>2.768552</v>
       </c>
       <c r="V34" t="n">
-        <v>-4.161507</v>
+        <v>4.802119</v>
       </c>
       <c r="W34" t="n">
-        <v>-4.40576</v>
+        <v>6.879624</v>
       </c>
       <c r="X34" t="n">
-        <v>-5.002715</v>
+        <v>2.301672</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.337242</v>
+        <v>1.374705</v>
       </c>
       <c r="Z34" t="n">
-        <v>-1.49092</v>
+        <v>-6.02954</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.434382</v>
+        <v>-7.102206</v>
       </c>
       <c r="AB34" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.565611</v>
+        <v>1.535836</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B35" t="n">
-        <v>122098</v>
+        <v>123907</v>
       </c>
       <c r="C35" t="n">
-        <v>118.660004</v>
+        <v>120.379997</v>
       </c>
       <c r="D35" t="n">
-        <v>96.870003</v>
+        <v>96.449997</v>
       </c>
       <c r="E35" t="n">
-        <v>308.200012</v>
+        <v>339.829987</v>
       </c>
       <c r="F35" t="n">
-        <v>5.2021</v>
+        <v>5.5005</v>
       </c>
       <c r="G35" t="n">
-        <v>5.6311</v>
+        <v>5.8909</v>
       </c>
       <c r="H35" t="n">
-        <v>5277.509766</v>
+        <v>5460.47998</v>
       </c>
       <c r="I35" t="n">
-        <v>16735.019531</v>
+        <v>17732.599609</v>
       </c>
       <c r="J35" t="n">
-        <v>38686.320312</v>
+        <v>39118.859375</v>
       </c>
       <c r="K35" t="n">
-        <v>2322.899902</v>
+        <v>2327.699951</v>
       </c>
       <c r="L35" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
       <c r="M35" t="n">
-        <v>81.620003</v>
+        <v>86.410004</v>
       </c>
       <c r="N35" t="n">
-        <v>1205</v>
+        <v>1150.5</v>
       </c>
       <c r="O35" t="n">
-        <v>446.25</v>
+        <v>397.25</v>
       </c>
       <c r="P35" t="n">
-        <v>-3.038341</v>
+        <v>1.481597</v>
       </c>
       <c r="Q35" t="n">
-        <v>-3.039707</v>
+        <v>1.449514</v>
       </c>
       <c r="R35" t="n">
-        <v>-3.611938</v>
+        <v>-0.433577</v>
       </c>
       <c r="S35" t="n">
-        <v>5.910657</v>
+        <v>10.262808</v>
       </c>
       <c r="T35" t="n">
-        <v>1.663078</v>
+        <v>5.736153</v>
       </c>
       <c r="U35" t="n">
-        <v>2.768552</v>
+        <v>4.613663</v>
       </c>
       <c r="V35" t="n">
-        <v>4.802119</v>
+        <v>3.46698</v>
       </c>
       <c r="W35" t="n">
-        <v>6.879624</v>
+        <v>5.961033</v>
       </c>
       <c r="X35" t="n">
-        <v>2.301672</v>
+        <v>1.118067</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.374705</v>
+        <v>0.20664</v>
       </c>
       <c r="Z35" t="n">
-        <v>-6.02954</v>
+        <v>5.909863</v>
       </c>
       <c r="AA35" t="n">
-        <v>-7.102206</v>
+        <v>5.868661</v>
       </c>
       <c r="AB35" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.535836</v>
+        <v>-10.980392</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B36" t="n">
-        <v>123907</v>
+        <v>127652</v>
       </c>
       <c r="C36" t="n">
-        <v>120.379997</v>
+        <v>124.040001</v>
       </c>
       <c r="D36" t="n">
-        <v>96.449997</v>
+        <v>98.5</v>
       </c>
       <c r="E36" t="n">
-        <v>339.829987</v>
+        <v>347.700012</v>
       </c>
       <c r="F36" t="n">
-        <v>5.5005</v>
+        <v>5.6111</v>
       </c>
       <c r="G36" t="n">
-        <v>5.8909</v>
+        <v>6.0695</v>
       </c>
       <c r="H36" t="n">
-        <v>5460.47998</v>
+        <v>5522.299805</v>
       </c>
       <c r="I36" t="n">
-        <v>17732.599609</v>
+        <v>17599.400391</v>
       </c>
       <c r="J36" t="n">
-        <v>39118.859375</v>
+        <v>40842.789062</v>
       </c>
       <c r="K36" t="n">
-        <v>2327.699951</v>
+        <v>2426.5</v>
       </c>
       <c r="L36" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
       <c r="M36" t="n">
-        <v>86.410004</v>
+        <v>80.720001</v>
       </c>
       <c r="N36" t="n">
-        <v>1150.5</v>
+        <v>1028.5</v>
       </c>
       <c r="O36" t="n">
-        <v>397.25</v>
+        <v>382.75</v>
       </c>
       <c r="P36" t="n">
-        <v>1.481597</v>
+        <v>3.022428</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.449514</v>
+        <v>3.040375</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.433577</v>
+        <v>2.125457</v>
       </c>
       <c r="S36" t="n">
-        <v>10.262808</v>
+        <v>2.315871</v>
       </c>
       <c r="T36" t="n">
-        <v>5.736153</v>
+        <v>2.010726</v>
       </c>
       <c r="U36" t="n">
-        <v>4.613663</v>
+        <v>3.031792</v>
       </c>
       <c r="V36" t="n">
-        <v>3.46698</v>
+        <v>1.132132</v>
       </c>
       <c r="W36" t="n">
-        <v>5.961033</v>
+        <v>-0.751154</v>
       </c>
       <c r="X36" t="n">
-        <v>1.118067</v>
+        <v>4.406902</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.20664</v>
+        <v>4.244535</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.909863</v>
+        <v>-4.451799</v>
       </c>
       <c r="AA36" t="n">
-        <v>5.868661</v>
+        <v>-6.584889</v>
       </c>
       <c r="AB36" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
       <c r="AC36" t="n">
-        <v>-10.980392</v>
+        <v>-3.650094</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B37" t="n">
-        <v>127652</v>
+        <v>136004</v>
       </c>
       <c r="C37" t="n">
-        <v>124.040001</v>
+        <v>132.600006</v>
       </c>
       <c r="D37" t="n">
-        <v>98.5</v>
+        <v>102.769997</v>
       </c>
       <c r="E37" t="n">
-        <v>347.700012</v>
+        <v>354.850006</v>
       </c>
       <c r="F37" t="n">
-        <v>5.6111</v>
+        <v>5.6277</v>
       </c>
       <c r="G37" t="n">
-        <v>6.0695</v>
+        <v>6.2224</v>
       </c>
       <c r="H37" t="n">
-        <v>5522.299805</v>
+        <v>5648.399902</v>
       </c>
       <c r="I37" t="n">
-        <v>17599.400391</v>
+        <v>17713.619141</v>
       </c>
       <c r="J37" t="n">
-        <v>40842.789062</v>
+        <v>41563.078125</v>
       </c>
       <c r="K37" t="n">
-        <v>2426.5</v>
+        <v>2493.800049</v>
       </c>
       <c r="L37" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
       <c r="M37" t="n">
-        <v>80.720001</v>
+        <v>78.800003</v>
       </c>
       <c r="N37" t="n">
-        <v>1028.5</v>
+        <v>982</v>
       </c>
       <c r="O37" t="n">
-        <v>382.75</v>
+        <v>378</v>
       </c>
       <c r="P37" t="n">
-        <v>3.022428</v>
+        <v>6.542788</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.040375</v>
+        <v>6.901004</v>
       </c>
       <c r="R37" t="n">
-        <v>2.125457</v>
+        <v>4.335022</v>
       </c>
       <c r="S37" t="n">
-        <v>2.315871</v>
+        <v>2.056369</v>
       </c>
       <c r="T37" t="n">
-        <v>2.010726</v>
+        <v>0.295836</v>
       </c>
       <c r="U37" t="n">
-        <v>3.031792</v>
+        <v>2.519157</v>
       </c>
       <c r="V37" t="n">
-        <v>1.132132</v>
+        <v>2.283471</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.751154</v>
+        <v>0.648992</v>
       </c>
       <c r="X37" t="n">
-        <v>4.406902</v>
+        <v>1.763565</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.244535</v>
+        <v>2.773544</v>
       </c>
       <c r="Z37" t="n">
-        <v>-4.451799</v>
+        <v>-5.596201</v>
       </c>
       <c r="AA37" t="n">
-        <v>-6.584889</v>
+        <v>-2.37859</v>
       </c>
       <c r="AB37" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
       <c r="AC37" t="n">
-        <v>-3.650094</v>
+        <v>-1.241019</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B38" t="n">
-        <v>136004</v>
+        <v>131816</v>
       </c>
       <c r="C38" t="n">
-        <v>132.600006</v>
+        <v>128.429993</v>
       </c>
       <c r="D38" t="n">
-        <v>102.769997</v>
+        <v>97.959999</v>
       </c>
       <c r="E38" t="n">
-        <v>354.850006</v>
+        <v>349.799988</v>
       </c>
       <c r="F38" t="n">
-        <v>5.6277</v>
+        <v>5.4332</v>
       </c>
       <c r="G38" t="n">
-        <v>6.2224</v>
+        <v>6.0652</v>
       </c>
       <c r="H38" t="n">
-        <v>5648.399902</v>
+        <v>5762.47998</v>
       </c>
       <c r="I38" t="n">
-        <v>17713.619141</v>
+        <v>18189.169922</v>
       </c>
       <c r="J38" t="n">
-        <v>41563.078125</v>
+        <v>42330.148438</v>
       </c>
       <c r="K38" t="n">
-        <v>2493.800049</v>
+        <v>2636.100098</v>
       </c>
       <c r="L38" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
       <c r="M38" t="n">
-        <v>78.800003</v>
+        <v>71.769997</v>
       </c>
       <c r="N38" t="n">
-        <v>982</v>
+        <v>1057</v>
       </c>
       <c r="O38" t="n">
-        <v>378</v>
+        <v>424.75</v>
       </c>
       <c r="P38" t="n">
-        <v>6.542788</v>
+        <v>-3.079321</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.901004</v>
+        <v>-3.144806</v>
       </c>
       <c r="R38" t="n">
-        <v>4.335022</v>
+        <v>-4.680352</v>
       </c>
       <c r="S38" t="n">
-        <v>2.056369</v>
+        <v>-1.423142</v>
       </c>
       <c r="T38" t="n">
-        <v>0.295836</v>
+        <v>-3.456118</v>
       </c>
       <c r="U38" t="n">
-        <v>2.519157</v>
+        <v>-2.526362</v>
       </c>
       <c r="V38" t="n">
-        <v>2.283471</v>
+        <v>2.019688</v>
       </c>
       <c r="W38" t="n">
-        <v>0.648992</v>
+        <v>2.684662</v>
       </c>
       <c r="X38" t="n">
-        <v>1.763565</v>
+        <v>1.845557</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.773544</v>
+        <v>5.706153</v>
       </c>
       <c r="Z38" t="n">
-        <v>-5.596201</v>
+        <v>-7.314758</v>
       </c>
       <c r="AA38" t="n">
-        <v>-2.37859</v>
+        <v>-8.921328000000001</v>
       </c>
       <c r="AB38" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
       <c r="AC38" t="n">
-        <v>-1.241019</v>
+        <v>12.367725</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B39" t="n">
-        <v>131816</v>
+        <v>129713</v>
       </c>
       <c r="C39" t="n">
-        <v>128.429993</v>
+        <v>126.260002</v>
       </c>
       <c r="D39" t="n">
-        <v>97.959999</v>
+        <v>97.25</v>
       </c>
       <c r="E39" t="n">
-        <v>349.799988</v>
+        <v>368.579987</v>
       </c>
       <c r="F39" t="n">
-        <v>5.4332</v>
+        <v>5.7623</v>
       </c>
       <c r="G39" t="n">
-        <v>6.0652</v>
+        <v>6.2522</v>
       </c>
       <c r="H39" t="n">
-        <v>5762.47998</v>
+        <v>5705.450195</v>
       </c>
       <c r="I39" t="n">
-        <v>18189.169922</v>
+        <v>18095.150391</v>
       </c>
       <c r="J39" t="n">
-        <v>42330.148438</v>
+        <v>41763.460938</v>
       </c>
       <c r="K39" t="n">
-        <v>2636.100098</v>
+        <v>2738.300049</v>
       </c>
       <c r="L39" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
       <c r="M39" t="n">
-        <v>71.769997</v>
+        <v>73.160004</v>
       </c>
       <c r="N39" t="n">
-        <v>1057</v>
+        <v>982.5</v>
       </c>
       <c r="O39" t="n">
-        <v>424.75</v>
+        <v>410.75</v>
       </c>
       <c r="P39" t="n">
-        <v>-3.079321</v>
+        <v>-1.595406</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3.144806</v>
+        <v>-1.689629</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.680352</v>
+        <v>-0.724785</v>
       </c>
       <c r="S39" t="n">
-        <v>-1.423142</v>
+        <v>5.368782</v>
       </c>
       <c r="T39" t="n">
-        <v>-3.456118</v>
+        <v>6.057206</v>
       </c>
       <c r="U39" t="n">
-        <v>-2.526362</v>
+        <v>3.083168</v>
       </c>
       <c r="V39" t="n">
-        <v>2.019688</v>
+        <v>-0.9896740000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>2.684662</v>
+        <v>-0.516898</v>
       </c>
       <c r="X39" t="n">
-        <v>1.845557</v>
+        <v>-1.338733</v>
       </c>
       <c r="Y39" t="n">
-        <v>5.706153</v>
+        <v>3.876937</v>
       </c>
       <c r="Z39" t="n">
-        <v>-7.314758</v>
+        <v>1.59895</v>
       </c>
       <c r="AA39" t="n">
-        <v>-8.921328000000001</v>
+        <v>1.936752</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
       <c r="AC39" t="n">
-        <v>12.367725</v>
+        <v>-3.296057</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B40" t="n">
-        <v>129713</v>
+        <v>125668</v>
       </c>
       <c r="C40" t="n">
-        <v>126.260002</v>
+        <v>122.32</v>
       </c>
       <c r="D40" t="n">
-        <v>97.25</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>368.579987</v>
+        <v>402.850006</v>
       </c>
       <c r="F40" t="n">
-        <v>5.7623</v>
+        <v>6.0139</v>
       </c>
       <c r="G40" t="n">
-        <v>6.2522</v>
+        <v>6.345178</v>
       </c>
       <c r="H40" t="n">
-        <v>5705.450195</v>
+        <v>6032.379883</v>
       </c>
       <c r="I40" t="n">
-        <v>18095.150391</v>
+        <v>19218.169922</v>
       </c>
       <c r="J40" t="n">
-        <v>41763.460938</v>
+        <v>44910.648438</v>
       </c>
       <c r="K40" t="n">
-        <v>2738.300049</v>
+        <v>2657</v>
       </c>
       <c r="L40" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
       <c r="M40" t="n">
-        <v>73.160004</v>
+        <v>72.94000200000001</v>
       </c>
       <c r="N40" t="n">
-        <v>982.5</v>
+        <v>989.5</v>
       </c>
       <c r="O40" t="n">
-        <v>410.75</v>
+        <v>423</v>
       </c>
       <c r="P40" t="n">
-        <v>-1.595406</v>
+        <v>-3.118423</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.689629</v>
+        <v>-3.120547</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.724785</v>
+        <v>-4.041131</v>
       </c>
       <c r="S40" t="n">
-        <v>5.368782</v>
+        <v>9.297851</v>
       </c>
       <c r="T40" t="n">
-        <v>6.057206</v>
+        <v>4.366308</v>
       </c>
       <c r="U40" t="n">
-        <v>3.083168</v>
+        <v>1.487125</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.9896740000000001</v>
+        <v>5.73013</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.516898</v>
+        <v>6.206191</v>
       </c>
       <c r="X40" t="n">
-        <v>-1.338733</v>
+        <v>7.535744</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.876937</v>
+        <v>-2.968997</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.59895</v>
+        <v>-1.819235</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.936752</v>
+        <v>-0.300712</v>
       </c>
       <c r="AB40" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
       <c r="AC40" t="n">
-        <v>-3.296057</v>
+        <v>2.982349</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B41" t="n">
-        <v>125668</v>
+        <v>120283</v>
       </c>
       <c r="C41" t="n">
-        <v>122.32</v>
+        <v>117.269997</v>
       </c>
       <c r="D41" t="n">
-        <v>93.31999999999999</v>
+        <v>85.949997</v>
       </c>
       <c r="E41" t="n">
-        <v>402.850006</v>
+        <v>407.700012</v>
       </c>
       <c r="F41" t="n">
-        <v>6.0139</v>
+        <v>6.1779</v>
       </c>
       <c r="G41" t="n">
-        <v>6.345178</v>
+        <v>6.422608</v>
       </c>
       <c r="H41" t="n">
-        <v>6032.379883</v>
+        <v>5881.629883</v>
       </c>
       <c r="I41" t="n">
-        <v>19218.169922</v>
+        <v>19310.789062</v>
       </c>
       <c r="J41" t="n">
-        <v>44910.648438</v>
+        <v>42544.21875</v>
       </c>
       <c r="K41" t="n">
-        <v>2657</v>
+        <v>2629.199951</v>
       </c>
       <c r="L41" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
       <c r="M41" t="n">
-        <v>72.94000200000001</v>
+        <v>74.639999</v>
       </c>
       <c r="N41" t="n">
-        <v>989.5</v>
+        <v>998.25</v>
       </c>
       <c r="O41" t="n">
-        <v>423</v>
+        <v>458.5</v>
       </c>
       <c r="P41" t="n">
-        <v>-3.118423</v>
+        <v>-4.2851</v>
       </c>
       <c r="Q41" t="n">
-        <v>-3.120547</v>
+        <v>-4.128518</v>
       </c>
       <c r="R41" t="n">
-        <v>-4.041131</v>
+        <v>-7.89756</v>
       </c>
       <c r="S41" t="n">
-        <v>9.297851</v>
+        <v>1.203924</v>
       </c>
       <c r="T41" t="n">
-        <v>4.366308</v>
+        <v>2.727016</v>
       </c>
       <c r="U41" t="n">
-        <v>1.487125</v>
+        <v>1.220293</v>
       </c>
       <c r="V41" t="n">
-        <v>5.73013</v>
+        <v>-2.499014</v>
       </c>
       <c r="W41" t="n">
-        <v>6.206191</v>
+        <v>0.481935</v>
       </c>
       <c r="X41" t="n">
-        <v>7.535744</v>
+        <v>-5.269195</v>
       </c>
       <c r="Y41" t="n">
-        <v>-2.968997</v>
+        <v>-1.046295</v>
       </c>
       <c r="Z41" t="n">
-        <v>-1.819235</v>
+        <v>5.47059</v>
       </c>
       <c r="AA41" t="n">
-        <v>-0.300712</v>
+        <v>2.330678</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.982349</v>
+        <v>8.392435000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>120283</v>
+        <v>126135</v>
       </c>
       <c r="C42" t="n">
-        <v>117.269997</v>
+        <v>123</v>
       </c>
       <c r="D42" t="n">
-        <v>85.949997</v>
+        <v>91.400002</v>
       </c>
       <c r="E42" t="n">
-        <v>407.700012</v>
+        <v>394.149994</v>
       </c>
       <c r="F42" t="n">
-        <v>6.1779</v>
+        <v>5.8745</v>
       </c>
       <c r="G42" t="n">
-        <v>6.422608</v>
+        <v>6.101281</v>
       </c>
       <c r="H42" t="n">
-        <v>5881.629883</v>
+        <v>6040.529785</v>
       </c>
       <c r="I42" t="n">
-        <v>19310.789062</v>
+        <v>19627.439453</v>
       </c>
       <c r="J42" t="n">
-        <v>42544.21875</v>
+        <v>44544.660156</v>
       </c>
       <c r="K42" t="n">
-        <v>2629.199951</v>
+        <v>2812.5</v>
       </c>
       <c r="L42" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
       <c r="M42" t="n">
-        <v>74.639999</v>
+        <v>76.760002</v>
       </c>
       <c r="N42" t="n">
-        <v>998.25</v>
+        <v>1042</v>
       </c>
       <c r="O42" t="n">
-        <v>458.5</v>
+        <v>482</v>
       </c>
       <c r="P42" t="n">
-        <v>-4.2851</v>
+        <v>4.865193</v>
       </c>
       <c r="Q42" t="n">
-        <v>-4.128518</v>
+        <v>4.886163</v>
       </c>
       <c r="R42" t="n">
-        <v>-7.89756</v>
+        <v>6.340901</v>
       </c>
       <c r="S42" t="n">
-        <v>1.203924</v>
+        <v>-3.323527</v>
       </c>
       <c r="T42" t="n">
-        <v>2.727016</v>
+        <v>-4.911055</v>
       </c>
       <c r="U42" t="n">
-        <v>1.220293</v>
+        <v>-5.003057</v>
       </c>
       <c r="V42" t="n">
-        <v>-2.499014</v>
+        <v>2.70163</v>
       </c>
       <c r="W42" t="n">
-        <v>0.481935</v>
+        <v>1.639759</v>
       </c>
       <c r="X42" t="n">
-        <v>-5.269195</v>
+        <v>4.702029</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.046295</v>
+        <v>6.971704</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.47059</v>
+        <v>1.129389</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.330678</v>
+        <v>2.840304</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.392435000000001</v>
+        <v>5.125409</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B43" t="n">
-        <v>126135</v>
+        <v>122799</v>
       </c>
       <c r="C43" t="n">
-        <v>123</v>
+        <v>120.010002</v>
       </c>
       <c r="D43" t="n">
-        <v>91.400002</v>
+        <v>87.599998</v>
       </c>
       <c r="E43" t="n">
-        <v>394.149994</v>
+        <v>392.700012</v>
       </c>
       <c r="F43" t="n">
-        <v>5.8745</v>
+        <v>5.839</v>
       </c>
       <c r="G43" t="n">
-        <v>6.101281</v>
+        <v>6.064281</v>
       </c>
       <c r="H43" t="n">
-        <v>6040.529785</v>
+        <v>5954.5</v>
       </c>
       <c r="I43" t="n">
-        <v>19627.439453</v>
+        <v>18847.279297</v>
       </c>
       <c r="J43" t="n">
-        <v>44544.660156</v>
+        <v>43840.910156</v>
       </c>
       <c r="K43" t="n">
-        <v>2812.5</v>
+        <v>2836.800049</v>
       </c>
       <c r="L43" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
       <c r="M43" t="n">
-        <v>76.760002</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>1042</v>
+        <v>1011.5</v>
       </c>
       <c r="O43" t="n">
-        <v>482</v>
+        <v>453.5</v>
       </c>
       <c r="P43" t="n">
-        <v>4.865193</v>
+        <v>-2.644785</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.886163</v>
+        <v>-2.430893</v>
       </c>
       <c r="R43" t="n">
-        <v>6.340901</v>
+        <v>-4.157553</v>
       </c>
       <c r="S43" t="n">
-        <v>-3.323527</v>
+        <v>-0.367876</v>
       </c>
       <c r="T43" t="n">
-        <v>-4.911055</v>
+        <v>-0.604299</v>
       </c>
       <c r="U43" t="n">
-        <v>-5.003057</v>
+        <v>-0.606433</v>
       </c>
       <c r="V43" t="n">
-        <v>2.70163</v>
+        <v>-1.424209</v>
       </c>
       <c r="W43" t="n">
-        <v>1.639759</v>
+        <v>-3.974844</v>
       </c>
       <c r="X43" t="n">
-        <v>4.702029</v>
+        <v>-1.579875</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.971704</v>
+        <v>0.864002</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.129389</v>
+        <v>-3.819105</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.840304</v>
+        <v>-4.66389</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.125409</v>
+        <v>-5.912863</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B44" t="n">
-        <v>122799</v>
+        <v>130260</v>
       </c>
       <c r="C44" t="n">
-        <v>120.010002</v>
+        <v>127.300003</v>
       </c>
       <c r="D44" t="n">
-        <v>87.599998</v>
+        <v>93.41999800000001</v>
       </c>
       <c r="E44" t="n">
-        <v>392.700012</v>
+        <v>358.700012</v>
       </c>
       <c r="F44" t="n">
-        <v>5.839</v>
+        <v>5.7581</v>
       </c>
       <c r="G44" t="n">
-        <v>6.064281</v>
+        <v>6.22665</v>
       </c>
       <c r="H44" t="n">
-        <v>5954.5</v>
+        <v>5611.850098</v>
       </c>
       <c r="I44" t="n">
-        <v>18847.279297</v>
+        <v>17299.289062</v>
       </c>
       <c r="J44" t="n">
-        <v>43840.910156</v>
+        <v>42001.761719</v>
       </c>
       <c r="K44" t="n">
-        <v>2836.800049</v>
+        <v>3122.800049</v>
       </c>
       <c r="L44" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
       <c r="M44" t="n">
-        <v>73.18000000000001</v>
+        <v>74.739998</v>
       </c>
       <c r="N44" t="n">
-        <v>1011.5</v>
+        <v>1014.75</v>
       </c>
       <c r="O44" t="n">
-        <v>453.5</v>
+        <v>457.25</v>
       </c>
       <c r="P44" t="n">
-        <v>-2.644785</v>
+        <v>6.075782</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2.430893</v>
+        <v>6.074494</v>
       </c>
       <c r="R44" t="n">
-        <v>-4.157553</v>
+        <v>6.643835</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.367876</v>
+        <v>-8.658008000000001</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.604299</v>
+        <v>-1.385514</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.606433</v>
+        <v>2.677469</v>
       </c>
       <c r="V44" t="n">
-        <v>-1.424209</v>
+        <v>-5.75447</v>
       </c>
       <c r="W44" t="n">
-        <v>-3.974844</v>
+        <v>-8.213335000000001</v>
       </c>
       <c r="X44" t="n">
-        <v>-1.579875</v>
+        <v>-4.195051</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.864002</v>
+        <v>10.081782</v>
       </c>
       <c r="Z44" t="n">
-        <v>-3.819105</v>
+        <v>2.465598</v>
       </c>
       <c r="AA44" t="n">
-        <v>-4.66389</v>
+        <v>2.131727</v>
       </c>
       <c r="AB44" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
       <c r="AC44" t="n">
-        <v>-5.912863</v>
+        <v>0.826902</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B45" t="n">
-        <v>130260</v>
+        <v>135067</v>
       </c>
       <c r="C45" t="n">
-        <v>127.300003</v>
+        <v>131.630005</v>
       </c>
       <c r="D45" t="n">
-        <v>93.41999800000001</v>
+        <v>101.5</v>
       </c>
       <c r="E45" t="n">
-        <v>358.700012</v>
+        <v>354.350006</v>
       </c>
       <c r="F45" t="n">
-        <v>5.7581</v>
+        <v>5.62</v>
       </c>
       <c r="G45" t="n">
-        <v>6.22665</v>
+        <v>6.393862</v>
       </c>
       <c r="H45" t="n">
-        <v>5611.850098</v>
+        <v>5569.060059</v>
       </c>
       <c r="I45" t="n">
-        <v>17299.289062</v>
+        <v>17446.339844</v>
       </c>
       <c r="J45" t="n">
-        <v>42001.761719</v>
+        <v>40669.359375</v>
       </c>
       <c r="K45" t="n">
-        <v>3122.800049</v>
+        <v>3305</v>
       </c>
       <c r="L45" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
       <c r="M45" t="n">
-        <v>74.739998</v>
+        <v>63.119999</v>
       </c>
       <c r="N45" t="n">
-        <v>1014.75</v>
+        <v>1034.75</v>
       </c>
       <c r="O45" t="n">
-        <v>457.25</v>
+        <v>467.25</v>
       </c>
       <c r="P45" t="n">
-        <v>6.075782</v>
+        <v>3.690312</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.074494</v>
+        <v>3.401415</v>
       </c>
       <c r="R45" t="n">
-        <v>6.643835</v>
+        <v>8.649114000000001</v>
       </c>
       <c r="S45" t="n">
-        <v>-8.658008000000001</v>
+        <v>-1.212714</v>
       </c>
       <c r="T45" t="n">
-        <v>-1.385514</v>
+        <v>-2.398363</v>
       </c>
       <c r="U45" t="n">
-        <v>2.677469</v>
+        <v>2.685417</v>
       </c>
       <c r="V45" t="n">
-        <v>-5.75447</v>
+        <v>-0.762494</v>
       </c>
       <c r="W45" t="n">
-        <v>-8.213335000000001</v>
+        <v>0.850039</v>
       </c>
       <c r="X45" t="n">
-        <v>-4.195051</v>
+        <v>-3.172253</v>
       </c>
       <c r="Y45" t="n">
-        <v>10.081782</v>
+        <v>5.834506</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.465598</v>
+        <v>-18.564639</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.131727</v>
+        <v>-15.547229</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.826902</v>
+        <v>2.186987</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B46" t="n">
-        <v>135067</v>
+        <v>137027</v>
       </c>
       <c r="C46" t="n">
-        <v>131.630005</v>
+        <v>133.990005</v>
       </c>
       <c r="D46" t="n">
-        <v>101.5</v>
+        <v>107.639999</v>
       </c>
       <c r="E46" t="n">
-        <v>354.350006</v>
+        <v>378.799988</v>
       </c>
       <c r="F46" t="n">
-        <v>5.62</v>
+        <v>5.6651</v>
       </c>
       <c r="G46" t="n">
-        <v>6.393862</v>
+        <v>6.43915</v>
       </c>
       <c r="H46" t="n">
-        <v>5569.060059</v>
+        <v>5911.689941</v>
       </c>
       <c r="I46" t="n">
-        <v>17446.339844</v>
+        <v>19113.769531</v>
       </c>
       <c r="J46" t="n">
-        <v>40669.359375</v>
+        <v>42270.070312</v>
       </c>
       <c r="K46" t="n">
-        <v>3305</v>
+        <v>3288.899902</v>
       </c>
       <c r="L46" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
       <c r="M46" t="n">
-        <v>63.119999</v>
+        <v>63.900002</v>
       </c>
       <c r="N46" t="n">
-        <v>1034.75</v>
+        <v>1041.75</v>
       </c>
       <c r="O46" t="n">
-        <v>467.25</v>
+        <v>444</v>
       </c>
       <c r="P46" t="n">
-        <v>3.690312</v>
+        <v>1.451132</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.401415</v>
+        <v>1.792905</v>
       </c>
       <c r="R46" t="n">
-        <v>8.649114000000001</v>
+        <v>6.04926</v>
       </c>
       <c r="S46" t="n">
-        <v>-1.212714</v>
+        <v>6.899952</v>
       </c>
       <c r="T46" t="n">
-        <v>-2.398363</v>
+        <v>0.802495</v>
       </c>
       <c r="U46" t="n">
-        <v>2.685417</v>
+        <v>0.708306</v>
       </c>
       <c r="V46" t="n">
-        <v>-0.762494</v>
+        <v>6.152383</v>
       </c>
       <c r="W46" t="n">
-        <v>0.850039</v>
+        <v>9.557475999999999</v>
       </c>
       <c r="X46" t="n">
-        <v>-3.172253</v>
+        <v>3.935914</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.834506</v>
+        <v>-0.487144</v>
       </c>
       <c r="Z46" t="n">
-        <v>-18.564639</v>
+        <v>4.432231</v>
       </c>
       <c r="AA46" t="n">
-        <v>-15.547229</v>
+        <v>1.235746</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.186987</v>
+        <v>-4.975923</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B47" t="n">
-        <v>137027</v>
+        <v>138855</v>
       </c>
       <c r="C47" t="n">
-        <v>133.990005</v>
+        <v>135.850006</v>
       </c>
       <c r="D47" t="n">
-        <v>107.639999</v>
+        <v>109.029999</v>
       </c>
       <c r="E47" t="n">
-        <v>378.799988</v>
+        <v>377.850006</v>
       </c>
       <c r="F47" t="n">
-        <v>5.6651</v>
+        <v>5.4784</v>
       </c>
       <c r="G47" t="n">
-        <v>6.43915</v>
+        <v>6.418485</v>
       </c>
       <c r="H47" t="n">
-        <v>5911.689941</v>
+        <v>6204.950195</v>
       </c>
       <c r="I47" t="n">
-        <v>19113.769531</v>
+        <v>20369.730469</v>
       </c>
       <c r="J47" t="n">
-        <v>42270.070312</v>
+        <v>44094.769531</v>
       </c>
       <c r="K47" t="n">
-        <v>3288.899902</v>
+        <v>3294.399902</v>
       </c>
       <c r="L47" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
       <c r="M47" t="n">
-        <v>63.900002</v>
+        <v>67.610001</v>
       </c>
       <c r="N47" t="n">
-        <v>1041.75</v>
+        <v>1024.25</v>
       </c>
       <c r="O47" t="n">
-        <v>444</v>
+        <v>420.5</v>
       </c>
       <c r="P47" t="n">
-        <v>1.451132</v>
+        <v>1.334044</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.792905</v>
+        <v>1.388164</v>
       </c>
       <c r="R47" t="n">
-        <v>6.04926</v>
+        <v>1.291341</v>
       </c>
       <c r="S47" t="n">
-        <v>6.899952</v>
+        <v>-0.250787</v>
       </c>
       <c r="T47" t="n">
-        <v>0.802495</v>
+        <v>-3.295615</v>
       </c>
       <c r="U47" t="n">
-        <v>0.708306</v>
+        <v>-0.320923</v>
       </c>
       <c r="V47" t="n">
-        <v>6.152383</v>
+        <v>4.960684</v>
       </c>
       <c r="W47" t="n">
-        <v>9.557475999999999</v>
+        <v>6.570975</v>
       </c>
       <c r="X47" t="n">
-        <v>3.935914</v>
+        <v>4.316764</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.487144</v>
+        <v>0.167229</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.432231</v>
+        <v>7.106431</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.235746</v>
+        <v>5.805945</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
       <c r="AC47" t="n">
-        <v>-4.975923</v>
+        <v>-5.292793</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B48" t="n">
-        <v>138855</v>
+        <v>133071</v>
       </c>
       <c r="C48" t="n">
-        <v>135.850006</v>
+        <v>129.880005</v>
       </c>
       <c r="D48" t="n">
-        <v>109.029999</v>
+        <v>101.919998</v>
       </c>
       <c r="E48" t="n">
-        <v>377.850006</v>
+        <v>398.01001</v>
       </c>
       <c r="F48" t="n">
-        <v>5.4784</v>
+        <v>5.5754</v>
       </c>
       <c r="G48" t="n">
-        <v>6.418485</v>
+        <v>6.365372</v>
       </c>
       <c r="H48" t="n">
-        <v>6204.950195</v>
+        <v>6339.390137</v>
       </c>
       <c r="I48" t="n">
-        <v>20369.730469</v>
+        <v>21122.449219</v>
       </c>
       <c r="J48" t="n">
-        <v>44094.769531</v>
+        <v>44130.980469</v>
       </c>
       <c r="K48" t="n">
-        <v>3294.399902</v>
+        <v>3293.199951</v>
       </c>
       <c r="L48" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
       <c r="M48" t="n">
-        <v>67.610001</v>
+        <v>72.529999</v>
       </c>
       <c r="N48" t="n">
-        <v>1024.25</v>
+        <v>961.75</v>
       </c>
       <c r="O48" t="n">
-        <v>420.5</v>
+        <v>394</v>
       </c>
       <c r="P48" t="n">
-        <v>1.334044</v>
+        <v>-4.165496</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.388164</v>
+        <v>-4.394554</v>
       </c>
       <c r="R48" t="n">
-        <v>1.291341</v>
+        <v>-6.521142</v>
       </c>
       <c r="S48" t="n">
-        <v>-0.250787</v>
+        <v>5.335451</v>
       </c>
       <c r="T48" t="n">
-        <v>-3.295615</v>
+        <v>1.770583</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.320923</v>
+        <v>-0.8275</v>
       </c>
       <c r="V48" t="n">
-        <v>4.960684</v>
+        <v>2.166656</v>
       </c>
       <c r="W48" t="n">
-        <v>6.570975</v>
+        <v>3.695281</v>
       </c>
       <c r="X48" t="n">
-        <v>4.316764</v>
+        <v>0.082121</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.167229</v>
+        <v>-0.036424</v>
       </c>
       <c r="Z48" t="n">
-        <v>7.106431</v>
+        <v>6.373831</v>
       </c>
       <c r="AA48" t="n">
-        <v>5.805945</v>
+        <v>7.277027</v>
       </c>
       <c r="AB48" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
       <c r="AC48" t="n">
-        <v>-5.292793</v>
+        <v>-6.302021</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B49" t="n">
-        <v>133071</v>
+        <v>141422</v>
       </c>
       <c r="C49" t="n">
-        <v>129.880005</v>
+        <v>138.5</v>
       </c>
       <c r="D49" t="n">
-        <v>101.919998</v>
+        <v>107.43</v>
       </c>
       <c r="E49" t="n">
-        <v>398.01001</v>
+        <v>393.850006</v>
       </c>
       <c r="F49" t="n">
-        <v>5.5754</v>
+        <v>5.413</v>
       </c>
       <c r="G49" t="n">
-        <v>6.365372</v>
+        <v>6.317119</v>
       </c>
       <c r="H49" t="n">
-        <v>6339.390137</v>
+        <v>6460.259766</v>
       </c>
       <c r="I49" t="n">
-        <v>21122.449219</v>
+        <v>21455.550781</v>
       </c>
       <c r="J49" t="n">
-        <v>44130.980469</v>
+        <v>45544.878906</v>
       </c>
       <c r="K49" t="n">
-        <v>3293.199951</v>
+        <v>3473.699951</v>
       </c>
       <c r="L49" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
       <c r="M49" t="n">
-        <v>72.529999</v>
+        <v>68.120003</v>
       </c>
       <c r="N49" t="n">
-        <v>961.75</v>
+        <v>1036.75</v>
       </c>
       <c r="O49" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P49" t="n">
-        <v>-4.165496</v>
+        <v>6.275597</v>
       </c>
       <c r="Q49" t="n">
-        <v>-4.394554</v>
+        <v>6.636892</v>
       </c>
       <c r="R49" t="n">
-        <v>-6.521142</v>
+        <v>5.406203</v>
       </c>
       <c r="S49" t="n">
-        <v>5.335451</v>
+        <v>-1.045201</v>
       </c>
       <c r="T49" t="n">
-        <v>1.770583</v>
+        <v>-2.912791</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.8275</v>
+        <v>-0.758056</v>
       </c>
       <c r="V49" t="n">
-        <v>2.166656</v>
+        <v>1.906644</v>
       </c>
       <c r="W49" t="n">
-        <v>3.695281</v>
+        <v>1.577003</v>
       </c>
       <c r="X49" t="n">
-        <v>0.082121</v>
+        <v>3.203868</v>
       </c>
       <c r="Y49" t="n">
-        <v>-0.036424</v>
+        <v>5.480991</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.373831</v>
+        <v>-7.580133</v>
       </c>
       <c r="AA49" t="n">
-        <v>7.277027</v>
+        <v>-6.080237</v>
       </c>
       <c r="AB49" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
       <c r="AC49" t="n">
-        <v>-6.302021</v>
+        <v>1.015228</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B50" t="n">
-        <v>141422</v>
+        <v>146237</v>
       </c>
       <c r="C50" t="n">
-        <v>138.5</v>
+        <v>143.240005</v>
       </c>
       <c r="D50" t="n">
-        <v>107.43</v>
+        <v>109.669998</v>
       </c>
       <c r="E50" t="n">
-        <v>393.850006</v>
+        <v>399.799988</v>
       </c>
       <c r="F50" t="n">
-        <v>5.413</v>
+        <v>5.3217</v>
       </c>
       <c r="G50" t="n">
-        <v>6.317119</v>
+        <v>6.238303</v>
       </c>
       <c r="H50" t="n">
-        <v>6460.259766</v>
+        <v>6688.459961</v>
       </c>
       <c r="I50" t="n">
-        <v>21455.550781</v>
+        <v>22660.009766</v>
       </c>
       <c r="J50" t="n">
-        <v>45544.878906</v>
+        <v>46397.890625</v>
       </c>
       <c r="K50" t="n">
-        <v>3473.699951</v>
+        <v>3840.800049</v>
       </c>
       <c r="L50" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
       <c r="M50" t="n">
-        <v>68.120003</v>
+        <v>67.019997</v>
       </c>
       <c r="N50" t="n">
-        <v>1036.75</v>
+        <v>1001.75</v>
       </c>
       <c r="O50" t="n">
-        <v>398</v>
+        <v>415.5</v>
       </c>
       <c r="P50" t="n">
-        <v>6.275597</v>
+        <v>3.404704</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.636892</v>
+        <v>3.422387</v>
       </c>
       <c r="R50" t="n">
-        <v>5.406203</v>
+        <v>2.085077</v>
       </c>
       <c r="S50" t="n">
-        <v>-1.045201</v>
+        <v>1.510723</v>
       </c>
       <c r="T50" t="n">
-        <v>-2.912791</v>
+        <v>-1.68668</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.758056</v>
+        <v>-1.247656</v>
       </c>
       <c r="V50" t="n">
-        <v>1.906644</v>
+        <v>3.532369</v>
       </c>
       <c r="W50" t="n">
-        <v>1.577003</v>
+        <v>5.613741</v>
       </c>
       <c r="X50" t="n">
-        <v>3.203868</v>
+        <v>1.872904</v>
       </c>
       <c r="Y50" t="n">
-        <v>5.480991</v>
+        <v>10.567985</v>
       </c>
       <c r="Z50" t="n">
-        <v>-7.580133</v>
+        <v>-2.562105</v>
       </c>
       <c r="AA50" t="n">
-        <v>-6.080237</v>
+        <v>-1.614806</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.015228</v>
+        <v>4.396985</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B51" t="n">
-        <v>146237</v>
+        <v>149540</v>
       </c>
       <c r="C51" t="n">
-        <v>143.240005</v>
+        <v>146.410004</v>
       </c>
       <c r="D51" t="n">
-        <v>109.669998</v>
+        <v>110.059998</v>
       </c>
       <c r="E51" t="n">
-        <v>399.799988</v>
+        <v>413.329987</v>
       </c>
       <c r="F51" t="n">
-        <v>5.3217</v>
+        <v>5.382</v>
       </c>
       <c r="G51" t="n">
-        <v>6.238303</v>
+        <v>6.222775</v>
       </c>
       <c r="H51" t="n">
-        <v>6688.459961</v>
+        <v>6840.200195</v>
       </c>
       <c r="I51" t="n">
-        <v>22660.009766</v>
+        <v>23724.960938</v>
       </c>
       <c r="J51" t="n">
-        <v>46397.890625</v>
+        <v>47562.871094</v>
       </c>
       <c r="K51" t="n">
-        <v>3840.800049</v>
+        <v>3982.199951</v>
       </c>
       <c r="L51" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
       <c r="M51" t="n">
-        <v>67.019997</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>1001.75</v>
+        <v>1099.75</v>
       </c>
       <c r="O51" t="n">
-        <v>415.5</v>
+        <v>431.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.404704</v>
+        <v>2.258662</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.422387</v>
+        <v>2.213068</v>
       </c>
       <c r="R51" t="n">
-        <v>2.085077</v>
+        <v>0.355612</v>
       </c>
       <c r="S51" t="n">
-        <v>1.510723</v>
+        <v>3.384192</v>
       </c>
       <c r="T51" t="n">
-        <v>-1.68668</v>
+        <v>1.133094</v>
       </c>
       <c r="U51" t="n">
-        <v>-1.247656</v>
+        <v>-0.248917</v>
       </c>
       <c r="V51" t="n">
-        <v>3.532369</v>
+        <v>2.268687</v>
       </c>
       <c r="W51" t="n">
-        <v>5.613741</v>
+        <v>4.699694</v>
       </c>
       <c r="X51" t="n">
-        <v>1.872904</v>
+        <v>2.510848</v>
       </c>
       <c r="Y51" t="n">
-        <v>10.567985</v>
+        <v>3.681522</v>
       </c>
       <c r="Z51" t="n">
-        <v>-2.562105</v>
+        <v>-2.228635</v>
       </c>
       <c r="AA51" t="n">
-        <v>-1.614806</v>
+        <v>-2.909575</v>
       </c>
       <c r="AB51" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.396985</v>
+        <v>3.850782</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B52" t="n">
-        <v>149540</v>
+        <v>159072</v>
       </c>
       <c r="C52" t="n">
-        <v>146.410004</v>
+        <v>155.850006</v>
       </c>
       <c r="D52" t="n">
-        <v>110.059998</v>
+        <v>116.489998</v>
       </c>
       <c r="E52" t="n">
-        <v>413.329987</v>
+        <v>411.089996</v>
       </c>
       <c r="F52" t="n">
-        <v>5.382</v>
+        <v>5.3554</v>
       </c>
       <c r="G52" t="n">
-        <v>6.222775</v>
+        <v>6.207325</v>
       </c>
       <c r="H52" t="n">
-        <v>6840.200195</v>
+        <v>6849.089844</v>
       </c>
       <c r="I52" t="n">
-        <v>23724.960938</v>
+        <v>23365.689453</v>
       </c>
       <c r="J52" t="n">
-        <v>47562.871094</v>
+        <v>47716.421875</v>
       </c>
       <c r="K52" t="n">
-        <v>3982.199951</v>
+        <v>4218.299805</v>
       </c>
       <c r="L52" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
       <c r="M52" t="n">
-        <v>65.06999999999999</v>
+        <v>63.200001</v>
       </c>
       <c r="N52" t="n">
-        <v>1099.75</v>
+        <v>1137.75</v>
       </c>
       <c r="O52" t="n">
-        <v>431.5</v>
+        <v>435.5</v>
       </c>
       <c r="P52" t="n">
-        <v>2.258662</v>
+        <v>6.374214</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.213068</v>
+        <v>6.447649</v>
       </c>
       <c r="R52" t="n">
-        <v>0.355612</v>
+        <v>5.842268</v>
       </c>
       <c r="S52" t="n">
-        <v>3.384192</v>
+        <v>-0.541938</v>
       </c>
       <c r="T52" t="n">
-        <v>1.133094</v>
+        <v>-0.494238</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.248917</v>
+        <v>-0.248282</v>
       </c>
       <c r="V52" t="n">
-        <v>2.268687</v>
+        <v>0.129962</v>
       </c>
       <c r="W52" t="n">
-        <v>4.699694</v>
+        <v>-1.514319</v>
       </c>
       <c r="X52" t="n">
-        <v>2.510848</v>
+        <v>0.322837</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.681522</v>
+        <v>5.92888</v>
       </c>
       <c r="Z52" t="n">
-        <v>-2.228635</v>
+        <v>-3.984914</v>
       </c>
       <c r="AA52" t="n">
-        <v>-2.909575</v>
+        <v>-2.873827</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.850782</v>
+        <v>0.926999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B53" t="n">
-        <v>159072</v>
+        <v>161125</v>
       </c>
       <c r="C53" t="n">
-        <v>155.850006</v>
+        <v>158</v>
       </c>
       <c r="D53" t="n">
-        <v>116.489998</v>
+        <v>112.449997</v>
       </c>
       <c r="E53" t="n">
-        <v>411.089996</v>
+        <v>424.200012</v>
       </c>
       <c r="F53" t="n">
-        <v>5.3554</v>
+        <v>5.4762</v>
       </c>
       <c r="G53" t="n">
-        <v>6.207325</v>
+        <v>6.426735</v>
       </c>
       <c r="H53" t="n">
-        <v>6849.089844</v>
+        <v>6845.5</v>
       </c>
       <c r="I53" t="n">
-        <v>23365.689453</v>
+        <v>23241.990234</v>
       </c>
       <c r="J53" t="n">
-        <v>47716.421875</v>
+        <v>48063.289062</v>
       </c>
       <c r="K53" t="n">
-        <v>4218.299805</v>
+        <v>4325.600098</v>
       </c>
       <c r="L53" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
       <c r="M53" t="n">
-        <v>63.200001</v>
+        <v>60.849998</v>
       </c>
       <c r="N53" t="n">
-        <v>1137.75</v>
+        <v>1030.5</v>
       </c>
       <c r="O53" t="n">
-        <v>435.5</v>
+        <v>440.25</v>
       </c>
       <c r="P53" t="n">
-        <v>6.374214</v>
+        <v>1.290611</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.447649</v>
+        <v>1.379528</v>
       </c>
       <c r="R53" t="n">
-        <v>5.842268</v>
+        <v>-3.46811</v>
       </c>
       <c r="S53" t="n">
-        <v>-0.541938</v>
+        <v>3.189087</v>
       </c>
       <c r="T53" t="n">
-        <v>-0.494238</v>
+        <v>2.255667</v>
       </c>
       <c r="U53" t="n">
-        <v>-0.248282</v>
+        <v>3.534694</v>
       </c>
       <c r="V53" t="n">
-        <v>0.129962</v>
+        <v>-0.052413</v>
       </c>
       <c r="W53" t="n">
-        <v>-1.514319</v>
+        <v>-0.529405</v>
       </c>
       <c r="X53" t="n">
-        <v>0.322837</v>
+        <v>0.726935</v>
       </c>
       <c r="Y53" t="n">
-        <v>5.92888</v>
+        <v>2.543686</v>
       </c>
       <c r="Z53" t="n">
-        <v>-3.984914</v>
+        <v>-1.929976</v>
       </c>
       <c r="AA53" t="n">
-        <v>-2.873827</v>
+        <v>-3.718358</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.926999</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B54" t="n">
-        <v>161125</v>
+        <v>181364</v>
       </c>
       <c r="C54" t="n">
-        <v>158</v>
+        <v>178.199997</v>
       </c>
       <c r="D54" t="n">
-        <v>112.449997</v>
+        <v>123.800003</v>
       </c>
       <c r="E54" t="n">
-        <v>424.200012</v>
+        <v>410.649994</v>
       </c>
       <c r="F54" t="n">
-        <v>5.4762</v>
+        <v>5.1892</v>
       </c>
       <c r="G54" t="n">
-        <v>6.426735</v>
+        <v>6.203474</v>
       </c>
       <c r="H54" t="n">
-        <v>6845.5</v>
+        <v>6939.029785</v>
       </c>
       <c r="I54" t="n">
-        <v>23241.990234</v>
+        <v>23461.820312</v>
       </c>
       <c r="J54" t="n">
-        <v>48063.289062</v>
+        <v>48892.46875</v>
       </c>
       <c r="K54" t="n">
-        <v>4325.600098</v>
+        <v>4713.899902</v>
       </c>
       <c r="L54" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
       <c r="M54" t="n">
-        <v>60.849998</v>
+        <v>70.69000200000001</v>
       </c>
       <c r="N54" t="n">
-        <v>1030.5</v>
+        <v>1064.25</v>
       </c>
       <c r="O54" t="n">
-        <v>440.25</v>
+        <v>428.25</v>
       </c>
       <c r="P54" t="n">
-        <v>1.290611</v>
+        <v>12.561055</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.379528</v>
+        <v>12.784808</v>
       </c>
       <c r="R54" t="n">
-        <v>-3.46811</v>
+        <v>10.093381</v>
       </c>
       <c r="S54" t="n">
-        <v>3.189087</v>
+        <v>-3.194252</v>
       </c>
       <c r="T54" t="n">
-        <v>2.255667</v>
+        <v>-5.240864</v>
       </c>
       <c r="U54" t="n">
-        <v>3.534694</v>
+        <v>-3.473939</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.052413</v>
+        <v>1.366296</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.529405</v>
+        <v>0.945832</v>
       </c>
       <c r="X54" t="n">
-        <v>0.726935</v>
+        <v>1.725183</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.543686</v>
+        <v>8.976785</v>
       </c>
       <c r="Z54" t="n">
-        <v>-1.929976</v>
+        <v>13.566704</v>
       </c>
       <c r="AA54" t="n">
-        <v>-3.718358</v>
+        <v>16.170919</v>
       </c>
       <c r="AB54" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.0907</v>
+        <v>-2.725724</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B55" t="n">
-        <v>181364</v>
+        <v>188787</v>
       </c>
       <c r="C55" t="n">
-        <v>178.199997</v>
+        <v>185.160004</v>
       </c>
       <c r="D55" t="n">
-        <v>123.800003</v>
+        <v>126.379997</v>
       </c>
       <c r="E55" t="n">
-        <v>410.649994</v>
+        <v>396.75</v>
       </c>
       <c r="F55" t="n">
-        <v>5.1892</v>
+        <v>5.1366</v>
       </c>
       <c r="G55" t="n">
-        <v>6.203474</v>
+        <v>6.056935</v>
       </c>
       <c r="H55" t="n">
-        <v>6939.029785</v>
+        <v>6878.879883</v>
       </c>
       <c r="I55" t="n">
-        <v>23461.820312</v>
+        <v>22668.210938</v>
       </c>
       <c r="J55" t="n">
-        <v>48892.46875</v>
+        <v>48977.921875</v>
       </c>
       <c r="K55" t="n">
-        <v>4713.899902</v>
+        <v>5230.5</v>
       </c>
       <c r="L55" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
       <c r="M55" t="n">
-        <v>70.69000200000001</v>
+        <v>72.480003</v>
       </c>
       <c r="N55" t="n">
-        <v>1064.25</v>
+        <v>1157.25</v>
       </c>
       <c r="O55" t="n">
-        <v>428.25</v>
+        <v>438.75</v>
       </c>
       <c r="P55" t="n">
-        <v>12.561055</v>
+        <v>4.092874</v>
       </c>
       <c r="Q55" t="n">
-        <v>12.784808</v>
+        <v>3.905728</v>
       </c>
       <c r="R55" t="n">
-        <v>10.093381</v>
+        <v>2.084002</v>
       </c>
       <c r="S55" t="n">
-        <v>-3.194252</v>
+        <v>-3.384876</v>
       </c>
       <c r="T55" t="n">
-        <v>-5.240864</v>
+        <v>-1.013642</v>
       </c>
       <c r="U55" t="n">
-        <v>-3.473939</v>
+        <v>-2.362212</v>
       </c>
       <c r="V55" t="n">
-        <v>1.366296</v>
+        <v>-0.866834</v>
       </c>
       <c r="W55" t="n">
-        <v>0.945832</v>
+        <v>-3.382557</v>
       </c>
       <c r="X55" t="n">
-        <v>1.725183</v>
+        <v>0.174778</v>
       </c>
       <c r="Y55" t="n">
-        <v>8.976785</v>
+        <v>10.959081</v>
       </c>
       <c r="Z55" t="n">
-        <v>13.566704</v>
+        <v>2.775644</v>
       </c>
       <c r="AA55" t="n">
-        <v>16.170919</v>
+        <v>2.532184</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
       <c r="AC55" t="n">
-        <v>-2.725724</v>
+        <v>2.451839</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B56" t="n">
-        <v>188787</v>
+        <v>187462</v>
       </c>
       <c r="C56" t="n">
-        <v>185.160004</v>
+        <v>184.279999</v>
       </c>
       <c r="D56" t="n">
-        <v>126.379997</v>
+        <v>120</v>
       </c>
       <c r="E56" t="n">
-        <v>396.75</v>
+        <v>380.149994</v>
       </c>
       <c r="F56" t="n">
-        <v>5.1366</v>
+        <v>5.264</v>
       </c>
       <c r="G56" t="n">
-        <v>6.056935</v>
+        <v>6.027728</v>
       </c>
       <c r="H56" t="n">
-        <v>6878.879883</v>
+        <v>6528.52002</v>
       </c>
       <c r="I56" t="n">
-        <v>22668.210938</v>
+        <v>21590.630859</v>
       </c>
       <c r="J56" t="n">
-        <v>48977.921875</v>
+        <v>46341.511719</v>
       </c>
       <c r="K56" t="n">
-        <v>5230.5</v>
+        <v>4647.600098</v>
       </c>
       <c r="L56" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
       <c r="M56" t="n">
-        <v>72.480003</v>
+        <v>118.349998</v>
       </c>
       <c r="N56" t="n">
-        <v>1157.25</v>
+        <v>1171</v>
       </c>
       <c r="O56" t="n">
-        <v>438.75</v>
+        <v>457.75</v>
       </c>
       <c r="P56" t="n">
-        <v>4.092874</v>
+        <v>-0.7018489999999999</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.905728</v>
+        <v>-0.475267</v>
       </c>
       <c r="R56" t="n">
-        <v>2.084002</v>
+        <v>-5.048265</v>
       </c>
       <c r="S56" t="n">
-        <v>-3.384876</v>
+        <v>-4.183996</v>
       </c>
       <c r="T56" t="n">
-        <v>-1.013642</v>
+        <v>2.480238</v>
       </c>
       <c r="U56" t="n">
-        <v>-2.362212</v>
+        <v>-0.482204</v>
       </c>
       <c r="V56" t="n">
-        <v>-0.866834</v>
+        <v>-5.093269</v>
       </c>
       <c r="W56" t="n">
-        <v>-3.382557</v>
+        <v>-4.753706</v>
       </c>
       <c r="X56" t="n">
-        <v>0.174778</v>
+        <v>-5.382854</v>
       </c>
       <c r="Y56" t="n">
-        <v>10.959081</v>
+        <v>-11.144248</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.775644</v>
+        <v>51.268282</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.532184</v>
+        <v>63.286414</v>
       </c>
       <c r="AB56" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.451839</v>
+        <v>4.330484</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B57" t="n">
-        <v>187462</v>
+        <v>187318</v>
       </c>
       <c r="C57" t="n">
-        <v>184.279999</v>
+        <v>184.089996</v>
       </c>
       <c r="D57" t="n">
-        <v>120</v>
+        <v>115.760002</v>
       </c>
       <c r="E57" t="n">
-        <v>380.149994</v>
+        <v>402.5</v>
       </c>
       <c r="F57" t="n">
-        <v>5.264</v>
+        <v>5.0175</v>
       </c>
       <c r="G57" t="n">
-        <v>6.027728</v>
+        <v>5.858231</v>
       </c>
       <c r="H57" t="n">
-        <v>6528.52002</v>
+        <v>7209.009766</v>
       </c>
       <c r="I57" t="n">
-        <v>21590.630859</v>
+        <v>24892.310547</v>
       </c>
       <c r="J57" t="n">
-        <v>46341.511719</v>
+        <v>49652.140625</v>
       </c>
       <c r="K57" t="n">
-        <v>4647.600098</v>
+        <v>4614.700195</v>
       </c>
       <c r="L57" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
       <c r="M57" t="n">
-        <v>118.349998</v>
+        <v>114.010002</v>
       </c>
       <c r="N57" t="n">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="O57" t="n">
-        <v>457.75</v>
+        <v>464.75</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.7018489999999999</v>
+        <v>-0.076816</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.475267</v>
+        <v>-0.103105</v>
       </c>
       <c r="R57" t="n">
-        <v>-5.048265</v>
+        <v>-3.533332</v>
       </c>
       <c r="S57" t="n">
-        <v>-4.183996</v>
+        <v>5.87926</v>
       </c>
       <c r="T57" t="n">
-        <v>2.480238</v>
+        <v>-4.682751</v>
       </c>
       <c r="U57" t="n">
-        <v>-0.482204</v>
+        <v>-2.811955</v>
       </c>
       <c r="V57" t="n">
-        <v>-5.093269</v>
+        <v>10.423339</v>
       </c>
       <c r="W57" t="n">
-        <v>-4.753706</v>
+        <v>15.292187</v>
       </c>
       <c r="X57" t="n">
-        <v>-5.382854</v>
+        <v>7.143981</v>
       </c>
       <c r="Y57" t="n">
-        <v>-11.144248</v>
+        <v>-0.70789</v>
       </c>
       <c r="Z57" t="n">
-        <v>51.268282</v>
+        <v>3.639774</v>
       </c>
       <c r="AA57" t="n">
-        <v>63.286414</v>
+        <v>-3.667086</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.330484</v>
+        <v>1.529219</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B58" t="n">
-        <v>187318</v>
+        <v>173788</v>
       </c>
       <c r="C58" t="n">
-        <v>184.089996</v>
+        <v>170.75</v>
       </c>
       <c r="D58" t="n">
-        <v>115.760002</v>
+        <v>110.989998</v>
       </c>
       <c r="E58" t="n">
-        <v>402.5</v>
+        <v>430.399994</v>
       </c>
       <c r="F58" t="n">
-        <v>5.0175</v>
+        <v>5.0517</v>
       </c>
       <c r="G58" t="n">
-        <v>5.858231</v>
+        <v>5.882353</v>
       </c>
       <c r="H58" t="n">
-        <v>7209.009766</v>
+        <v>7580.060059</v>
       </c>
       <c r="I58" t="n">
-        <v>24892.310547</v>
+        <v>26972.619141</v>
       </c>
       <c r="J58" t="n">
-        <v>49652.140625</v>
+        <v>51032.460938</v>
       </c>
       <c r="K58" t="n">
-        <v>4614.700195</v>
+        <v>4560.5</v>
       </c>
       <c r="L58" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
       <c r="M58" t="n">
-        <v>114.010002</v>
+        <v>92.050003</v>
       </c>
       <c r="N58" t="n">
-        <v>1182</v>
+        <v>1186.75</v>
       </c>
       <c r="O58" t="n">
-        <v>464.75</v>
+        <v>446.75</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.076816</v>
+        <v>-7.223011</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.103105</v>
+        <v>-7.246454</v>
       </c>
       <c r="R58" t="n">
-        <v>-3.533332</v>
+        <v>-4.120598</v>
       </c>
       <c r="S58" t="n">
-        <v>5.87926</v>
+        <v>6.931676</v>
       </c>
       <c r="T58" t="n">
-        <v>-4.682751</v>
+        <v>0.6816179999999999</v>
       </c>
       <c r="U58" t="n">
-        <v>-2.811955</v>
+        <v>0.411758</v>
       </c>
       <c r="V58" t="n">
-        <v>10.423339</v>
+        <v>5.147036</v>
       </c>
       <c r="W58" t="n">
-        <v>15.292187</v>
+        <v>8.357234</v>
       </c>
       <c r="X58" t="n">
-        <v>7.143981</v>
+        <v>2.779981</v>
       </c>
       <c r="Y58" t="n">
-        <v>-0.70789</v>
+        <v>-1.174512</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.639774</v>
+        <v>-16.855429</v>
       </c>
       <c r="AA58" t="n">
-        <v>-3.667086</v>
+        <v>-19.261467</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.529219</v>
+        <v>-3.87305</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B59" t="n">
-        <v>173788</v>
+        <v>172024</v>
       </c>
       <c r="C59" t="n">
-        <v>170.75</v>
+        <v>169.050003</v>
       </c>
       <c r="D59" t="n">
-        <v>110.989998</v>
+        <v>107.980003</v>
       </c>
       <c r="E59" t="n">
-        <v>430.399994</v>
+        <v>435.649994</v>
       </c>
       <c r="F59" t="n">
-        <v>5.0517</v>
+        <v>5.181787</v>
       </c>
       <c r="G59" t="n">
-        <v>5.882353</v>
+        <v>5.91716</v>
       </c>
       <c r="H59" t="n">
-        <v>7580.060059</v>
+        <v>7499.359863</v>
       </c>
       <c r="I59" t="n">
-        <v>26972.619141</v>
+        <v>26213.720703</v>
       </c>
       <c r="J59" t="n">
-        <v>51032.460938</v>
+        <v>52319.199219</v>
       </c>
       <c r="K59" t="n">
-        <v>4560.5</v>
+        <v>4022.899902</v>
       </c>
       <c r="L59" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
       <c r="M59" t="n">
-        <v>92.050003</v>
+        <v>72.91999800000001</v>
       </c>
       <c r="N59" t="n">
-        <v>1186.75</v>
+        <v>1116.75</v>
       </c>
       <c r="O59" t="n">
-        <v>446.75</v>
+        <v>412.75</v>
       </c>
       <c r="P59" t="n">
-        <v>-7.223011</v>
+        <v>-1.01503</v>
       </c>
       <c r="Q59" t="n">
-        <v>-7.246454</v>
+        <v>-0.995606</v>
       </c>
       <c r="R59" t="n">
-        <v>-4.120598</v>
+        <v>-2.711951</v>
       </c>
       <c r="S59" t="n">
-        <v>6.931676</v>
+        <v>1.219796</v>
       </c>
       <c r="T59" t="n">
-        <v>0.6816179999999999</v>
+        <v>2.575111</v>
       </c>
       <c r="U59" t="n">
-        <v>0.411758</v>
+        <v>0.591722</v>
       </c>
       <c r="V59" t="n">
-        <v>5.147036</v>
+        <v>-1.064638</v>
       </c>
       <c r="W59" t="n">
-        <v>8.357234</v>
+        <v>-2.813588</v>
       </c>
       <c r="X59" t="n">
-        <v>2.779981</v>
+        <v>2.521411</v>
       </c>
       <c r="Y59" t="n">
-        <v>-1.174512</v>
+        <v>-11.788183</v>
       </c>
       <c r="Z59" t="n">
-        <v>-16.855429</v>
+        <v>-20.44414</v>
       </c>
       <c r="AA59" t="n">
-        <v>-19.261467</v>
+        <v>-20.782188</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
       <c r="AC59" t="n">
-        <v>-3.87305</v>
+        <v>-7.61052</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B60" t="n">
-        <v>172024</v>
+        <v>177999</v>
       </c>
       <c r="C60" t="n">
-        <v>169.050003</v>
+        <v>175.020004</v>
       </c>
       <c r="D60" t="n">
-        <v>107.980003</v>
+        <v>107.25</v>
       </c>
       <c r="E60" t="n">
-        <v>435.649994</v>
+        <v>428.390015</v>
       </c>
       <c r="F60" t="n">
-        <v>5.181787</v>
+        <v>5.0781</v>
       </c>
       <c r="G60" t="n">
-        <v>5.91716</v>
+        <v>5.847953</v>
       </c>
       <c r="H60" t="n">
-        <v>7499.359863</v>
+        <v>7489.720215</v>
       </c>
       <c r="I60" t="n">
-        <v>26213.720703</v>
+        <v>25373.849609</v>
       </c>
       <c r="J60" t="n">
-        <v>52319.199219</v>
+        <v>52485.03125</v>
       </c>
       <c r="K60" t="n">
-        <v>4022.899902</v>
+        <v>4049.100098</v>
       </c>
       <c r="L60" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
       <c r="M60" t="n">
-        <v>72.91999800000001</v>
+        <v>90.120003</v>
       </c>
       <c r="N60" t="n">
-        <v>1116.75</v>
+        <v>1172</v>
       </c>
       <c r="O60" t="n">
-        <v>412.75</v>
+        <v>440.75</v>
       </c>
       <c r="P60" t="n">
-        <v>-1.01503</v>
+        <v>3.473353</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.995606</v>
+        <v>3.5315</v>
       </c>
       <c r="R60" t="n">
-        <v>-2.711951</v>
+        <v>-0.676054</v>
       </c>
       <c r="S60" t="n">
-        <v>1.219796</v>
+        <v>-1.666471</v>
       </c>
       <c r="T60" t="n">
-        <v>2.575111</v>
+        <v>-2.000986</v>
       </c>
       <c r="U60" t="n">
-        <v>0.591722</v>
+        <v>-1.169601</v>
       </c>
       <c r="V60" t="n">
-        <v>-1.064638</v>
+        <v>-0.12854</v>
       </c>
       <c r="W60" t="n">
-        <v>-2.813588</v>
+        <v>-3.203937</v>
       </c>
       <c r="X60" t="n">
-        <v>2.521411</v>
+        <v>0.316962</v>
       </c>
       <c r="Y60" t="n">
-        <v>-11.788183</v>
+        <v>0.651276</v>
       </c>
       <c r="Z60" t="n">
-        <v>-20.44414</v>
+        <v>21.827335</v>
       </c>
       <c r="AA60" t="n">
-        <v>-20.782188</v>
+        <v>23.5875</v>
       </c>
       <c r="AB60" t="n">
-        <v>-5.898462</v>
+        <v>4.947392</v>
       </c>
       <c r="AC60" t="n">
-        <v>-7.61052</v>
+        <v>6.783767</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B61" t="n">
-        <v>177999</v>
+        <v>177419</v>
       </c>
       <c r="C61" t="n">
-        <v>175.020004</v>
+        <v>172.720001</v>
       </c>
       <c r="D61" t="n">
-        <v>107.25</v>
+        <v>104.580002</v>
       </c>
       <c r="E61" t="n">
-        <v>428.390015</v>
+        <v>452.049988</v>
       </c>
       <c r="F61" t="n">
-        <v>5.0781</v>
+        <v>5.1912</v>
       </c>
       <c r="G61" t="n">
-        <v>5.847953</v>
+        <v>6.009615</v>
       </c>
       <c r="H61" t="n">
-        <v>7489.720215</v>
+        <v>7686.140137</v>
       </c>
       <c r="I61" t="n">
-        <v>25373.849609</v>
+        <v>26370.890625</v>
       </c>
       <c r="J61" t="n">
-        <v>52485.03125</v>
+        <v>53185.898438</v>
       </c>
       <c r="K61" t="n">
-        <v>4049.100098</v>
+        <v>4431.100098</v>
       </c>
       <c r="L61" t="n">
-        <v>84.66999800000001</v>
+        <v>85.760002</v>
       </c>
       <c r="M61" t="n">
-        <v>90.120003</v>
+        <v>90.489998</v>
       </c>
       <c r="N61" t="n">
-        <v>1172</v>
+        <v>1275.25</v>
       </c>
       <c r="O61" t="n">
-        <v>440.75</v>
+        <v>515</v>
       </c>
       <c r="P61" t="n">
-        <v>3.473353</v>
+        <v>-0.325845</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5315</v>
+        <v>-1.314137</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.676054</v>
+        <v>-2.489509</v>
       </c>
       <c r="S61" t="n">
-        <v>-1.666471</v>
+        <v>5.522998</v>
       </c>
       <c r="T61" t="n">
-        <v>-2.000986</v>
+        <v>2.227203</v>
       </c>
       <c r="U61" t="n">
-        <v>-1.169601</v>
+        <v>2.764422</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.12854</v>
+        <v>2.622527</v>
       </c>
       <c r="W61" t="n">
-        <v>-3.203937</v>
+        <v>3.929404</v>
       </c>
       <c r="X61" t="n">
-        <v>0.316962</v>
+        <v>1.335366</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.651276</v>
+        <v>9.434195000000001</v>
       </c>
       <c r="Z61" t="n">
-        <v>21.827335</v>
+        <v>1.287356</v>
       </c>
       <c r="AA61" t="n">
-        <v>23.5875</v>
+        <v>0.410558</v>
       </c>
       <c r="AB61" t="n">
-        <v>4.947392</v>
+        <v>8.809727000000001</v>
       </c>
       <c r="AC61" t="n">
-        <v>6.783767</v>
+        <v>16.846285</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>177580.765625</v>
+        <v>180393.8125</v>
       </c>
       <c r="C62" t="n">
-        <v>174.800003</v>
+        <v>177.610001</v>
       </c>
       <c r="D62" t="n">
-        <v>106.550003</v>
+        <v>108.040001</v>
       </c>
       <c r="E62" t="n">
-        <v>449.230011</v>
+        <v>444.790009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1834</v>
+        <v>5.1434</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0184</v>
+        <v>5.9697</v>
       </c>
       <c r="H62" t="n">
-        <v>7672.839844</v>
+        <v>7659.640137</v>
       </c>
       <c r="I62" t="n">
-        <v>26289.875</v>
+        <v>26179.060547</v>
       </c>
       <c r="J62" t="n">
-        <v>53199.460938</v>
+        <v>53141.730469</v>
       </c>
       <c r="K62" t="n">
-        <v>4483.399902</v>
+        <v>4419.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>85.68000000000001</v>
+        <v>87.650002</v>
       </c>
       <c r="M62" t="n">
-        <v>88.269997</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1290</v>
+        <v>1312</v>
       </c>
       <c r="O62" t="n">
-        <v>538</v>
+        <v>542.25</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.234964</v>
+        <v>1.676716</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.125701</v>
+        <v>2.831171</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.652678</v>
+        <v>3.308471</v>
       </c>
       <c r="S62" t="n">
-        <v>4.864725</v>
+        <v>-1.606012</v>
       </c>
       <c r="T62" t="n">
-        <v>2.073609</v>
+        <v>-0.920781</v>
       </c>
       <c r="U62" t="n">
-        <v>2.91465</v>
+        <v>-0.664187</v>
       </c>
       <c r="V62" t="n">
-        <v>2.444946</v>
+        <v>-0.344776</v>
       </c>
       <c r="W62" t="n">
-        <v>3.610116</v>
+        <v>-0.727431</v>
       </c>
       <c r="X62" t="n">
-        <v>1.361207</v>
+        <v>-0.08304499999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>10.725835</v>
+        <v>-0.270813</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.192869</v>
+        <v>2.203824</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.052825</v>
+        <v>1.746051</v>
       </c>
       <c r="AB62" t="n">
-        <v>10.068259</v>
+        <v>2.881788</v>
       </c>
       <c r="AC62" t="n">
-        <v>22.064663</v>
+        <v>5.291262</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5798,13 +5798,13 @@
         <v>177419</v>
       </c>
       <c r="C61" t="n">
-        <v>172.720001</v>
+        <v>174.779999</v>
       </c>
       <c r="D61" t="n">
-        <v>104.580002</v>
+        <v>106.129997</v>
       </c>
       <c r="E61" t="n">
-        <v>452.049988</v>
+        <v>449.350006</v>
       </c>
       <c r="F61" t="n">
         <v>5.1912</v>
@@ -5840,13 +5840,13 @@
         <v>-0.325845</v>
       </c>
       <c r="Q61" t="n">
-        <v>-1.314137</v>
+        <v>-0.13713</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.489509</v>
+        <v>-1.044292</v>
       </c>
       <c r="S61" t="n">
-        <v>5.522998</v>
+        <v>4.892736</v>
       </c>
       <c r="T61" t="n">
         <v>2.227203</v>
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>180393.8125</v>
+        <v>183242.234375</v>
       </c>
       <c r="C62" t="n">
-        <v>177.610001</v>
+        <v>180.369995</v>
       </c>
       <c r="D62" t="n">
-        <v>108.040001</v>
+        <v>109.370003</v>
       </c>
       <c r="E62" t="n">
-        <v>444.790009</v>
+        <v>442.920013</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1434</v>
+        <v>5.1304</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9697</v>
+        <v>5.9502</v>
       </c>
       <c r="H62" t="n">
-        <v>7659.640137</v>
+        <v>7656.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26179.060547</v>
+        <v>26157.546875</v>
       </c>
       <c r="J62" t="n">
-        <v>53141.730469</v>
+        <v>53092.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4419.100098</v>
+        <v>4431.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>87.650002</v>
+        <v>89.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>92.06999999999999</v>
+        <v>93.889999</v>
       </c>
       <c r="N62" t="n">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="O62" t="n">
-        <v>542.25</v>
+        <v>541</v>
       </c>
       <c r="P62" t="n">
-        <v>1.676716</v>
+        <v>3.282193</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.831171</v>
+        <v>3.198304</v>
       </c>
       <c r="R62" t="n">
-        <v>3.308471</v>
+        <v>3.052865</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.606012</v>
+        <v>-1.430954</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.920781</v>
+        <v>-1.171205</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.664187</v>
+        <v>-0.988663</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.344776</v>
+        <v>-0.382118</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.727431</v>
+        <v>-0.809012</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.08304499999999999</v>
+        <v>-0.175776</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.270813</v>
+        <v>0.004507</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.203824</v>
+        <v>3.929565</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.746051</v>
+        <v>3.757323</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.881788</v>
+        <v>2.25446</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.291262</v>
+        <v>5.048544</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>183242.234375</v>
+        <v>187884.234375</v>
       </c>
       <c r="C62" t="n">
-        <v>180.369995</v>
+        <v>184.940002</v>
       </c>
       <c r="D62" t="n">
-        <v>109.370003</v>
+        <v>112.779999</v>
       </c>
       <c r="E62" t="n">
-        <v>442.920013</v>
+        <v>444.200012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1304</v>
+        <v>5.0978</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9502</v>
+        <v>5.9255</v>
       </c>
       <c r="H62" t="n">
-        <v>7656.77002</v>
+        <v>7696.549805</v>
       </c>
       <c r="I62" t="n">
-        <v>26157.546875</v>
+        <v>26400.578125</v>
       </c>
       <c r="J62" t="n">
-        <v>53092.410156</v>
+        <v>53321.730469</v>
       </c>
       <c r="K62" t="n">
-        <v>4431.299805</v>
+        <v>4514.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>89.129997</v>
+        <v>91.870003</v>
       </c>
       <c r="M62" t="n">
-        <v>93.889999</v>
+        <v>96.199997</v>
       </c>
       <c r="N62" t="n">
-        <v>1304</v>
+        <v>1292.5</v>
       </c>
       <c r="O62" t="n">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="P62" t="n">
-        <v>3.282193</v>
+        <v>5.898598</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.198304</v>
+        <v>5.813024</v>
       </c>
       <c r="R62" t="n">
-        <v>3.052865</v>
+        <v>6.265902</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.430954</v>
+        <v>-1.146099</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.171205</v>
+        <v>-1.799199</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.988663</v>
+        <v>-1.399674</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.382118</v>
+        <v>0.135434</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.809012</v>
+        <v>0.112577</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.175776</v>
+        <v>0.255391</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.004507</v>
+        <v>1.888915</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.929565</v>
+        <v>7.124534</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.757323</v>
+        <v>6.310089</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.25446</v>
+        <v>1.352676</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.048544</v>
+        <v>2.330097</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -610,9 +610,7 @@
       <c r="N2" t="n">
         <v>1256</v>
       </c>
-      <c r="O2" t="n">
-        <v>536.75</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -671,9 +669,7 @@
       <c r="N3" t="n">
         <v>1235.75</v>
       </c>
-      <c r="O3" t="n">
-        <v>568.25</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>-6.738212</v>
       </c>
@@ -713,9 +709,7 @@
       <c r="AB3" t="n">
         <v>-1.612261</v>
       </c>
-      <c r="AC3" t="n">
-        <v>5.868654</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -760,9 +754,7 @@
       <c r="N4" t="n">
         <v>1217.25</v>
       </c>
-      <c r="O4" t="n">
-        <v>567</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>-1.532352</v>
       </c>
@@ -802,9 +794,7 @@
       <c r="AB4" t="n">
         <v>-1.497067</v>
       </c>
-      <c r="AC4" t="n">
-        <v>-0.219974</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -849,9 +839,7 @@
       <c r="N5" t="n">
         <v>1328.75</v>
       </c>
-      <c r="O5" t="n">
-        <v>593.25</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>2.852377</v>
       </c>
@@ -891,9 +879,7 @@
       <c r="AB5" t="n">
         <v>9.159992000000001</v>
       </c>
-      <c r="AC5" t="n">
-        <v>4.62963</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -938,9 +924,7 @@
       <c r="N6" t="n">
         <v>1490.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>626</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>7.21795</v>
       </c>
@@ -980,9 +964,7 @@
       <c r="AB6" t="n">
         <v>12.173095</v>
       </c>
-      <c r="AC6" t="n">
-        <v>5.520438</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1027,9 +1009,7 @@
       <c r="N7" t="n">
         <v>1644.25</v>
       </c>
-      <c r="O7" t="n">
-        <v>697.5</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0.67089</v>
       </c>
@@ -1069,9 +1049,7 @@
       <c r="AB7" t="n">
         <v>10.31533</v>
       </c>
-      <c r="AC7" t="n">
-        <v>11.421725</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1116,9 +1094,7 @@
       <c r="N8" t="n">
         <v>1618.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>748.75</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>6.060526</v>
       </c>
@@ -1158,9 +1134,7 @@
       <c r="AB8" t="n">
         <v>-1.581268</v>
       </c>
-      <c r="AC8" t="n">
-        <v>7.34767</v>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1205,9 +1179,7 @@
       <c r="N9" t="n">
         <v>1708.25</v>
       </c>
-      <c r="O9" t="n">
-        <v>818.25</v>
-      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>-10.102584</v>
       </c>
@@ -1247,9 +1219,7 @@
       <c r="AB9" t="n">
         <v>5.561563</v>
       </c>
-      <c r="AC9" t="n">
-        <v>9.282137000000001</v>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1294,9 +1264,7 @@
       <c r="N10" t="n">
         <v>1683.25</v>
       </c>
-      <c r="O10" t="n">
-        <v>753.5</v>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>3.221291</v>
       </c>
@@ -1336,9 +1304,7 @@
       <c r="AB10" t="n">
         <v>-1.463486</v>
       </c>
-      <c r="AC10" t="n">
-        <v>-7.913229</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1383,9 +1349,7 @@
       <c r="N11" t="n">
         <v>1675</v>
       </c>
-      <c r="O11" t="n">
-        <v>743.75</v>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>-11.503264</v>
       </c>
@@ -1425,9 +1389,7 @@
       <c r="AB11" t="n">
         <v>-0.490123</v>
       </c>
-      <c r="AC11" t="n">
-        <v>-1.293962</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1472,9 +1434,7 @@
       <c r="N12" t="n">
         <v>1637</v>
       </c>
-      <c r="O12" t="n">
-        <v>616.25</v>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>4.691401</v>
       </c>
@@ -1514,9 +1474,7 @@
       <c r="AB12" t="n">
         <v>-2.268657</v>
       </c>
-      <c r="AC12" t="n">
-        <v>-17.142857</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1561,9 +1519,7 @@
       <c r="N13" t="n">
         <v>1507.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>673.75</v>
-      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>6.162943</v>
       </c>
@@ -1603,9 +1559,7 @@
       <c r="AB13" t="n">
         <v>-7.910812</v>
       </c>
-      <c r="AC13" t="n">
-        <v>9.330629</v>
-      </c>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1650,9 +1604,7 @@
       <c r="N14" t="n">
         <v>1364.75</v>
       </c>
-      <c r="O14" t="n">
-        <v>677.5</v>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0.469308</v>
       </c>
@@ -1692,9 +1644,7 @@
       <c r="AB14" t="n">
         <v>-9.46932</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0.556586</v>
-      </c>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1739,9 +1689,7 @@
       <c r="N15" t="n">
         <v>1407</v>
       </c>
-      <c r="O15" t="n">
-        <v>691.5</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>5.452711</v>
       </c>
@@ -1781,9 +1729,7 @@
       <c r="AB15" t="n">
         <v>3.095805</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.066421</v>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1828,9 +1774,7 @@
       <c r="N16" t="n">
         <v>1469.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>662</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>-3.060231</v>
       </c>
@@ -1870,9 +1814,7 @@
       <c r="AB16" t="n">
         <v>4.442075</v>
       </c>
-      <c r="AC16" t="n">
-        <v>-4.266088</v>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1917,9 +1859,7 @@
       <c r="N17" t="n">
         <v>1519.25</v>
       </c>
-      <c r="O17" t="n">
-        <v>678.5</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>-2.182494</v>
       </c>
@@ -1959,9 +1899,7 @@
       <c r="AB17" t="n">
         <v>3.385505</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.492447</v>
-      </c>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2006,9 +1944,7 @@
       <c r="N18" t="n">
         <v>1538</v>
       </c>
-      <c r="O18" t="n">
-        <v>679.75</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>3.181831</v>
       </c>
@@ -2048,9 +1984,7 @@
       <c r="AB18" t="n">
         <v>1.234162</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0.18423</v>
-      </c>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2095,9 +2029,7 @@
       <c r="N19" t="n">
         <v>1490.5</v>
       </c>
-      <c r="O19" t="n">
-        <v>629.5</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>-7.574957</v>
       </c>
@@ -2137,9 +2069,7 @@
       <c r="AB19" t="n">
         <v>-3.088427</v>
       </c>
-      <c r="AC19" t="n">
-        <v>-7.392424</v>
-      </c>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2184,9 +2114,7 @@
       <c r="N20" t="n">
         <v>1505.5</v>
       </c>
-      <c r="O20" t="n">
-        <v>660.5</v>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>-2.906644</v>
       </c>
@@ -2226,9 +2154,7 @@
       <c r="AB20" t="n">
         <v>1.006374</v>
       </c>
-      <c r="AC20" t="n">
-        <v>4.924543</v>
-      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2273,9 +2199,7 @@
       <c r="N21" t="n">
         <v>1444.25</v>
       </c>
-      <c r="O21" t="n">
-        <v>636</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>2.502896</v>
       </c>
@@ -2315,9 +2239,7 @@
       <c r="AB21" t="n">
         <v>-4.068416</v>
       </c>
-      <c r="AC21" t="n">
-        <v>-3.709311</v>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2362,9 +2284,7 @@
       <c r="N22" t="n">
         <v>1299.75</v>
       </c>
-      <c r="O22" t="n">
-        <v>594</v>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>3.73736</v>
       </c>
@@ -2404,9 +2324,7 @@
       <c r="AB22" t="n">
         <v>-10.005193</v>
       </c>
-      <c r="AC22" t="n">
-        <v>-6.603774</v>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2451,9 +2369,7 @@
       <c r="N23" t="n">
         <v>1557.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>554.5</v>
-      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>9.001708000000001</v>
       </c>
@@ -2493,9 +2409,7 @@
       <c r="AB23" t="n">
         <v>19.811502</v>
       </c>
-      <c r="AC23" t="n">
-        <v>-6.649832</v>
-      </c>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2540,9 +2454,7 @@
       <c r="N24" t="n">
         <v>1445.75</v>
       </c>
-      <c r="O24" t="n">
-        <v>504</v>
-      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>3.265389</v>
       </c>
@@ -2582,9 +2494,7 @@
       <c r="AB24" t="n">
         <v>-7.160058</v>
       </c>
-      <c r="AC24" t="n">
-        <v>-9.107303999999999</v>
-      </c>
+      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2629,9 +2539,7 @@
       <c r="N25" t="n">
         <v>1360</v>
       </c>
-      <c r="O25" t="n">
-        <v>461</v>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>-5.085163</v>
       </c>
@@ -2671,9 +2579,7 @@
       <c r="AB25" t="n">
         <v>-5.931178</v>
       </c>
-      <c r="AC25" t="n">
-        <v>-8.531746</v>
-      </c>
+      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2718,9 +2624,7 @@
       <c r="N26" t="n">
         <v>1275</v>
       </c>
-      <c r="O26" t="n">
-        <v>476.75</v>
-      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>0.711064</v>
       </c>
@@ -2760,9 +2664,7 @@
       <c r="AB26" t="n">
         <v>-6.25</v>
       </c>
-      <c r="AC26" t="n">
-        <v>3.416486</v>
-      </c>
+      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2807,9 +2709,7 @@
       <c r="N27" t="n">
         <v>1287</v>
       </c>
-      <c r="O27" t="n">
-        <v>478.75</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>-2.934843</v>
       </c>
@@ -2849,9 +2749,7 @@
       <c r="AB27" t="n">
         <v>0.941176</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0.419507</v>
-      </c>
+      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2896,9 +2794,7 @@
       <c r="N28" t="n">
         <v>1342.75</v>
       </c>
-      <c r="O28" t="n">
-        <v>461.75</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
         <v>12.538888</v>
       </c>
@@ -2938,9 +2834,7 @@
       <c r="AB28" t="n">
         <v>4.331779</v>
       </c>
-      <c r="AC28" t="n">
-        <v>-3.550914</v>
-      </c>
+      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2985,9 +2879,7 @@
       <c r="N29" t="n">
         <v>1293.5</v>
       </c>
-      <c r="O29" t="n">
-        <v>471.25</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>5.382821</v>
       </c>
@@ -3027,9 +2919,7 @@
       <c r="AB29" t="n">
         <v>-3.667846</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.05739</v>
-      </c>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3074,9 +2964,7 @@
       <c r="N30" t="n">
         <v>1222.25</v>
       </c>
-      <c r="O30" t="n">
-        <v>448.25</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
         <v>-4.794128</v>
       </c>
@@ -3116,9 +3004,7 @@
       <c r="AB30" t="n">
         <v>-5.508311</v>
       </c>
-      <c r="AC30" t="n">
-        <v>-4.880637</v>
-      </c>
+      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3163,9 +3049,7 @@
       <c r="N31" t="n">
         <v>1128.25</v>
       </c>
-      <c r="O31" t="n">
-        <v>415.75</v>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>0.992548</v>
       </c>
@@ -3205,9 +3089,7 @@
       <c r="AB31" t="n">
         <v>-7.690734</v>
       </c>
-      <c r="AC31" t="n">
-        <v>-7.250418</v>
-      </c>
+      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3252,9 +3134,7 @@
       <c r="N32" t="n">
         <v>1191.5</v>
       </c>
-      <c r="O32" t="n">
-        <v>442</v>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
         <v>-0.708417</v>
       </c>
@@ -3294,9 +3174,7 @@
       <c r="AB32" t="n">
         <v>5.606027</v>
       </c>
-      <c r="AC32" t="n">
-        <v>6.313891</v>
-      </c>
+      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3341,9 +3219,7 @@
       <c r="N33" t="n">
         <v>1145.5</v>
       </c>
-      <c r="O33" t="n">
-        <v>439.5</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
         <v>-1.703277</v>
       </c>
@@ -3383,9 +3259,7 @@
       <c r="AB33" t="n">
         <v>-3.86068</v>
       </c>
-      <c r="AC33" t="n">
-        <v>-0.565611</v>
-      </c>
+      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3430,9 +3304,7 @@
       <c r="N34" t="n">
         <v>1205</v>
       </c>
-      <c r="O34" t="n">
-        <v>446.25</v>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
         <v>-3.038341</v>
       </c>
@@ -3472,9 +3344,7 @@
       <c r="AB34" t="n">
         <v>5.194238</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.535836</v>
-      </c>
+      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3519,9 +3389,7 @@
       <c r="N35" t="n">
         <v>1150.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>397.25</v>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>1.481597</v>
       </c>
@@ -3561,9 +3429,7 @@
       <c r="AB35" t="n">
         <v>-4.522822</v>
       </c>
-      <c r="AC35" t="n">
-        <v>-10.980392</v>
-      </c>
+      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3608,9 +3474,7 @@
       <c r="N36" t="n">
         <v>1028.5</v>
       </c>
-      <c r="O36" t="n">
-        <v>382.75</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
         <v>3.022428</v>
       </c>
@@ -3650,9 +3514,7 @@
       <c r="AB36" t="n">
         <v>-10.604085</v>
       </c>
-      <c r="AC36" t="n">
-        <v>-3.650094</v>
-      </c>
+      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3697,9 +3559,7 @@
       <c r="N37" t="n">
         <v>982</v>
       </c>
-      <c r="O37" t="n">
-        <v>378</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
         <v>6.542788</v>
       </c>
@@ -3739,9 +3599,7 @@
       <c r="AB37" t="n">
         <v>-4.521147</v>
       </c>
-      <c r="AC37" t="n">
-        <v>-1.241019</v>
-      </c>
+      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3786,9 +3644,7 @@
       <c r="N38" t="n">
         <v>1057</v>
       </c>
-      <c r="O38" t="n">
-        <v>424.75</v>
-      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
         <v>-3.079321</v>
       </c>
@@ -3828,9 +3684,7 @@
       <c r="AB38" t="n">
         <v>7.637475</v>
       </c>
-      <c r="AC38" t="n">
-        <v>12.367725</v>
-      </c>
+      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3875,9 +3729,7 @@
       <c r="N39" t="n">
         <v>982.5</v>
       </c>
-      <c r="O39" t="n">
-        <v>410.75</v>
-      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>-1.595406</v>
       </c>
@@ -3917,9 +3769,7 @@
       <c r="AB39" t="n">
         <v>-7.04825</v>
       </c>
-      <c r="AC39" t="n">
-        <v>-3.296057</v>
-      </c>
+      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3964,9 +3814,7 @@
       <c r="N40" t="n">
         <v>989.5</v>
       </c>
-      <c r="O40" t="n">
-        <v>423</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>-3.118423</v>
       </c>
@@ -4006,9 +3854,7 @@
       <c r="AB40" t="n">
         <v>0.712468</v>
       </c>
-      <c r="AC40" t="n">
-        <v>2.982349</v>
-      </c>
+      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4053,9 +3899,7 @@
       <c r="N41" t="n">
         <v>998.25</v>
       </c>
-      <c r="O41" t="n">
-        <v>458.5</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>-4.2851</v>
       </c>
@@ -4095,9 +3939,7 @@
       <c r="AB41" t="n">
         <v>0.884285</v>
       </c>
-      <c r="AC41" t="n">
-        <v>8.392435000000001</v>
-      </c>
+      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4142,9 +3984,7 @@
       <c r="N42" t="n">
         <v>1042</v>
       </c>
-      <c r="O42" t="n">
-        <v>482</v>
-      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>4.865193</v>
       </c>
@@ -4184,9 +4024,7 @@
       <c r="AB42" t="n">
         <v>4.38267</v>
       </c>
-      <c r="AC42" t="n">
-        <v>5.125409</v>
-      </c>
+      <c r="AC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4231,9 +4069,7 @@
       <c r="N43" t="n">
         <v>1011.5</v>
       </c>
-      <c r="O43" t="n">
-        <v>453.5</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>-2.644785</v>
       </c>
@@ -4273,9 +4109,7 @@
       <c r="AB43" t="n">
         <v>-2.927063</v>
       </c>
-      <c r="AC43" t="n">
-        <v>-5.912863</v>
-      </c>
+      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4320,9 +4154,7 @@
       <c r="N44" t="n">
         <v>1014.75</v>
       </c>
-      <c r="O44" t="n">
-        <v>457.25</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
         <v>6.075782</v>
       </c>
@@ -4362,9 +4194,7 @@
       <c r="AB44" t="n">
         <v>0.321305</v>
       </c>
-      <c r="AC44" t="n">
-        <v>0.826902</v>
-      </c>
+      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4409,9 +4239,7 @@
       <c r="N45" t="n">
         <v>1034.75</v>
       </c>
-      <c r="O45" t="n">
-        <v>467.25</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
         <v>3.690312</v>
       </c>
@@ -4451,9 +4279,7 @@
       <c r="AB45" t="n">
         <v>1.970929</v>
       </c>
-      <c r="AC45" t="n">
-        <v>2.186987</v>
-      </c>
+      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4498,9 +4324,7 @@
       <c r="N46" t="n">
         <v>1041.75</v>
       </c>
-      <c r="O46" t="n">
-        <v>444</v>
-      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
         <v>1.451132</v>
       </c>
@@ -4540,9 +4364,7 @@
       <c r="AB46" t="n">
         <v>0.676492</v>
       </c>
-      <c r="AC46" t="n">
-        <v>-4.975923</v>
-      </c>
+      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4587,9 +4409,7 @@
       <c r="N47" t="n">
         <v>1024.25</v>
       </c>
-      <c r="O47" t="n">
-        <v>420.5</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>1.334044</v>
       </c>
@@ -4629,9 +4449,7 @@
       <c r="AB47" t="n">
         <v>-1.679866</v>
       </c>
-      <c r="AC47" t="n">
-        <v>-5.292793</v>
-      </c>
+      <c r="AC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4676,9 +4494,7 @@
       <c r="N48" t="n">
         <v>961.75</v>
       </c>
-      <c r="O48" t="n">
-        <v>394</v>
-      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>-4.165496</v>
       </c>
@@ -4718,9 +4534,7 @@
       <c r="AB48" t="n">
         <v>-6.102026</v>
       </c>
-      <c r="AC48" t="n">
-        <v>-6.302021</v>
-      </c>
+      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4765,9 +4579,7 @@
       <c r="N49" t="n">
         <v>1036.75</v>
       </c>
-      <c r="O49" t="n">
-        <v>398</v>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
         <v>6.275597</v>
       </c>
@@ -4807,9 +4619,7 @@
       <c r="AB49" t="n">
         <v>7.798284</v>
       </c>
-      <c r="AC49" t="n">
-        <v>1.015228</v>
-      </c>
+      <c r="AC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4854,9 +4664,7 @@
       <c r="N50" t="n">
         <v>1001.75</v>
       </c>
-      <c r="O50" t="n">
-        <v>415.5</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>3.404704</v>
       </c>
@@ -4896,9 +4704,7 @@
       <c r="AB50" t="n">
         <v>-3.375934</v>
       </c>
-      <c r="AC50" t="n">
-        <v>4.396985</v>
-      </c>
+      <c r="AC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4943,9 +4749,7 @@
       <c r="N51" t="n">
         <v>1099.75</v>
       </c>
-      <c r="O51" t="n">
-        <v>431.5</v>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
         <v>2.258662</v>
       </c>
@@ -4985,9 +4789,7 @@
       <c r="AB51" t="n">
         <v>9.78288</v>
       </c>
-      <c r="AC51" t="n">
-        <v>3.850782</v>
-      </c>
+      <c r="AC51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5032,9 +4834,7 @@
       <c r="N52" t="n">
         <v>1137.75</v>
       </c>
-      <c r="O52" t="n">
-        <v>435.5</v>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
         <v>6.374214</v>
       </c>
@@ -5074,9 +4874,7 @@
       <c r="AB52" t="n">
         <v>3.455331</v>
       </c>
-      <c r="AC52" t="n">
-        <v>0.926999</v>
-      </c>
+      <c r="AC52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5121,9 +4919,7 @@
       <c r="N53" t="n">
         <v>1030.5</v>
       </c>
-      <c r="O53" t="n">
-        <v>440.25</v>
-      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
         <v>1.290611</v>
       </c>
@@ -5163,9 +4959,7 @@
       <c r="AB53" t="n">
         <v>-9.426500000000001</v>
       </c>
-      <c r="AC53" t="n">
-        <v>1.0907</v>
-      </c>
+      <c r="AC53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5210,9 +5004,7 @@
       <c r="N54" t="n">
         <v>1064.25</v>
       </c>
-      <c r="O54" t="n">
-        <v>428.25</v>
-      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
         <v>12.561055</v>
       </c>
@@ -5252,9 +5044,7 @@
       <c r="AB54" t="n">
         <v>3.275109</v>
       </c>
-      <c r="AC54" t="n">
-        <v>-2.725724</v>
-      </c>
+      <c r="AC54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5299,9 +5089,7 @@
       <c r="N55" t="n">
         <v>1157.25</v>
       </c>
-      <c r="O55" t="n">
-        <v>438.75</v>
-      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>4.092874</v>
       </c>
@@ -5341,9 +5129,7 @@
       <c r="AB55" t="n">
         <v>8.738548</v>
       </c>
-      <c r="AC55" t="n">
-        <v>2.451839</v>
-      </c>
+      <c r="AC55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5388,9 +5174,7 @@
       <c r="N56" t="n">
         <v>1171</v>
       </c>
-      <c r="O56" t="n">
-        <v>457.75</v>
-      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
         <v>-0.7018489999999999</v>
       </c>
@@ -5430,9 +5214,7 @@
       <c r="AB56" t="n">
         <v>1.188162</v>
       </c>
-      <c r="AC56" t="n">
-        <v>4.330484</v>
-      </c>
+      <c r="AC56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5477,9 +5259,7 @@
       <c r="N57" t="n">
         <v>1182</v>
       </c>
-      <c r="O57" t="n">
-        <v>464.75</v>
-      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
         <v>-0.076816</v>
       </c>
@@ -5519,9 +5299,7 @@
       <c r="AB57" t="n">
         <v>0.939368</v>
       </c>
-      <c r="AC57" t="n">
-        <v>1.529219</v>
-      </c>
+      <c r="AC57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5566,9 +5344,7 @@
       <c r="N58" t="n">
         <v>1186.75</v>
       </c>
-      <c r="O58" t="n">
-        <v>446.75</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
         <v>-7.223011</v>
       </c>
@@ -5608,9 +5384,7 @@
       <c r="AB58" t="n">
         <v>0.401861</v>
       </c>
-      <c r="AC58" t="n">
-        <v>-3.87305</v>
-      </c>
+      <c r="AC58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5655,9 +5429,7 @@
       <c r="N59" t="n">
         <v>1116.75</v>
       </c>
-      <c r="O59" t="n">
-        <v>412.75</v>
-      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
         <v>-1.01503</v>
       </c>
@@ -5697,9 +5469,7 @@
       <c r="AB59" t="n">
         <v>-5.898462</v>
       </c>
-      <c r="AC59" t="n">
-        <v>-7.61052</v>
-      </c>
+      <c r="AC59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5744,9 +5514,7 @@
       <c r="N60" t="n">
         <v>1172</v>
       </c>
-      <c r="O60" t="n">
-        <v>440.75</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
         <v>3.473353</v>
       </c>
@@ -5786,9 +5554,7 @@
       <c r="AB60" t="n">
         <v>4.947392</v>
       </c>
-      <c r="AC60" t="n">
-        <v>6.783767</v>
-      </c>
+      <c r="AC60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5833,9 +5599,7 @@
       <c r="N61" t="n">
         <v>1275.25</v>
       </c>
-      <c r="O61" t="n">
-        <v>515</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
         <v>-0.325845</v>
       </c>
@@ -5875,98 +5639,92 @@
       <c r="AB61" t="n">
         <v>8.809727000000001</v>
       </c>
-      <c r="AC61" t="n">
-        <v>16.846285</v>
-      </c>
+      <c r="AC61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187884.234375</v>
+        <v>184429.421875</v>
       </c>
       <c r="C62" t="n">
-        <v>184.940002</v>
+        <v>181.509995</v>
       </c>
       <c r="D62" t="n">
-        <v>112.779999</v>
+        <v>110.269997</v>
       </c>
       <c r="E62" t="n">
-        <v>444.200012</v>
+        <v>447.329987</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0978</v>
+        <v>5.1283</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9255</v>
+        <v>5.9542</v>
       </c>
       <c r="H62" t="n">
-        <v>7696.549805</v>
+        <v>7736.689941</v>
       </c>
       <c r="I62" t="n">
-        <v>26400.578125</v>
+        <v>26610.115234</v>
       </c>
       <c r="J62" t="n">
-        <v>53321.730469</v>
+        <v>53466.398438</v>
       </c>
       <c r="K62" t="n">
-        <v>4514.799805</v>
+        <v>4469.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>91.870003</v>
+        <v>88.91999800000001</v>
       </c>
       <c r="M62" t="n">
-        <v>96.199997</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1292.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>527</v>
-      </c>
+        <v>1307</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>5.898598</v>
+        <v>3.951337</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.813024</v>
+        <v>3.850553</v>
       </c>
       <c r="R62" t="n">
-        <v>6.265902</v>
+        <v>3.900876</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.146099</v>
+        <v>-0.449543</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.799199</v>
+        <v>-1.211658</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.399674</v>
+        <v>-0.922108</v>
       </c>
       <c r="V62" t="n">
-        <v>0.135434</v>
+        <v>0.657675</v>
       </c>
       <c r="W62" t="n">
-        <v>0.112577</v>
+        <v>0.907154</v>
       </c>
       <c r="X62" t="n">
-        <v>0.255391</v>
+        <v>0.5273949999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.888915</v>
+        <v>0.868859</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.124534</v>
+        <v>3.684697</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.310089</v>
+        <v>3.127419</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.352676</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>2.330097</v>
-      </c>
+        <v>2.489708</v>
+      </c>
+      <c r="AC62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -610,7 +610,9 @@
       <c r="N2" t="n">
         <v>1256</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>536.75</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -669,7 +671,9 @@
       <c r="N3" t="n">
         <v>1235.75</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>568.25</v>
+      </c>
       <c r="P3" t="n">
         <v>-6.738212</v>
       </c>
@@ -709,7 +713,9 @@
       <c r="AB3" t="n">
         <v>-1.612261</v>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>5.868654</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -754,7 +760,9 @@
       <c r="N4" t="n">
         <v>1217.25</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>567</v>
+      </c>
       <c r="P4" t="n">
         <v>-1.532352</v>
       </c>
@@ -794,7 +802,9 @@
       <c r="AB4" t="n">
         <v>-1.497067</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>-0.219974</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -839,7 +849,9 @@
       <c r="N5" t="n">
         <v>1328.75</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>593.25</v>
+      </c>
       <c r="P5" t="n">
         <v>2.852377</v>
       </c>
@@ -879,7 +891,9 @@
       <c r="AB5" t="n">
         <v>9.159992000000001</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>4.62963</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -924,7 +938,9 @@
       <c r="N6" t="n">
         <v>1490.5</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>626</v>
+      </c>
       <c r="P6" t="n">
         <v>7.21795</v>
       </c>
@@ -964,7 +980,9 @@
       <c r="AB6" t="n">
         <v>12.173095</v>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>5.520438</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1009,7 +1027,9 @@
       <c r="N7" t="n">
         <v>1644.25</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>697.5</v>
+      </c>
       <c r="P7" t="n">
         <v>0.67089</v>
       </c>
@@ -1049,7 +1069,9 @@
       <c r="AB7" t="n">
         <v>10.31533</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>11.421725</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1094,7 +1116,9 @@
       <c r="N8" t="n">
         <v>1618.25</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>748.75</v>
+      </c>
       <c r="P8" t="n">
         <v>6.060526</v>
       </c>
@@ -1134,7 +1158,9 @@
       <c r="AB8" t="n">
         <v>-1.581268</v>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>7.34767</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1179,7 +1205,9 @@
       <c r="N9" t="n">
         <v>1708.25</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>818.25</v>
+      </c>
       <c r="P9" t="n">
         <v>-10.102584</v>
       </c>
@@ -1219,7 +1247,9 @@
       <c r="AB9" t="n">
         <v>5.561563</v>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>9.282137000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1264,7 +1294,9 @@
       <c r="N10" t="n">
         <v>1683.25</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>753.5</v>
+      </c>
       <c r="P10" t="n">
         <v>3.221291</v>
       </c>
@@ -1304,7 +1336,9 @@
       <c r="AB10" t="n">
         <v>-1.463486</v>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>-7.913229</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1349,7 +1383,9 @@
       <c r="N11" t="n">
         <v>1675</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>743.75</v>
+      </c>
       <c r="P11" t="n">
         <v>-11.503264</v>
       </c>
@@ -1389,7 +1425,9 @@
       <c r="AB11" t="n">
         <v>-0.490123</v>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>-1.293962</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1434,7 +1472,9 @@
       <c r="N12" t="n">
         <v>1637</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>616.25</v>
+      </c>
       <c r="P12" t="n">
         <v>4.691401</v>
       </c>
@@ -1474,7 +1514,9 @@
       <c r="AB12" t="n">
         <v>-2.268657</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>-17.142857</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1519,7 +1561,9 @@
       <c r="N13" t="n">
         <v>1507.5</v>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>673.75</v>
+      </c>
       <c r="P13" t="n">
         <v>6.162943</v>
       </c>
@@ -1559,7 +1603,9 @@
       <c r="AB13" t="n">
         <v>-7.910812</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>9.330629</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1604,7 +1650,9 @@
       <c r="N14" t="n">
         <v>1364.75</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>677.5</v>
+      </c>
       <c r="P14" t="n">
         <v>0.469308</v>
       </c>
@@ -1644,7 +1692,9 @@
       <c r="AB14" t="n">
         <v>-9.46932</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>0.556586</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1689,7 +1739,9 @@
       <c r="N15" t="n">
         <v>1407</v>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>691.5</v>
+      </c>
       <c r="P15" t="n">
         <v>5.452711</v>
       </c>
@@ -1729,7 +1781,9 @@
       <c r="AB15" t="n">
         <v>3.095805</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>2.066421</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1774,7 +1828,9 @@
       <c r="N16" t="n">
         <v>1469.5</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>662</v>
+      </c>
       <c r="P16" t="n">
         <v>-3.060231</v>
       </c>
@@ -1814,7 +1870,9 @@
       <c r="AB16" t="n">
         <v>4.442075</v>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>-4.266088</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1859,7 +1917,9 @@
       <c r="N17" t="n">
         <v>1519.25</v>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>678.5</v>
+      </c>
       <c r="P17" t="n">
         <v>-2.182494</v>
       </c>
@@ -1899,7 +1959,9 @@
       <c r="AB17" t="n">
         <v>3.385505</v>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>2.492447</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1944,7 +2006,9 @@
       <c r="N18" t="n">
         <v>1538</v>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>679.75</v>
+      </c>
       <c r="P18" t="n">
         <v>3.181831</v>
       </c>
@@ -1984,7 +2048,9 @@
       <c r="AB18" t="n">
         <v>1.234162</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>0.18423</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2029,7 +2095,9 @@
       <c r="N19" t="n">
         <v>1490.5</v>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>629.5</v>
+      </c>
       <c r="P19" t="n">
         <v>-7.574957</v>
       </c>
@@ -2069,7 +2137,9 @@
       <c r="AB19" t="n">
         <v>-3.088427</v>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>-7.392424</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2114,7 +2184,9 @@
       <c r="N20" t="n">
         <v>1505.5</v>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>660.5</v>
+      </c>
       <c r="P20" t="n">
         <v>-2.906644</v>
       </c>
@@ -2154,7 +2226,9 @@
       <c r="AB20" t="n">
         <v>1.006374</v>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>4.924543</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2199,7 +2273,9 @@
       <c r="N21" t="n">
         <v>1444.25</v>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>636</v>
+      </c>
       <c r="P21" t="n">
         <v>2.502896</v>
       </c>
@@ -2239,7 +2315,9 @@
       <c r="AB21" t="n">
         <v>-4.068416</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>-3.709311</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2284,7 +2362,9 @@
       <c r="N22" t="n">
         <v>1299.75</v>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>594</v>
+      </c>
       <c r="P22" t="n">
         <v>3.73736</v>
       </c>
@@ -2324,7 +2404,9 @@
       <c r="AB22" t="n">
         <v>-10.005193</v>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>-6.603774</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2369,7 +2451,9 @@
       <c r="N23" t="n">
         <v>1557.25</v>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>554.5</v>
+      </c>
       <c r="P23" t="n">
         <v>9.001708000000001</v>
       </c>
@@ -2409,7 +2493,9 @@
       <c r="AB23" t="n">
         <v>19.811502</v>
       </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>-6.649832</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2454,7 +2540,9 @@
       <c r="N24" t="n">
         <v>1445.75</v>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>504</v>
+      </c>
       <c r="P24" t="n">
         <v>3.265389</v>
       </c>
@@ -2494,7 +2582,9 @@
       <c r="AB24" t="n">
         <v>-7.160058</v>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>-9.107303999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2539,7 +2629,9 @@
       <c r="N25" t="n">
         <v>1360</v>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>461</v>
+      </c>
       <c r="P25" t="n">
         <v>-5.085163</v>
       </c>
@@ -2579,7 +2671,9 @@
       <c r="AB25" t="n">
         <v>-5.931178</v>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>-8.531746</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2624,7 +2718,9 @@
       <c r="N26" t="n">
         <v>1275</v>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>476.75</v>
+      </c>
       <c r="P26" t="n">
         <v>0.711064</v>
       </c>
@@ -2664,7 +2760,9 @@
       <c r="AB26" t="n">
         <v>-6.25</v>
       </c>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>3.416486</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2709,7 +2807,9 @@
       <c r="N27" t="n">
         <v>1287</v>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>478.75</v>
+      </c>
       <c r="P27" t="n">
         <v>-2.934843</v>
       </c>
@@ -2749,7 +2849,9 @@
       <c r="AB27" t="n">
         <v>0.941176</v>
       </c>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>0.419507</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2794,7 +2896,9 @@
       <c r="N28" t="n">
         <v>1342.75</v>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>461.75</v>
+      </c>
       <c r="P28" t="n">
         <v>12.538888</v>
       </c>
@@ -2834,7 +2938,9 @@
       <c r="AB28" t="n">
         <v>4.331779</v>
       </c>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>-3.550914</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2879,7 +2985,9 @@
       <c r="N29" t="n">
         <v>1293.5</v>
       </c>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>471.25</v>
+      </c>
       <c r="P29" t="n">
         <v>5.382821</v>
       </c>
@@ -2919,7 +3027,9 @@
       <c r="AB29" t="n">
         <v>-3.667846</v>
       </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>2.05739</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2964,7 +3074,9 @@
       <c r="N30" t="n">
         <v>1222.25</v>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>448.25</v>
+      </c>
       <c r="P30" t="n">
         <v>-4.794128</v>
       </c>
@@ -3004,7 +3116,9 @@
       <c r="AB30" t="n">
         <v>-5.508311</v>
       </c>
-      <c r="AC30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>-4.880637</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3049,7 +3163,9 @@
       <c r="N31" t="n">
         <v>1128.25</v>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>415.75</v>
+      </c>
       <c r="P31" t="n">
         <v>0.992548</v>
       </c>
@@ -3089,7 +3205,9 @@
       <c r="AB31" t="n">
         <v>-7.690734</v>
       </c>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>-7.250418</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3134,7 +3252,9 @@
       <c r="N32" t="n">
         <v>1191.5</v>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>442</v>
+      </c>
       <c r="P32" t="n">
         <v>-0.708417</v>
       </c>
@@ -3174,7 +3294,9 @@
       <c r="AB32" t="n">
         <v>5.606027</v>
       </c>
-      <c r="AC32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>6.313891</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3219,7 +3341,9 @@
       <c r="N33" t="n">
         <v>1145.5</v>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>439.5</v>
+      </c>
       <c r="P33" t="n">
         <v>-1.703277</v>
       </c>
@@ -3259,7 +3383,9 @@
       <c r="AB33" t="n">
         <v>-3.86068</v>
       </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AC33" t="n">
+        <v>-0.565611</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3304,7 +3430,9 @@
       <c r="N34" t="n">
         <v>1205</v>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>446.25</v>
+      </c>
       <c r="P34" t="n">
         <v>-3.038341</v>
       </c>
@@ -3344,7 +3472,9 @@
       <c r="AB34" t="n">
         <v>5.194238</v>
       </c>
-      <c r="AC34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>1.535836</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3389,7 +3519,9 @@
       <c r="N35" t="n">
         <v>1150.5</v>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>397.25</v>
+      </c>
       <c r="P35" t="n">
         <v>1.481597</v>
       </c>
@@ -3429,7 +3561,9 @@
       <c r="AB35" t="n">
         <v>-4.522822</v>
       </c>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>-10.980392</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3474,7 +3608,9 @@
       <c r="N36" t="n">
         <v>1028.5</v>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>382.75</v>
+      </c>
       <c r="P36" t="n">
         <v>3.022428</v>
       </c>
@@ -3514,7 +3650,9 @@
       <c r="AB36" t="n">
         <v>-10.604085</v>
       </c>
-      <c r="AC36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>-3.650094</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3559,7 +3697,9 @@
       <c r="N37" t="n">
         <v>982</v>
       </c>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>378</v>
+      </c>
       <c r="P37" t="n">
         <v>6.542788</v>
       </c>
@@ -3599,7 +3739,9 @@
       <c r="AB37" t="n">
         <v>-4.521147</v>
       </c>
-      <c r="AC37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>-1.241019</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3644,7 +3786,9 @@
       <c r="N38" t="n">
         <v>1057</v>
       </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>424.75</v>
+      </c>
       <c r="P38" t="n">
         <v>-3.079321</v>
       </c>
@@ -3684,7 +3828,9 @@
       <c r="AB38" t="n">
         <v>7.637475</v>
       </c>
-      <c r="AC38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>12.367725</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3729,7 +3875,9 @@
       <c r="N39" t="n">
         <v>982.5</v>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>410.75</v>
+      </c>
       <c r="P39" t="n">
         <v>-1.595406</v>
       </c>
@@ -3769,7 +3917,9 @@
       <c r="AB39" t="n">
         <v>-7.04825</v>
       </c>
-      <c r="AC39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>-3.296057</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3814,7 +3964,9 @@
       <c r="N40" t="n">
         <v>989.5</v>
       </c>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>423</v>
+      </c>
       <c r="P40" t="n">
         <v>-3.118423</v>
       </c>
@@ -3854,7 +4006,9 @@
       <c r="AB40" t="n">
         <v>0.712468</v>
       </c>
-      <c r="AC40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>2.982349</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3899,7 +4053,9 @@
       <c r="N41" t="n">
         <v>998.25</v>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>458.5</v>
+      </c>
       <c r="P41" t="n">
         <v>-4.2851</v>
       </c>
@@ -3939,7 +4095,9 @@
       <c r="AB41" t="n">
         <v>0.884285</v>
       </c>
-      <c r="AC41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>8.392435000000001</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3984,7 +4142,9 @@
       <c r="N42" t="n">
         <v>1042</v>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>482</v>
+      </c>
       <c r="P42" t="n">
         <v>4.865193</v>
       </c>
@@ -4024,7 +4184,9 @@
       <c r="AB42" t="n">
         <v>4.38267</v>
       </c>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>5.125409</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4069,7 +4231,9 @@
       <c r="N43" t="n">
         <v>1011.5</v>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>453.5</v>
+      </c>
       <c r="P43" t="n">
         <v>-2.644785</v>
       </c>
@@ -4109,7 +4273,9 @@
       <c r="AB43" t="n">
         <v>-2.927063</v>
       </c>
-      <c r="AC43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>-5.912863</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4154,7 +4320,9 @@
       <c r="N44" t="n">
         <v>1014.75</v>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>457.25</v>
+      </c>
       <c r="P44" t="n">
         <v>6.075782</v>
       </c>
@@ -4194,7 +4362,9 @@
       <c r="AB44" t="n">
         <v>0.321305</v>
       </c>
-      <c r="AC44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>0.826902</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4239,7 +4409,9 @@
       <c r="N45" t="n">
         <v>1034.75</v>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>467.25</v>
+      </c>
       <c r="P45" t="n">
         <v>3.690312</v>
       </c>
@@ -4279,7 +4451,9 @@
       <c r="AB45" t="n">
         <v>1.970929</v>
       </c>
-      <c r="AC45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>2.186987</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4324,7 +4498,9 @@
       <c r="N46" t="n">
         <v>1041.75</v>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>444</v>
+      </c>
       <c r="P46" t="n">
         <v>1.451132</v>
       </c>
@@ -4364,7 +4540,9 @@
       <c r="AB46" t="n">
         <v>0.676492</v>
       </c>
-      <c r="AC46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>-4.975923</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4409,7 +4587,9 @@
       <c r="N47" t="n">
         <v>1024.25</v>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>420.5</v>
+      </c>
       <c r="P47" t="n">
         <v>1.334044</v>
       </c>
@@ -4449,7 +4629,9 @@
       <c r="AB47" t="n">
         <v>-1.679866</v>
       </c>
-      <c r="AC47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>-5.292793</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4494,7 +4676,9 @@
       <c r="N48" t="n">
         <v>961.75</v>
       </c>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="n">
+        <v>394</v>
+      </c>
       <c r="P48" t="n">
         <v>-4.165496</v>
       </c>
@@ -4534,7 +4718,9 @@
       <c r="AB48" t="n">
         <v>-6.102026</v>
       </c>
-      <c r="AC48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>-6.302021</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4579,7 +4765,9 @@
       <c r="N49" t="n">
         <v>1036.75</v>
       </c>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="n">
+        <v>398</v>
+      </c>
       <c r="P49" t="n">
         <v>6.275597</v>
       </c>
@@ -4619,7 +4807,9 @@
       <c r="AB49" t="n">
         <v>7.798284</v>
       </c>
-      <c r="AC49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>1.015228</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4664,7 +4854,9 @@
       <c r="N50" t="n">
         <v>1001.75</v>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>415.5</v>
+      </c>
       <c r="P50" t="n">
         <v>3.404704</v>
       </c>
@@ -4704,7 +4896,9 @@
       <c r="AB50" t="n">
         <v>-3.375934</v>
       </c>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>4.396985</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4749,7 +4943,9 @@
       <c r="N51" t="n">
         <v>1099.75</v>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>431.5</v>
+      </c>
       <c r="P51" t="n">
         <v>2.258662</v>
       </c>
@@ -4789,7 +4985,9 @@
       <c r="AB51" t="n">
         <v>9.78288</v>
       </c>
-      <c r="AC51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>3.850782</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4834,7 +5032,9 @@
       <c r="N52" t="n">
         <v>1137.75</v>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>435.5</v>
+      </c>
       <c r="P52" t="n">
         <v>6.374214</v>
       </c>
@@ -4874,7 +5074,9 @@
       <c r="AB52" t="n">
         <v>3.455331</v>
       </c>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>0.926999</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4919,7 +5121,9 @@
       <c r="N53" t="n">
         <v>1030.5</v>
       </c>
-      <c r="O53" t="inlineStr"/>
+      <c r="O53" t="n">
+        <v>440.25</v>
+      </c>
       <c r="P53" t="n">
         <v>1.290611</v>
       </c>
@@ -4959,7 +5163,9 @@
       <c r="AB53" t="n">
         <v>-9.426500000000001</v>
       </c>
-      <c r="AC53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>1.0907</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5004,7 +5210,9 @@
       <c r="N54" t="n">
         <v>1064.25</v>
       </c>
-      <c r="O54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>428.25</v>
+      </c>
       <c r="P54" t="n">
         <v>12.561055</v>
       </c>
@@ -5044,7 +5252,9 @@
       <c r="AB54" t="n">
         <v>3.275109</v>
       </c>
-      <c r="AC54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>-2.725724</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5089,7 +5299,9 @@
       <c r="N55" t="n">
         <v>1157.25</v>
       </c>
-      <c r="O55" t="inlineStr"/>
+      <c r="O55" t="n">
+        <v>438.75</v>
+      </c>
       <c r="P55" t="n">
         <v>4.092874</v>
       </c>
@@ -5129,7 +5341,9 @@
       <c r="AB55" t="n">
         <v>8.738548</v>
       </c>
-      <c r="AC55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>2.451839</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5174,7 +5388,9 @@
       <c r="N56" t="n">
         <v>1171</v>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>457.75</v>
+      </c>
       <c r="P56" t="n">
         <v>-0.7018489999999999</v>
       </c>
@@ -5214,7 +5430,9 @@
       <c r="AB56" t="n">
         <v>1.188162</v>
       </c>
-      <c r="AC56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>4.330484</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5259,7 +5477,9 @@
       <c r="N57" t="n">
         <v>1182</v>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>464.75</v>
+      </c>
       <c r="P57" t="n">
         <v>-0.076816</v>
       </c>
@@ -5299,7 +5519,9 @@
       <c r="AB57" t="n">
         <v>0.939368</v>
       </c>
-      <c r="AC57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>1.529219</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5344,7 +5566,9 @@
       <c r="N58" t="n">
         <v>1186.75</v>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>446.75</v>
+      </c>
       <c r="P58" t="n">
         <v>-7.223011</v>
       </c>
@@ -5384,7 +5608,9 @@
       <c r="AB58" t="n">
         <v>0.401861</v>
       </c>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>-3.87305</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5429,7 +5655,9 @@
       <c r="N59" t="n">
         <v>1116.75</v>
       </c>
-      <c r="O59" t="inlineStr"/>
+      <c r="O59" t="n">
+        <v>412.75</v>
+      </c>
       <c r="P59" t="n">
         <v>-1.01503</v>
       </c>
@@ -5469,7 +5697,9 @@
       <c r="AB59" t="n">
         <v>-5.898462</v>
       </c>
-      <c r="AC59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>-7.61052</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5514,7 +5744,9 @@
       <c r="N60" t="n">
         <v>1172</v>
       </c>
-      <c r="O60" t="inlineStr"/>
+      <c r="O60" t="n">
+        <v>440.75</v>
+      </c>
       <c r="P60" t="n">
         <v>3.473353</v>
       </c>
@@ -5554,7 +5786,9 @@
       <c r="AB60" t="n">
         <v>4.947392</v>
       </c>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>6.783767</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5599,7 +5833,9 @@
       <c r="N61" t="n">
         <v>1275.25</v>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>515</v>
+      </c>
       <c r="P61" t="n">
         <v>-0.325845</v>
       </c>
@@ -5639,92 +5875,98 @@
       <c r="AB61" t="n">
         <v>8.809727000000001</v>
       </c>
-      <c r="AC61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>16.846285</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>184429.421875</v>
+        <v>185147</v>
       </c>
       <c r="C62" t="n">
-        <v>181.509995</v>
+        <v>182.25</v>
       </c>
       <c r="D62" t="n">
-        <v>110.269997</v>
+        <v>111.059998</v>
       </c>
       <c r="E62" t="n">
-        <v>447.329987</v>
+        <v>446</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1283</v>
+        <v>5.1237</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9542</v>
+        <v>5.9496</v>
       </c>
       <c r="H62" t="n">
-        <v>7736.689941</v>
+        <v>7718.600098</v>
       </c>
       <c r="I62" t="n">
-        <v>26610.115234</v>
+        <v>26506.990234</v>
       </c>
       <c r="J62" t="n">
-        <v>53466.398438</v>
+        <v>53414.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4469.600098</v>
+        <v>4429.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>88.91999800000001</v>
+        <v>91.480003</v>
       </c>
       <c r="M62" t="n">
-        <v>93.31999999999999</v>
+        <v>96.279999</v>
       </c>
       <c r="N62" t="n">
-        <v>1307</v>
-      </c>
-      <c r="O62" t="inlineStr"/>
+        <v>1293.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>512</v>
+      </c>
       <c r="P62" t="n">
-        <v>3.951337</v>
+        <v>4.355791</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.850553</v>
+        <v>4.273945</v>
       </c>
       <c r="R62" t="n">
-        <v>3.900876</v>
+        <v>4.645247</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.449543</v>
+        <v>-0.745523</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.211658</v>
+        <v>-1.30027</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.922108</v>
+        <v>-0.998645</v>
       </c>
       <c r="V62" t="n">
-        <v>0.657675</v>
+        <v>0.422318</v>
       </c>
       <c r="W62" t="n">
-        <v>0.907154</v>
+        <v>0.5160979999999999</v>
       </c>
       <c r="X62" t="n">
-        <v>0.5273949999999999</v>
+        <v>0.429346</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.868859</v>
+        <v>-0.029345</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.684697</v>
+        <v>6.669777</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.127419</v>
+        <v>6.398498</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.489708</v>
-      </c>
-      <c r="AC62" t="inlineStr"/>
+        <v>1.450696</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>-0.582524</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,13 +5887,13 @@
         <v>185147</v>
       </c>
       <c r="C62" t="n">
-        <v>182.25</v>
+        <v>181.940002</v>
       </c>
       <c r="D62" t="n">
-        <v>111.059998</v>
+        <v>110.989998</v>
       </c>
       <c r="E62" t="n">
-        <v>446</v>
+        <v>447.350006</v>
       </c>
       <c r="F62" t="n">
         <v>5.1237</v>
@@ -5929,13 +5929,13 @@
         <v>4.355791</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.273945</v>
+        <v>4.096581</v>
       </c>
       <c r="R62" t="n">
-        <v>4.645247</v>
+        <v>4.57929</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.745523</v>
+        <v>-0.445087</v>
       </c>
       <c r="T62" t="n">
         <v>-1.30027</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5911,7 +5911,7 @@
         <v>53414.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4429.799805</v>
+        <v>4476.600098</v>
       </c>
       <c r="L62" t="n">
         <v>91.480003</v>
@@ -5920,10 +5920,10 @@
         <v>96.279999</v>
       </c>
       <c r="N62" t="n">
-        <v>1293.75</v>
+        <v>1309.75</v>
       </c>
       <c r="O62" t="n">
-        <v>512</v>
+        <v>536.75</v>
       </c>
       <c r="P62" t="n">
         <v>4.355791</v>
@@ -5953,7 +5953,7 @@
         <v>0.429346</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.029345</v>
+        <v>1.026833</v>
       </c>
       <c r="Z62" t="n">
         <v>6.669777</v>
@@ -5962,10 +5962,10 @@
         <v>6.398498</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.450696</v>
+        <v>2.705352</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.582524</v>
+        <v>4.223301</v>
       </c>
     </row>
   </sheetData>
